--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA6790D-9FC3-4D33-9C42-14AE2BB18E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3004C8E2-8327-4524-9427-6D95AF7B9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1468,9 +1468,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
@@ -1478,6 +1475,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1752,23 +1752,23 @@
         <v>283</v>
       </c>
       <c r="M1" s="26"/>
-      <c r="N1" s="53" t="s">
+      <c r="N1" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
       <c r="AD1" s="33" t="s">
         <v>279</v>
       </c>
@@ -23436,27 +23436,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="53" t="s">
         <v>305</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54" t="s">
+      <c r="F1" s="53"/>
+      <c r="G1" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="53" t="s">
         <v>309</v>
       </c>
     </row>
@@ -23465,23 +23465,23 @@
         <v>310</v>
       </c>
       <c r="B2" s="41"/>
-      <c r="C2" s="55">
+      <c r="C2" s="54">
         <v>40.1</v>
       </c>
-      <c r="D2" s="55">
+      <c r="D2" s="54">
         <v>38.700000000000003</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="54">
         <v>39</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55">
+      <c r="F2" s="54"/>
+      <c r="G2" s="54">
         <v>25.1</v>
       </c>
-      <c r="H2" s="55">
+      <c r="H2" s="54">
         <v>29.1</v>
       </c>
-      <c r="I2" s="55">
+      <c r="I2" s="54">
         <v>25.8</v>
       </c>
     </row>
@@ -23490,23 +23490,23 @@
         <v>311</v>
       </c>
       <c r="B3" s="41"/>
-      <c r="C3" s="55">
+      <c r="C3" s="54">
         <v>58.3</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="54">
         <v>56.9</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="54">
         <v>61.4</v>
       </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54">
         <v>45.5</v>
       </c>
-      <c r="H3" s="55">
+      <c r="H3" s="54">
         <v>41.7</v>
       </c>
-      <c r="I3" s="55">
+      <c r="I3" s="54">
         <v>43.3</v>
       </c>
     </row>
@@ -23515,23 +23515,23 @@
         <v>312</v>
       </c>
       <c r="B4" s="41"/>
-      <c r="C4" s="55">
+      <c r="C4" s="54">
         <v>43.1</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="54">
         <v>43.1</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="54">
         <v>41.5</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55">
+      <c r="F4" s="54"/>
+      <c r="G4" s="54">
         <v>24.4</v>
       </c>
-      <c r="H4" s="55">
+      <c r="H4" s="54">
         <v>23.9</v>
       </c>
-      <c r="I4" s="55">
+      <c r="I4" s="54">
         <v>25.6</v>
       </c>
     </row>
@@ -23540,23 +23540,23 @@
         <v>313</v>
       </c>
       <c r="B5" s="41"/>
-      <c r="C5" s="55">
+      <c r="C5" s="54">
         <v>42.8</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="54">
         <v>42.5</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="54">
         <v>48.6</v>
       </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55">
+      <c r="F5" s="54"/>
+      <c r="G5" s="54">
         <v>23.1</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="54">
         <v>25.2</v>
       </c>
-      <c r="I5" s="55">
+      <c r="I5" s="54">
         <v>25.8</v>
       </c>
     </row>
@@ -23565,23 +23565,23 @@
         <v>314</v>
       </c>
       <c r="B6" s="41"/>
-      <c r="C6" s="55">
+      <c r="C6" s="54">
         <v>51.4</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="54">
         <v>50.5</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="54">
         <v>52.7</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55">
+      <c r="F6" s="54"/>
+      <c r="G6" s="54">
         <v>29.2</v>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="54">
         <v>31.7</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="54">
         <v>32.5</v>
       </c>
     </row>
@@ -23590,23 +23590,23 @@
         <v>315</v>
       </c>
       <c r="B7" s="41"/>
-      <c r="C7" s="55">
+      <c r="C7" s="54">
         <v>40.9</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="54">
         <v>41.1</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="54">
         <v>41.9</v>
       </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54">
         <v>25.5</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="54">
         <v>28.3</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="54">
         <v>28</v>
       </c>
     </row>
@@ -23615,23 +23615,23 @@
         <v>316</v>
       </c>
       <c r="B8" s="41"/>
-      <c r="C8" s="55">
+      <c r="C8" s="54">
         <v>50.7</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="54">
         <v>50</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="54">
         <v>52.3</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55">
+      <c r="F8" s="54"/>
+      <c r="G8" s="54">
         <v>31.1</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="54">
         <v>33.700000000000003</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="54">
         <v>35.5</v>
       </c>
     </row>
@@ -23640,23 +23640,23 @@
         <v>30</v>
       </c>
       <c r="B9" s="41"/>
-      <c r="C9" s="55">
+      <c r="C9" s="54">
         <v>35.299999999999997</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="54">
         <v>35.200000000000003</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="54">
         <v>34.200000000000003</v>
       </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55">
+      <c r="F9" s="54"/>
+      <c r="G9" s="54">
         <v>24.6</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="54">
         <v>22.6</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="54">
         <v>23.5</v>
       </c>
     </row>
@@ -23665,73 +23665,73 @@
         <v>317</v>
       </c>
       <c r="B10" s="41"/>
-      <c r="C10" s="55">
+      <c r="C10" s="54">
         <v>46.1</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="54">
         <v>47.2</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="54">
         <v>47.9</v>
       </c>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55">
+      <c r="F10" s="54"/>
+      <c r="G10" s="54">
         <v>26.5</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="54">
         <v>27.4</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="54">
         <v>26.1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="55" t="s">
         <v>318</v>
       </c>
       <c r="B11" s="41"/>
-      <c r="C11" s="55">
+      <c r="C11" s="54">
         <v>50.7</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="54">
         <v>49.1</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="54">
         <v>50.1</v>
       </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54">
         <v>30.2</v>
       </c>
-      <c r="H11" s="55">
+      <c r="H11" s="54">
         <v>28.6</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="54">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="55" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="41"/>
-      <c r="C12" s="55">
+      <c r="C12" s="54">
         <v>59.6</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="54">
         <v>58.8</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="54">
         <v>61.1</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55">
+      <c r="F12" s="54"/>
+      <c r="G12" s="54">
         <v>42.2</v>
       </c>
-      <c r="H12" s="55">
+      <c r="H12" s="54">
         <v>43.7</v>
       </c>
-      <c r="I12" s="55">
+      <c r="I12" s="54">
         <v>39</v>
       </c>
     </row>
@@ -23740,23 +23740,23 @@
         <v>319</v>
       </c>
       <c r="B13" s="41"/>
-      <c r="C13" s="55">
+      <c r="C13" s="54">
         <v>48.7</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="54">
         <v>46</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="54">
         <v>50</v>
       </c>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55">
+      <c r="F13" s="54"/>
+      <c r="G13" s="54">
         <v>29.4</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="54">
         <v>30.2</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="54">
         <v>32.200000000000003</v>
       </c>
     </row>
@@ -23765,23 +23765,23 @@
         <v>320</v>
       </c>
       <c r="B14" s="41"/>
-      <c r="C14" s="55">
+      <c r="C14" s="54">
         <v>47.7</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="54">
         <v>46.9</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="54">
         <v>48.7</v>
       </c>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55">
+      <c r="F14" s="54"/>
+      <c r="G14" s="54">
         <v>29.2</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="54">
         <v>30.3</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="54">
         <v>30.6</v>
       </c>
     </row>
@@ -23790,23 +23790,23 @@
         <v>321</v>
       </c>
       <c r="B15" s="41"/>
-      <c r="C15" s="55">
+      <c r="C15" s="54">
         <v>43</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="54">
         <v>39.1</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="54">
         <v>42.9</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54">
         <v>24.6</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="54">
         <v>25.2</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="54">
         <v>27.2</v>
       </c>
     </row>
@@ -23815,23 +23815,23 @@
         <v>322</v>
       </c>
       <c r="B16" s="41"/>
-      <c r="C16" s="55">
+      <c r="C16" s="54">
         <v>41.7</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="54">
         <v>45.5</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="54">
         <v>49.6</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55">
+      <c r="F16" s="54"/>
+      <c r="G16" s="54">
         <v>25.4</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="54">
         <v>29.2</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="54">
         <v>29.3</v>
       </c>
     </row>
@@ -23840,23 +23840,23 @@
         <v>323</v>
       </c>
       <c r="B17" s="41"/>
-      <c r="C17" s="55">
+      <c r="C17" s="54">
         <v>37.5</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="54">
         <v>40.700000000000003</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="54">
         <v>41.5</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55">
+      <c r="F17" s="54"/>
+      <c r="G17" s="54">
         <v>20.3</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="54">
         <v>23.3</v>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="54">
         <v>22.9</v>
       </c>
     </row>
@@ -23865,23 +23865,23 @@
         <v>324</v>
       </c>
       <c r="B18" s="41"/>
-      <c r="C18" s="55">
+      <c r="C18" s="54">
         <v>41.5</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="54">
         <v>37.700000000000003</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="54">
         <v>39.5</v>
       </c>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55">
+      <c r="F18" s="54"/>
+      <c r="G18" s="54">
         <v>22.5</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="54">
         <v>24.3</v>
       </c>
-      <c r="I18" s="55">
+      <c r="I18" s="54">
         <v>20.7</v>
       </c>
     </row>
@@ -23890,23 +23890,23 @@
         <v>325</v>
       </c>
       <c r="B19" s="41"/>
-      <c r="C19" s="55">
+      <c r="C19" s="54">
         <v>39.200000000000003</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="54">
         <v>40.200000000000003</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="54">
         <v>41.6</v>
       </c>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55">
+      <c r="F19" s="54"/>
+      <c r="G19" s="54">
         <v>24.6</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="54">
         <v>28.4</v>
       </c>
-      <c r="I19" s="55">
+      <c r="I19" s="54">
         <v>28.9</v>
       </c>
     </row>
@@ -23915,23 +23915,23 @@
         <v>59</v>
       </c>
       <c r="B20" s="41"/>
-      <c r="C20" s="55">
+      <c r="C20" s="54">
         <v>39.4</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="54">
         <v>41.3</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="54">
         <v>39.299999999999997</v>
       </c>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55">
+      <c r="F20" s="54"/>
+      <c r="G20" s="54">
         <v>23.7</v>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="54">
         <v>24.7</v>
       </c>
-      <c r="I20" s="55">
+      <c r="I20" s="54">
         <v>24.7</v>
       </c>
     </row>
@@ -23940,23 +23940,23 @@
         <v>62</v>
       </c>
       <c r="B21" s="41"/>
-      <c r="C21" s="55">
+      <c r="C21" s="54">
         <v>41.2</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="54">
         <v>39.4</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="54">
         <v>30.3</v>
       </c>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55">
+      <c r="F21" s="54"/>
+      <c r="G21" s="54">
         <v>21.4</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="54">
         <v>22.9</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="54">
         <v>17.600000000000001</v>
       </c>
     </row>
@@ -23965,23 +23965,23 @@
         <v>326</v>
       </c>
       <c r="B22" s="41"/>
-      <c r="C22" s="55">
+      <c r="C22" s="54">
         <v>37.6</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="54">
         <v>39.799999999999997</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="54">
         <v>37.1</v>
       </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55">
+      <c r="F22" s="54"/>
+      <c r="G22" s="54">
         <v>25.7</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="54">
         <v>27.1</v>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="54">
         <v>23</v>
       </c>
     </row>
@@ -23990,23 +23990,23 @@
         <v>68</v>
       </c>
       <c r="B23" s="41"/>
-      <c r="C23" s="55">
+      <c r="C23" s="54">
         <v>39.4</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="54">
         <v>37.799999999999997</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="54">
         <v>42.8</v>
       </c>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55">
+      <c r="F23" s="54"/>
+      <c r="G23" s="54">
         <v>21.3</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="54">
         <v>23.7</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="54">
         <v>21.4</v>
       </c>
     </row>
@@ -24015,23 +24015,23 @@
         <v>71</v>
       </c>
       <c r="B24" s="41"/>
-      <c r="C24" s="55">
+      <c r="C24" s="54">
         <v>29.2</v>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="54">
         <v>28.6</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="54">
         <v>30.7</v>
       </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55">
+      <c r="F24" s="54"/>
+      <c r="G24" s="54">
         <v>21.5</v>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="54">
         <v>20</v>
       </c>
-      <c r="I24" s="55">
+      <c r="I24" s="54">
         <v>23.4</v>
       </c>
     </row>
@@ -24040,23 +24040,23 @@
         <v>327</v>
       </c>
       <c r="B25" s="41"/>
-      <c r="C25" s="55">
+      <c r="C25" s="54">
         <v>38.299999999999997</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="54">
         <v>41.1</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="54">
         <v>38.200000000000003</v>
       </c>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55">
+      <c r="F25" s="54"/>
+      <c r="G25" s="54">
         <v>24.3</v>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="54">
         <v>21.2</v>
       </c>
-      <c r="I25" s="55">
+      <c r="I25" s="54">
         <v>23.7</v>
       </c>
     </row>
@@ -24065,23 +24065,23 @@
         <v>328</v>
       </c>
       <c r="B26" s="41"/>
-      <c r="C26" s="55">
+      <c r="C26" s="54">
         <v>39.200000000000003</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="54">
         <v>39.200000000000003</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="54">
         <v>38.799999999999997</v>
       </c>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55">
+      <c r="F26" s="54"/>
+      <c r="G26" s="54">
         <v>22.9</v>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="54">
         <v>24.3</v>
       </c>
-      <c r="I26" s="55">
+      <c r="I26" s="54">
         <v>23.4</v>
       </c>
     </row>
@@ -24090,23 +24090,23 @@
         <v>329</v>
       </c>
       <c r="B27" s="41"/>
-      <c r="C27" s="55">
+      <c r="C27" s="54">
         <v>26.6</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="54">
         <v>27.8</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="54">
         <v>27.9</v>
       </c>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55">
+      <c r="F27" s="54"/>
+      <c r="G27" s="54">
         <v>16.899999999999999</v>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="54">
         <v>17</v>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="54">
         <v>17.100000000000001</v>
       </c>
     </row>
@@ -24115,23 +24115,23 @@
         <v>81</v>
       </c>
       <c r="B28" s="41"/>
-      <c r="C28" s="55">
+      <c r="C28" s="54">
         <v>28.9</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="54">
         <v>28.8</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="54">
         <v>30.1</v>
       </c>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55">
+      <c r="F28" s="54"/>
+      <c r="G28" s="54">
         <v>20</v>
       </c>
-      <c r="H28" s="55">
+      <c r="H28" s="54">
         <v>19.8</v>
       </c>
-      <c r="I28" s="55">
+      <c r="I28" s="54">
         <v>22.9</v>
       </c>
     </row>
@@ -24140,23 +24140,23 @@
         <v>330</v>
       </c>
       <c r="B29" s="41"/>
-      <c r="C29" s="55">
+      <c r="C29" s="54">
         <v>29.3</v>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="54">
         <v>29.3</v>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="54">
         <v>27.7</v>
       </c>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55">
+      <c r="F29" s="54"/>
+      <c r="G29" s="54">
         <v>19.899999999999999</v>
       </c>
-      <c r="H29" s="55">
+      <c r="H29" s="54">
         <v>18</v>
       </c>
-      <c r="I29" s="55">
+      <c r="I29" s="54">
         <v>21.1</v>
       </c>
     </row>
@@ -24165,23 +24165,23 @@
         <v>331</v>
       </c>
       <c r="B30" s="41"/>
-      <c r="C30" s="55">
+      <c r="C30" s="54">
         <v>28.3</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="54">
         <v>28.6</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="54">
         <v>26.6</v>
       </c>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55">
+      <c r="F30" s="54"/>
+      <c r="G30" s="54">
         <v>19.100000000000001</v>
       </c>
-      <c r="H30" s="55">
+      <c r="H30" s="54">
         <v>18.600000000000001</v>
       </c>
-      <c r="I30" s="55">
+      <c r="I30" s="54">
         <v>20.9</v>
       </c>
     </row>
@@ -24190,23 +24190,23 @@
         <v>332</v>
       </c>
       <c r="B31" s="41"/>
-      <c r="C31" s="55">
+      <c r="C31" s="54">
         <v>49.4</v>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="54">
         <v>47.2</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="54">
         <v>46.3</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55">
+      <c r="F31" s="54"/>
+      <c r="G31" s="54">
         <v>32.799999999999997</v>
       </c>
-      <c r="H31" s="55">
+      <c r="H31" s="54">
         <v>32.200000000000003</v>
       </c>
-      <c r="I31" s="55">
+      <c r="I31" s="54">
         <v>26.9</v>
       </c>
     </row>
@@ -24215,23 +24215,23 @@
         <v>333</v>
       </c>
       <c r="B32" s="41"/>
-      <c r="C32" s="55">
+      <c r="C32" s="54">
         <v>51.1</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="54">
         <v>52.1</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="54">
         <v>50</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55">
+      <c r="F32" s="54"/>
+      <c r="G32" s="54">
         <v>38.200000000000003</v>
       </c>
-      <c r="H32" s="55">
+      <c r="H32" s="54">
         <v>43.3</v>
       </c>
-      <c r="I32" s="55">
+      <c r="I32" s="54">
         <v>42</v>
       </c>
     </row>
@@ -24240,23 +24240,23 @@
         <v>334</v>
       </c>
       <c r="B33" s="41"/>
-      <c r="C33" s="55">
+      <c r="C33" s="54">
         <v>47.1</v>
       </c>
-      <c r="D33" s="55">
+      <c r="D33" s="54">
         <v>44.1</v>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="54">
         <v>41.6</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55">
+      <c r="F33" s="54"/>
+      <c r="G33" s="54">
         <v>28.8</v>
       </c>
-      <c r="H33" s="55">
+      <c r="H33" s="54">
         <v>33.5</v>
       </c>
-      <c r="I33" s="55">
+      <c r="I33" s="54">
         <v>34</v>
       </c>
     </row>
@@ -24265,23 +24265,23 @@
         <v>335</v>
       </c>
       <c r="B34" s="41"/>
-      <c r="C34" s="55">
+      <c r="C34" s="54">
         <v>55.1</v>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="54">
         <v>50.1</v>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="54">
         <v>52.9</v>
       </c>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55">
+      <c r="F34" s="54"/>
+      <c r="G34" s="54">
         <v>43.1</v>
       </c>
-      <c r="H34" s="55">
+      <c r="H34" s="54">
         <v>40.1</v>
       </c>
-      <c r="I34" s="55">
+      <c r="I34" s="54">
         <v>39.4</v>
       </c>
     </row>
@@ -24290,23 +24290,23 @@
         <v>100</v>
       </c>
       <c r="B35" s="41"/>
-      <c r="C35" s="55">
+      <c r="C35" s="54">
         <v>54.8</v>
       </c>
-      <c r="D35" s="55">
+      <c r="D35" s="54">
         <v>52.2</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="54">
         <v>52</v>
       </c>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55">
+      <c r="F35" s="54"/>
+      <c r="G35" s="54">
         <v>37.1</v>
       </c>
-      <c r="H35" s="55">
+      <c r="H35" s="54">
         <v>46.8</v>
       </c>
-      <c r="I35" s="55">
+      <c r="I35" s="54">
         <v>41.6</v>
       </c>
     </row>
@@ -24315,23 +24315,23 @@
         <v>336</v>
       </c>
       <c r="B36" s="41"/>
-      <c r="C36" s="55">
+      <c r="C36" s="54">
         <v>54.8</v>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="54">
         <v>55</v>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="54">
         <v>58.2</v>
       </c>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55">
+      <c r="F36" s="54"/>
+      <c r="G36" s="54">
         <v>38.799999999999997</v>
       </c>
-      <c r="H36" s="55">
+      <c r="H36" s="54">
         <v>39.200000000000003</v>
       </c>
-      <c r="I36" s="55">
+      <c r="I36" s="54">
         <v>37.700000000000003</v>
       </c>
     </row>
@@ -24340,23 +24340,23 @@
         <v>337</v>
       </c>
       <c r="B37" s="41"/>
-      <c r="C37" s="55">
+      <c r="C37" s="54">
         <v>45.7</v>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="54">
         <v>46.7</v>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="54">
         <v>47.4</v>
       </c>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55">
+      <c r="F37" s="54"/>
+      <c r="G37" s="54">
         <v>34.799999999999997</v>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="54">
         <v>34.799999999999997</v>
       </c>
-      <c r="I37" s="55">
+      <c r="I37" s="54">
         <v>35.6</v>
       </c>
     </row>
@@ -24365,23 +24365,23 @@
         <v>338</v>
       </c>
       <c r="B38" s="41"/>
-      <c r="C38" s="55">
+      <c r="C38" s="54">
         <v>45.9</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="54">
         <v>49.1</v>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="54">
         <v>47.4</v>
       </c>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55">
+      <c r="F38" s="54"/>
+      <c r="G38" s="54">
         <v>38.9</v>
       </c>
-      <c r="H38" s="55">
+      <c r="H38" s="54">
         <v>40.700000000000003</v>
       </c>
-      <c r="I38" s="55">
+      <c r="I38" s="54">
         <v>37.6</v>
       </c>
     </row>
@@ -24390,23 +24390,23 @@
         <v>339</v>
       </c>
       <c r="B39" s="41"/>
-      <c r="C39" s="55">
+      <c r="C39" s="54">
         <v>47.2</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="54">
         <v>47.9</v>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="54">
         <v>45.4</v>
       </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55">
+      <c r="F39" s="54"/>
+      <c r="G39" s="54">
         <v>29.1</v>
       </c>
-      <c r="H39" s="55">
+      <c r="H39" s="54">
         <v>38.6</v>
       </c>
-      <c r="I39" s="55">
+      <c r="I39" s="54">
         <v>40.700000000000003</v>
       </c>
     </row>
@@ -24415,23 +24415,23 @@
         <v>340</v>
       </c>
       <c r="B40" s="41"/>
-      <c r="C40" s="55">
+      <c r="C40" s="54">
         <v>47.4</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="54">
         <v>44.4</v>
       </c>
-      <c r="E40" s="55">
+      <c r="E40" s="54">
         <v>47.1</v>
       </c>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55">
+      <c r="F40" s="54"/>
+      <c r="G40" s="54">
         <v>34.9</v>
       </c>
-      <c r="H40" s="55">
+      <c r="H40" s="54">
         <v>34.799999999999997</v>
       </c>
-      <c r="I40" s="55">
+      <c r="I40" s="54">
         <v>31.4</v>
       </c>
     </row>
@@ -24440,23 +24440,23 @@
         <v>341</v>
       </c>
       <c r="B41" s="41"/>
-      <c r="C41" s="55">
+      <c r="C41" s="54">
         <v>47.7</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="54">
         <v>45.8</v>
       </c>
-      <c r="E41" s="55">
+      <c r="E41" s="54">
         <v>45</v>
       </c>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55">
+      <c r="F41" s="54"/>
+      <c r="G41" s="54">
         <v>39.200000000000003</v>
       </c>
-      <c r="H41" s="55">
+      <c r="H41" s="54">
         <v>41.8</v>
       </c>
-      <c r="I41" s="55">
+      <c r="I41" s="54">
         <v>39.5</v>
       </c>
     </row>
@@ -24465,23 +24465,23 @@
         <v>342</v>
       </c>
       <c r="B42" s="41"/>
-      <c r="C42" s="55">
+      <c r="C42" s="54">
         <v>37.4</v>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="54">
         <v>40.6</v>
       </c>
-      <c r="E42" s="55">
+      <c r="E42" s="54">
         <v>41.4</v>
       </c>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55">
+      <c r="F42" s="54"/>
+      <c r="G42" s="54">
         <v>33.299999999999997</v>
       </c>
-      <c r="H42" s="55">
+      <c r="H42" s="54">
         <v>36.9</v>
       </c>
-      <c r="I42" s="55">
+      <c r="I42" s="54">
         <v>37.4</v>
       </c>
     </row>
@@ -24490,23 +24490,23 @@
         <v>343</v>
       </c>
       <c r="B43" s="41"/>
-      <c r="C43" s="55">
+      <c r="C43" s="54">
         <v>51.4</v>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="54">
         <v>53</v>
       </c>
-      <c r="E43" s="55">
+      <c r="E43" s="54">
         <v>52.6</v>
       </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55">
+      <c r="F43" s="54"/>
+      <c r="G43" s="54">
         <v>43.1</v>
       </c>
-      <c r="H43" s="55">
+      <c r="H43" s="54">
         <v>44.6</v>
       </c>
-      <c r="I43" s="55">
+      <c r="I43" s="54">
         <v>43.5</v>
       </c>
     </row>
@@ -24515,23 +24515,23 @@
         <v>344</v>
       </c>
       <c r="B44" s="41"/>
-      <c r="C44" s="55">
+      <c r="C44" s="54">
         <v>45.1</v>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="54">
         <v>43.1</v>
       </c>
-      <c r="E44" s="55">
+      <c r="E44" s="54">
         <v>42</v>
       </c>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55">
+      <c r="F44" s="54"/>
+      <c r="G44" s="54">
         <v>29.4</v>
       </c>
-      <c r="H44" s="55">
+      <c r="H44" s="54">
         <v>31.9</v>
       </c>
-      <c r="I44" s="55">
+      <c r="I44" s="54">
         <v>35.4</v>
       </c>
     </row>
@@ -24540,23 +24540,23 @@
         <v>345</v>
       </c>
       <c r="B45" s="41"/>
-      <c r="C45" s="55">
+      <c r="C45" s="54">
         <v>47.9</v>
       </c>
-      <c r="D45" s="55">
+      <c r="D45" s="54">
         <v>47.9</v>
       </c>
-      <c r="E45" s="55">
+      <c r="E45" s="54">
         <v>46.3</v>
       </c>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55">
+      <c r="F45" s="54"/>
+      <c r="G45" s="54">
         <v>35.200000000000003</v>
       </c>
-      <c r="H45" s="55">
+      <c r="H45" s="54">
         <v>38.9</v>
       </c>
-      <c r="I45" s="55">
+      <c r="I45" s="54">
         <v>38.799999999999997</v>
       </c>
     </row>
@@ -24565,23 +24565,23 @@
         <v>130</v>
       </c>
       <c r="B46" s="41"/>
-      <c r="C46" s="55">
+      <c r="C46" s="54">
         <v>51.6</v>
       </c>
-      <c r="D46" s="55">
+      <c r="D46" s="54">
         <v>50.6</v>
       </c>
-      <c r="E46" s="55">
+      <c r="E46" s="54">
         <v>52.8</v>
       </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55">
+      <c r="F46" s="54"/>
+      <c r="G46" s="54">
         <v>42.2</v>
       </c>
-      <c r="H46" s="55">
+      <c r="H46" s="54">
         <v>40.6</v>
       </c>
-      <c r="I46" s="55">
+      <c r="I46" s="54">
         <v>39.9</v>
       </c>
     </row>
@@ -24590,23 +24590,23 @@
         <v>133</v>
       </c>
       <c r="B47" s="41"/>
-      <c r="C47" s="55">
+      <c r="C47" s="54">
         <v>49.1</v>
       </c>
-      <c r="D47" s="55">
+      <c r="D47" s="54">
         <v>50</v>
       </c>
-      <c r="E47" s="55">
+      <c r="E47" s="54">
         <v>52.5</v>
       </c>
-      <c r="F47" s="55"/>
-      <c r="G47" s="55">
+      <c r="F47" s="54"/>
+      <c r="G47" s="54">
         <v>46.2</v>
       </c>
-      <c r="H47" s="55">
+      <c r="H47" s="54">
         <v>40</v>
       </c>
-      <c r="I47" s="55">
+      <c r="I47" s="54">
         <v>39.6</v>
       </c>
     </row>
@@ -24615,23 +24615,23 @@
         <v>136</v>
       </c>
       <c r="B48" s="41"/>
-      <c r="C48" s="55">
+      <c r="C48" s="54">
         <v>55.8</v>
       </c>
-      <c r="D48" s="55">
+      <c r="D48" s="54">
         <v>54.5</v>
       </c>
-      <c r="E48" s="55">
+      <c r="E48" s="54">
         <v>53.9</v>
       </c>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55">
+      <c r="F48" s="54"/>
+      <c r="G48" s="54">
         <v>41.7</v>
       </c>
-      <c r="H48" s="55">
+      <c r="H48" s="54">
         <v>48.7</v>
       </c>
-      <c r="I48" s="55">
+      <c r="I48" s="54">
         <v>42.5</v>
       </c>
     </row>
@@ -24640,23 +24640,23 @@
         <v>346</v>
       </c>
       <c r="B49" s="41"/>
-      <c r="C49" s="55">
+      <c r="C49" s="54">
         <v>45.7</v>
       </c>
-      <c r="D49" s="55">
+      <c r="D49" s="54">
         <v>44.1</v>
       </c>
-      <c r="E49" s="55">
+      <c r="E49" s="54">
         <v>48.5</v>
       </c>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55">
+      <c r="F49" s="54"/>
+      <c r="G49" s="54">
         <v>28.3</v>
       </c>
-      <c r="H49" s="55">
+      <c r="H49" s="54">
         <v>32.4</v>
       </c>
-      <c r="I49" s="55">
+      <c r="I49" s="54">
         <v>28</v>
       </c>
     </row>
@@ -24665,23 +24665,23 @@
         <v>347</v>
       </c>
       <c r="B50" s="41"/>
-      <c r="C50" s="55">
-        <v>60.9</v>
-      </c>
-      <c r="D50" s="55">
+      <c r="C50" s="54">
+        <v>50.9</v>
+      </c>
+      <c r="D50" s="54">
         <v>48.9</v>
       </c>
-      <c r="E50" s="55">
+      <c r="E50" s="54">
         <v>47.8</v>
       </c>
-      <c r="F50" s="55"/>
-      <c r="G50" s="55">
+      <c r="F50" s="54"/>
+      <c r="G50" s="54">
         <v>28.7</v>
       </c>
-      <c r="H50" s="55">
+      <c r="H50" s="54">
         <v>31.5</v>
       </c>
-      <c r="I50" s="55">
+      <c r="I50" s="54">
         <v>34.700000000000003</v>
       </c>
     </row>
@@ -24690,23 +24690,23 @@
         <v>348</v>
       </c>
       <c r="B51" s="41"/>
-      <c r="C51" s="55">
+      <c r="C51" s="54">
         <v>47.2</v>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="54">
         <v>48.9</v>
       </c>
-      <c r="E51" s="55">
+      <c r="E51" s="54">
         <v>47.3</v>
       </c>
-      <c r="F51" s="55"/>
-      <c r="G51" s="55">
+      <c r="F51" s="54"/>
+      <c r="G51" s="54">
         <v>33.799999999999997</v>
       </c>
-      <c r="H51" s="55">
+      <c r="H51" s="54">
         <v>36.5</v>
       </c>
-      <c r="I51" s="55">
+      <c r="I51" s="54">
         <v>32.4</v>
       </c>
     </row>
@@ -24715,23 +24715,23 @@
         <v>349</v>
       </c>
       <c r="B52" s="41"/>
-      <c r="C52" s="55">
+      <c r="C52" s="54">
         <v>55.4</v>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="54">
         <v>56.4</v>
       </c>
-      <c r="E52" s="55">
+      <c r="E52" s="54">
         <v>56.9</v>
       </c>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55">
+      <c r="F52" s="54"/>
+      <c r="G52" s="54">
         <v>39.5</v>
       </c>
-      <c r="H52" s="55">
+      <c r="H52" s="54">
         <v>40.200000000000003</v>
       </c>
-      <c r="I52" s="55">
+      <c r="I52" s="54">
         <v>40.700000000000003</v>
       </c>
     </row>
@@ -24740,23 +24740,23 @@
         <v>350</v>
       </c>
       <c r="B53" s="41"/>
-      <c r="C53" s="55">
+      <c r="C53" s="54">
         <v>49.4</v>
       </c>
-      <c r="D53" s="55">
+      <c r="D53" s="54">
         <v>44.8</v>
       </c>
-      <c r="E53" s="55">
+      <c r="E53" s="54">
         <v>40.4</v>
       </c>
-      <c r="F53" s="55"/>
-      <c r="G53" s="55">
+      <c r="F53" s="54"/>
+      <c r="G53" s="54">
         <v>38</v>
       </c>
-      <c r="H53" s="55">
+      <c r="H53" s="54">
         <v>36.799999999999997</v>
       </c>
-      <c r="I53" s="55">
+      <c r="I53" s="54">
         <v>33.700000000000003</v>
       </c>
     </row>
@@ -24765,23 +24765,23 @@
         <v>351</v>
       </c>
       <c r="B54" s="41"/>
-      <c r="C54" s="55">
+      <c r="C54" s="54">
         <v>30.2</v>
       </c>
-      <c r="D54" s="55">
+      <c r="D54" s="54">
         <v>29.9</v>
       </c>
-      <c r="E54" s="55">
+      <c r="E54" s="54">
         <v>28.5</v>
       </c>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55">
+      <c r="F54" s="54"/>
+      <c r="G54" s="54">
         <v>26.6</v>
       </c>
-      <c r="H54" s="55">
+      <c r="H54" s="54">
         <v>25.6</v>
       </c>
-      <c r="I54" s="55">
+      <c r="I54" s="54">
         <v>27.8</v>
       </c>
     </row>
@@ -24790,23 +24790,23 @@
         <v>156</v>
       </c>
       <c r="B55" s="41"/>
-      <c r="C55" s="55">
+      <c r="C55" s="54">
         <v>51.8</v>
       </c>
-      <c r="D55" s="55">
+      <c r="D55" s="54">
         <v>51.1</v>
       </c>
-      <c r="E55" s="55">
+      <c r="E55" s="54">
         <v>52.3</v>
       </c>
-      <c r="F55" s="55"/>
-      <c r="G55" s="55">
+      <c r="F55" s="54"/>
+      <c r="G55" s="54">
         <v>43</v>
       </c>
-      <c r="H55" s="55">
+      <c r="H55" s="54">
         <v>39.299999999999997</v>
       </c>
-      <c r="I55" s="55">
+      <c r="I55" s="54">
         <v>36.6</v>
       </c>
     </row>
@@ -24815,23 +24815,23 @@
         <v>159</v>
       </c>
       <c r="B56" s="41"/>
-      <c r="C56" s="55">
+      <c r="C56" s="54">
         <v>46.2</v>
       </c>
-      <c r="D56" s="55">
+      <c r="D56" s="54">
         <v>46.7</v>
       </c>
-      <c r="E56" s="55">
+      <c r="E56" s="54">
         <v>48.8</v>
       </c>
-      <c r="F56" s="55"/>
-      <c r="G56" s="55">
+      <c r="F56" s="54"/>
+      <c r="G56" s="54">
         <v>38</v>
       </c>
-      <c r="H56" s="55">
+      <c r="H56" s="54">
         <v>39.4</v>
       </c>
-      <c r="I56" s="55">
+      <c r="I56" s="54">
         <v>34.799999999999997</v>
       </c>
     </row>
@@ -24840,23 +24840,23 @@
         <v>162</v>
       </c>
       <c r="B57" s="41"/>
-      <c r="C57" s="55">
+      <c r="C57" s="54">
         <v>54.7</v>
       </c>
-      <c r="D57" s="55">
+      <c r="D57" s="54">
         <v>54</v>
       </c>
-      <c r="E57" s="55">
+      <c r="E57" s="54">
         <v>52.6</v>
       </c>
-      <c r="F57" s="55"/>
-      <c r="G57" s="55">
+      <c r="F57" s="54"/>
+      <c r="G57" s="54">
         <v>39.299999999999997</v>
       </c>
-      <c r="H57" s="55">
+      <c r="H57" s="54">
         <v>39.9</v>
       </c>
-      <c r="I57" s="55">
+      <c r="I57" s="54">
         <v>39.700000000000003</v>
       </c>
     </row>
@@ -24865,23 +24865,23 @@
         <v>165</v>
       </c>
       <c r="B58" s="41"/>
-      <c r="C58" s="55">
+      <c r="C58" s="54">
         <v>49</v>
       </c>
-      <c r="D58" s="55">
+      <c r="D58" s="54">
         <v>52.1</v>
       </c>
-      <c r="E58" s="55">
+      <c r="E58" s="54">
         <v>53.1</v>
       </c>
-      <c r="F58" s="55"/>
-      <c r="G58" s="55">
+      <c r="F58" s="54"/>
+      <c r="G58" s="54">
         <v>30</v>
       </c>
-      <c r="H58" s="55">
+      <c r="H58" s="54">
         <v>30.6</v>
       </c>
-      <c r="I58" s="55">
+      <c r="I58" s="54">
         <v>30.1</v>
       </c>
     </row>
@@ -24890,23 +24890,23 @@
         <v>168</v>
       </c>
       <c r="B59" s="41"/>
-      <c r="C59" s="55">
+      <c r="C59" s="54">
         <v>47.9</v>
       </c>
-      <c r="D59" s="55">
+      <c r="D59" s="54">
         <v>46.5</v>
       </c>
-      <c r="E59" s="55">
+      <c r="E59" s="54">
         <v>49.8</v>
       </c>
-      <c r="F59" s="55"/>
-      <c r="G59" s="55">
+      <c r="F59" s="54"/>
+      <c r="G59" s="54">
         <v>39.4</v>
       </c>
-      <c r="H59" s="55">
+      <c r="H59" s="54">
         <v>36.4</v>
       </c>
-      <c r="I59" s="55">
+      <c r="I59" s="54">
         <v>35.700000000000003</v>
       </c>
     </row>
@@ -24915,23 +24915,23 @@
         <v>352</v>
       </c>
       <c r="B60" s="41"/>
-      <c r="C60" s="55">
+      <c r="C60" s="54">
         <v>45.7</v>
       </c>
-      <c r="D60" s="55">
+      <c r="D60" s="54">
         <v>46</v>
       </c>
-      <c r="E60" s="55">
+      <c r="E60" s="54">
         <v>44</v>
       </c>
-      <c r="F60" s="55"/>
-      <c r="G60" s="55">
+      <c r="F60" s="54"/>
+      <c r="G60" s="54">
         <v>30.3</v>
       </c>
-      <c r="H60" s="55">
+      <c r="H60" s="54">
         <v>34.1</v>
       </c>
-      <c r="I60" s="55">
+      <c r="I60" s="54">
         <v>36.1</v>
       </c>
     </row>
@@ -24940,23 +24940,23 @@
         <v>174</v>
       </c>
       <c r="B61" s="41"/>
-      <c r="C61" s="55">
+      <c r="C61" s="54">
         <v>50.3</v>
       </c>
-      <c r="D61" s="55">
+      <c r="D61" s="54">
         <v>52.3</v>
       </c>
-      <c r="E61" s="55">
+      <c r="E61" s="54">
         <v>49.7</v>
       </c>
-      <c r="F61" s="55"/>
-      <c r="G61" s="55">
+      <c r="F61" s="54"/>
+      <c r="G61" s="54">
         <v>44.2</v>
       </c>
-      <c r="H61" s="55">
+      <c r="H61" s="54">
         <v>39.799999999999997</v>
       </c>
-      <c r="I61" s="55">
+      <c r="I61" s="54">
         <v>46.7</v>
       </c>
     </row>
@@ -24965,23 +24965,23 @@
         <v>177</v>
       </c>
       <c r="B62" s="41"/>
-      <c r="C62" s="55">
+      <c r="C62" s="54">
         <v>49.3</v>
       </c>
-      <c r="D62" s="55">
+      <c r="D62" s="54">
         <v>47.4</v>
       </c>
-      <c r="E62" s="55">
+      <c r="E62" s="54">
         <v>47.5</v>
       </c>
-      <c r="F62" s="55"/>
-      <c r="G62" s="55">
+      <c r="F62" s="54"/>
+      <c r="G62" s="54">
         <v>32.4</v>
       </c>
-      <c r="H62" s="55">
+      <c r="H62" s="54">
         <v>32.6</v>
       </c>
-      <c r="I62" s="55">
+      <c r="I62" s="54">
         <v>29.5</v>
       </c>
     </row>
@@ -24990,23 +24990,23 @@
         <v>180</v>
       </c>
       <c r="B63" s="41"/>
-      <c r="C63" s="55">
+      <c r="C63" s="54">
         <v>45.2</v>
       </c>
-      <c r="D63" s="55">
+      <c r="D63" s="54">
         <v>48.1</v>
       </c>
-      <c r="E63" s="55">
+      <c r="E63" s="54">
         <v>51.3</v>
       </c>
-      <c r="F63" s="55"/>
-      <c r="G63" s="55">
+      <c r="F63" s="54"/>
+      <c r="G63" s="54">
         <v>35.299999999999997</v>
       </c>
-      <c r="H63" s="55">
+      <c r="H63" s="54">
         <v>37.700000000000003</v>
       </c>
-      <c r="I63" s="55">
+      <c r="I63" s="54">
         <v>36.799999999999997</v>
       </c>
     </row>
@@ -25015,23 +25015,23 @@
         <v>353</v>
       </c>
       <c r="B64" s="41"/>
-      <c r="C64" s="55">
+      <c r="C64" s="54">
         <v>57.8</v>
       </c>
-      <c r="D64" s="55">
+      <c r="D64" s="54">
         <v>52.7</v>
       </c>
-      <c r="E64" s="55">
+      <c r="E64" s="54">
         <v>58.3</v>
       </c>
-      <c r="F64" s="55"/>
-      <c r="G64" s="55">
+      <c r="F64" s="54"/>
+      <c r="G64" s="54">
         <v>32.6</v>
       </c>
-      <c r="H64" s="55">
+      <c r="H64" s="54">
         <v>32.5</v>
       </c>
-      <c r="I64" s="55">
+      <c r="I64" s="54">
         <v>30.7</v>
       </c>
     </row>
@@ -25040,23 +25040,23 @@
         <v>354</v>
       </c>
       <c r="B65" s="41"/>
-      <c r="C65" s="55">
+      <c r="C65" s="54">
         <v>41.9</v>
       </c>
-      <c r="D65" s="55">
+      <c r="D65" s="54">
         <v>40.9</v>
       </c>
-      <c r="E65" s="55">
+      <c r="E65" s="54">
         <v>34.799999999999997</v>
       </c>
-      <c r="F65" s="55"/>
-      <c r="G65" s="55">
+      <c r="F65" s="54"/>
+      <c r="G65" s="54">
         <v>34.1</v>
       </c>
-      <c r="H65" s="55">
+      <c r="H65" s="54">
         <v>31.6</v>
       </c>
-      <c r="I65" s="55">
+      <c r="I65" s="54">
         <v>28.8</v>
       </c>
     </row>
@@ -25065,23 +25065,23 @@
         <v>355</v>
       </c>
       <c r="B66" s="41"/>
-      <c r="C66" s="55">
+      <c r="C66" s="54">
         <v>37.9</v>
       </c>
-      <c r="D66" s="55">
+      <c r="D66" s="54">
         <v>37.1</v>
       </c>
-      <c r="E66" s="55">
+      <c r="E66" s="54">
         <v>39.1</v>
       </c>
-      <c r="F66" s="55"/>
-      <c r="G66" s="55">
+      <c r="F66" s="54"/>
+      <c r="G66" s="54">
         <v>27.4</v>
       </c>
-      <c r="H66" s="55">
+      <c r="H66" s="54">
         <v>28.4</v>
       </c>
-      <c r="I66" s="55">
+      <c r="I66" s="54">
         <v>27.2</v>
       </c>
     </row>
@@ -25090,23 +25090,23 @@
         <v>356</v>
       </c>
       <c r="B67" s="41"/>
-      <c r="C67" s="55">
+      <c r="C67" s="54">
         <v>48.4</v>
       </c>
-      <c r="D67" s="55">
+      <c r="D67" s="54">
         <v>46.9</v>
       </c>
-      <c r="E67" s="55">
+      <c r="E67" s="54">
         <v>48.7</v>
       </c>
-      <c r="F67" s="55"/>
-      <c r="G67" s="55">
+      <c r="F67" s="54"/>
+      <c r="G67" s="54">
         <v>34.4</v>
       </c>
-      <c r="H67" s="55">
+      <c r="H67" s="54">
         <v>34.4</v>
       </c>
-      <c r="I67" s="55">
+      <c r="I67" s="54">
         <v>31.4</v>
       </c>
     </row>
@@ -25115,23 +25115,23 @@
         <v>191</v>
       </c>
       <c r="B68" s="41"/>
-      <c r="C68" s="55">
+      <c r="C68" s="54">
         <v>39.1</v>
       </c>
-      <c r="D68" s="55">
+      <c r="D68" s="54">
         <v>36.9</v>
       </c>
-      <c r="E68" s="55">
+      <c r="E68" s="54">
         <v>34.700000000000003</v>
       </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55">
+      <c r="F68" s="54"/>
+      <c r="G68" s="54">
         <v>27.7</v>
       </c>
-      <c r="H68" s="55">
+      <c r="H68" s="54">
         <v>32.6</v>
       </c>
-      <c r="I68" s="55">
+      <c r="I68" s="54">
         <v>34.5</v>
       </c>
     </row>
@@ -25140,23 +25140,23 @@
         <v>357</v>
       </c>
       <c r="B69" s="41"/>
-      <c r="C69" s="55">
+      <c r="C69" s="54">
         <v>49.3</v>
       </c>
-      <c r="D69" s="55">
+      <c r="D69" s="54">
         <v>48.5</v>
       </c>
-      <c r="E69" s="55">
+      <c r="E69" s="54">
         <v>49.2</v>
       </c>
-      <c r="F69" s="55"/>
-      <c r="G69" s="55">
+      <c r="F69" s="54"/>
+      <c r="G69" s="54">
         <v>36.4</v>
       </c>
-      <c r="H69" s="55">
+      <c r="H69" s="54">
         <v>37.6</v>
       </c>
-      <c r="I69" s="55">
+      <c r="I69" s="54">
         <v>36.1</v>
       </c>
     </row>
@@ -25165,23 +25165,23 @@
         <v>358</v>
       </c>
       <c r="B70" s="41"/>
-      <c r="C70" s="55">
+      <c r="C70" s="54">
         <v>58.1</v>
       </c>
-      <c r="D70" s="55">
+      <c r="D70" s="54">
         <v>56.1</v>
       </c>
-      <c r="E70" s="55">
+      <c r="E70" s="54">
         <v>58.5</v>
       </c>
-      <c r="F70" s="55"/>
-      <c r="G70" s="55">
+      <c r="F70" s="54"/>
+      <c r="G70" s="54">
         <v>39.1</v>
       </c>
-      <c r="H70" s="55">
+      <c r="H70" s="54">
         <v>33.200000000000003</v>
       </c>
-      <c r="I70" s="55">
+      <c r="I70" s="54">
         <v>36.9</v>
       </c>
     </row>
@@ -25190,23 +25190,23 @@
         <v>359</v>
       </c>
       <c r="B71" s="41"/>
-      <c r="C71" s="55">
+      <c r="C71" s="54">
         <v>47.7</v>
       </c>
-      <c r="D71" s="55">
+      <c r="D71" s="54">
         <v>46.8</v>
       </c>
-      <c r="E71" s="55">
+      <c r="E71" s="54">
         <v>47.7</v>
       </c>
-      <c r="F71" s="55"/>
-      <c r="G71" s="55">
+      <c r="F71" s="54"/>
+      <c r="G71" s="54">
         <v>33.299999999999997</v>
       </c>
-      <c r="H71" s="55">
+      <c r="H71" s="54">
         <v>34.200000000000003</v>
       </c>
-      <c r="I71" s="55">
+      <c r="I71" s="54">
         <v>33.4</v>
       </c>
     </row>
@@ -25215,23 +25215,23 @@
         <v>360</v>
       </c>
       <c r="B72" s="41"/>
-      <c r="C72" s="55">
+      <c r="C72" s="54">
         <v>24.4</v>
       </c>
-      <c r="D72" s="55">
+      <c r="D72" s="54">
         <v>28</v>
       </c>
-      <c r="E72" s="55">
+      <c r="E72" s="54">
         <v>21.1</v>
       </c>
-      <c r="F72" s="55"/>
-      <c r="G72" s="55">
+      <c r="F72" s="54"/>
+      <c r="G72" s="54">
         <v>22.5</v>
       </c>
-      <c r="H72" s="55">
+      <c r="H72" s="54">
         <v>23.7</v>
       </c>
-      <c r="I72" s="55">
+      <c r="I72" s="54">
         <v>18.600000000000001</v>
       </c>
     </row>
@@ -25240,23 +25240,23 @@
         <v>361</v>
       </c>
       <c r="B73" s="41"/>
-      <c r="C73" s="57" t="s">
+      <c r="C73" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57" t="s">
+      <c r="F73" s="56"/>
+      <c r="G73" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H73" s="57" t="s">
+      <c r="H73" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I73" s="57" t="s">
+      <c r="I73" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25265,23 +25265,23 @@
         <v>363</v>
       </c>
       <c r="B74" s="41"/>
-      <c r="C74" s="55">
+      <c r="C74" s="54">
         <v>28.4</v>
       </c>
-      <c r="D74" s="55">
+      <c r="D74" s="54">
         <v>25.1</v>
       </c>
-      <c r="E74" s="55">
+      <c r="E74" s="54">
         <v>27.2</v>
       </c>
-      <c r="F74" s="55"/>
-      <c r="G74" s="55">
+      <c r="F74" s="54"/>
+      <c r="G74" s="54">
         <v>20.399999999999999</v>
       </c>
-      <c r="H74" s="55">
+      <c r="H74" s="54">
         <v>18.5</v>
       </c>
-      <c r="I74" s="55">
+      <c r="I74" s="54">
         <v>16.7</v>
       </c>
     </row>
@@ -25290,23 +25290,23 @@
         <v>364</v>
       </c>
       <c r="B75" s="41"/>
-      <c r="C75" s="57" t="s">
+      <c r="C75" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D75" s="57" t="s">
+      <c r="D75" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E75" s="57" t="s">
+      <c r="E75" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57" t="s">
+      <c r="F75" s="56"/>
+      <c r="G75" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H75" s="57" t="s">
+      <c r="H75" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I75" s="57" t="s">
+      <c r="I75" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25315,23 +25315,23 @@
         <v>365</v>
       </c>
       <c r="B76" s="41"/>
-      <c r="C76" s="55">
+      <c r="C76" s="54">
         <v>59.1</v>
       </c>
-      <c r="D76" s="55">
+      <c r="D76" s="54">
         <v>60.8</v>
       </c>
-      <c r="E76" s="55">
+      <c r="E76" s="54">
         <v>60.8</v>
       </c>
-      <c r="F76" s="55"/>
-      <c r="G76" s="55">
+      <c r="F76" s="54"/>
+      <c r="G76" s="54">
         <v>43.1</v>
       </c>
-      <c r="H76" s="55">
+      <c r="H76" s="54">
         <v>42.6</v>
       </c>
-      <c r="I76" s="55">
+      <c r="I76" s="54">
         <v>40.299999999999997</v>
       </c>
     </row>
@@ -25340,23 +25340,23 @@
         <v>366</v>
       </c>
       <c r="B77" s="41"/>
-      <c r="C77" s="55">
+      <c r="C77" s="54">
         <v>32.4</v>
       </c>
-      <c r="D77" s="55">
+      <c r="D77" s="54">
         <v>31.5</v>
       </c>
-      <c r="E77" s="55">
+      <c r="E77" s="54">
         <v>30</v>
       </c>
-      <c r="F77" s="55"/>
-      <c r="G77" s="55">
+      <c r="F77" s="54"/>
+      <c r="G77" s="54">
         <v>17.899999999999999</v>
       </c>
-      <c r="H77" s="55">
+      <c r="H77" s="54">
         <v>19.8</v>
       </c>
-      <c r="I77" s="55">
+      <c r="I77" s="54">
         <v>17.600000000000001</v>
       </c>
     </row>
@@ -25365,23 +25365,23 @@
         <v>367</v>
       </c>
       <c r="B78" s="41"/>
-      <c r="C78" s="55">
+      <c r="C78" s="54">
         <v>62.5</v>
       </c>
-      <c r="D78" s="55">
+      <c r="D78" s="54">
         <v>66.2</v>
       </c>
-      <c r="E78" s="55">
+      <c r="E78" s="54">
         <v>61.1</v>
       </c>
-      <c r="F78" s="55"/>
-      <c r="G78" s="55">
+      <c r="F78" s="54"/>
+      <c r="G78" s="54">
         <v>52.3</v>
       </c>
-      <c r="H78" s="55">
+      <c r="H78" s="54">
         <v>45.8</v>
       </c>
-      <c r="I78" s="55">
+      <c r="I78" s="54">
         <v>44.9</v>
       </c>
     </row>
@@ -25390,23 +25390,23 @@
         <v>368</v>
       </c>
       <c r="B79" s="41"/>
-      <c r="C79" s="55">
+      <c r="C79" s="54">
         <v>35.4</v>
       </c>
-      <c r="D79" s="55">
+      <c r="D79" s="54">
         <v>34.799999999999997</v>
       </c>
-      <c r="E79" s="55">
+      <c r="E79" s="54">
         <v>29.1</v>
       </c>
-      <c r="F79" s="55"/>
-      <c r="G79" s="55">
+      <c r="F79" s="54"/>
+      <c r="G79" s="54">
         <v>21.9</v>
       </c>
-      <c r="H79" s="55">
+      <c r="H79" s="54">
         <v>23.3</v>
       </c>
-      <c r="I79" s="55">
+      <c r="I79" s="54">
         <v>20.6</v>
       </c>
     </row>
@@ -25415,23 +25415,23 @@
         <v>369</v>
       </c>
       <c r="B80" s="41"/>
-      <c r="C80" s="55">
+      <c r="C80" s="54">
         <v>36.700000000000003</v>
       </c>
-      <c r="D80" s="55">
+      <c r="D80" s="54">
         <v>33.700000000000003</v>
       </c>
-      <c r="E80" s="55">
+      <c r="E80" s="54">
         <v>35.700000000000003</v>
       </c>
-      <c r="F80" s="55"/>
-      <c r="G80" s="55">
+      <c r="F80" s="54"/>
+      <c r="G80" s="54">
         <v>24.3</v>
       </c>
-      <c r="H80" s="55">
+      <c r="H80" s="54">
         <v>23.9</v>
       </c>
-      <c r="I80" s="55">
+      <c r="I80" s="54">
         <v>23.1</v>
       </c>
     </row>
@@ -25440,23 +25440,23 @@
         <v>370</v>
       </c>
       <c r="B81" s="41"/>
-      <c r="C81" s="55">
+      <c r="C81" s="54">
         <v>31.4</v>
       </c>
-      <c r="D81" s="55">
+      <c r="D81" s="54">
         <v>33.1</v>
       </c>
-      <c r="E81" s="55">
+      <c r="E81" s="54">
         <v>34.5</v>
       </c>
-      <c r="F81" s="55"/>
-      <c r="G81" s="55">
+      <c r="F81" s="54"/>
+      <c r="G81" s="54">
         <v>19.3</v>
       </c>
-      <c r="H81" s="55">
+      <c r="H81" s="54">
         <v>19.7</v>
       </c>
-      <c r="I81" s="55">
+      <c r="I81" s="54">
         <v>24.7</v>
       </c>
     </row>
@@ -25465,23 +25465,23 @@
         <v>371</v>
       </c>
       <c r="B82" s="41"/>
-      <c r="C82" s="55">
+      <c r="C82" s="54">
         <v>40.4</v>
       </c>
-      <c r="D82" s="55">
+      <c r="D82" s="54">
         <v>38.799999999999997</v>
       </c>
-      <c r="E82" s="55">
+      <c r="E82" s="54">
         <v>36</v>
       </c>
-      <c r="F82" s="55"/>
-      <c r="G82" s="55">
+      <c r="F82" s="54"/>
+      <c r="G82" s="54">
         <v>28.8</v>
       </c>
-      <c r="H82" s="55">
+      <c r="H82" s="54">
         <v>27.2</v>
       </c>
-      <c r="I82" s="55">
+      <c r="I82" s="54">
         <v>25.7</v>
       </c>
     </row>
@@ -25490,23 +25490,23 @@
         <v>372</v>
       </c>
       <c r="B83" s="41"/>
-      <c r="C83" s="57" t="s">
+      <c r="C83" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D83" s="57" t="s">
+      <c r="D83" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E83" s="57" t="s">
+      <c r="E83" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57" t="s">
+      <c r="F83" s="56"/>
+      <c r="G83" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H83" s="57" t="s">
+      <c r="H83" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I83" s="57" t="s">
+      <c r="I83" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25515,23 +25515,23 @@
         <v>373</v>
       </c>
       <c r="B84" s="41"/>
-      <c r="C84" s="55">
+      <c r="C84" s="54">
         <v>52.1</v>
       </c>
-      <c r="D84" s="55">
+      <c r="D84" s="54">
         <v>47.5</v>
       </c>
-      <c r="E84" s="55">
+      <c r="E84" s="54">
         <v>49.1</v>
       </c>
-      <c r="F84" s="55"/>
-      <c r="G84" s="55">
+      <c r="F84" s="54"/>
+      <c r="G84" s="54">
         <v>33</v>
       </c>
-      <c r="H84" s="55">
+      <c r="H84" s="54">
         <v>35.700000000000003</v>
       </c>
-      <c r="I84" s="55">
+      <c r="I84" s="54">
         <v>35.700000000000003</v>
       </c>
     </row>
@@ -25540,23 +25540,23 @@
         <v>374</v>
       </c>
       <c r="B85" s="41"/>
-      <c r="C85" s="55">
+      <c r="C85" s="54">
         <v>36.299999999999997</v>
       </c>
-      <c r="D85" s="55">
+      <c r="D85" s="54">
         <v>29</v>
       </c>
-      <c r="E85" s="55">
+      <c r="E85" s="54">
         <v>36.6</v>
       </c>
-      <c r="F85" s="55"/>
-      <c r="G85" s="55">
+      <c r="F85" s="54"/>
+      <c r="G85" s="54">
         <v>21.1</v>
       </c>
-      <c r="H85" s="55">
+      <c r="H85" s="54">
         <v>16.600000000000001</v>
       </c>
-      <c r="I85" s="55">
+      <c r="I85" s="54">
         <v>28.2</v>
       </c>
     </row>
@@ -25565,23 +25565,23 @@
         <v>375</v>
       </c>
       <c r="B86" s="41"/>
-      <c r="C86" s="55">
+      <c r="C86" s="54">
         <v>46</v>
       </c>
-      <c r="D86" s="55">
+      <c r="D86" s="54">
         <v>45.2</v>
       </c>
-      <c r="E86" s="55">
+      <c r="E86" s="54">
         <v>48.6</v>
       </c>
-      <c r="F86" s="55"/>
-      <c r="G86" s="55">
+      <c r="F86" s="54"/>
+      <c r="G86" s="54">
         <v>32.6</v>
       </c>
-      <c r="H86" s="55">
+      <c r="H86" s="54">
         <v>31.4</v>
       </c>
-      <c r="I86" s="55">
+      <c r="I86" s="54">
         <v>37.4</v>
       </c>
     </row>
@@ -25590,23 +25590,23 @@
         <v>376</v>
       </c>
       <c r="B87" s="41"/>
-      <c r="C87" s="57" t="s">
+      <c r="C87" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D87" s="57" t="s">
+      <c r="D87" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E87" s="55">
+      <c r="E87" s="54">
         <v>34.1</v>
       </c>
-      <c r="F87" s="55"/>
-      <c r="G87" s="57" t="s">
+      <c r="F87" s="54"/>
+      <c r="G87" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H87" s="57" t="s">
+      <c r="H87" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I87" s="55">
+      <c r="I87" s="54">
         <v>21.8</v>
       </c>
     </row>
@@ -25615,23 +25615,23 @@
         <v>377</v>
       </c>
       <c r="B88" s="41"/>
-      <c r="C88" s="55">
-        <v>5.18</v>
-      </c>
-      <c r="D88" s="55">
+      <c r="C88" s="54">
+        <v>51.8</v>
+      </c>
+      <c r="D88" s="54">
         <v>52.3</v>
       </c>
-      <c r="E88" s="55">
+      <c r="E88" s="54">
         <v>51.1</v>
       </c>
-      <c r="F88" s="55"/>
-      <c r="G88" s="55">
+      <c r="F88" s="54"/>
+      <c r="G88" s="54">
         <v>43</v>
       </c>
-      <c r="H88" s="55">
+      <c r="H88" s="54">
         <v>41.3</v>
       </c>
-      <c r="I88" s="55">
+      <c r="I88" s="54">
         <v>42</v>
       </c>
     </row>
@@ -25640,23 +25640,23 @@
         <v>378</v>
       </c>
       <c r="B89" s="41"/>
-      <c r="C89" s="55">
+      <c r="C89" s="54">
         <v>44</v>
       </c>
-      <c r="D89" s="55">
+      <c r="D89" s="54">
         <v>47.5</v>
       </c>
-      <c r="E89" s="55">
+      <c r="E89" s="54">
         <v>44.7</v>
       </c>
-      <c r="F89" s="55"/>
-      <c r="G89" s="55">
+      <c r="F89" s="54"/>
+      <c r="G89" s="54">
         <v>24.5</v>
       </c>
-      <c r="H89" s="55">
+      <c r="H89" s="54">
         <v>27</v>
       </c>
-      <c r="I89" s="55">
+      <c r="I89" s="54">
         <v>25.7</v>
       </c>
     </row>
@@ -25665,23 +25665,23 @@
         <v>379</v>
       </c>
       <c r="B90" s="41"/>
-      <c r="C90" s="55">
+      <c r="C90" s="54">
         <v>30.9</v>
       </c>
-      <c r="D90" s="55">
+      <c r="D90" s="54">
         <v>31.8</v>
       </c>
-      <c r="E90" s="55">
+      <c r="E90" s="54">
         <v>30.8</v>
       </c>
-      <c r="F90" s="55"/>
-      <c r="G90" s="55">
+      <c r="F90" s="54"/>
+      <c r="G90" s="54">
         <v>18.5</v>
       </c>
-      <c r="H90" s="55">
+      <c r="H90" s="54">
         <v>20</v>
       </c>
-      <c r="I90" s="55">
+      <c r="I90" s="54">
         <v>33.9</v>
       </c>
     </row>
@@ -25690,23 +25690,23 @@
         <v>380</v>
       </c>
       <c r="B91" s="41"/>
-      <c r="C91" s="55">
+      <c r="C91" s="54">
         <v>19.7</v>
       </c>
-      <c r="D91" s="55">
+      <c r="D91" s="54">
         <v>20.100000000000001</v>
       </c>
-      <c r="E91" s="55">
+      <c r="E91" s="54">
         <v>21</v>
       </c>
-      <c r="F91" s="55"/>
-      <c r="G91" s="55">
+      <c r="F91" s="54"/>
+      <c r="G91" s="54">
         <v>19.7</v>
       </c>
-      <c r="H91" s="55">
+      <c r="H91" s="54">
         <v>19.7</v>
       </c>
-      <c r="I91" s="55">
+      <c r="I91" s="54">
         <v>19.3</v>
       </c>
     </row>
@@ -25715,23 +25715,23 @@
         <v>381</v>
       </c>
       <c r="B92" s="41"/>
-      <c r="C92" s="55">
+      <c r="C92" s="54">
         <v>45.6</v>
       </c>
-      <c r="D92" s="55">
+      <c r="D92" s="54">
         <v>45.5</v>
       </c>
-      <c r="E92" s="55">
+      <c r="E92" s="54">
         <v>45.6</v>
       </c>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55">
+      <c r="F92" s="54"/>
+      <c r="G92" s="54">
         <v>32.1</v>
       </c>
-      <c r="H92" s="55">
+      <c r="H92" s="54">
         <v>31</v>
       </c>
-      <c r="I92" s="55">
+      <c r="I92" s="54">
         <v>33.5</v>
       </c>
     </row>
@@ -25740,23 +25740,23 @@
         <v>382</v>
       </c>
       <c r="B93" s="41"/>
-      <c r="C93" s="55">
+      <c r="C93" s="54">
         <v>30.2</v>
       </c>
-      <c r="D93" s="55">
+      <c r="D93" s="54">
         <v>29.5</v>
       </c>
-      <c r="E93" s="55">
+      <c r="E93" s="54">
         <v>31.7</v>
       </c>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55">
+      <c r="F93" s="54"/>
+      <c r="G93" s="54">
         <v>26.8</v>
       </c>
-      <c r="H93" s="55">
+      <c r="H93" s="54">
         <v>19.899999999999999</v>
       </c>
-      <c r="I93" s="55">
+      <c r="I93" s="54">
         <v>22.5</v>
       </c>
     </row>
@@ -25765,23 +25765,23 @@
         <v>383</v>
       </c>
       <c r="B94" s="41"/>
-      <c r="C94" s="57" t="s">
+      <c r="C94" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D94" s="57" t="s">
+      <c r="D94" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E94" s="57" t="s">
+      <c r="E94" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F94" s="57"/>
-      <c r="G94" s="57" t="s">
+      <c r="F94" s="56"/>
+      <c r="G94" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H94" s="57" t="s">
+      <c r="H94" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I94" s="57" t="s">
+      <c r="I94" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25790,42 +25790,42 @@
         <v>256</v>
       </c>
       <c r="B95" s="41"/>
-      <c r="C95" s="57" t="s">
+      <c r="C95" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D95" s="57" t="s">
+      <c r="D95" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E95" s="57" t="s">
+      <c r="E95" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F95" s="57"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="57"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="56"/>
+      <c r="I95" s="56"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="41" t="s">
         <v>384</v>
       </c>
       <c r="B96" s="41"/>
-      <c r="C96" s="57" t="s">
+      <c r="C96" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D96" s="57" t="s">
+      <c r="D96" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E96" s="57" t="s">
+      <c r="E96" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F96" s="57"/>
-      <c r="G96" s="57" t="s">
+      <c r="F96" s="56"/>
+      <c r="G96" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H96" s="57" t="s">
+      <c r="H96" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I96" s="57" t="s">
+      <c r="I96" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25834,23 +25834,23 @@
         <v>385</v>
       </c>
       <c r="B97" s="41"/>
-      <c r="C97" s="57" t="s">
+      <c r="C97" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D97" s="57" t="s">
+      <c r="D97" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E97" s="57" t="s">
+      <c r="E97" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57" t="s">
+      <c r="F97" s="56"/>
+      <c r="G97" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H97" s="57" t="s">
+      <c r="H97" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I97" s="57" t="s">
+      <c r="I97" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25859,23 +25859,23 @@
         <v>386</v>
       </c>
       <c r="B98" s="41"/>
-      <c r="C98" s="57" t="s">
+      <c r="C98" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D98" s="57" t="s">
+      <c r="D98" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E98" s="57" t="s">
+      <c r="E98" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57" t="s">
+      <c r="F98" s="56"/>
+      <c r="G98" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H98" s="57" t="s">
+      <c r="H98" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I98" s="57" t="s">
+      <c r="I98" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25884,23 +25884,23 @@
         <v>387</v>
       </c>
       <c r="B99" s="41"/>
-      <c r="C99" s="57" t="s">
+      <c r="C99" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D99" s="57" t="s">
+      <c r="D99" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E99" s="57" t="s">
+      <c r="E99" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F99" s="57"/>
-      <c r="G99" s="57" t="s">
+      <c r="F99" s="56"/>
+      <c r="G99" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H99" s="57" t="s">
+      <c r="H99" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I99" s="57" t="s">
+      <c r="I99" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25909,23 +25909,23 @@
         <v>388</v>
       </c>
       <c r="B100" s="41"/>
-      <c r="C100" s="57" t="s">
+      <c r="C100" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D100" s="57" t="s">
+      <c r="D100" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="E100" s="57" t="s">
+      <c r="E100" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57" t="s">
+      <c r="F100" s="56"/>
+      <c r="G100" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="H100" s="57" t="s">
+      <c r="H100" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="I100" s="57" t="s">
+      <c r="I100" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25934,23 +25934,23 @@
         <v>389</v>
       </c>
       <c r="B101" s="41"/>
-      <c r="C101" s="55">
+      <c r="C101" s="54">
         <v>63.9</v>
       </c>
-      <c r="D101" s="55">
+      <c r="D101" s="54">
         <v>59.8</v>
       </c>
-      <c r="E101" s="55" t="s">
+      <c r="E101" s="54" t="s">
         <v>362</v>
       </c>
-      <c r="F101" s="55"/>
-      <c r="G101" s="55">
+      <c r="F101" s="54"/>
+      <c r="G101" s="54">
         <v>41</v>
       </c>
-      <c r="H101" s="55">
+      <c r="H101" s="54">
         <v>48.8</v>
       </c>
-      <c r="I101" s="57" t="s">
+      <c r="I101" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25959,23 +25959,23 @@
         <v>390</v>
       </c>
       <c r="B102" s="41"/>
-      <c r="C102" s="55">
+      <c r="C102" s="54">
         <v>49.8</v>
       </c>
-      <c r="D102" s="55">
+      <c r="D102" s="54">
         <v>47.9</v>
       </c>
-      <c r="E102" s="55" t="s">
+      <c r="E102" s="54" t="s">
         <v>362</v>
       </c>
-      <c r="F102" s="55"/>
-      <c r="G102" s="55">
+      <c r="F102" s="54"/>
+      <c r="G102" s="54">
         <v>35</v>
       </c>
-      <c r="H102" s="55">
+      <c r="H102" s="54">
         <v>35</v>
       </c>
-      <c r="I102" s="57" t="s">
+      <c r="I102" s="56" t="s">
         <v>362</v>
       </c>
     </row>
@@ -25984,3402 +25984,3402 @@
         <v>391</v>
       </c>
       <c r="B103" s="41"/>
-      <c r="C103" s="55">
+      <c r="C103" s="54">
         <v>47.2</v>
       </c>
-      <c r="D103" s="55">
+      <c r="D103" s="54">
         <v>46.1</v>
       </c>
-      <c r="E103" s="55">
+      <c r="E103" s="54">
         <v>46.7</v>
       </c>
-      <c r="F103" s="55"/>
-      <c r="G103" s="55">
+      <c r="F103" s="54"/>
+      <c r="G103" s="54">
         <v>33</v>
       </c>
-      <c r="H103" s="55">
+      <c r="H103" s="54">
         <v>33.5</v>
       </c>
-      <c r="I103" s="55">
+      <c r="I103" s="54">
         <v>32.700000000000003</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="41"/>
       <c r="B104" s="41"/>
-      <c r="C104" s="55"/>
-      <c r="D104" s="55"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="55"/>
-      <c r="I104" s="55"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="54"/>
+      <c r="I104" s="54"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="41"/>
       <c r="B105" s="41"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="55"/>
+      <c r="C105" s="54"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="54"/>
+      <c r="G105" s="54"/>
+      <c r="H105" s="54"/>
+      <c r="I105" s="54"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="41"/>
       <c r="B106" s="41"/>
-      <c r="C106" s="55"/>
-      <c r="D106" s="55"/>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55"/>
-      <c r="G106" s="55"/>
-      <c r="H106" s="55"/>
-      <c r="I106" s="55"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="54"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="54"/>
+      <c r="H106" s="54"/>
+      <c r="I106" s="54"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="41"/>
       <c r="B107" s="41"/>
-      <c r="C107" s="55"/>
-      <c r="D107" s="55"/>
-      <c r="E107" s="55"/>
-      <c r="F107" s="55"/>
-      <c r="G107" s="55"/>
-      <c r="H107" s="55"/>
-      <c r="I107" s="55"/>
+      <c r="C107" s="54"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="54"/>
+      <c r="H107" s="54"/>
+      <c r="I107" s="54"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="41"/>
       <c r="B108" s="41"/>
-      <c r="C108" s="55"/>
-      <c r="D108" s="55"/>
-      <c r="E108" s="55"/>
-      <c r="F108" s="55"/>
-      <c r="G108" s="55"/>
-      <c r="H108" s="55"/>
-      <c r="I108" s="55"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="54"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="54"/>
+      <c r="I108" s="54"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="41"/>
       <c r="B109" s="41"/>
-      <c r="C109" s="55"/>
-      <c r="D109" s="55"/>
-      <c r="E109" s="55"/>
-      <c r="F109" s="55"/>
-      <c r="G109" s="55"/>
-      <c r="H109" s="55"/>
-      <c r="I109" s="55"/>
+      <c r="C109" s="54"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="54"/>
+      <c r="I109" s="54"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
-      <c r="C110" s="55"/>
-      <c r="D110" s="55"/>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55"/>
-      <c r="G110" s="55"/>
-      <c r="H110" s="55"/>
-      <c r="I110" s="55"/>
+      <c r="C110" s="54"/>
+      <c r="D110" s="54"/>
+      <c r="E110" s="54"/>
+      <c r="F110" s="54"/>
+      <c r="G110" s="54"/>
+      <c r="H110" s="54"/>
+      <c r="I110" s="54"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="41"/>
       <c r="B111" s="41"/>
-      <c r="C111" s="55"/>
-      <c r="D111" s="55"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55"/>
-      <c r="G111" s="55"/>
-      <c r="H111" s="55"/>
-      <c r="I111" s="55"/>
+      <c r="C111" s="54"/>
+      <c r="D111" s="54"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="54"/>
+      <c r="H111" s="54"/>
+      <c r="I111" s="54"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="41"/>
       <c r="B112" s="41"/>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="55"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="55"/>
-      <c r="H112" s="55"/>
-      <c r="I112" s="55"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="54"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="41"/>
       <c r="B113" s="41"/>
-      <c r="C113" s="55"/>
-      <c r="D113" s="55"/>
-      <c r="E113" s="55"/>
-      <c r="F113" s="55"/>
-      <c r="G113" s="55"/>
-      <c r="H113" s="55"/>
-      <c r="I113" s="55"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="54"/>
+      <c r="I113" s="54"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="41"/>
       <c r="B114" s="41"/>
-      <c r="C114" s="55"/>
-      <c r="D114" s="55"/>
-      <c r="E114" s="55"/>
-      <c r="F114" s="55"/>
-      <c r="G114" s="55"/>
-      <c r="H114" s="55"/>
-      <c r="I114" s="55"/>
+      <c r="C114" s="54"/>
+      <c r="D114" s="54"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="54"/>
+      <c r="H114" s="54"/>
+      <c r="I114" s="54"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="41"/>
       <c r="B115" s="41"/>
-      <c r="C115" s="55"/>
-      <c r="D115" s="55"/>
-      <c r="E115" s="55"/>
-      <c r="F115" s="55"/>
-      <c r="G115" s="55"/>
-      <c r="H115" s="55"/>
-      <c r="I115" s="55"/>
+      <c r="C115" s="54"/>
+      <c r="D115" s="54"/>
+      <c r="E115" s="54"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="54"/>
+      <c r="H115" s="54"/>
+      <c r="I115" s="54"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="41"/>
       <c r="B116" s="41"/>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="55"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="55"/>
-      <c r="H116" s="55"/>
-      <c r="I116" s="55"/>
+      <c r="C116" s="54"/>
+      <c r="D116" s="54"/>
+      <c r="E116" s="54"/>
+      <c r="F116" s="54"/>
+      <c r="G116" s="54"/>
+      <c r="H116" s="54"/>
+      <c r="I116" s="54"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="41"/>
       <c r="B117" s="41"/>
-      <c r="C117" s="55"/>
-      <c r="D117" s="55"/>
-      <c r="E117" s="55"/>
-      <c r="F117" s="55"/>
-      <c r="G117" s="55"/>
-      <c r="H117" s="55"/>
-      <c r="I117" s="55"/>
+      <c r="C117" s="54"/>
+      <c r="D117" s="54"/>
+      <c r="E117" s="54"/>
+      <c r="F117" s="54"/>
+      <c r="G117" s="54"/>
+      <c r="H117" s="54"/>
+      <c r="I117" s="54"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
-      <c r="C118" s="55"/>
-      <c r="D118" s="55"/>
-      <c r="E118" s="55"/>
-      <c r="F118" s="55"/>
-      <c r="G118" s="55"/>
-      <c r="H118" s="55"/>
-      <c r="I118" s="55"/>
+      <c r="C118" s="54"/>
+      <c r="D118" s="54"/>
+      <c r="E118" s="54"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="54"/>
+      <c r="H118" s="54"/>
+      <c r="I118" s="54"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
-      <c r="C119" s="55"/>
-      <c r="D119" s="55"/>
-      <c r="E119" s="55"/>
-      <c r="F119" s="55"/>
-      <c r="G119" s="55"/>
-      <c r="H119" s="55"/>
-      <c r="I119" s="55"/>
+      <c r="C119" s="54"/>
+      <c r="D119" s="54"/>
+      <c r="E119" s="54"/>
+      <c r="F119" s="54"/>
+      <c r="G119" s="54"/>
+      <c r="H119" s="54"/>
+      <c r="I119" s="54"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
-      <c r="C120" s="55"/>
-      <c r="D120" s="55"/>
-      <c r="E120" s="55"/>
-      <c r="F120" s="55"/>
-      <c r="G120" s="55"/>
-      <c r="H120" s="55"/>
-      <c r="I120" s="55"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="54"/>
+      <c r="E120" s="54"/>
+      <c r="F120" s="54"/>
+      <c r="G120" s="54"/>
+      <c r="H120" s="54"/>
+      <c r="I120" s="54"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
-      <c r="C121" s="55"/>
-      <c r="D121" s="55"/>
-      <c r="E121" s="55"/>
-      <c r="F121" s="55"/>
-      <c r="G121" s="55"/>
-      <c r="H121" s="55"/>
-      <c r="I121" s="55"/>
+      <c r="C121" s="54"/>
+      <c r="D121" s="54"/>
+      <c r="E121" s="54"/>
+      <c r="F121" s="54"/>
+      <c r="G121" s="54"/>
+      <c r="H121" s="54"/>
+      <c r="I121" s="54"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
-      <c r="C122" s="55"/>
-      <c r="D122" s="55"/>
-      <c r="E122" s="55"/>
-      <c r="F122" s="55"/>
-      <c r="G122" s="55"/>
-      <c r="H122" s="55"/>
-      <c r="I122" s="55"/>
+      <c r="C122" s="54"/>
+      <c r="D122" s="54"/>
+      <c r="E122" s="54"/>
+      <c r="F122" s="54"/>
+      <c r="G122" s="54"/>
+      <c r="H122" s="54"/>
+      <c r="I122" s="54"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
-      <c r="C123" s="55"/>
-      <c r="D123" s="55"/>
-      <c r="E123" s="55"/>
-      <c r="F123" s="55"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="55"/>
-      <c r="I123" s="55"/>
+      <c r="C123" s="54"/>
+      <c r="D123" s="54"/>
+      <c r="E123" s="54"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="54"/>
+      <c r="H123" s="54"/>
+      <c r="I123" s="54"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
-      <c r="C124" s="55"/>
-      <c r="D124" s="55"/>
-      <c r="E124" s="55"/>
-      <c r="F124" s="55"/>
-      <c r="G124" s="55"/>
-      <c r="H124" s="55"/>
-      <c r="I124" s="55"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="54"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="54"/>
+      <c r="H124" s="54"/>
+      <c r="I124" s="54"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
-      <c r="C125" s="55"/>
-      <c r="D125" s="55"/>
-      <c r="E125" s="55"/>
-      <c r="F125" s="55"/>
-      <c r="G125" s="55"/>
-      <c r="H125" s="55"/>
-      <c r="I125" s="55"/>
+      <c r="C125" s="54"/>
+      <c r="D125" s="54"/>
+      <c r="E125" s="54"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="54"/>
+      <c r="H125" s="54"/>
+      <c r="I125" s="54"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
-      <c r="C126" s="55"/>
-      <c r="D126" s="55"/>
-      <c r="E126" s="55"/>
-      <c r="F126" s="55"/>
-      <c r="G126" s="55"/>
-      <c r="H126" s="55"/>
-      <c r="I126" s="55"/>
+      <c r="C126" s="54"/>
+      <c r="D126" s="54"/>
+      <c r="E126" s="54"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="54"/>
+      <c r="H126" s="54"/>
+      <c r="I126" s="54"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
-      <c r="C127" s="55"/>
-      <c r="D127" s="55"/>
-      <c r="E127" s="55"/>
-      <c r="F127" s="55"/>
-      <c r="G127" s="55"/>
-      <c r="H127" s="55"/>
-      <c r="I127" s="55"/>
+      <c r="C127" s="54"/>
+      <c r="D127" s="54"/>
+      <c r="E127" s="54"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="54"/>
+      <c r="H127" s="54"/>
+      <c r="I127" s="54"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
-      <c r="C128" s="55"/>
-      <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
-      <c r="F128" s="55"/>
-      <c r="G128" s="55"/>
-      <c r="H128" s="55"/>
-      <c r="I128" s="55"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="54"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="54"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
-      <c r="C129" s="55"/>
-      <c r="D129" s="55"/>
-      <c r="E129" s="55"/>
-      <c r="F129" s="55"/>
-      <c r="G129" s="55"/>
-      <c r="H129" s="55"/>
-      <c r="I129" s="55"/>
+      <c r="C129" s="54"/>
+      <c r="D129" s="54"/>
+      <c r="E129" s="54"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="54"/>
+      <c r="I129" s="54"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
-      <c r="C130" s="55"/>
-      <c r="D130" s="55"/>
-      <c r="E130" s="55"/>
-      <c r="F130" s="55"/>
-      <c r="G130" s="55"/>
-      <c r="H130" s="55"/>
-      <c r="I130" s="55"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="54"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
+      <c r="H130" s="54"/>
+      <c r="I130" s="54"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
-      <c r="C131" s="55"/>
-      <c r="D131" s="55"/>
-      <c r="E131" s="55"/>
-      <c r="F131" s="55"/>
-      <c r="G131" s="55"/>
-      <c r="H131" s="55"/>
-      <c r="I131" s="55"/>
+      <c r="C131" s="54"/>
+      <c r="D131" s="54"/>
+      <c r="E131" s="54"/>
+      <c r="F131" s="54"/>
+      <c r="G131" s="54"/>
+      <c r="H131" s="54"/>
+      <c r="I131" s="54"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
-      <c r="C132" s="55"/>
-      <c r="D132" s="55"/>
-      <c r="E132" s="55"/>
-      <c r="F132" s="55"/>
-      <c r="G132" s="55"/>
-      <c r="H132" s="55"/>
-      <c r="I132" s="55"/>
+      <c r="C132" s="54"/>
+      <c r="D132" s="54"/>
+      <c r="E132" s="54"/>
+      <c r="F132" s="54"/>
+      <c r="G132" s="54"/>
+      <c r="H132" s="54"/>
+      <c r="I132" s="54"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
-      <c r="C133" s="55"/>
-      <c r="D133" s="55"/>
-      <c r="E133" s="55"/>
-      <c r="F133" s="55"/>
-      <c r="G133" s="55"/>
-      <c r="H133" s="55"/>
-      <c r="I133" s="55"/>
+      <c r="C133" s="54"/>
+      <c r="D133" s="54"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="54"/>
+      <c r="H133" s="54"/>
+      <c r="I133" s="54"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
-      <c r="C134" s="55"/>
-      <c r="D134" s="55"/>
-      <c r="E134" s="55"/>
-      <c r="F134" s="55"/>
-      <c r="G134" s="55"/>
-      <c r="H134" s="55"/>
-      <c r="I134" s="55"/>
+      <c r="C134" s="54"/>
+      <c r="D134" s="54"/>
+      <c r="E134" s="54"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="54"/>
+      <c r="H134" s="54"/>
+      <c r="I134" s="54"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
-      <c r="C135" s="55"/>
-      <c r="D135" s="55"/>
-      <c r="E135" s="55"/>
-      <c r="F135" s="55"/>
-      <c r="G135" s="55"/>
-      <c r="H135" s="55"/>
-      <c r="I135" s="55"/>
+      <c r="C135" s="54"/>
+      <c r="D135" s="54"/>
+      <c r="E135" s="54"/>
+      <c r="F135" s="54"/>
+      <c r="G135" s="54"/>
+      <c r="H135" s="54"/>
+      <c r="I135" s="54"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
-      <c r="C136" s="55"/>
-      <c r="D136" s="55"/>
-      <c r="E136" s="55"/>
-      <c r="F136" s="55"/>
-      <c r="G136" s="55"/>
-      <c r="H136" s="55"/>
-      <c r="I136" s="55"/>
+      <c r="C136" s="54"/>
+      <c r="D136" s="54"/>
+      <c r="E136" s="54"/>
+      <c r="F136" s="54"/>
+      <c r="G136" s="54"/>
+      <c r="H136" s="54"/>
+      <c r="I136" s="54"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="41"/>
       <c r="B137" s="41"/>
-      <c r="C137" s="55"/>
-      <c r="D137" s="55"/>
-      <c r="E137" s="55"/>
-      <c r="F137" s="55"/>
-      <c r="G137" s="55"/>
-      <c r="H137" s="55"/>
-      <c r="I137" s="55"/>
+      <c r="C137" s="54"/>
+      <c r="D137" s="54"/>
+      <c r="E137" s="54"/>
+      <c r="F137" s="54"/>
+      <c r="G137" s="54"/>
+      <c r="H137" s="54"/>
+      <c r="I137" s="54"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="41"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="55"/>
-      <c r="D138" s="55"/>
-      <c r="E138" s="55"/>
-      <c r="F138" s="55"/>
-      <c r="G138" s="55"/>
-      <c r="H138" s="55"/>
-      <c r="I138" s="55"/>
+      <c r="C138" s="54"/>
+      <c r="D138" s="54"/>
+      <c r="E138" s="54"/>
+      <c r="F138" s="54"/>
+      <c r="G138" s="54"/>
+      <c r="H138" s="54"/>
+      <c r="I138" s="54"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="41"/>
       <c r="B139" s="41"/>
-      <c r="C139" s="55"/>
-      <c r="D139" s="55"/>
-      <c r="E139" s="55"/>
-      <c r="F139" s="55"/>
-      <c r="G139" s="55"/>
-      <c r="H139" s="55"/>
-      <c r="I139" s="55"/>
+      <c r="C139" s="54"/>
+      <c r="D139" s="54"/>
+      <c r="E139" s="54"/>
+      <c r="F139" s="54"/>
+      <c r="G139" s="54"/>
+      <c r="H139" s="54"/>
+      <c r="I139" s="54"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="41"/>
       <c r="B140" s="41"/>
-      <c r="C140" s="55"/>
-      <c r="D140" s="55"/>
-      <c r="E140" s="55"/>
-      <c r="F140" s="55"/>
-      <c r="G140" s="55"/>
-      <c r="H140" s="55"/>
-      <c r="I140" s="55"/>
+      <c r="C140" s="54"/>
+      <c r="D140" s="54"/>
+      <c r="E140" s="54"/>
+      <c r="F140" s="54"/>
+      <c r="G140" s="54"/>
+      <c r="H140" s="54"/>
+      <c r="I140" s="54"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="41"/>
       <c r="B141" s="41"/>
-      <c r="C141" s="55"/>
-      <c r="D141" s="55"/>
-      <c r="E141" s="55"/>
-      <c r="F141" s="55"/>
-      <c r="G141" s="55"/>
-      <c r="H141" s="55"/>
-      <c r="I141" s="55"/>
+      <c r="C141" s="54"/>
+      <c r="D141" s="54"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="54"/>
+      <c r="G141" s="54"/>
+      <c r="H141" s="54"/>
+      <c r="I141" s="54"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="41"/>
       <c r="B142" s="41"/>
-      <c r="C142" s="55"/>
-      <c r="D142" s="55"/>
-      <c r="E142" s="55"/>
-      <c r="F142" s="55"/>
-      <c r="G142" s="55"/>
-      <c r="H142" s="55"/>
-      <c r="I142" s="55"/>
+      <c r="C142" s="54"/>
+      <c r="D142" s="54"/>
+      <c r="E142" s="54"/>
+      <c r="F142" s="54"/>
+      <c r="G142" s="54"/>
+      <c r="H142" s="54"/>
+      <c r="I142" s="54"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="41"/>
       <c r="B143" s="41"/>
-      <c r="C143" s="55"/>
-      <c r="D143" s="55"/>
-      <c r="E143" s="55"/>
-      <c r="F143" s="55"/>
-      <c r="G143" s="55"/>
-      <c r="H143" s="55"/>
-      <c r="I143" s="55"/>
+      <c r="C143" s="54"/>
+      <c r="D143" s="54"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="54"/>
+      <c r="G143" s="54"/>
+      <c r="H143" s="54"/>
+      <c r="I143" s="54"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="41"/>
       <c r="B144" s="41"/>
-      <c r="C144" s="55"/>
-      <c r="D144" s="55"/>
-      <c r="E144" s="55"/>
-      <c r="F144" s="55"/>
-      <c r="G144" s="55"/>
-      <c r="H144" s="55"/>
-      <c r="I144" s="55"/>
+      <c r="C144" s="54"/>
+      <c r="D144" s="54"/>
+      <c r="E144" s="54"/>
+      <c r="F144" s="54"/>
+      <c r="G144" s="54"/>
+      <c r="H144" s="54"/>
+      <c r="I144" s="54"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="41"/>
       <c r="B145" s="41"/>
-      <c r="C145" s="55"/>
-      <c r="D145" s="55"/>
-      <c r="E145" s="55"/>
-      <c r="F145" s="55"/>
-      <c r="G145" s="55"/>
-      <c r="H145" s="55"/>
-      <c r="I145" s="55"/>
+      <c r="C145" s="54"/>
+      <c r="D145" s="54"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="54"/>
+      <c r="G145" s="54"/>
+      <c r="H145" s="54"/>
+      <c r="I145" s="54"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="41"/>
       <c r="B146" s="41"/>
-      <c r="C146" s="55"/>
-      <c r="D146" s="55"/>
-      <c r="E146" s="55"/>
-      <c r="F146" s="55"/>
-      <c r="G146" s="55"/>
-      <c r="H146" s="55"/>
-      <c r="I146" s="55"/>
+      <c r="C146" s="54"/>
+      <c r="D146" s="54"/>
+      <c r="E146" s="54"/>
+      <c r="F146" s="54"/>
+      <c r="G146" s="54"/>
+      <c r="H146" s="54"/>
+      <c r="I146" s="54"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="41"/>
       <c r="B147" s="41"/>
-      <c r="C147" s="55"/>
-      <c r="D147" s="55"/>
-      <c r="E147" s="55"/>
-      <c r="F147" s="55"/>
-      <c r="G147" s="55"/>
-      <c r="H147" s="55"/>
-      <c r="I147" s="55"/>
+      <c r="C147" s="54"/>
+      <c r="D147" s="54"/>
+      <c r="E147" s="54"/>
+      <c r="F147" s="54"/>
+      <c r="G147" s="54"/>
+      <c r="H147" s="54"/>
+      <c r="I147" s="54"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="41"/>
       <c r="B148" s="41"/>
-      <c r="C148" s="55"/>
-      <c r="D148" s="55"/>
-      <c r="E148" s="55"/>
-      <c r="F148" s="55"/>
-      <c r="G148" s="55"/>
-      <c r="H148" s="55"/>
-      <c r="I148" s="55"/>
+      <c r="C148" s="54"/>
+      <c r="D148" s="54"/>
+      <c r="E148" s="54"/>
+      <c r="F148" s="54"/>
+      <c r="G148" s="54"/>
+      <c r="H148" s="54"/>
+      <c r="I148" s="54"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="41"/>
       <c r="B149" s="41"/>
-      <c r="C149" s="55"/>
-      <c r="D149" s="55"/>
-      <c r="E149" s="55"/>
-      <c r="F149" s="55"/>
-      <c r="G149" s="55"/>
-      <c r="H149" s="55"/>
-      <c r="I149" s="55"/>
+      <c r="C149" s="54"/>
+      <c r="D149" s="54"/>
+      <c r="E149" s="54"/>
+      <c r="F149" s="54"/>
+      <c r="G149" s="54"/>
+      <c r="H149" s="54"/>
+      <c r="I149" s="54"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="41"/>
       <c r="B150" s="41"/>
-      <c r="C150" s="55"/>
-      <c r="D150" s="55"/>
-      <c r="E150" s="55"/>
-      <c r="F150" s="55"/>
-      <c r="G150" s="55"/>
-      <c r="H150" s="55"/>
-      <c r="I150" s="55"/>
+      <c r="C150" s="54"/>
+      <c r="D150" s="54"/>
+      <c r="E150" s="54"/>
+      <c r="F150" s="54"/>
+      <c r="G150" s="54"/>
+      <c r="H150" s="54"/>
+      <c r="I150" s="54"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
-      <c r="C151" s="55"/>
-      <c r="D151" s="55"/>
-      <c r="E151" s="55"/>
-      <c r="F151" s="55"/>
-      <c r="G151" s="55"/>
-      <c r="H151" s="55"/>
-      <c r="I151" s="55"/>
+      <c r="C151" s="54"/>
+      <c r="D151" s="54"/>
+      <c r="E151" s="54"/>
+      <c r="F151" s="54"/>
+      <c r="G151" s="54"/>
+      <c r="H151" s="54"/>
+      <c r="I151" s="54"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="41"/>
       <c r="B152" s="41"/>
-      <c r="C152" s="55"/>
-      <c r="D152" s="55"/>
-      <c r="E152" s="55"/>
-      <c r="F152" s="55"/>
-      <c r="G152" s="55"/>
-      <c r="H152" s="55"/>
-      <c r="I152" s="55"/>
+      <c r="C152" s="54"/>
+      <c r="D152" s="54"/>
+      <c r="E152" s="54"/>
+      <c r="F152" s="54"/>
+      <c r="G152" s="54"/>
+      <c r="H152" s="54"/>
+      <c r="I152" s="54"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="41"/>
       <c r="B153" s="41"/>
-      <c r="C153" s="55"/>
-      <c r="D153" s="55"/>
-      <c r="E153" s="55"/>
-      <c r="F153" s="55"/>
-      <c r="G153" s="55"/>
-      <c r="H153" s="55"/>
-      <c r="I153" s="55"/>
+      <c r="C153" s="54"/>
+      <c r="D153" s="54"/>
+      <c r="E153" s="54"/>
+      <c r="F153" s="54"/>
+      <c r="G153" s="54"/>
+      <c r="H153" s="54"/>
+      <c r="I153" s="54"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="41"/>
       <c r="B154" s="41"/>
-      <c r="C154" s="55"/>
-      <c r="D154" s="55"/>
-      <c r="E154" s="55"/>
-      <c r="F154" s="55"/>
-      <c r="G154" s="55"/>
-      <c r="H154" s="55"/>
-      <c r="I154" s="55"/>
+      <c r="C154" s="54"/>
+      <c r="D154" s="54"/>
+      <c r="E154" s="54"/>
+      <c r="F154" s="54"/>
+      <c r="G154" s="54"/>
+      <c r="H154" s="54"/>
+      <c r="I154" s="54"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="41"/>
       <c r="B155" s="41"/>
-      <c r="C155" s="55"/>
-      <c r="D155" s="55"/>
-      <c r="E155" s="55"/>
-      <c r="F155" s="55"/>
-      <c r="G155" s="55"/>
-      <c r="H155" s="55"/>
-      <c r="I155" s="55"/>
+      <c r="C155" s="54"/>
+      <c r="D155" s="54"/>
+      <c r="E155" s="54"/>
+      <c r="F155" s="54"/>
+      <c r="G155" s="54"/>
+      <c r="H155" s="54"/>
+      <c r="I155" s="54"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="41"/>
       <c r="B156" s="41"/>
-      <c r="C156" s="55"/>
-      <c r="D156" s="55"/>
-      <c r="E156" s="55"/>
-      <c r="F156" s="55"/>
-      <c r="G156" s="55"/>
-      <c r="H156" s="55"/>
-      <c r="I156" s="55"/>
+      <c r="C156" s="54"/>
+      <c r="D156" s="54"/>
+      <c r="E156" s="54"/>
+      <c r="F156" s="54"/>
+      <c r="G156" s="54"/>
+      <c r="H156" s="54"/>
+      <c r="I156" s="54"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="41"/>
       <c r="B157" s="41"/>
-      <c r="C157" s="55"/>
-      <c r="D157" s="55"/>
-      <c r="E157" s="55"/>
-      <c r="F157" s="55"/>
-      <c r="G157" s="55"/>
-      <c r="H157" s="55"/>
-      <c r="I157" s="55"/>
+      <c r="C157" s="54"/>
+      <c r="D157" s="54"/>
+      <c r="E157" s="54"/>
+      <c r="F157" s="54"/>
+      <c r="G157" s="54"/>
+      <c r="H157" s="54"/>
+      <c r="I157" s="54"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="41"/>
       <c r="B158" s="41"/>
-      <c r="C158" s="55"/>
-      <c r="D158" s="55"/>
-      <c r="E158" s="55"/>
-      <c r="F158" s="55"/>
-      <c r="G158" s="55"/>
-      <c r="H158" s="55"/>
-      <c r="I158" s="55"/>
+      <c r="C158" s="54"/>
+      <c r="D158" s="54"/>
+      <c r="E158" s="54"/>
+      <c r="F158" s="54"/>
+      <c r="G158" s="54"/>
+      <c r="H158" s="54"/>
+      <c r="I158" s="54"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="41"/>
       <c r="B159" s="41"/>
-      <c r="C159" s="55"/>
-      <c r="D159" s="55"/>
-      <c r="E159" s="55"/>
-      <c r="F159" s="55"/>
-      <c r="G159" s="55"/>
-      <c r="H159" s="55"/>
-      <c r="I159" s="55"/>
+      <c r="C159" s="54"/>
+      <c r="D159" s="54"/>
+      <c r="E159" s="54"/>
+      <c r="F159" s="54"/>
+      <c r="G159" s="54"/>
+      <c r="H159" s="54"/>
+      <c r="I159" s="54"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="41"/>
       <c r="B160" s="41"/>
-      <c r="C160" s="55"/>
-      <c r="D160" s="55"/>
-      <c r="E160" s="55"/>
-      <c r="F160" s="55"/>
-      <c r="G160" s="55"/>
-      <c r="H160" s="55"/>
-      <c r="I160" s="55"/>
+      <c r="C160" s="54"/>
+      <c r="D160" s="54"/>
+      <c r="E160" s="54"/>
+      <c r="F160" s="54"/>
+      <c r="G160" s="54"/>
+      <c r="H160" s="54"/>
+      <c r="I160" s="54"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="41"/>
       <c r="B161" s="41"/>
-      <c r="C161" s="55"/>
-      <c r="D161" s="55"/>
-      <c r="E161" s="55"/>
-      <c r="F161" s="55"/>
-      <c r="G161" s="55"/>
-      <c r="H161" s="55"/>
-      <c r="I161" s="55"/>
+      <c r="C161" s="54"/>
+      <c r="D161" s="54"/>
+      <c r="E161" s="54"/>
+      <c r="F161" s="54"/>
+      <c r="G161" s="54"/>
+      <c r="H161" s="54"/>
+      <c r="I161" s="54"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="41"/>
       <c r="B162" s="41"/>
-      <c r="C162" s="55"/>
-      <c r="D162" s="55"/>
-      <c r="E162" s="55"/>
-      <c r="F162" s="55"/>
-      <c r="G162" s="55"/>
-      <c r="H162" s="55"/>
-      <c r="I162" s="55"/>
+      <c r="C162" s="54"/>
+      <c r="D162" s="54"/>
+      <c r="E162" s="54"/>
+      <c r="F162" s="54"/>
+      <c r="G162" s="54"/>
+      <c r="H162" s="54"/>
+      <c r="I162" s="54"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="41"/>
       <c r="B163" s="41"/>
-      <c r="C163" s="55"/>
-      <c r="D163" s="55"/>
-      <c r="E163" s="55"/>
-      <c r="F163" s="55"/>
-      <c r="G163" s="55"/>
-      <c r="H163" s="55"/>
-      <c r="I163" s="55"/>
+      <c r="C163" s="54"/>
+      <c r="D163" s="54"/>
+      <c r="E163" s="54"/>
+      <c r="F163" s="54"/>
+      <c r="G163" s="54"/>
+      <c r="H163" s="54"/>
+      <c r="I163" s="54"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="41"/>
       <c r="B164" s="41"/>
-      <c r="C164" s="55"/>
-      <c r="D164" s="55"/>
-      <c r="E164" s="55"/>
-      <c r="F164" s="55"/>
-      <c r="G164" s="55"/>
-      <c r="H164" s="55"/>
-      <c r="I164" s="55"/>
+      <c r="C164" s="54"/>
+      <c r="D164" s="54"/>
+      <c r="E164" s="54"/>
+      <c r="F164" s="54"/>
+      <c r="G164" s="54"/>
+      <c r="H164" s="54"/>
+      <c r="I164" s="54"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="41"/>
       <c r="B165" s="41"/>
-      <c r="C165" s="55"/>
-      <c r="D165" s="55"/>
-      <c r="E165" s="55"/>
-      <c r="F165" s="55"/>
-      <c r="G165" s="55"/>
-      <c r="H165" s="55"/>
-      <c r="I165" s="55"/>
+      <c r="C165" s="54"/>
+      <c r="D165" s="54"/>
+      <c r="E165" s="54"/>
+      <c r="F165" s="54"/>
+      <c r="G165" s="54"/>
+      <c r="H165" s="54"/>
+      <c r="I165" s="54"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="41"/>
       <c r="B166" s="41"/>
-      <c r="C166" s="55"/>
-      <c r="D166" s="55"/>
-      <c r="E166" s="55"/>
-      <c r="F166" s="55"/>
-      <c r="G166" s="55"/>
-      <c r="H166" s="55"/>
-      <c r="I166" s="55"/>
+      <c r="C166" s="54"/>
+      <c r="D166" s="54"/>
+      <c r="E166" s="54"/>
+      <c r="F166" s="54"/>
+      <c r="G166" s="54"/>
+      <c r="H166" s="54"/>
+      <c r="I166" s="54"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="41"/>
       <c r="B167" s="41"/>
-      <c r="C167" s="55"/>
-      <c r="D167" s="55"/>
-      <c r="E167" s="55"/>
-      <c r="F167" s="55"/>
-      <c r="G167" s="55"/>
-      <c r="H167" s="55"/>
-      <c r="I167" s="55"/>
+      <c r="C167" s="54"/>
+      <c r="D167" s="54"/>
+      <c r="E167" s="54"/>
+      <c r="F167" s="54"/>
+      <c r="G167" s="54"/>
+      <c r="H167" s="54"/>
+      <c r="I167" s="54"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="41"/>
       <c r="B168" s="41"/>
-      <c r="C168" s="55"/>
-      <c r="D168" s="55"/>
-      <c r="E168" s="55"/>
-      <c r="F168" s="55"/>
-      <c r="G168" s="55"/>
-      <c r="H168" s="55"/>
-      <c r="I168" s="55"/>
+      <c r="C168" s="54"/>
+      <c r="D168" s="54"/>
+      <c r="E168" s="54"/>
+      <c r="F168" s="54"/>
+      <c r="G168" s="54"/>
+      <c r="H168" s="54"/>
+      <c r="I168" s="54"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="41"/>
       <c r="B169" s="41"/>
-      <c r="C169" s="55"/>
-      <c r="D169" s="55"/>
-      <c r="E169" s="55"/>
-      <c r="F169" s="55"/>
-      <c r="G169" s="55"/>
-      <c r="H169" s="55"/>
-      <c r="I169" s="55"/>
+      <c r="C169" s="54"/>
+      <c r="D169" s="54"/>
+      <c r="E169" s="54"/>
+      <c r="F169" s="54"/>
+      <c r="G169" s="54"/>
+      <c r="H169" s="54"/>
+      <c r="I169" s="54"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="41"/>
       <c r="B170" s="41"/>
-      <c r="C170" s="55"/>
-      <c r="D170" s="55"/>
-      <c r="E170" s="55"/>
-      <c r="F170" s="55"/>
-      <c r="G170" s="55"/>
-      <c r="H170" s="55"/>
-      <c r="I170" s="55"/>
+      <c r="C170" s="54"/>
+      <c r="D170" s="54"/>
+      <c r="E170" s="54"/>
+      <c r="F170" s="54"/>
+      <c r="G170" s="54"/>
+      <c r="H170" s="54"/>
+      <c r="I170" s="54"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="41"/>
       <c r="B171" s="41"/>
-      <c r="C171" s="55"/>
-      <c r="D171" s="55"/>
-      <c r="E171" s="55"/>
-      <c r="F171" s="55"/>
-      <c r="G171" s="55"/>
-      <c r="H171" s="55"/>
-      <c r="I171" s="55"/>
+      <c r="C171" s="54"/>
+      <c r="D171" s="54"/>
+      <c r="E171" s="54"/>
+      <c r="F171" s="54"/>
+      <c r="G171" s="54"/>
+      <c r="H171" s="54"/>
+      <c r="I171" s="54"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="41"/>
       <c r="B172" s="41"/>
-      <c r="C172" s="55"/>
-      <c r="D172" s="55"/>
-      <c r="E172" s="55"/>
-      <c r="F172" s="55"/>
-      <c r="G172" s="55"/>
-      <c r="H172" s="55"/>
-      <c r="I172" s="55"/>
+      <c r="C172" s="54"/>
+      <c r="D172" s="54"/>
+      <c r="E172" s="54"/>
+      <c r="F172" s="54"/>
+      <c r="G172" s="54"/>
+      <c r="H172" s="54"/>
+      <c r="I172" s="54"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="41"/>
       <c r="B173" s="41"/>
-      <c r="C173" s="55"/>
-      <c r="D173" s="55"/>
-      <c r="E173" s="55"/>
-      <c r="F173" s="55"/>
-      <c r="G173" s="55"/>
-      <c r="H173" s="55"/>
-      <c r="I173" s="55"/>
+      <c r="C173" s="54"/>
+      <c r="D173" s="54"/>
+      <c r="E173" s="54"/>
+      <c r="F173" s="54"/>
+      <c r="G173" s="54"/>
+      <c r="H173" s="54"/>
+      <c r="I173" s="54"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="41"/>
       <c r="B174" s="41"/>
-      <c r="C174" s="55"/>
-      <c r="D174" s="55"/>
-      <c r="E174" s="55"/>
-      <c r="F174" s="55"/>
-      <c r="G174" s="55"/>
-      <c r="H174" s="55"/>
-      <c r="I174" s="55"/>
+      <c r="C174" s="54"/>
+      <c r="D174" s="54"/>
+      <c r="E174" s="54"/>
+      <c r="F174" s="54"/>
+      <c r="G174" s="54"/>
+      <c r="H174" s="54"/>
+      <c r="I174" s="54"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
-      <c r="C175" s="55"/>
-      <c r="D175" s="55"/>
-      <c r="E175" s="55"/>
-      <c r="F175" s="55"/>
-      <c r="G175" s="55"/>
-      <c r="H175" s="55"/>
-      <c r="I175" s="55"/>
+      <c r="C175" s="54"/>
+      <c r="D175" s="54"/>
+      <c r="E175" s="54"/>
+      <c r="F175" s="54"/>
+      <c r="G175" s="54"/>
+      <c r="H175" s="54"/>
+      <c r="I175" s="54"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="41"/>
       <c r="B176" s="41"/>
-      <c r="C176" s="55"/>
-      <c r="D176" s="55"/>
-      <c r="E176" s="55"/>
-      <c r="F176" s="55"/>
-      <c r="G176" s="55"/>
-      <c r="H176" s="55"/>
-      <c r="I176" s="55"/>
+      <c r="C176" s="54"/>
+      <c r="D176" s="54"/>
+      <c r="E176" s="54"/>
+      <c r="F176" s="54"/>
+      <c r="G176" s="54"/>
+      <c r="H176" s="54"/>
+      <c r="I176" s="54"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="41"/>
       <c r="B177" s="41"/>
-      <c r="C177" s="55"/>
-      <c r="D177" s="55"/>
-      <c r="E177" s="55"/>
-      <c r="F177" s="55"/>
-      <c r="G177" s="55"/>
-      <c r="H177" s="55"/>
-      <c r="I177" s="55"/>
+      <c r="C177" s="54"/>
+      <c r="D177" s="54"/>
+      <c r="E177" s="54"/>
+      <c r="F177" s="54"/>
+      <c r="G177" s="54"/>
+      <c r="H177" s="54"/>
+      <c r="I177" s="54"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="41"/>
       <c r="B178" s="41"/>
-      <c r="C178" s="55"/>
-      <c r="D178" s="55"/>
-      <c r="E178" s="55"/>
-      <c r="F178" s="55"/>
-      <c r="G178" s="55"/>
-      <c r="H178" s="55"/>
-      <c r="I178" s="55"/>
+      <c r="C178" s="54"/>
+      <c r="D178" s="54"/>
+      <c r="E178" s="54"/>
+      <c r="F178" s="54"/>
+      <c r="G178" s="54"/>
+      <c r="H178" s="54"/>
+      <c r="I178" s="54"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="41"/>
       <c r="B179" s="41"/>
-      <c r="C179" s="55"/>
-      <c r="D179" s="55"/>
-      <c r="E179" s="55"/>
-      <c r="F179" s="55"/>
-      <c r="G179" s="55"/>
-      <c r="H179" s="55"/>
-      <c r="I179" s="55"/>
+      <c r="C179" s="54"/>
+      <c r="D179" s="54"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="54"/>
+      <c r="H179" s="54"/>
+      <c r="I179" s="54"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="41"/>
       <c r="B180" s="41"/>
-      <c r="C180" s="55"/>
-      <c r="D180" s="55"/>
-      <c r="E180" s="55"/>
-      <c r="F180" s="55"/>
-      <c r="G180" s="55"/>
-      <c r="H180" s="55"/>
-      <c r="I180" s="55"/>
+      <c r="C180" s="54"/>
+      <c r="D180" s="54"/>
+      <c r="E180" s="54"/>
+      <c r="F180" s="54"/>
+      <c r="G180" s="54"/>
+      <c r="H180" s="54"/>
+      <c r="I180" s="54"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="41"/>
       <c r="B181" s="41"/>
-      <c r="C181" s="55"/>
-      <c r="D181" s="55"/>
-      <c r="E181" s="55"/>
-      <c r="F181" s="55"/>
-      <c r="G181" s="55"/>
-      <c r="H181" s="55"/>
-      <c r="I181" s="55"/>
+      <c r="C181" s="54"/>
+      <c r="D181" s="54"/>
+      <c r="E181" s="54"/>
+      <c r="F181" s="54"/>
+      <c r="G181" s="54"/>
+      <c r="H181" s="54"/>
+      <c r="I181" s="54"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="41"/>
       <c r="B182" s="41"/>
-      <c r="C182" s="55"/>
-      <c r="D182" s="55"/>
-      <c r="E182" s="55"/>
-      <c r="F182" s="55"/>
-      <c r="G182" s="55"/>
-      <c r="H182" s="55"/>
-      <c r="I182" s="55"/>
+      <c r="C182" s="54"/>
+      <c r="D182" s="54"/>
+      <c r="E182" s="54"/>
+      <c r="F182" s="54"/>
+      <c r="G182" s="54"/>
+      <c r="H182" s="54"/>
+      <c r="I182" s="54"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="41"/>
       <c r="B183" s="41"/>
-      <c r="C183" s="55"/>
-      <c r="D183" s="55"/>
-      <c r="E183" s="55"/>
-      <c r="F183" s="55"/>
-      <c r="G183" s="55"/>
-      <c r="H183" s="55"/>
-      <c r="I183" s="55"/>
+      <c r="C183" s="54"/>
+      <c r="D183" s="54"/>
+      <c r="E183" s="54"/>
+      <c r="F183" s="54"/>
+      <c r="G183" s="54"/>
+      <c r="H183" s="54"/>
+      <c r="I183" s="54"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="41"/>
       <c r="B184" s="41"/>
-      <c r="C184" s="55"/>
-      <c r="D184" s="55"/>
-      <c r="E184" s="55"/>
-      <c r="F184" s="55"/>
-      <c r="G184" s="55"/>
-      <c r="H184" s="55"/>
-      <c r="I184" s="55"/>
+      <c r="C184" s="54"/>
+      <c r="D184" s="54"/>
+      <c r="E184" s="54"/>
+      <c r="F184" s="54"/>
+      <c r="G184" s="54"/>
+      <c r="H184" s="54"/>
+      <c r="I184" s="54"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="41"/>
       <c r="B185" s="41"/>
-      <c r="C185" s="55"/>
-      <c r="D185" s="55"/>
-      <c r="E185" s="55"/>
-      <c r="F185" s="55"/>
-      <c r="G185" s="55"/>
-      <c r="H185" s="55"/>
-      <c r="I185" s="55"/>
+      <c r="C185" s="54"/>
+      <c r="D185" s="54"/>
+      <c r="E185" s="54"/>
+      <c r="F185" s="54"/>
+      <c r="G185" s="54"/>
+      <c r="H185" s="54"/>
+      <c r="I185" s="54"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="41"/>
       <c r="B186" s="41"/>
-      <c r="C186" s="55"/>
-      <c r="D186" s="55"/>
-      <c r="E186" s="55"/>
-      <c r="F186" s="55"/>
-      <c r="G186" s="55"/>
-      <c r="H186" s="55"/>
-      <c r="I186" s="55"/>
+      <c r="C186" s="54"/>
+      <c r="D186" s="54"/>
+      <c r="E186" s="54"/>
+      <c r="F186" s="54"/>
+      <c r="G186" s="54"/>
+      <c r="H186" s="54"/>
+      <c r="I186" s="54"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="41"/>
       <c r="B187" s="41"/>
-      <c r="C187" s="55"/>
-      <c r="D187" s="55"/>
-      <c r="E187" s="55"/>
-      <c r="F187" s="55"/>
-      <c r="G187" s="55"/>
-      <c r="H187" s="55"/>
-      <c r="I187" s="55"/>
+      <c r="C187" s="54"/>
+      <c r="D187" s="54"/>
+      <c r="E187" s="54"/>
+      <c r="F187" s="54"/>
+      <c r="G187" s="54"/>
+      <c r="H187" s="54"/>
+      <c r="I187" s="54"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="41"/>
       <c r="B188" s="41"/>
-      <c r="C188" s="55"/>
-      <c r="D188" s="55"/>
-      <c r="E188" s="55"/>
-      <c r="F188" s="55"/>
-      <c r="G188" s="55"/>
-      <c r="H188" s="55"/>
-      <c r="I188" s="55"/>
+      <c r="C188" s="54"/>
+      <c r="D188" s="54"/>
+      <c r="E188" s="54"/>
+      <c r="F188" s="54"/>
+      <c r="G188" s="54"/>
+      <c r="H188" s="54"/>
+      <c r="I188" s="54"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="41"/>
       <c r="B189" s="41"/>
-      <c r="C189" s="55"/>
-      <c r="D189" s="55"/>
-      <c r="E189" s="55"/>
-      <c r="F189" s="55"/>
-      <c r="G189" s="55"/>
-      <c r="H189" s="55"/>
-      <c r="I189" s="55"/>
+      <c r="C189" s="54"/>
+      <c r="D189" s="54"/>
+      <c r="E189" s="54"/>
+      <c r="F189" s="54"/>
+      <c r="G189" s="54"/>
+      <c r="H189" s="54"/>
+      <c r="I189" s="54"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="41"/>
       <c r="B190" s="41"/>
-      <c r="C190" s="55"/>
-      <c r="D190" s="55"/>
-      <c r="E190" s="55"/>
-      <c r="F190" s="55"/>
-      <c r="G190" s="55"/>
-      <c r="H190" s="55"/>
-      <c r="I190" s="55"/>
+      <c r="C190" s="54"/>
+      <c r="D190" s="54"/>
+      <c r="E190" s="54"/>
+      <c r="F190" s="54"/>
+      <c r="G190" s="54"/>
+      <c r="H190" s="54"/>
+      <c r="I190" s="54"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="41"/>
       <c r="B191" s="41"/>
-      <c r="C191" s="55"/>
-      <c r="D191" s="55"/>
-      <c r="E191" s="55"/>
-      <c r="F191" s="55"/>
-      <c r="G191" s="55"/>
-      <c r="H191" s="55"/>
-      <c r="I191" s="55"/>
+      <c r="C191" s="54"/>
+      <c r="D191" s="54"/>
+      <c r="E191" s="54"/>
+      <c r="F191" s="54"/>
+      <c r="G191" s="54"/>
+      <c r="H191" s="54"/>
+      <c r="I191" s="54"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="41"/>
       <c r="B192" s="41"/>
-      <c r="C192" s="55"/>
-      <c r="D192" s="55"/>
-      <c r="E192" s="55"/>
-      <c r="F192" s="55"/>
-      <c r="G192" s="55"/>
-      <c r="H192" s="55"/>
-      <c r="I192" s="55"/>
+      <c r="C192" s="54"/>
+      <c r="D192" s="54"/>
+      <c r="E192" s="54"/>
+      <c r="F192" s="54"/>
+      <c r="G192" s="54"/>
+      <c r="H192" s="54"/>
+      <c r="I192" s="54"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="41"/>
       <c r="B193" s="41"/>
-      <c r="C193" s="55"/>
-      <c r="D193" s="55"/>
-      <c r="E193" s="55"/>
-      <c r="F193" s="55"/>
-      <c r="G193" s="55"/>
-      <c r="H193" s="55"/>
-      <c r="I193" s="55"/>
+      <c r="C193" s="54"/>
+      <c r="D193" s="54"/>
+      <c r="E193" s="54"/>
+      <c r="F193" s="54"/>
+      <c r="G193" s="54"/>
+      <c r="H193" s="54"/>
+      <c r="I193" s="54"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="41"/>
       <c r="B194" s="41"/>
-      <c r="C194" s="55"/>
-      <c r="D194" s="55"/>
-      <c r="E194" s="55"/>
-      <c r="F194" s="55"/>
-      <c r="G194" s="55"/>
-      <c r="H194" s="55"/>
-      <c r="I194" s="55"/>
+      <c r="C194" s="54"/>
+      <c r="D194" s="54"/>
+      <c r="E194" s="54"/>
+      <c r="F194" s="54"/>
+      <c r="G194" s="54"/>
+      <c r="H194" s="54"/>
+      <c r="I194" s="54"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="41"/>
       <c r="B195" s="41"/>
-      <c r="C195" s="55"/>
-      <c r="D195" s="55"/>
-      <c r="E195" s="55"/>
-      <c r="F195" s="55"/>
-      <c r="G195" s="55"/>
-      <c r="H195" s="55"/>
-      <c r="I195" s="55"/>
+      <c r="C195" s="54"/>
+      <c r="D195" s="54"/>
+      <c r="E195" s="54"/>
+      <c r="F195" s="54"/>
+      <c r="G195" s="54"/>
+      <c r="H195" s="54"/>
+      <c r="I195" s="54"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="41"/>
       <c r="B196" s="41"/>
-      <c r="C196" s="55"/>
-      <c r="D196" s="55"/>
-      <c r="E196" s="55"/>
-      <c r="F196" s="55"/>
-      <c r="G196" s="55"/>
-      <c r="H196" s="55"/>
-      <c r="I196" s="55"/>
+      <c r="C196" s="54"/>
+      <c r="D196" s="54"/>
+      <c r="E196" s="54"/>
+      <c r="F196" s="54"/>
+      <c r="G196" s="54"/>
+      <c r="H196" s="54"/>
+      <c r="I196" s="54"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="41"/>
       <c r="B197" s="41"/>
-      <c r="C197" s="55"/>
-      <c r="D197" s="55"/>
-      <c r="E197" s="55"/>
-      <c r="F197" s="55"/>
-      <c r="G197" s="55"/>
-      <c r="H197" s="55"/>
-      <c r="I197" s="55"/>
+      <c r="C197" s="54"/>
+      <c r="D197" s="54"/>
+      <c r="E197" s="54"/>
+      <c r="F197" s="54"/>
+      <c r="G197" s="54"/>
+      <c r="H197" s="54"/>
+      <c r="I197" s="54"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="41"/>
       <c r="B198" s="41"/>
-      <c r="C198" s="55"/>
-      <c r="D198" s="55"/>
-      <c r="E198" s="55"/>
-      <c r="F198" s="55"/>
-      <c r="G198" s="55"/>
-      <c r="H198" s="55"/>
-      <c r="I198" s="55"/>
+      <c r="C198" s="54"/>
+      <c r="D198" s="54"/>
+      <c r="E198" s="54"/>
+      <c r="F198" s="54"/>
+      <c r="G198" s="54"/>
+      <c r="H198" s="54"/>
+      <c r="I198" s="54"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="41"/>
       <c r="B199" s="41"/>
-      <c r="C199" s="55"/>
-      <c r="D199" s="55"/>
-      <c r="E199" s="55"/>
-      <c r="F199" s="55"/>
-      <c r="G199" s="55"/>
-      <c r="H199" s="55"/>
-      <c r="I199" s="55"/>
+      <c r="C199" s="54"/>
+      <c r="D199" s="54"/>
+      <c r="E199" s="54"/>
+      <c r="F199" s="54"/>
+      <c r="G199" s="54"/>
+      <c r="H199" s="54"/>
+      <c r="I199" s="54"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="41"/>
       <c r="B200" s="41"/>
-      <c r="C200" s="55"/>
-      <c r="D200" s="55"/>
-      <c r="E200" s="55"/>
-      <c r="F200" s="55"/>
-      <c r="G200" s="55"/>
-      <c r="H200" s="55"/>
-      <c r="I200" s="55"/>
+      <c r="C200" s="54"/>
+      <c r="D200" s="54"/>
+      <c r="E200" s="54"/>
+      <c r="F200" s="54"/>
+      <c r="G200" s="54"/>
+      <c r="H200" s="54"/>
+      <c r="I200" s="54"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="41"/>
       <c r="B201" s="41"/>
-      <c r="C201" s="55"/>
-      <c r="D201" s="55"/>
-      <c r="E201" s="55"/>
-      <c r="F201" s="55"/>
-      <c r="G201" s="55"/>
-      <c r="H201" s="55"/>
-      <c r="I201" s="55"/>
+      <c r="C201" s="54"/>
+      <c r="D201" s="54"/>
+      <c r="E201" s="54"/>
+      <c r="F201" s="54"/>
+      <c r="G201" s="54"/>
+      <c r="H201" s="54"/>
+      <c r="I201" s="54"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="41"/>
       <c r="B202" s="41"/>
-      <c r="C202" s="55"/>
-      <c r="D202" s="55"/>
-      <c r="E202" s="55"/>
-      <c r="F202" s="55"/>
-      <c r="G202" s="55"/>
-      <c r="H202" s="55"/>
-      <c r="I202" s="55"/>
+      <c r="C202" s="54"/>
+      <c r="D202" s="54"/>
+      <c r="E202" s="54"/>
+      <c r="F202" s="54"/>
+      <c r="G202" s="54"/>
+      <c r="H202" s="54"/>
+      <c r="I202" s="54"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="41"/>
       <c r="B203" s="41"/>
-      <c r="C203" s="55"/>
-      <c r="D203" s="55"/>
-      <c r="E203" s="55"/>
-      <c r="F203" s="55"/>
-      <c r="G203" s="55"/>
-      <c r="H203" s="55"/>
-      <c r="I203" s="55"/>
+      <c r="C203" s="54"/>
+      <c r="D203" s="54"/>
+      <c r="E203" s="54"/>
+      <c r="F203" s="54"/>
+      <c r="G203" s="54"/>
+      <c r="H203" s="54"/>
+      <c r="I203" s="54"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="41"/>
       <c r="B204" s="41"/>
-      <c r="C204" s="55"/>
-      <c r="D204" s="55"/>
-      <c r="E204" s="55"/>
-      <c r="F204" s="55"/>
-      <c r="G204" s="55"/>
-      <c r="H204" s="55"/>
-      <c r="I204" s="55"/>
+      <c r="C204" s="54"/>
+      <c r="D204" s="54"/>
+      <c r="E204" s="54"/>
+      <c r="F204" s="54"/>
+      <c r="G204" s="54"/>
+      <c r="H204" s="54"/>
+      <c r="I204" s="54"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="41"/>
       <c r="B205" s="41"/>
-      <c r="C205" s="55"/>
-      <c r="D205" s="55"/>
-      <c r="E205" s="55"/>
-      <c r="F205" s="55"/>
-      <c r="G205" s="55"/>
-      <c r="H205" s="55"/>
-      <c r="I205" s="55"/>
+      <c r="C205" s="54"/>
+      <c r="D205" s="54"/>
+      <c r="E205" s="54"/>
+      <c r="F205" s="54"/>
+      <c r="G205" s="54"/>
+      <c r="H205" s="54"/>
+      <c r="I205" s="54"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="41"/>
       <c r="B206" s="41"/>
-      <c r="C206" s="55"/>
-      <c r="D206" s="55"/>
-      <c r="E206" s="55"/>
-      <c r="F206" s="55"/>
-      <c r="G206" s="55"/>
-      <c r="H206" s="55"/>
-      <c r="I206" s="55"/>
+      <c r="C206" s="54"/>
+      <c r="D206" s="54"/>
+      <c r="E206" s="54"/>
+      <c r="F206" s="54"/>
+      <c r="G206" s="54"/>
+      <c r="H206" s="54"/>
+      <c r="I206" s="54"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="41"/>
       <c r="B207" s="41"/>
-      <c r="C207" s="55"/>
-      <c r="D207" s="55"/>
-      <c r="E207" s="55"/>
-      <c r="F207" s="55"/>
-      <c r="G207" s="55"/>
-      <c r="H207" s="55"/>
-      <c r="I207" s="55"/>
+      <c r="C207" s="54"/>
+      <c r="D207" s="54"/>
+      <c r="E207" s="54"/>
+      <c r="F207" s="54"/>
+      <c r="G207" s="54"/>
+      <c r="H207" s="54"/>
+      <c r="I207" s="54"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="41"/>
       <c r="B208" s="41"/>
-      <c r="C208" s="55"/>
-      <c r="D208" s="55"/>
-      <c r="E208" s="55"/>
-      <c r="F208" s="55"/>
-      <c r="G208" s="55"/>
-      <c r="H208" s="55"/>
-      <c r="I208" s="55"/>
+      <c r="C208" s="54"/>
+      <c r="D208" s="54"/>
+      <c r="E208" s="54"/>
+      <c r="F208" s="54"/>
+      <c r="G208" s="54"/>
+      <c r="H208" s="54"/>
+      <c r="I208" s="54"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="41"/>
       <c r="B209" s="41"/>
-      <c r="C209" s="55"/>
-      <c r="D209" s="55"/>
-      <c r="E209" s="55"/>
-      <c r="F209" s="55"/>
-      <c r="G209" s="55"/>
-      <c r="H209" s="55"/>
-      <c r="I209" s="55"/>
+      <c r="C209" s="54"/>
+      <c r="D209" s="54"/>
+      <c r="E209" s="54"/>
+      <c r="F209" s="54"/>
+      <c r="G209" s="54"/>
+      <c r="H209" s="54"/>
+      <c r="I209" s="54"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="41"/>
       <c r="B210" s="41"/>
-      <c r="C210" s="55"/>
-      <c r="D210" s="55"/>
-      <c r="E210" s="55"/>
-      <c r="F210" s="55"/>
-      <c r="G210" s="55"/>
-      <c r="H210" s="55"/>
-      <c r="I210" s="55"/>
+      <c r="C210" s="54"/>
+      <c r="D210" s="54"/>
+      <c r="E210" s="54"/>
+      <c r="F210" s="54"/>
+      <c r="G210" s="54"/>
+      <c r="H210" s="54"/>
+      <c r="I210" s="54"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="41"/>
       <c r="B211" s="41"/>
-      <c r="C211" s="55"/>
-      <c r="D211" s="55"/>
-      <c r="E211" s="55"/>
-      <c r="F211" s="55"/>
-      <c r="G211" s="55"/>
-      <c r="H211" s="55"/>
-      <c r="I211" s="55"/>
+      <c r="C211" s="54"/>
+      <c r="D211" s="54"/>
+      <c r="E211" s="54"/>
+      <c r="F211" s="54"/>
+      <c r="G211" s="54"/>
+      <c r="H211" s="54"/>
+      <c r="I211" s="54"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="41"/>
       <c r="B212" s="41"/>
-      <c r="C212" s="55"/>
-      <c r="D212" s="55"/>
-      <c r="E212" s="55"/>
-      <c r="F212" s="55"/>
-      <c r="G212" s="55"/>
-      <c r="H212" s="55"/>
-      <c r="I212" s="55"/>
+      <c r="C212" s="54"/>
+      <c r="D212" s="54"/>
+      <c r="E212" s="54"/>
+      <c r="F212" s="54"/>
+      <c r="G212" s="54"/>
+      <c r="H212" s="54"/>
+      <c r="I212" s="54"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="41"/>
       <c r="B213" s="41"/>
-      <c r="C213" s="55"/>
-      <c r="D213" s="55"/>
-      <c r="E213" s="55"/>
-      <c r="F213" s="55"/>
-      <c r="G213" s="55"/>
-      <c r="H213" s="55"/>
-      <c r="I213" s="55"/>
+      <c r="C213" s="54"/>
+      <c r="D213" s="54"/>
+      <c r="E213" s="54"/>
+      <c r="F213" s="54"/>
+      <c r="G213" s="54"/>
+      <c r="H213" s="54"/>
+      <c r="I213" s="54"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="41"/>
       <c r="B214" s="41"/>
-      <c r="C214" s="55"/>
-      <c r="D214" s="55"/>
-      <c r="E214" s="55"/>
-      <c r="F214" s="55"/>
-      <c r="G214" s="55"/>
-      <c r="H214" s="55"/>
-      <c r="I214" s="55"/>
+      <c r="C214" s="54"/>
+      <c r="D214" s="54"/>
+      <c r="E214" s="54"/>
+      <c r="F214" s="54"/>
+      <c r="G214" s="54"/>
+      <c r="H214" s="54"/>
+      <c r="I214" s="54"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="41"/>
       <c r="B215" s="41"/>
-      <c r="C215" s="55"/>
-      <c r="D215" s="55"/>
-      <c r="E215" s="55"/>
-      <c r="F215" s="55"/>
-      <c r="G215" s="55"/>
-      <c r="H215" s="55"/>
-      <c r="I215" s="55"/>
+      <c r="C215" s="54"/>
+      <c r="D215" s="54"/>
+      <c r="E215" s="54"/>
+      <c r="F215" s="54"/>
+      <c r="G215" s="54"/>
+      <c r="H215" s="54"/>
+      <c r="I215" s="54"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="41"/>
       <c r="B216" s="41"/>
-      <c r="C216" s="55"/>
-      <c r="D216" s="55"/>
-      <c r="E216" s="55"/>
-      <c r="F216" s="55"/>
-      <c r="G216" s="55"/>
-      <c r="H216" s="55"/>
-      <c r="I216" s="55"/>
+      <c r="C216" s="54"/>
+      <c r="D216" s="54"/>
+      <c r="E216" s="54"/>
+      <c r="F216" s="54"/>
+      <c r="G216" s="54"/>
+      <c r="H216" s="54"/>
+      <c r="I216" s="54"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="41"/>
       <c r="B217" s="41"/>
-      <c r="C217" s="55"/>
-      <c r="D217" s="55"/>
-      <c r="E217" s="55"/>
-      <c r="F217" s="55"/>
-      <c r="G217" s="55"/>
-      <c r="H217" s="55"/>
-      <c r="I217" s="55"/>
+      <c r="C217" s="54"/>
+      <c r="D217" s="54"/>
+      <c r="E217" s="54"/>
+      <c r="F217" s="54"/>
+      <c r="G217" s="54"/>
+      <c r="H217" s="54"/>
+      <c r="I217" s="54"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="41"/>
       <c r="B218" s="41"/>
-      <c r="C218" s="55"/>
-      <c r="D218" s="55"/>
-      <c r="E218" s="55"/>
-      <c r="F218" s="55"/>
-      <c r="G218" s="55"/>
-      <c r="H218" s="55"/>
-      <c r="I218" s="55"/>
+      <c r="C218" s="54"/>
+      <c r="D218" s="54"/>
+      <c r="E218" s="54"/>
+      <c r="F218" s="54"/>
+      <c r="G218" s="54"/>
+      <c r="H218" s="54"/>
+      <c r="I218" s="54"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="41"/>
       <c r="B219" s="41"/>
-      <c r="C219" s="55"/>
-      <c r="D219" s="55"/>
-      <c r="E219" s="55"/>
-      <c r="F219" s="55"/>
-      <c r="G219" s="55"/>
-      <c r="H219" s="55"/>
-      <c r="I219" s="55"/>
+      <c r="C219" s="54"/>
+      <c r="D219" s="54"/>
+      <c r="E219" s="54"/>
+      <c r="F219" s="54"/>
+      <c r="G219" s="54"/>
+      <c r="H219" s="54"/>
+      <c r="I219" s="54"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="41"/>
       <c r="B220" s="41"/>
-      <c r="C220" s="55"/>
-      <c r="D220" s="55"/>
-      <c r="E220" s="55"/>
-      <c r="F220" s="55"/>
-      <c r="G220" s="55"/>
-      <c r="H220" s="55"/>
-      <c r="I220" s="55"/>
+      <c r="C220" s="54"/>
+      <c r="D220" s="54"/>
+      <c r="E220" s="54"/>
+      <c r="F220" s="54"/>
+      <c r="G220" s="54"/>
+      <c r="H220" s="54"/>
+      <c r="I220" s="54"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="41"/>
       <c r="B221" s="41"/>
-      <c r="C221" s="55"/>
-      <c r="D221" s="55"/>
-      <c r="E221" s="55"/>
-      <c r="F221" s="55"/>
-      <c r="G221" s="55"/>
-      <c r="H221" s="55"/>
-      <c r="I221" s="55"/>
+      <c r="C221" s="54"/>
+      <c r="D221" s="54"/>
+      <c r="E221" s="54"/>
+      <c r="F221" s="54"/>
+      <c r="G221" s="54"/>
+      <c r="H221" s="54"/>
+      <c r="I221" s="54"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="41"/>
       <c r="B222" s="41"/>
-      <c r="C222" s="55"/>
-      <c r="D222" s="55"/>
-      <c r="E222" s="55"/>
-      <c r="F222" s="55"/>
-      <c r="G222" s="55"/>
-      <c r="H222" s="55"/>
-      <c r="I222" s="55"/>
+      <c r="C222" s="54"/>
+      <c r="D222" s="54"/>
+      <c r="E222" s="54"/>
+      <c r="F222" s="54"/>
+      <c r="G222" s="54"/>
+      <c r="H222" s="54"/>
+      <c r="I222" s="54"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="41"/>
       <c r="B223" s="41"/>
-      <c r="C223" s="55"/>
-      <c r="D223" s="55"/>
-      <c r="E223" s="55"/>
-      <c r="F223" s="55"/>
-      <c r="G223" s="55"/>
-      <c r="H223" s="55"/>
-      <c r="I223" s="55"/>
+      <c r="C223" s="54"/>
+      <c r="D223" s="54"/>
+      <c r="E223" s="54"/>
+      <c r="F223" s="54"/>
+      <c r="G223" s="54"/>
+      <c r="H223" s="54"/>
+      <c r="I223" s="54"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="41"/>
       <c r="B224" s="41"/>
-      <c r="C224" s="55"/>
-      <c r="D224" s="55"/>
-      <c r="E224" s="55"/>
-      <c r="F224" s="55"/>
-      <c r="G224" s="55"/>
-      <c r="H224" s="55"/>
-      <c r="I224" s="55"/>
+      <c r="C224" s="54"/>
+      <c r="D224" s="54"/>
+      <c r="E224" s="54"/>
+      <c r="F224" s="54"/>
+      <c r="G224" s="54"/>
+      <c r="H224" s="54"/>
+      <c r="I224" s="54"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="41"/>
       <c r="B225" s="41"/>
-      <c r="C225" s="55"/>
-      <c r="D225" s="55"/>
-      <c r="E225" s="55"/>
-      <c r="F225" s="55"/>
-      <c r="G225" s="55"/>
-      <c r="H225" s="55"/>
-      <c r="I225" s="55"/>
+      <c r="C225" s="54"/>
+      <c r="D225" s="54"/>
+      <c r="E225" s="54"/>
+      <c r="F225" s="54"/>
+      <c r="G225" s="54"/>
+      <c r="H225" s="54"/>
+      <c r="I225" s="54"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="41"/>
       <c r="B226" s="41"/>
-      <c r="C226" s="55"/>
-      <c r="D226" s="55"/>
-      <c r="E226" s="55"/>
-      <c r="F226" s="55"/>
-      <c r="G226" s="55"/>
-      <c r="H226" s="55"/>
-      <c r="I226" s="55"/>
+      <c r="C226" s="54"/>
+      <c r="D226" s="54"/>
+      <c r="E226" s="54"/>
+      <c r="F226" s="54"/>
+      <c r="G226" s="54"/>
+      <c r="H226" s="54"/>
+      <c r="I226" s="54"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="41"/>
       <c r="B227" s="41"/>
-      <c r="C227" s="55"/>
-      <c r="D227" s="55"/>
-      <c r="E227" s="55"/>
-      <c r="F227" s="55"/>
-      <c r="G227" s="55"/>
-      <c r="H227" s="55"/>
-      <c r="I227" s="55"/>
+      <c r="C227" s="54"/>
+      <c r="D227" s="54"/>
+      <c r="E227" s="54"/>
+      <c r="F227" s="54"/>
+      <c r="G227" s="54"/>
+      <c r="H227" s="54"/>
+      <c r="I227" s="54"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="41"/>
       <c r="B228" s="41"/>
-      <c r="C228" s="55"/>
-      <c r="D228" s="55"/>
-      <c r="E228" s="55"/>
-      <c r="F228" s="55"/>
-      <c r="G228" s="55"/>
-      <c r="H228" s="55"/>
-      <c r="I228" s="55"/>
+      <c r="C228" s="54"/>
+      <c r="D228" s="54"/>
+      <c r="E228" s="54"/>
+      <c r="F228" s="54"/>
+      <c r="G228" s="54"/>
+      <c r="H228" s="54"/>
+      <c r="I228" s="54"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="41"/>
       <c r="B229" s="41"/>
-      <c r="C229" s="55"/>
-      <c r="D229" s="55"/>
-      <c r="E229" s="55"/>
-      <c r="F229" s="55"/>
-      <c r="G229" s="55"/>
-      <c r="H229" s="55"/>
-      <c r="I229" s="55"/>
+      <c r="C229" s="54"/>
+      <c r="D229" s="54"/>
+      <c r="E229" s="54"/>
+      <c r="F229" s="54"/>
+      <c r="G229" s="54"/>
+      <c r="H229" s="54"/>
+      <c r="I229" s="54"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="41"/>
       <c r="B230" s="41"/>
-      <c r="C230" s="55"/>
-      <c r="D230" s="55"/>
-      <c r="E230" s="55"/>
-      <c r="F230" s="55"/>
-      <c r="G230" s="55"/>
-      <c r="H230" s="55"/>
-      <c r="I230" s="55"/>
+      <c r="C230" s="54"/>
+      <c r="D230" s="54"/>
+      <c r="E230" s="54"/>
+      <c r="F230" s="54"/>
+      <c r="G230" s="54"/>
+      <c r="H230" s="54"/>
+      <c r="I230" s="54"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="41"/>
       <c r="B231" s="41"/>
-      <c r="C231" s="55"/>
-      <c r="D231" s="55"/>
-      <c r="E231" s="55"/>
-      <c r="F231" s="55"/>
-      <c r="G231" s="55"/>
-      <c r="H231" s="55"/>
-      <c r="I231" s="55"/>
+      <c r="C231" s="54"/>
+      <c r="D231" s="54"/>
+      <c r="E231" s="54"/>
+      <c r="F231" s="54"/>
+      <c r="G231" s="54"/>
+      <c r="H231" s="54"/>
+      <c r="I231" s="54"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="41"/>
       <c r="B232" s="41"/>
-      <c r="C232" s="55"/>
-      <c r="D232" s="55"/>
-      <c r="E232" s="55"/>
-      <c r="F232" s="55"/>
-      <c r="G232" s="55"/>
-      <c r="H232" s="55"/>
-      <c r="I232" s="55"/>
+      <c r="C232" s="54"/>
+      <c r="D232" s="54"/>
+      <c r="E232" s="54"/>
+      <c r="F232" s="54"/>
+      <c r="G232" s="54"/>
+      <c r="H232" s="54"/>
+      <c r="I232" s="54"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="41"/>
       <c r="B233" s="41"/>
-      <c r="C233" s="55"/>
-      <c r="D233" s="55"/>
-      <c r="E233" s="55"/>
-      <c r="F233" s="55"/>
-      <c r="G233" s="55"/>
-      <c r="H233" s="55"/>
-      <c r="I233" s="55"/>
+      <c r="C233" s="54"/>
+      <c r="D233" s="54"/>
+      <c r="E233" s="54"/>
+      <c r="F233" s="54"/>
+      <c r="G233" s="54"/>
+      <c r="H233" s="54"/>
+      <c r="I233" s="54"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="41"/>
       <c r="B234" s="41"/>
-      <c r="C234" s="55"/>
-      <c r="D234" s="55"/>
-      <c r="E234" s="55"/>
-      <c r="F234" s="55"/>
-      <c r="G234" s="55"/>
-      <c r="H234" s="55"/>
-      <c r="I234" s="55"/>
+      <c r="C234" s="54"/>
+      <c r="D234" s="54"/>
+      <c r="E234" s="54"/>
+      <c r="F234" s="54"/>
+      <c r="G234" s="54"/>
+      <c r="H234" s="54"/>
+      <c r="I234" s="54"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="41"/>
       <c r="B235" s="41"/>
-      <c r="C235" s="55"/>
-      <c r="D235" s="55"/>
-      <c r="E235" s="55"/>
-      <c r="F235" s="55"/>
-      <c r="G235" s="55"/>
-      <c r="H235" s="55"/>
-      <c r="I235" s="55"/>
+      <c r="C235" s="54"/>
+      <c r="D235" s="54"/>
+      <c r="E235" s="54"/>
+      <c r="F235" s="54"/>
+      <c r="G235" s="54"/>
+      <c r="H235" s="54"/>
+      <c r="I235" s="54"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="41"/>
       <c r="B236" s="41"/>
-      <c r="C236" s="55"/>
-      <c r="D236" s="55"/>
-      <c r="E236" s="55"/>
-      <c r="F236" s="55"/>
-      <c r="G236" s="55"/>
-      <c r="H236" s="55"/>
-      <c r="I236" s="55"/>
+      <c r="C236" s="54"/>
+      <c r="D236" s="54"/>
+      <c r="E236" s="54"/>
+      <c r="F236" s="54"/>
+      <c r="G236" s="54"/>
+      <c r="H236" s="54"/>
+      <c r="I236" s="54"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="41"/>
       <c r="B237" s="41"/>
-      <c r="C237" s="55"/>
-      <c r="D237" s="55"/>
-      <c r="E237" s="55"/>
-      <c r="F237" s="55"/>
-      <c r="G237" s="55"/>
-      <c r="H237" s="55"/>
-      <c r="I237" s="55"/>
+      <c r="C237" s="54"/>
+      <c r="D237" s="54"/>
+      <c r="E237" s="54"/>
+      <c r="F237" s="54"/>
+      <c r="G237" s="54"/>
+      <c r="H237" s="54"/>
+      <c r="I237" s="54"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="41"/>
       <c r="B238" s="41"/>
-      <c r="C238" s="55"/>
-      <c r="D238" s="55"/>
-      <c r="E238" s="55"/>
-      <c r="F238" s="55"/>
-      <c r="G238" s="55"/>
-      <c r="H238" s="55"/>
-      <c r="I238" s="55"/>
+      <c r="C238" s="54"/>
+      <c r="D238" s="54"/>
+      <c r="E238" s="54"/>
+      <c r="F238" s="54"/>
+      <c r="G238" s="54"/>
+      <c r="H238" s="54"/>
+      <c r="I238" s="54"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="41"/>
       <c r="B239" s="41"/>
-      <c r="C239" s="55"/>
-      <c r="D239" s="55"/>
-      <c r="E239" s="55"/>
-      <c r="F239" s="55"/>
-      <c r="G239" s="55"/>
-      <c r="H239" s="55"/>
-      <c r="I239" s="55"/>
+      <c r="C239" s="54"/>
+      <c r="D239" s="54"/>
+      <c r="E239" s="54"/>
+      <c r="F239" s="54"/>
+      <c r="G239" s="54"/>
+      <c r="H239" s="54"/>
+      <c r="I239" s="54"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="41"/>
       <c r="B240" s="41"/>
-      <c r="C240" s="55"/>
-      <c r="D240" s="55"/>
-      <c r="E240" s="55"/>
-      <c r="F240" s="55"/>
-      <c r="G240" s="55"/>
-      <c r="H240" s="55"/>
-      <c r="I240" s="55"/>
+      <c r="C240" s="54"/>
+      <c r="D240" s="54"/>
+      <c r="E240" s="54"/>
+      <c r="F240" s="54"/>
+      <c r="G240" s="54"/>
+      <c r="H240" s="54"/>
+      <c r="I240" s="54"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="41"/>
       <c r="B241" s="41"/>
-      <c r="C241" s="55"/>
-      <c r="D241" s="55"/>
-      <c r="E241" s="55"/>
-      <c r="F241" s="55"/>
-      <c r="G241" s="55"/>
-      <c r="H241" s="55"/>
-      <c r="I241" s="55"/>
+      <c r="C241" s="54"/>
+      <c r="D241" s="54"/>
+      <c r="E241" s="54"/>
+      <c r="F241" s="54"/>
+      <c r="G241" s="54"/>
+      <c r="H241" s="54"/>
+      <c r="I241" s="54"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="41"/>
       <c r="B242" s="41"/>
-      <c r="C242" s="55"/>
-      <c r="D242" s="55"/>
-      <c r="E242" s="55"/>
-      <c r="F242" s="55"/>
-      <c r="G242" s="55"/>
-      <c r="H242" s="55"/>
-      <c r="I242" s="55"/>
+      <c r="C242" s="54"/>
+      <c r="D242" s="54"/>
+      <c r="E242" s="54"/>
+      <c r="F242" s="54"/>
+      <c r="G242" s="54"/>
+      <c r="H242" s="54"/>
+      <c r="I242" s="54"/>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="41"/>
       <c r="B243" s="41"/>
-      <c r="C243" s="55"/>
-      <c r="D243" s="55"/>
-      <c r="E243" s="55"/>
-      <c r="F243" s="55"/>
-      <c r="G243" s="55"/>
-      <c r="H243" s="55"/>
-      <c r="I243" s="55"/>
+      <c r="C243" s="54"/>
+      <c r="D243" s="54"/>
+      <c r="E243" s="54"/>
+      <c r="F243" s="54"/>
+      <c r="G243" s="54"/>
+      <c r="H243" s="54"/>
+      <c r="I243" s="54"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="41"/>
       <c r="B244" s="41"/>
-      <c r="C244" s="55"/>
-      <c r="D244" s="55"/>
-      <c r="E244" s="55"/>
-      <c r="F244" s="55"/>
-      <c r="G244" s="55"/>
-      <c r="H244" s="55"/>
-      <c r="I244" s="55"/>
+      <c r="C244" s="54"/>
+      <c r="D244" s="54"/>
+      <c r="E244" s="54"/>
+      <c r="F244" s="54"/>
+      <c r="G244" s="54"/>
+      <c r="H244" s="54"/>
+      <c r="I244" s="54"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="41"/>
       <c r="B245" s="41"/>
-      <c r="C245" s="55"/>
-      <c r="D245" s="55"/>
-      <c r="E245" s="55"/>
-      <c r="F245" s="55"/>
-      <c r="G245" s="55"/>
-      <c r="H245" s="55"/>
-      <c r="I245" s="55"/>
+      <c r="C245" s="54"/>
+      <c r="D245" s="54"/>
+      <c r="E245" s="54"/>
+      <c r="F245" s="54"/>
+      <c r="G245" s="54"/>
+      <c r="H245" s="54"/>
+      <c r="I245" s="54"/>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="41"/>
       <c r="B246" s="41"/>
-      <c r="C246" s="55"/>
-      <c r="D246" s="55"/>
-      <c r="E246" s="55"/>
-      <c r="F246" s="55"/>
-      <c r="G246" s="55"/>
-      <c r="H246" s="55"/>
-      <c r="I246" s="55"/>
+      <c r="C246" s="54"/>
+      <c r="D246" s="54"/>
+      <c r="E246" s="54"/>
+      <c r="F246" s="54"/>
+      <c r="G246" s="54"/>
+      <c r="H246" s="54"/>
+      <c r="I246" s="54"/>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="41"/>
       <c r="B247" s="41"/>
-      <c r="C247" s="55"/>
-      <c r="D247" s="55"/>
-      <c r="E247" s="55"/>
-      <c r="F247" s="55"/>
-      <c r="G247" s="55"/>
-      <c r="H247" s="55"/>
-      <c r="I247" s="55"/>
+      <c r="C247" s="54"/>
+      <c r="D247" s="54"/>
+      <c r="E247" s="54"/>
+      <c r="F247" s="54"/>
+      <c r="G247" s="54"/>
+      <c r="H247" s="54"/>
+      <c r="I247" s="54"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="41"/>
       <c r="B248" s="41"/>
-      <c r="C248" s="55"/>
-      <c r="D248" s="55"/>
-      <c r="E248" s="55"/>
-      <c r="F248" s="55"/>
-      <c r="G248" s="55"/>
-      <c r="H248" s="55"/>
-      <c r="I248" s="55"/>
+      <c r="C248" s="54"/>
+      <c r="D248" s="54"/>
+      <c r="E248" s="54"/>
+      <c r="F248" s="54"/>
+      <c r="G248" s="54"/>
+      <c r="H248" s="54"/>
+      <c r="I248" s="54"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="41"/>
       <c r="B249" s="41"/>
-      <c r="C249" s="55"/>
-      <c r="D249" s="55"/>
-      <c r="E249" s="55"/>
-      <c r="F249" s="55"/>
-      <c r="G249" s="55"/>
-      <c r="H249" s="55"/>
-      <c r="I249" s="55"/>
+      <c r="C249" s="54"/>
+      <c r="D249" s="54"/>
+      <c r="E249" s="54"/>
+      <c r="F249" s="54"/>
+      <c r="G249" s="54"/>
+      <c r="H249" s="54"/>
+      <c r="I249" s="54"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="41"/>
       <c r="B250" s="41"/>
-      <c r="C250" s="55"/>
-      <c r="D250" s="55"/>
-      <c r="E250" s="55"/>
-      <c r="F250" s="55"/>
-      <c r="G250" s="55"/>
-      <c r="H250" s="55"/>
-      <c r="I250" s="55"/>
+      <c r="C250" s="54"/>
+      <c r="D250" s="54"/>
+      <c r="E250" s="54"/>
+      <c r="F250" s="54"/>
+      <c r="G250" s="54"/>
+      <c r="H250" s="54"/>
+      <c r="I250" s="54"/>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="41"/>
       <c r="B251" s="41"/>
-      <c r="C251" s="55"/>
-      <c r="D251" s="55"/>
-      <c r="E251" s="55"/>
-      <c r="F251" s="55"/>
-      <c r="G251" s="55"/>
-      <c r="H251" s="55"/>
-      <c r="I251" s="55"/>
+      <c r="C251" s="54"/>
+      <c r="D251" s="54"/>
+      <c r="E251" s="54"/>
+      <c r="F251" s="54"/>
+      <c r="G251" s="54"/>
+      <c r="H251" s="54"/>
+      <c r="I251" s="54"/>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="41"/>
       <c r="B252" s="41"/>
-      <c r="C252" s="55"/>
-      <c r="D252" s="55"/>
-      <c r="E252" s="55"/>
-      <c r="F252" s="55"/>
-      <c r="G252" s="55"/>
-      <c r="H252" s="55"/>
-      <c r="I252" s="55"/>
+      <c r="C252" s="54"/>
+      <c r="D252" s="54"/>
+      <c r="E252" s="54"/>
+      <c r="F252" s="54"/>
+      <c r="G252" s="54"/>
+      <c r="H252" s="54"/>
+      <c r="I252" s="54"/>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="41"/>
       <c r="B253" s="41"/>
-      <c r="C253" s="55"/>
-      <c r="D253" s="55"/>
-      <c r="E253" s="55"/>
-      <c r="F253" s="55"/>
-      <c r="G253" s="55"/>
-      <c r="H253" s="55"/>
-      <c r="I253" s="55"/>
+      <c r="C253" s="54"/>
+      <c r="D253" s="54"/>
+      <c r="E253" s="54"/>
+      <c r="F253" s="54"/>
+      <c r="G253" s="54"/>
+      <c r="H253" s="54"/>
+      <c r="I253" s="54"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="41"/>
       <c r="B254" s="41"/>
-      <c r="C254" s="55"/>
-      <c r="D254" s="55"/>
-      <c r="E254" s="55"/>
-      <c r="F254" s="55"/>
-      <c r="G254" s="55"/>
-      <c r="H254" s="55"/>
-      <c r="I254" s="55"/>
+      <c r="C254" s="54"/>
+      <c r="D254" s="54"/>
+      <c r="E254" s="54"/>
+      <c r="F254" s="54"/>
+      <c r="G254" s="54"/>
+      <c r="H254" s="54"/>
+      <c r="I254" s="54"/>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="41"/>
       <c r="B255" s="41"/>
-      <c r="C255" s="55"/>
-      <c r="D255" s="55"/>
-      <c r="E255" s="55"/>
-      <c r="F255" s="55"/>
-      <c r="G255" s="55"/>
-      <c r="H255" s="55"/>
-      <c r="I255" s="55"/>
+      <c r="C255" s="54"/>
+      <c r="D255" s="54"/>
+      <c r="E255" s="54"/>
+      <c r="F255" s="54"/>
+      <c r="G255" s="54"/>
+      <c r="H255" s="54"/>
+      <c r="I255" s="54"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="41"/>
       <c r="B256" s="41"/>
-      <c r="C256" s="55"/>
-      <c r="D256" s="55"/>
-      <c r="E256" s="55"/>
-      <c r="F256" s="55"/>
-      <c r="G256" s="55"/>
-      <c r="H256" s="55"/>
-      <c r="I256" s="55"/>
+      <c r="C256" s="54"/>
+      <c r="D256" s="54"/>
+      <c r="E256" s="54"/>
+      <c r="F256" s="54"/>
+      <c r="G256" s="54"/>
+      <c r="H256" s="54"/>
+      <c r="I256" s="54"/>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="41"/>
       <c r="B257" s="41"/>
-      <c r="C257" s="55"/>
-      <c r="D257" s="55"/>
-      <c r="E257" s="55"/>
-      <c r="F257" s="55"/>
-      <c r="G257" s="55"/>
-      <c r="H257" s="55"/>
-      <c r="I257" s="55"/>
+      <c r="C257" s="54"/>
+      <c r="D257" s="54"/>
+      <c r="E257" s="54"/>
+      <c r="F257" s="54"/>
+      <c r="G257" s="54"/>
+      <c r="H257" s="54"/>
+      <c r="I257" s="54"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="41"/>
       <c r="B258" s="41"/>
-      <c r="C258" s="55"/>
-      <c r="D258" s="55"/>
-      <c r="E258" s="55"/>
-      <c r="F258" s="55"/>
-      <c r="G258" s="55"/>
-      <c r="H258" s="55"/>
-      <c r="I258" s="55"/>
+      <c r="C258" s="54"/>
+      <c r="D258" s="54"/>
+      <c r="E258" s="54"/>
+      <c r="F258" s="54"/>
+      <c r="G258" s="54"/>
+      <c r="H258" s="54"/>
+      <c r="I258" s="54"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="41"/>
       <c r="B259" s="41"/>
-      <c r="C259" s="55"/>
-      <c r="D259" s="55"/>
-      <c r="E259" s="55"/>
-      <c r="F259" s="55"/>
-      <c r="G259" s="55"/>
-      <c r="H259" s="55"/>
-      <c r="I259" s="55"/>
+      <c r="C259" s="54"/>
+      <c r="D259" s="54"/>
+      <c r="E259" s="54"/>
+      <c r="F259" s="54"/>
+      <c r="G259" s="54"/>
+      <c r="H259" s="54"/>
+      <c r="I259" s="54"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="41"/>
       <c r="B260" s="41"/>
-      <c r="C260" s="55"/>
-      <c r="D260" s="55"/>
-      <c r="E260" s="55"/>
-      <c r="F260" s="55"/>
-      <c r="G260" s="55"/>
-      <c r="H260" s="55"/>
-      <c r="I260" s="55"/>
+      <c r="C260" s="54"/>
+      <c r="D260" s="54"/>
+      <c r="E260" s="54"/>
+      <c r="F260" s="54"/>
+      <c r="G260" s="54"/>
+      <c r="H260" s="54"/>
+      <c r="I260" s="54"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="41"/>
       <c r="B261" s="41"/>
-      <c r="C261" s="55"/>
-      <c r="D261" s="55"/>
-      <c r="E261" s="55"/>
-      <c r="F261" s="55"/>
-      <c r="G261" s="55"/>
-      <c r="H261" s="55"/>
-      <c r="I261" s="55"/>
+      <c r="C261" s="54"/>
+      <c r="D261" s="54"/>
+      <c r="E261" s="54"/>
+      <c r="F261" s="54"/>
+      <c r="G261" s="54"/>
+      <c r="H261" s="54"/>
+      <c r="I261" s="54"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="41"/>
       <c r="B262" s="41"/>
-      <c r="C262" s="55"/>
-      <c r="D262" s="55"/>
-      <c r="E262" s="55"/>
-      <c r="F262" s="55"/>
-      <c r="G262" s="55"/>
-      <c r="H262" s="55"/>
-      <c r="I262" s="55"/>
+      <c r="C262" s="54"/>
+      <c r="D262" s="54"/>
+      <c r="E262" s="54"/>
+      <c r="F262" s="54"/>
+      <c r="G262" s="54"/>
+      <c r="H262" s="54"/>
+      <c r="I262" s="54"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="41"/>
       <c r="B263" s="41"/>
-      <c r="C263" s="55"/>
-      <c r="D263" s="55"/>
-      <c r="E263" s="55"/>
-      <c r="F263" s="55"/>
-      <c r="G263" s="55"/>
-      <c r="H263" s="55"/>
-      <c r="I263" s="55"/>
+      <c r="C263" s="54"/>
+      <c r="D263" s="54"/>
+      <c r="E263" s="54"/>
+      <c r="F263" s="54"/>
+      <c r="G263" s="54"/>
+      <c r="H263" s="54"/>
+      <c r="I263" s="54"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="41"/>
       <c r="B264" s="41"/>
-      <c r="C264" s="55"/>
-      <c r="D264" s="55"/>
-      <c r="E264" s="55"/>
-      <c r="F264" s="55"/>
-      <c r="G264" s="55"/>
-      <c r="H264" s="55"/>
-      <c r="I264" s="55"/>
+      <c r="C264" s="54"/>
+      <c r="D264" s="54"/>
+      <c r="E264" s="54"/>
+      <c r="F264" s="54"/>
+      <c r="G264" s="54"/>
+      <c r="H264" s="54"/>
+      <c r="I264" s="54"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="41"/>
       <c r="B265" s="41"/>
-      <c r="C265" s="55"/>
-      <c r="D265" s="55"/>
-      <c r="E265" s="55"/>
-      <c r="F265" s="55"/>
-      <c r="G265" s="55"/>
-      <c r="H265" s="55"/>
-      <c r="I265" s="55"/>
+      <c r="C265" s="54"/>
+      <c r="D265" s="54"/>
+      <c r="E265" s="54"/>
+      <c r="F265" s="54"/>
+      <c r="G265" s="54"/>
+      <c r="H265" s="54"/>
+      <c r="I265" s="54"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="41"/>
       <c r="B266" s="41"/>
-      <c r="C266" s="55"/>
-      <c r="D266" s="55"/>
-      <c r="E266" s="55"/>
-      <c r="F266" s="55"/>
-      <c r="G266" s="55"/>
-      <c r="H266" s="55"/>
-      <c r="I266" s="55"/>
+      <c r="C266" s="54"/>
+      <c r="D266" s="54"/>
+      <c r="E266" s="54"/>
+      <c r="F266" s="54"/>
+      <c r="G266" s="54"/>
+      <c r="H266" s="54"/>
+      <c r="I266" s="54"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="41"/>
       <c r="B267" s="41"/>
-      <c r="C267" s="55"/>
-      <c r="D267" s="55"/>
-      <c r="E267" s="55"/>
-      <c r="F267" s="55"/>
-      <c r="G267" s="55"/>
-      <c r="H267" s="55"/>
-      <c r="I267" s="55"/>
+      <c r="C267" s="54"/>
+      <c r="D267" s="54"/>
+      <c r="E267" s="54"/>
+      <c r="F267" s="54"/>
+      <c r="G267" s="54"/>
+      <c r="H267" s="54"/>
+      <c r="I267" s="54"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="41"/>
       <c r="B268" s="41"/>
-      <c r="C268" s="55"/>
-      <c r="D268" s="55"/>
-      <c r="E268" s="55"/>
-      <c r="F268" s="55"/>
-      <c r="G268" s="55"/>
-      <c r="H268" s="55"/>
-      <c r="I268" s="55"/>
+      <c r="C268" s="54"/>
+      <c r="D268" s="54"/>
+      <c r="E268" s="54"/>
+      <c r="F268" s="54"/>
+      <c r="G268" s="54"/>
+      <c r="H268" s="54"/>
+      <c r="I268" s="54"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="41"/>
       <c r="B269" s="41"/>
-      <c r="C269" s="55"/>
-      <c r="D269" s="55"/>
-      <c r="E269" s="55"/>
-      <c r="F269" s="55"/>
-      <c r="G269" s="55"/>
-      <c r="H269" s="55"/>
-      <c r="I269" s="55"/>
+      <c r="C269" s="54"/>
+      <c r="D269" s="54"/>
+      <c r="E269" s="54"/>
+      <c r="F269" s="54"/>
+      <c r="G269" s="54"/>
+      <c r="H269" s="54"/>
+      <c r="I269" s="54"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="41"/>
       <c r="B270" s="41"/>
-      <c r="C270" s="55"/>
-      <c r="D270" s="55"/>
-      <c r="E270" s="55"/>
-      <c r="F270" s="55"/>
-      <c r="G270" s="55"/>
-      <c r="H270" s="55"/>
-      <c r="I270" s="55"/>
+      <c r="C270" s="54"/>
+      <c r="D270" s="54"/>
+      <c r="E270" s="54"/>
+      <c r="F270" s="54"/>
+      <c r="G270" s="54"/>
+      <c r="H270" s="54"/>
+      <c r="I270" s="54"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="41"/>
       <c r="B271" s="41"/>
-      <c r="C271" s="55"/>
-      <c r="D271" s="55"/>
-      <c r="E271" s="55"/>
-      <c r="F271" s="55"/>
-      <c r="G271" s="55"/>
-      <c r="H271" s="55"/>
-      <c r="I271" s="55"/>
+      <c r="C271" s="54"/>
+      <c r="D271" s="54"/>
+      <c r="E271" s="54"/>
+      <c r="F271" s="54"/>
+      <c r="G271" s="54"/>
+      <c r="H271" s="54"/>
+      <c r="I271" s="54"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="41"/>
       <c r="B272" s="41"/>
-      <c r="C272" s="55"/>
-      <c r="D272" s="55"/>
-      <c r="E272" s="55"/>
-      <c r="F272" s="55"/>
-      <c r="G272" s="55"/>
-      <c r="H272" s="55"/>
-      <c r="I272" s="55"/>
+      <c r="C272" s="54"/>
+      <c r="D272" s="54"/>
+      <c r="E272" s="54"/>
+      <c r="F272" s="54"/>
+      <c r="G272" s="54"/>
+      <c r="H272" s="54"/>
+      <c r="I272" s="54"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="41"/>
       <c r="B273" s="41"/>
-      <c r="C273" s="55"/>
-      <c r="D273" s="55"/>
-      <c r="E273" s="55"/>
-      <c r="F273" s="55"/>
-      <c r="G273" s="55"/>
-      <c r="H273" s="55"/>
-      <c r="I273" s="55"/>
+      <c r="C273" s="54"/>
+      <c r="D273" s="54"/>
+      <c r="E273" s="54"/>
+      <c r="F273" s="54"/>
+      <c r="G273" s="54"/>
+      <c r="H273" s="54"/>
+      <c r="I273" s="54"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="41"/>
       <c r="B274" s="41"/>
-      <c r="C274" s="55"/>
-      <c r="D274" s="55"/>
-      <c r="E274" s="55"/>
-      <c r="F274" s="55"/>
-      <c r="G274" s="55"/>
-      <c r="H274" s="55"/>
-      <c r="I274" s="55"/>
+      <c r="C274" s="54"/>
+      <c r="D274" s="54"/>
+      <c r="E274" s="54"/>
+      <c r="F274" s="54"/>
+      <c r="G274" s="54"/>
+      <c r="H274" s="54"/>
+      <c r="I274" s="54"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="41"/>
       <c r="B275" s="41"/>
-      <c r="C275" s="55"/>
-      <c r="D275" s="55"/>
-      <c r="E275" s="55"/>
-      <c r="F275" s="55"/>
-      <c r="G275" s="55"/>
-      <c r="H275" s="55"/>
-      <c r="I275" s="55"/>
+      <c r="C275" s="54"/>
+      <c r="D275" s="54"/>
+      <c r="E275" s="54"/>
+      <c r="F275" s="54"/>
+      <c r="G275" s="54"/>
+      <c r="H275" s="54"/>
+      <c r="I275" s="54"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="41"/>
       <c r="B276" s="41"/>
-      <c r="C276" s="55"/>
-      <c r="D276" s="55"/>
-      <c r="E276" s="55"/>
-      <c r="F276" s="55"/>
-      <c r="G276" s="55"/>
-      <c r="H276" s="55"/>
-      <c r="I276" s="55"/>
+      <c r="C276" s="54"/>
+      <c r="D276" s="54"/>
+      <c r="E276" s="54"/>
+      <c r="F276" s="54"/>
+      <c r="G276" s="54"/>
+      <c r="H276" s="54"/>
+      <c r="I276" s="54"/>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="41"/>
       <c r="B277" s="41"/>
-      <c r="C277" s="55"/>
-      <c r="D277" s="55"/>
-      <c r="E277" s="55"/>
-      <c r="F277" s="55"/>
-      <c r="G277" s="55"/>
-      <c r="H277" s="55"/>
-      <c r="I277" s="55"/>
+      <c r="C277" s="54"/>
+      <c r="D277" s="54"/>
+      <c r="E277" s="54"/>
+      <c r="F277" s="54"/>
+      <c r="G277" s="54"/>
+      <c r="H277" s="54"/>
+      <c r="I277" s="54"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="41"/>
       <c r="B278" s="41"/>
-      <c r="C278" s="55"/>
-      <c r="D278" s="55"/>
-      <c r="E278" s="55"/>
-      <c r="F278" s="55"/>
-      <c r="G278" s="55"/>
-      <c r="H278" s="55"/>
-      <c r="I278" s="55"/>
+      <c r="C278" s="54"/>
+      <c r="D278" s="54"/>
+      <c r="E278" s="54"/>
+      <c r="F278" s="54"/>
+      <c r="G278" s="54"/>
+      <c r="H278" s="54"/>
+      <c r="I278" s="54"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="41"/>
       <c r="B279" s="41"/>
-      <c r="C279" s="55"/>
-      <c r="D279" s="55"/>
-      <c r="E279" s="55"/>
-      <c r="F279" s="55"/>
-      <c r="G279" s="55"/>
-      <c r="H279" s="55"/>
-      <c r="I279" s="55"/>
+      <c r="C279" s="54"/>
+      <c r="D279" s="54"/>
+      <c r="E279" s="54"/>
+      <c r="F279" s="54"/>
+      <c r="G279" s="54"/>
+      <c r="H279" s="54"/>
+      <c r="I279" s="54"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="41"/>
       <c r="B280" s="41"/>
-      <c r="C280" s="55"/>
-      <c r="D280" s="55"/>
-      <c r="E280" s="55"/>
-      <c r="F280" s="55"/>
-      <c r="G280" s="55"/>
-      <c r="H280" s="55"/>
-      <c r="I280" s="55"/>
+      <c r="C280" s="54"/>
+      <c r="D280" s="54"/>
+      <c r="E280" s="54"/>
+      <c r="F280" s="54"/>
+      <c r="G280" s="54"/>
+      <c r="H280" s="54"/>
+      <c r="I280" s="54"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="41"/>
       <c r="B281" s="41"/>
-      <c r="C281" s="55"/>
-      <c r="D281" s="55"/>
-      <c r="E281" s="55"/>
-      <c r="F281" s="55"/>
-      <c r="G281" s="55"/>
-      <c r="H281" s="55"/>
-      <c r="I281" s="55"/>
+      <c r="C281" s="54"/>
+      <c r="D281" s="54"/>
+      <c r="E281" s="54"/>
+      <c r="F281" s="54"/>
+      <c r="G281" s="54"/>
+      <c r="H281" s="54"/>
+      <c r="I281" s="54"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="41"/>
       <c r="B282" s="41"/>
-      <c r="C282" s="55"/>
-      <c r="D282" s="55"/>
-      <c r="E282" s="55"/>
-      <c r="F282" s="55"/>
-      <c r="G282" s="55"/>
-      <c r="H282" s="55"/>
-      <c r="I282" s="55"/>
+      <c r="C282" s="54"/>
+      <c r="D282" s="54"/>
+      <c r="E282" s="54"/>
+      <c r="F282" s="54"/>
+      <c r="G282" s="54"/>
+      <c r="H282" s="54"/>
+      <c r="I282" s="54"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="41"/>
       <c r="B283" s="41"/>
-      <c r="C283" s="55"/>
-      <c r="D283" s="55"/>
-      <c r="E283" s="55"/>
-      <c r="F283" s="55"/>
-      <c r="G283" s="55"/>
-      <c r="H283" s="55"/>
-      <c r="I283" s="55"/>
+      <c r="C283" s="54"/>
+      <c r="D283" s="54"/>
+      <c r="E283" s="54"/>
+      <c r="F283" s="54"/>
+      <c r="G283" s="54"/>
+      <c r="H283" s="54"/>
+      <c r="I283" s="54"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="41"/>
       <c r="B284" s="41"/>
-      <c r="C284" s="55"/>
-      <c r="D284" s="55"/>
-      <c r="E284" s="55"/>
-      <c r="F284" s="55"/>
-      <c r="G284" s="55"/>
-      <c r="H284" s="55"/>
-      <c r="I284" s="55"/>
+      <c r="C284" s="54"/>
+      <c r="D284" s="54"/>
+      <c r="E284" s="54"/>
+      <c r="F284" s="54"/>
+      <c r="G284" s="54"/>
+      <c r="H284" s="54"/>
+      <c r="I284" s="54"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="41"/>
       <c r="B285" s="41"/>
-      <c r="C285" s="55"/>
-      <c r="D285" s="55"/>
-      <c r="E285" s="55"/>
-      <c r="F285" s="55"/>
-      <c r="G285" s="55"/>
-      <c r="H285" s="55"/>
-      <c r="I285" s="55"/>
+      <c r="C285" s="54"/>
+      <c r="D285" s="54"/>
+      <c r="E285" s="54"/>
+      <c r="F285" s="54"/>
+      <c r="G285" s="54"/>
+      <c r="H285" s="54"/>
+      <c r="I285" s="54"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="41"/>
       <c r="B286" s="41"/>
-      <c r="C286" s="55"/>
-      <c r="D286" s="55"/>
-      <c r="E286" s="55"/>
-      <c r="F286" s="55"/>
-      <c r="G286" s="55"/>
-      <c r="H286" s="55"/>
-      <c r="I286" s="55"/>
+      <c r="C286" s="54"/>
+      <c r="D286" s="54"/>
+      <c r="E286" s="54"/>
+      <c r="F286" s="54"/>
+      <c r="G286" s="54"/>
+      <c r="H286" s="54"/>
+      <c r="I286" s="54"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="41"/>
       <c r="B287" s="41"/>
-      <c r="C287" s="55"/>
-      <c r="D287" s="55"/>
-      <c r="E287" s="55"/>
-      <c r="F287" s="55"/>
-      <c r="G287" s="55"/>
-      <c r="H287" s="55"/>
-      <c r="I287" s="55"/>
+      <c r="C287" s="54"/>
+      <c r="D287" s="54"/>
+      <c r="E287" s="54"/>
+      <c r="F287" s="54"/>
+      <c r="G287" s="54"/>
+      <c r="H287" s="54"/>
+      <c r="I287" s="54"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="41"/>
       <c r="B288" s="41"/>
-      <c r="C288" s="55"/>
-      <c r="D288" s="55"/>
-      <c r="E288" s="55"/>
-      <c r="F288" s="55"/>
-      <c r="G288" s="55"/>
-      <c r="H288" s="55"/>
-      <c r="I288" s="55"/>
+      <c r="C288" s="54"/>
+      <c r="D288" s="54"/>
+      <c r="E288" s="54"/>
+      <c r="F288" s="54"/>
+      <c r="G288" s="54"/>
+      <c r="H288" s="54"/>
+      <c r="I288" s="54"/>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="41"/>
       <c r="B289" s="41"/>
-      <c r="C289" s="55"/>
-      <c r="D289" s="55"/>
-      <c r="E289" s="55"/>
-      <c r="F289" s="55"/>
-      <c r="G289" s="55"/>
-      <c r="H289" s="55"/>
-      <c r="I289" s="55"/>
+      <c r="C289" s="54"/>
+      <c r="D289" s="54"/>
+      <c r="E289" s="54"/>
+      <c r="F289" s="54"/>
+      <c r="G289" s="54"/>
+      <c r="H289" s="54"/>
+      <c r="I289" s="54"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="41"/>
       <c r="B290" s="41"/>
-      <c r="C290" s="55"/>
-      <c r="D290" s="55"/>
-      <c r="E290" s="55"/>
-      <c r="F290" s="55"/>
-      <c r="G290" s="55"/>
-      <c r="H290" s="55"/>
-      <c r="I290" s="55"/>
+      <c r="C290" s="54"/>
+      <c r="D290" s="54"/>
+      <c r="E290" s="54"/>
+      <c r="F290" s="54"/>
+      <c r="G290" s="54"/>
+      <c r="H290" s="54"/>
+      <c r="I290" s="54"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="41"/>
       <c r="B291" s="41"/>
-      <c r="C291" s="55"/>
-      <c r="D291" s="55"/>
-      <c r="E291" s="55"/>
-      <c r="F291" s="55"/>
-      <c r="G291" s="55"/>
-      <c r="H291" s="55"/>
-      <c r="I291" s="55"/>
+      <c r="C291" s="54"/>
+      <c r="D291" s="54"/>
+      <c r="E291" s="54"/>
+      <c r="F291" s="54"/>
+      <c r="G291" s="54"/>
+      <c r="H291" s="54"/>
+      <c r="I291" s="54"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="41"/>
       <c r="B292" s="41"/>
-      <c r="C292" s="55"/>
-      <c r="D292" s="55"/>
-      <c r="E292" s="55"/>
-      <c r="F292" s="55"/>
-      <c r="G292" s="55"/>
-      <c r="H292" s="55"/>
-      <c r="I292" s="55"/>
+      <c r="C292" s="54"/>
+      <c r="D292" s="54"/>
+      <c r="E292" s="54"/>
+      <c r="F292" s="54"/>
+      <c r="G292" s="54"/>
+      <c r="H292" s="54"/>
+      <c r="I292" s="54"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="41"/>
       <c r="B293" s="41"/>
-      <c r="C293" s="55"/>
-      <c r="D293" s="55"/>
-      <c r="E293" s="55"/>
-      <c r="F293" s="55"/>
-      <c r="G293" s="55"/>
-      <c r="H293" s="55"/>
-      <c r="I293" s="55"/>
+      <c r="C293" s="54"/>
+      <c r="D293" s="54"/>
+      <c r="E293" s="54"/>
+      <c r="F293" s="54"/>
+      <c r="G293" s="54"/>
+      <c r="H293" s="54"/>
+      <c r="I293" s="54"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="41"/>
       <c r="B294" s="41"/>
-      <c r="C294" s="55"/>
-      <c r="D294" s="55"/>
-      <c r="E294" s="55"/>
-      <c r="F294" s="55"/>
-      <c r="G294" s="55"/>
-      <c r="H294" s="55"/>
-      <c r="I294" s="55"/>
+      <c r="C294" s="54"/>
+      <c r="D294" s="54"/>
+      <c r="E294" s="54"/>
+      <c r="F294" s="54"/>
+      <c r="G294" s="54"/>
+      <c r="H294" s="54"/>
+      <c r="I294" s="54"/>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="41"/>
       <c r="B295" s="41"/>
-      <c r="C295" s="55"/>
-      <c r="D295" s="55"/>
-      <c r="E295" s="55"/>
-      <c r="F295" s="55"/>
-      <c r="G295" s="55"/>
-      <c r="H295" s="55"/>
-      <c r="I295" s="55"/>
+      <c r="C295" s="54"/>
+      <c r="D295" s="54"/>
+      <c r="E295" s="54"/>
+      <c r="F295" s="54"/>
+      <c r="G295" s="54"/>
+      <c r="H295" s="54"/>
+      <c r="I295" s="54"/>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="41"/>
       <c r="B296" s="41"/>
-      <c r="C296" s="55"/>
-      <c r="D296" s="55"/>
-      <c r="E296" s="55"/>
-      <c r="F296" s="55"/>
-      <c r="G296" s="55"/>
-      <c r="H296" s="55"/>
-      <c r="I296" s="55"/>
+      <c r="C296" s="54"/>
+      <c r="D296" s="54"/>
+      <c r="E296" s="54"/>
+      <c r="F296" s="54"/>
+      <c r="G296" s="54"/>
+      <c r="H296" s="54"/>
+      <c r="I296" s="54"/>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="41"/>
       <c r="B297" s="41"/>
-      <c r="C297" s="55"/>
-      <c r="D297" s="55"/>
-      <c r="E297" s="55"/>
-      <c r="F297" s="55"/>
-      <c r="G297" s="55"/>
-      <c r="H297" s="55"/>
-      <c r="I297" s="55"/>
+      <c r="C297" s="54"/>
+      <c r="D297" s="54"/>
+      <c r="E297" s="54"/>
+      <c r="F297" s="54"/>
+      <c r="G297" s="54"/>
+      <c r="H297" s="54"/>
+      <c r="I297" s="54"/>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="41"/>
       <c r="B298" s="41"/>
-      <c r="C298" s="55"/>
-      <c r="D298" s="55"/>
-      <c r="E298" s="55"/>
-      <c r="F298" s="55"/>
-      <c r="G298" s="55"/>
-      <c r="H298" s="55"/>
-      <c r="I298" s="55"/>
+      <c r="C298" s="54"/>
+      <c r="D298" s="54"/>
+      <c r="E298" s="54"/>
+      <c r="F298" s="54"/>
+      <c r="G298" s="54"/>
+      <c r="H298" s="54"/>
+      <c r="I298" s="54"/>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="41"/>
       <c r="B299" s="41"/>
-      <c r="C299" s="55"/>
-      <c r="D299" s="55"/>
-      <c r="E299" s="55"/>
-      <c r="F299" s="55"/>
-      <c r="G299" s="55"/>
-      <c r="H299" s="55"/>
-      <c r="I299" s="55"/>
+      <c r="C299" s="54"/>
+      <c r="D299" s="54"/>
+      <c r="E299" s="54"/>
+      <c r="F299" s="54"/>
+      <c r="G299" s="54"/>
+      <c r="H299" s="54"/>
+      <c r="I299" s="54"/>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="41"/>
       <c r="B300" s="41"/>
-      <c r="C300" s="55"/>
-      <c r="D300" s="55"/>
-      <c r="E300" s="55"/>
-      <c r="F300" s="55"/>
-      <c r="G300" s="55"/>
-      <c r="H300" s="55"/>
-      <c r="I300" s="55"/>
+      <c r="C300" s="54"/>
+      <c r="D300" s="54"/>
+      <c r="E300" s="54"/>
+      <c r="F300" s="54"/>
+      <c r="G300" s="54"/>
+      <c r="H300" s="54"/>
+      <c r="I300" s="54"/>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="41"/>
       <c r="B301" s="41"/>
-      <c r="C301" s="55"/>
-      <c r="D301" s="55"/>
-      <c r="E301" s="55"/>
-      <c r="F301" s="55"/>
-      <c r="G301" s="55"/>
-      <c r="H301" s="55"/>
-      <c r="I301" s="55"/>
+      <c r="C301" s="54"/>
+      <c r="D301" s="54"/>
+      <c r="E301" s="54"/>
+      <c r="F301" s="54"/>
+      <c r="G301" s="54"/>
+      <c r="H301" s="54"/>
+      <c r="I301" s="54"/>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="41"/>
       <c r="B302" s="41"/>
-      <c r="C302" s="55"/>
-      <c r="D302" s="55"/>
-      <c r="E302" s="55"/>
-      <c r="F302" s="55"/>
-      <c r="G302" s="55"/>
-      <c r="H302" s="55"/>
-      <c r="I302" s="55"/>
+      <c r="C302" s="54"/>
+      <c r="D302" s="54"/>
+      <c r="E302" s="54"/>
+      <c r="F302" s="54"/>
+      <c r="G302" s="54"/>
+      <c r="H302" s="54"/>
+      <c r="I302" s="54"/>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="41"/>
       <c r="B303" s="41"/>
-      <c r="C303" s="55"/>
-      <c r="D303" s="55"/>
-      <c r="E303" s="55"/>
-      <c r="F303" s="55"/>
-      <c r="G303" s="55"/>
-      <c r="H303" s="55"/>
-      <c r="I303" s="55"/>
+      <c r="C303" s="54"/>
+      <c r="D303" s="54"/>
+      <c r="E303" s="54"/>
+      <c r="F303" s="54"/>
+      <c r="G303" s="54"/>
+      <c r="H303" s="54"/>
+      <c r="I303" s="54"/>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="41"/>
       <c r="B304" s="41"/>
-      <c r="C304" s="55"/>
-      <c r="D304" s="55"/>
-      <c r="E304" s="55"/>
-      <c r="F304" s="55"/>
-      <c r="G304" s="55"/>
-      <c r="H304" s="55"/>
-      <c r="I304" s="55"/>
+      <c r="C304" s="54"/>
+      <c r="D304" s="54"/>
+      <c r="E304" s="54"/>
+      <c r="F304" s="54"/>
+      <c r="G304" s="54"/>
+      <c r="H304" s="54"/>
+      <c r="I304" s="54"/>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="41"/>
       <c r="B305" s="41"/>
-      <c r="C305" s="55"/>
-      <c r="D305" s="55"/>
-      <c r="E305" s="55"/>
-      <c r="F305" s="55"/>
-      <c r="G305" s="55"/>
-      <c r="H305" s="55"/>
-      <c r="I305" s="55"/>
+      <c r="C305" s="54"/>
+      <c r="D305" s="54"/>
+      <c r="E305" s="54"/>
+      <c r="F305" s="54"/>
+      <c r="G305" s="54"/>
+      <c r="H305" s="54"/>
+      <c r="I305" s="54"/>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="41"/>
       <c r="B306" s="41"/>
-      <c r="C306" s="55"/>
-      <c r="D306" s="55"/>
-      <c r="E306" s="55"/>
-      <c r="F306" s="55"/>
-      <c r="G306" s="55"/>
-      <c r="H306" s="55"/>
-      <c r="I306" s="55"/>
+      <c r="C306" s="54"/>
+      <c r="D306" s="54"/>
+      <c r="E306" s="54"/>
+      <c r="F306" s="54"/>
+      <c r="G306" s="54"/>
+      <c r="H306" s="54"/>
+      <c r="I306" s="54"/>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="41"/>
       <c r="B307" s="41"/>
-      <c r="C307" s="55"/>
-      <c r="D307" s="55"/>
-      <c r="E307" s="55"/>
-      <c r="F307" s="55"/>
-      <c r="G307" s="55"/>
-      <c r="H307" s="55"/>
-      <c r="I307" s="55"/>
+      <c r="C307" s="54"/>
+      <c r="D307" s="54"/>
+      <c r="E307" s="54"/>
+      <c r="F307" s="54"/>
+      <c r="G307" s="54"/>
+      <c r="H307" s="54"/>
+      <c r="I307" s="54"/>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="41"/>
       <c r="B308" s="41"/>
-      <c r="C308" s="55"/>
-      <c r="D308" s="55"/>
-      <c r="E308" s="55"/>
-      <c r="F308" s="55"/>
-      <c r="G308" s="55"/>
-      <c r="H308" s="55"/>
-      <c r="I308" s="55"/>
+      <c r="C308" s="54"/>
+      <c r="D308" s="54"/>
+      <c r="E308" s="54"/>
+      <c r="F308" s="54"/>
+      <c r="G308" s="54"/>
+      <c r="H308" s="54"/>
+      <c r="I308" s="54"/>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="41"/>
       <c r="B309" s="41"/>
-      <c r="C309" s="55"/>
-      <c r="D309" s="55"/>
-      <c r="E309" s="55"/>
-      <c r="F309" s="55"/>
-      <c r="G309" s="55"/>
-      <c r="H309" s="55"/>
-      <c r="I309" s="55"/>
+      <c r="C309" s="54"/>
+      <c r="D309" s="54"/>
+      <c r="E309" s="54"/>
+      <c r="F309" s="54"/>
+      <c r="G309" s="54"/>
+      <c r="H309" s="54"/>
+      <c r="I309" s="54"/>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="41"/>
       <c r="B310" s="41"/>
-      <c r="C310" s="55"/>
-      <c r="D310" s="55"/>
-      <c r="E310" s="55"/>
-      <c r="F310" s="55"/>
-      <c r="G310" s="55"/>
-      <c r="H310" s="55"/>
-      <c r="I310" s="55"/>
+      <c r="C310" s="54"/>
+      <c r="D310" s="54"/>
+      <c r="E310" s="54"/>
+      <c r="F310" s="54"/>
+      <c r="G310" s="54"/>
+      <c r="H310" s="54"/>
+      <c r="I310" s="54"/>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="41"/>
       <c r="B311" s="41"/>
-      <c r="C311" s="55"/>
-      <c r="D311" s="55"/>
-      <c r="E311" s="55"/>
-      <c r="F311" s="55"/>
-      <c r="G311" s="55"/>
-      <c r="H311" s="55"/>
-      <c r="I311" s="55"/>
+      <c r="C311" s="54"/>
+      <c r="D311" s="54"/>
+      <c r="E311" s="54"/>
+      <c r="F311" s="54"/>
+      <c r="G311" s="54"/>
+      <c r="H311" s="54"/>
+      <c r="I311" s="54"/>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="41"/>
       <c r="B312" s="41"/>
-      <c r="C312" s="55"/>
-      <c r="D312" s="55"/>
-      <c r="E312" s="55"/>
-      <c r="F312" s="55"/>
-      <c r="G312" s="55"/>
-      <c r="H312" s="55"/>
-      <c r="I312" s="55"/>
+      <c r="C312" s="54"/>
+      <c r="D312" s="54"/>
+      <c r="E312" s="54"/>
+      <c r="F312" s="54"/>
+      <c r="G312" s="54"/>
+      <c r="H312" s="54"/>
+      <c r="I312" s="54"/>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="41"/>
       <c r="B313" s="41"/>
-      <c r="C313" s="55"/>
-      <c r="D313" s="55"/>
-      <c r="E313" s="55"/>
-      <c r="F313" s="55"/>
-      <c r="G313" s="55"/>
-      <c r="H313" s="55"/>
-      <c r="I313" s="55"/>
+      <c r="C313" s="54"/>
+      <c r="D313" s="54"/>
+      <c r="E313" s="54"/>
+      <c r="F313" s="54"/>
+      <c r="G313" s="54"/>
+      <c r="H313" s="54"/>
+      <c r="I313" s="54"/>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="41"/>
       <c r="B314" s="41"/>
-      <c r="C314" s="55"/>
-      <c r="D314" s="55"/>
-      <c r="E314" s="55"/>
-      <c r="F314" s="55"/>
-      <c r="G314" s="55"/>
-      <c r="H314" s="55"/>
-      <c r="I314" s="55"/>
+      <c r="C314" s="54"/>
+      <c r="D314" s="54"/>
+      <c r="E314" s="54"/>
+      <c r="F314" s="54"/>
+      <c r="G314" s="54"/>
+      <c r="H314" s="54"/>
+      <c r="I314" s="54"/>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="41"/>
       <c r="B315" s="41"/>
-      <c r="C315" s="55"/>
-      <c r="D315" s="55"/>
-      <c r="E315" s="55"/>
-      <c r="F315" s="55"/>
-      <c r="G315" s="55"/>
-      <c r="H315" s="55"/>
-      <c r="I315" s="55"/>
+      <c r="C315" s="54"/>
+      <c r="D315" s="54"/>
+      <c r="E315" s="54"/>
+      <c r="F315" s="54"/>
+      <c r="G315" s="54"/>
+      <c r="H315" s="54"/>
+      <c r="I315" s="54"/>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="41"/>
       <c r="B316" s="41"/>
-      <c r="C316" s="55"/>
-      <c r="D316" s="55"/>
-      <c r="E316" s="55"/>
-      <c r="F316" s="55"/>
-      <c r="G316" s="55"/>
-      <c r="H316" s="55"/>
-      <c r="I316" s="55"/>
+      <c r="C316" s="54"/>
+      <c r="D316" s="54"/>
+      <c r="E316" s="54"/>
+      <c r="F316" s="54"/>
+      <c r="G316" s="54"/>
+      <c r="H316" s="54"/>
+      <c r="I316" s="54"/>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="41"/>
       <c r="B317" s="41"/>
-      <c r="C317" s="55"/>
-      <c r="D317" s="55"/>
-      <c r="E317" s="55"/>
-      <c r="F317" s="55"/>
-      <c r="G317" s="55"/>
-      <c r="H317" s="55"/>
-      <c r="I317" s="55"/>
+      <c r="C317" s="54"/>
+      <c r="D317" s="54"/>
+      <c r="E317" s="54"/>
+      <c r="F317" s="54"/>
+      <c r="G317" s="54"/>
+      <c r="H317" s="54"/>
+      <c r="I317" s="54"/>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="41"/>
       <c r="B318" s="41"/>
-      <c r="C318" s="55"/>
-      <c r="D318" s="55"/>
-      <c r="E318" s="55"/>
-      <c r="F318" s="55"/>
-      <c r="G318" s="55"/>
-      <c r="H318" s="55"/>
-      <c r="I318" s="55"/>
+      <c r="C318" s="54"/>
+      <c r="D318" s="54"/>
+      <c r="E318" s="54"/>
+      <c r="F318" s="54"/>
+      <c r="G318" s="54"/>
+      <c r="H318" s="54"/>
+      <c r="I318" s="54"/>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="41"/>
       <c r="B319" s="41"/>
-      <c r="C319" s="55"/>
-      <c r="D319" s="55"/>
-      <c r="E319" s="55"/>
-      <c r="F319" s="55"/>
-      <c r="G319" s="55"/>
-      <c r="H319" s="55"/>
-      <c r="I319" s="55"/>
+      <c r="C319" s="54"/>
+      <c r="D319" s="54"/>
+      <c r="E319" s="54"/>
+      <c r="F319" s="54"/>
+      <c r="G319" s="54"/>
+      <c r="H319" s="54"/>
+      <c r="I319" s="54"/>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="41"/>
       <c r="B320" s="41"/>
-      <c r="C320" s="55"/>
-      <c r="D320" s="55"/>
-      <c r="E320" s="55"/>
-      <c r="F320" s="55"/>
-      <c r="G320" s="55"/>
-      <c r="H320" s="55"/>
-      <c r="I320" s="55"/>
+      <c r="C320" s="54"/>
+      <c r="D320" s="54"/>
+      <c r="E320" s="54"/>
+      <c r="F320" s="54"/>
+      <c r="G320" s="54"/>
+      <c r="H320" s="54"/>
+      <c r="I320" s="54"/>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="41"/>
       <c r="B321" s="41"/>
-      <c r="C321" s="55"/>
-      <c r="D321" s="55"/>
-      <c r="E321" s="55"/>
-      <c r="F321" s="55"/>
-      <c r="G321" s="55"/>
-      <c r="H321" s="55"/>
-      <c r="I321" s="55"/>
+      <c r="C321" s="54"/>
+      <c r="D321" s="54"/>
+      <c r="E321" s="54"/>
+      <c r="F321" s="54"/>
+      <c r="G321" s="54"/>
+      <c r="H321" s="54"/>
+      <c r="I321" s="54"/>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="41"/>
       <c r="B322" s="41"/>
-      <c r="C322" s="55"/>
-      <c r="D322" s="55"/>
-      <c r="E322" s="55"/>
-      <c r="F322" s="55"/>
-      <c r="G322" s="55"/>
-      <c r="H322" s="55"/>
-      <c r="I322" s="55"/>
+      <c r="C322" s="54"/>
+      <c r="D322" s="54"/>
+      <c r="E322" s="54"/>
+      <c r="F322" s="54"/>
+      <c r="G322" s="54"/>
+      <c r="H322" s="54"/>
+      <c r="I322" s="54"/>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="41"/>
       <c r="B323" s="41"/>
-      <c r="C323" s="55"/>
-      <c r="D323" s="55"/>
-      <c r="E323" s="55"/>
-      <c r="F323" s="55"/>
-      <c r="G323" s="55"/>
-      <c r="H323" s="55"/>
-      <c r="I323" s="55"/>
+      <c r="C323" s="54"/>
+      <c r="D323" s="54"/>
+      <c r="E323" s="54"/>
+      <c r="F323" s="54"/>
+      <c r="G323" s="54"/>
+      <c r="H323" s="54"/>
+      <c r="I323" s="54"/>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="41"/>
       <c r="B324" s="41"/>
-      <c r="C324" s="55"/>
-      <c r="D324" s="55"/>
-      <c r="E324" s="55"/>
-      <c r="F324" s="55"/>
-      <c r="G324" s="55"/>
-      <c r="H324" s="55"/>
-      <c r="I324" s="55"/>
+      <c r="C324" s="54"/>
+      <c r="D324" s="54"/>
+      <c r="E324" s="54"/>
+      <c r="F324" s="54"/>
+      <c r="G324" s="54"/>
+      <c r="H324" s="54"/>
+      <c r="I324" s="54"/>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="41"/>
       <c r="B325" s="41"/>
-      <c r="C325" s="55"/>
-      <c r="D325" s="55"/>
-      <c r="E325" s="55"/>
-      <c r="F325" s="55"/>
-      <c r="G325" s="55"/>
-      <c r="H325" s="55"/>
-      <c r="I325" s="55"/>
+      <c r="C325" s="54"/>
+      <c r="D325" s="54"/>
+      <c r="E325" s="54"/>
+      <c r="F325" s="54"/>
+      <c r="G325" s="54"/>
+      <c r="H325" s="54"/>
+      <c r="I325" s="54"/>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="41"/>
       <c r="B326" s="41"/>
-      <c r="C326" s="55"/>
-      <c r="D326" s="55"/>
-      <c r="E326" s="55"/>
-      <c r="F326" s="55"/>
-      <c r="G326" s="55"/>
-      <c r="H326" s="55"/>
-      <c r="I326" s="55"/>
+      <c r="C326" s="54"/>
+      <c r="D326" s="54"/>
+      <c r="E326" s="54"/>
+      <c r="F326" s="54"/>
+      <c r="G326" s="54"/>
+      <c r="H326" s="54"/>
+      <c r="I326" s="54"/>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="41"/>
       <c r="B327" s="41"/>
-      <c r="C327" s="55"/>
-      <c r="D327" s="55"/>
-      <c r="E327" s="55"/>
-      <c r="F327" s="55"/>
-      <c r="G327" s="55"/>
-      <c r="H327" s="55"/>
-      <c r="I327" s="55"/>
+      <c r="C327" s="54"/>
+      <c r="D327" s="54"/>
+      <c r="E327" s="54"/>
+      <c r="F327" s="54"/>
+      <c r="G327" s="54"/>
+      <c r="H327" s="54"/>
+      <c r="I327" s="54"/>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="41"/>
       <c r="B328" s="41"/>
-      <c r="C328" s="55"/>
-      <c r="D328" s="55"/>
-      <c r="E328" s="55"/>
-      <c r="F328" s="55"/>
-      <c r="G328" s="55"/>
-      <c r="H328" s="55"/>
-      <c r="I328" s="55"/>
+      <c r="C328" s="54"/>
+      <c r="D328" s="54"/>
+      <c r="E328" s="54"/>
+      <c r="F328" s="54"/>
+      <c r="G328" s="54"/>
+      <c r="H328" s="54"/>
+      <c r="I328" s="54"/>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="41"/>
       <c r="B329" s="41"/>
-      <c r="C329" s="55"/>
-      <c r="D329" s="55"/>
-      <c r="E329" s="55"/>
-      <c r="F329" s="55"/>
-      <c r="G329" s="55"/>
-      <c r="H329" s="55"/>
-      <c r="I329" s="55"/>
+      <c r="C329" s="54"/>
+      <c r="D329" s="54"/>
+      <c r="E329" s="54"/>
+      <c r="F329" s="54"/>
+      <c r="G329" s="54"/>
+      <c r="H329" s="54"/>
+      <c r="I329" s="54"/>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="41"/>
       <c r="B330" s="41"/>
-      <c r="C330" s="55"/>
-      <c r="D330" s="55"/>
-      <c r="E330" s="55"/>
-      <c r="F330" s="55"/>
-      <c r="G330" s="55"/>
-      <c r="H330" s="55"/>
-      <c r="I330" s="55"/>
+      <c r="C330" s="54"/>
+      <c r="D330" s="54"/>
+      <c r="E330" s="54"/>
+      <c r="F330" s="54"/>
+      <c r="G330" s="54"/>
+      <c r="H330" s="54"/>
+      <c r="I330" s="54"/>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="41"/>
       <c r="B331" s="41"/>
-      <c r="C331" s="55"/>
-      <c r="D331" s="55"/>
-      <c r="E331" s="55"/>
-      <c r="F331" s="55"/>
-      <c r="G331" s="55"/>
-      <c r="H331" s="55"/>
-      <c r="I331" s="55"/>
+      <c r="C331" s="54"/>
+      <c r="D331" s="54"/>
+      <c r="E331" s="54"/>
+      <c r="F331" s="54"/>
+      <c r="G331" s="54"/>
+      <c r="H331" s="54"/>
+      <c r="I331" s="54"/>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="41"/>
       <c r="B332" s="41"/>
-      <c r="C332" s="55"/>
-      <c r="D332" s="55"/>
-      <c r="E332" s="55"/>
-      <c r="F332" s="55"/>
-      <c r="G332" s="55"/>
-      <c r="H332" s="55"/>
-      <c r="I332" s="55"/>
+      <c r="C332" s="54"/>
+      <c r="D332" s="54"/>
+      <c r="E332" s="54"/>
+      <c r="F332" s="54"/>
+      <c r="G332" s="54"/>
+      <c r="H332" s="54"/>
+      <c r="I332" s="54"/>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="41"/>
       <c r="B333" s="41"/>
-      <c r="C333" s="55"/>
-      <c r="D333" s="55"/>
-      <c r="E333" s="55"/>
-      <c r="F333" s="55"/>
-      <c r="G333" s="55"/>
-      <c r="H333" s="55"/>
-      <c r="I333" s="55"/>
+      <c r="C333" s="54"/>
+      <c r="D333" s="54"/>
+      <c r="E333" s="54"/>
+      <c r="F333" s="54"/>
+      <c r="G333" s="54"/>
+      <c r="H333" s="54"/>
+      <c r="I333" s="54"/>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="41"/>
       <c r="B334" s="41"/>
-      <c r="C334" s="55"/>
-      <c r="D334" s="55"/>
-      <c r="E334" s="55"/>
-      <c r="F334" s="55"/>
-      <c r="G334" s="55"/>
-      <c r="H334" s="55"/>
-      <c r="I334" s="55"/>
+      <c r="C334" s="54"/>
+      <c r="D334" s="54"/>
+      <c r="E334" s="54"/>
+      <c r="F334" s="54"/>
+      <c r="G334" s="54"/>
+      <c r="H334" s="54"/>
+      <c r="I334" s="54"/>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="41"/>
       <c r="B335" s="41"/>
-      <c r="C335" s="55"/>
-      <c r="D335" s="55"/>
-      <c r="E335" s="55"/>
-      <c r="F335" s="55"/>
-      <c r="G335" s="55"/>
-      <c r="H335" s="55"/>
-      <c r="I335" s="55"/>
+      <c r="C335" s="54"/>
+      <c r="D335" s="54"/>
+      <c r="E335" s="54"/>
+      <c r="F335" s="54"/>
+      <c r="G335" s="54"/>
+      <c r="H335" s="54"/>
+      <c r="I335" s="54"/>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="41"/>
       <c r="B336" s="41"/>
-      <c r="C336" s="55"/>
-      <c r="D336" s="55"/>
-      <c r="E336" s="55"/>
-      <c r="F336" s="55"/>
-      <c r="G336" s="55"/>
-      <c r="H336" s="55"/>
-      <c r="I336" s="55"/>
+      <c r="C336" s="54"/>
+      <c r="D336" s="54"/>
+      <c r="E336" s="54"/>
+      <c r="F336" s="54"/>
+      <c r="G336" s="54"/>
+      <c r="H336" s="54"/>
+      <c r="I336" s="54"/>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="41"/>
       <c r="B337" s="41"/>
-      <c r="C337" s="55"/>
-      <c r="D337" s="55"/>
-      <c r="E337" s="55"/>
-      <c r="F337" s="55"/>
-      <c r="G337" s="55"/>
-      <c r="H337" s="55"/>
-      <c r="I337" s="55"/>
+      <c r="C337" s="54"/>
+      <c r="D337" s="54"/>
+      <c r="E337" s="54"/>
+      <c r="F337" s="54"/>
+      <c r="G337" s="54"/>
+      <c r="H337" s="54"/>
+      <c r="I337" s="54"/>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="41"/>
       <c r="B338" s="41"/>
-      <c r="C338" s="55"/>
-      <c r="D338" s="55"/>
-      <c r="E338" s="55"/>
-      <c r="F338" s="55"/>
-      <c r="G338" s="55"/>
-      <c r="H338" s="55"/>
-      <c r="I338" s="55"/>
+      <c r="C338" s="54"/>
+      <c r="D338" s="54"/>
+      <c r="E338" s="54"/>
+      <c r="F338" s="54"/>
+      <c r="G338" s="54"/>
+      <c r="H338" s="54"/>
+      <c r="I338" s="54"/>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="41"/>
       <c r="B339" s="41"/>
-      <c r="C339" s="55"/>
-      <c r="D339" s="55"/>
-      <c r="E339" s="55"/>
-      <c r="F339" s="55"/>
-      <c r="G339" s="55"/>
-      <c r="H339" s="55"/>
-      <c r="I339" s="55"/>
+      <c r="C339" s="54"/>
+      <c r="D339" s="54"/>
+      <c r="E339" s="54"/>
+      <c r="F339" s="54"/>
+      <c r="G339" s="54"/>
+      <c r="H339" s="54"/>
+      <c r="I339" s="54"/>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="41"/>
       <c r="B340" s="41"/>
-      <c r="C340" s="55"/>
-      <c r="D340" s="55"/>
-      <c r="E340" s="55"/>
-      <c r="F340" s="55"/>
-      <c r="G340" s="55"/>
-      <c r="H340" s="55"/>
-      <c r="I340" s="55"/>
+      <c r="C340" s="54"/>
+      <c r="D340" s="54"/>
+      <c r="E340" s="54"/>
+      <c r="F340" s="54"/>
+      <c r="G340" s="54"/>
+      <c r="H340" s="54"/>
+      <c r="I340" s="54"/>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="41"/>
       <c r="B341" s="41"/>
-      <c r="C341" s="55"/>
-      <c r="D341" s="55"/>
-      <c r="E341" s="55"/>
-      <c r="F341" s="55"/>
-      <c r="G341" s="55"/>
-      <c r="H341" s="55"/>
-      <c r="I341" s="55"/>
+      <c r="C341" s="54"/>
+      <c r="D341" s="54"/>
+      <c r="E341" s="54"/>
+      <c r="F341" s="54"/>
+      <c r="G341" s="54"/>
+      <c r="H341" s="54"/>
+      <c r="I341" s="54"/>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="41"/>
       <c r="B342" s="41"/>
-      <c r="C342" s="55"/>
-      <c r="D342" s="55"/>
-      <c r="E342" s="55"/>
-      <c r="F342" s="55"/>
-      <c r="G342" s="55"/>
-      <c r="H342" s="55"/>
-      <c r="I342" s="55"/>
+      <c r="C342" s="54"/>
+      <c r="D342" s="54"/>
+      <c r="E342" s="54"/>
+      <c r="F342" s="54"/>
+      <c r="G342" s="54"/>
+      <c r="H342" s="54"/>
+      <c r="I342" s="54"/>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="41"/>
       <c r="B343" s="41"/>
-      <c r="C343" s="55"/>
-      <c r="D343" s="55"/>
-      <c r="E343" s="55"/>
-      <c r="F343" s="55"/>
-      <c r="G343" s="55"/>
-      <c r="H343" s="55"/>
-      <c r="I343" s="55"/>
+      <c r="C343" s="54"/>
+      <c r="D343" s="54"/>
+      <c r="E343" s="54"/>
+      <c r="F343" s="54"/>
+      <c r="G343" s="54"/>
+      <c r="H343" s="54"/>
+      <c r="I343" s="54"/>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="41"/>
       <c r="B344" s="41"/>
-      <c r="C344" s="55"/>
-      <c r="D344" s="55"/>
-      <c r="E344" s="55"/>
-      <c r="F344" s="55"/>
-      <c r="G344" s="55"/>
-      <c r="H344" s="55"/>
-      <c r="I344" s="55"/>
+      <c r="C344" s="54"/>
+      <c r="D344" s="54"/>
+      <c r="E344" s="54"/>
+      <c r="F344" s="54"/>
+      <c r="G344" s="54"/>
+      <c r="H344" s="54"/>
+      <c r="I344" s="54"/>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="41"/>
       <c r="B345" s="41"/>
-      <c r="C345" s="55"/>
-      <c r="D345" s="55"/>
-      <c r="E345" s="55"/>
-      <c r="F345" s="55"/>
-      <c r="G345" s="55"/>
-      <c r="H345" s="55"/>
-      <c r="I345" s="55"/>
+      <c r="C345" s="54"/>
+      <c r="D345" s="54"/>
+      <c r="E345" s="54"/>
+      <c r="F345" s="54"/>
+      <c r="G345" s="54"/>
+      <c r="H345" s="54"/>
+      <c r="I345" s="54"/>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="41"/>
       <c r="B346" s="41"/>
-      <c r="C346" s="55"/>
-      <c r="D346" s="55"/>
-      <c r="E346" s="55"/>
-      <c r="F346" s="55"/>
-      <c r="G346" s="55"/>
-      <c r="H346" s="55"/>
-      <c r="I346" s="55"/>
+      <c r="C346" s="54"/>
+      <c r="D346" s="54"/>
+      <c r="E346" s="54"/>
+      <c r="F346" s="54"/>
+      <c r="G346" s="54"/>
+      <c r="H346" s="54"/>
+      <c r="I346" s="54"/>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="41"/>
       <c r="B347" s="41"/>
-      <c r="C347" s="55"/>
-      <c r="D347" s="55"/>
-      <c r="E347" s="55"/>
-      <c r="F347" s="55"/>
-      <c r="G347" s="55"/>
-      <c r="H347" s="55"/>
-      <c r="I347" s="55"/>
+      <c r="C347" s="54"/>
+      <c r="D347" s="54"/>
+      <c r="E347" s="54"/>
+      <c r="F347" s="54"/>
+      <c r="G347" s="54"/>
+      <c r="H347" s="54"/>
+      <c r="I347" s="54"/>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="41"/>
       <c r="B348" s="41"/>
-      <c r="C348" s="55"/>
-      <c r="D348" s="55"/>
-      <c r="E348" s="55"/>
-      <c r="F348" s="55"/>
-      <c r="G348" s="55"/>
-      <c r="H348" s="55"/>
-      <c r="I348" s="55"/>
+      <c r="C348" s="54"/>
+      <c r="D348" s="54"/>
+      <c r="E348" s="54"/>
+      <c r="F348" s="54"/>
+      <c r="G348" s="54"/>
+      <c r="H348" s="54"/>
+      <c r="I348" s="54"/>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="41"/>
       <c r="B349" s="41"/>
-      <c r="C349" s="55"/>
-      <c r="D349" s="55"/>
-      <c r="E349" s="55"/>
-      <c r="F349" s="55"/>
-      <c r="G349" s="55"/>
-      <c r="H349" s="55"/>
-      <c r="I349" s="55"/>
+      <c r="C349" s="54"/>
+      <c r="D349" s="54"/>
+      <c r="E349" s="54"/>
+      <c r="F349" s="54"/>
+      <c r="G349" s="54"/>
+      <c r="H349" s="54"/>
+      <c r="I349" s="54"/>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="41"/>
       <c r="B350" s="41"/>
-      <c r="C350" s="55"/>
-      <c r="D350" s="55"/>
-      <c r="E350" s="55"/>
-      <c r="F350" s="55"/>
-      <c r="G350" s="55"/>
-      <c r="H350" s="55"/>
-      <c r="I350" s="55"/>
+      <c r="C350" s="54"/>
+      <c r="D350" s="54"/>
+      <c r="E350" s="54"/>
+      <c r="F350" s="54"/>
+      <c r="G350" s="54"/>
+      <c r="H350" s="54"/>
+      <c r="I350" s="54"/>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="41"/>
       <c r="B351" s="41"/>
-      <c r="C351" s="55"/>
-      <c r="D351" s="55"/>
-      <c r="E351" s="55"/>
-      <c r="F351" s="55"/>
-      <c r="G351" s="55"/>
-      <c r="H351" s="55"/>
-      <c r="I351" s="55"/>
+      <c r="C351" s="54"/>
+      <c r="D351" s="54"/>
+      <c r="E351" s="54"/>
+      <c r="F351" s="54"/>
+      <c r="G351" s="54"/>
+      <c r="H351" s="54"/>
+      <c r="I351" s="54"/>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="41"/>
       <c r="B352" s="41"/>
-      <c r="C352" s="55"/>
-      <c r="D352" s="55"/>
-      <c r="E352" s="55"/>
-      <c r="F352" s="55"/>
-      <c r="G352" s="55"/>
-      <c r="H352" s="55"/>
-      <c r="I352" s="55"/>
+      <c r="C352" s="54"/>
+      <c r="D352" s="54"/>
+      <c r="E352" s="54"/>
+      <c r="F352" s="54"/>
+      <c r="G352" s="54"/>
+      <c r="H352" s="54"/>
+      <c r="I352" s="54"/>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="41"/>
       <c r="B353" s="41"/>
-      <c r="C353" s="55"/>
-      <c r="D353" s="55"/>
-      <c r="E353" s="55"/>
-      <c r="F353" s="55"/>
-      <c r="G353" s="55"/>
-      <c r="H353" s="55"/>
-      <c r="I353" s="55"/>
+      <c r="C353" s="54"/>
+      <c r="D353" s="54"/>
+      <c r="E353" s="54"/>
+      <c r="F353" s="54"/>
+      <c r="G353" s="54"/>
+      <c r="H353" s="54"/>
+      <c r="I353" s="54"/>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="41"/>
       <c r="B354" s="41"/>
-      <c r="C354" s="55"/>
-      <c r="D354" s="55"/>
-      <c r="E354" s="55"/>
-      <c r="F354" s="55"/>
-      <c r="G354" s="55"/>
-      <c r="H354" s="55"/>
-      <c r="I354" s="55"/>
+      <c r="C354" s="54"/>
+      <c r="D354" s="54"/>
+      <c r="E354" s="54"/>
+      <c r="F354" s="54"/>
+      <c r="G354" s="54"/>
+      <c r="H354" s="54"/>
+      <c r="I354" s="54"/>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="41"/>
       <c r="B355" s="41"/>
-      <c r="C355" s="55"/>
-      <c r="D355" s="55"/>
-      <c r="E355" s="55"/>
-      <c r="F355" s="55"/>
-      <c r="G355" s="55"/>
-      <c r="H355" s="55"/>
-      <c r="I355" s="55"/>
+      <c r="C355" s="54"/>
+      <c r="D355" s="54"/>
+      <c r="E355" s="54"/>
+      <c r="F355" s="54"/>
+      <c r="G355" s="54"/>
+      <c r="H355" s="54"/>
+      <c r="I355" s="54"/>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="41"/>
       <c r="B356" s="41"/>
-      <c r="C356" s="55"/>
-      <c r="D356" s="55"/>
-      <c r="E356" s="55"/>
-      <c r="F356" s="55"/>
-      <c r="G356" s="55"/>
-      <c r="H356" s="55"/>
-      <c r="I356" s="55"/>
+      <c r="C356" s="54"/>
+      <c r="D356" s="54"/>
+      <c r="E356" s="54"/>
+      <c r="F356" s="54"/>
+      <c r="G356" s="54"/>
+      <c r="H356" s="54"/>
+      <c r="I356" s="54"/>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="41"/>
       <c r="B357" s="41"/>
-      <c r="C357" s="55"/>
-      <c r="D357" s="55"/>
-      <c r="E357" s="55"/>
-      <c r="F357" s="55"/>
-      <c r="G357" s="55"/>
-      <c r="H357" s="55"/>
-      <c r="I357" s="55"/>
+      <c r="C357" s="54"/>
+      <c r="D357" s="54"/>
+      <c r="E357" s="54"/>
+      <c r="F357" s="54"/>
+      <c r="G357" s="54"/>
+      <c r="H357" s="54"/>
+      <c r="I357" s="54"/>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="41"/>
       <c r="B358" s="41"/>
-      <c r="C358" s="55"/>
-      <c r="D358" s="55"/>
-      <c r="E358" s="55"/>
-      <c r="F358" s="55"/>
-      <c r="G358" s="55"/>
-      <c r="H358" s="55"/>
-      <c r="I358" s="55"/>
+      <c r="C358" s="54"/>
+      <c r="D358" s="54"/>
+      <c r="E358" s="54"/>
+      <c r="F358" s="54"/>
+      <c r="G358" s="54"/>
+      <c r="H358" s="54"/>
+      <c r="I358" s="54"/>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="41"/>
       <c r="B359" s="41"/>
-      <c r="C359" s="55"/>
-      <c r="D359" s="55"/>
-      <c r="E359" s="55"/>
-      <c r="F359" s="55"/>
-      <c r="G359" s="55"/>
-      <c r="H359" s="55"/>
-      <c r="I359" s="55"/>
+      <c r="C359" s="54"/>
+      <c r="D359" s="54"/>
+      <c r="E359" s="54"/>
+      <c r="F359" s="54"/>
+      <c r="G359" s="54"/>
+      <c r="H359" s="54"/>
+      <c r="I359" s="54"/>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="41"/>
       <c r="B360" s="41"/>
-      <c r="C360" s="55"/>
-      <c r="D360" s="55"/>
-      <c r="E360" s="55"/>
-      <c r="F360" s="55"/>
-      <c r="G360" s="55"/>
-      <c r="H360" s="55"/>
-      <c r="I360" s="55"/>
+      <c r="C360" s="54"/>
+      <c r="D360" s="54"/>
+      <c r="E360" s="54"/>
+      <c r="F360" s="54"/>
+      <c r="G360" s="54"/>
+      <c r="H360" s="54"/>
+      <c r="I360" s="54"/>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="41"/>
       <c r="B361" s="41"/>
-      <c r="C361" s="55"/>
-      <c r="D361" s="55"/>
-      <c r="E361" s="55"/>
-      <c r="F361" s="55"/>
-      <c r="G361" s="55"/>
-      <c r="H361" s="55"/>
-      <c r="I361" s="55"/>
+      <c r="C361" s="54"/>
+      <c r="D361" s="54"/>
+      <c r="E361" s="54"/>
+      <c r="F361" s="54"/>
+      <c r="G361" s="54"/>
+      <c r="H361" s="54"/>
+      <c r="I361" s="54"/>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="41"/>
       <c r="B362" s="41"/>
-      <c r="C362" s="55"/>
-      <c r="D362" s="55"/>
-      <c r="E362" s="55"/>
-      <c r="F362" s="55"/>
-      <c r="G362" s="55"/>
-      <c r="H362" s="55"/>
-      <c r="I362" s="55"/>
+      <c r="C362" s="54"/>
+      <c r="D362" s="54"/>
+      <c r="E362" s="54"/>
+      <c r="F362" s="54"/>
+      <c r="G362" s="54"/>
+      <c r="H362" s="54"/>
+      <c r="I362" s="54"/>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="41"/>
       <c r="B363" s="41"/>
-      <c r="C363" s="55"/>
-      <c r="D363" s="55"/>
-      <c r="E363" s="55"/>
-      <c r="F363" s="55"/>
-      <c r="G363" s="55"/>
-      <c r="H363" s="55"/>
-      <c r="I363" s="55"/>
+      <c r="C363" s="54"/>
+      <c r="D363" s="54"/>
+      <c r="E363" s="54"/>
+      <c r="F363" s="54"/>
+      <c r="G363" s="54"/>
+      <c r="H363" s="54"/>
+      <c r="I363" s="54"/>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="41"/>
       <c r="B364" s="41"/>
-      <c r="C364" s="55"/>
-      <c r="D364" s="55"/>
-      <c r="E364" s="55"/>
-      <c r="F364" s="55"/>
-      <c r="G364" s="55"/>
-      <c r="H364" s="55"/>
-      <c r="I364" s="55"/>
+      <c r="C364" s="54"/>
+      <c r="D364" s="54"/>
+      <c r="E364" s="54"/>
+      <c r="F364" s="54"/>
+      <c r="G364" s="54"/>
+      <c r="H364" s="54"/>
+      <c r="I364" s="54"/>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="41"/>
       <c r="B365" s="41"/>
-      <c r="C365" s="55"/>
-      <c r="D365" s="55"/>
-      <c r="E365" s="55"/>
-      <c r="F365" s="55"/>
-      <c r="G365" s="55"/>
-      <c r="H365" s="55"/>
-      <c r="I365" s="55"/>
+      <c r="C365" s="54"/>
+      <c r="D365" s="54"/>
+      <c r="E365" s="54"/>
+      <c r="F365" s="54"/>
+      <c r="G365" s="54"/>
+      <c r="H365" s="54"/>
+      <c r="I365" s="54"/>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="41"/>
       <c r="B366" s="41"/>
-      <c r="C366" s="55"/>
-      <c r="D366" s="55"/>
-      <c r="E366" s="55"/>
-      <c r="F366" s="55"/>
-      <c r="G366" s="55"/>
-      <c r="H366" s="55"/>
-      <c r="I366" s="55"/>
+      <c r="C366" s="54"/>
+      <c r="D366" s="54"/>
+      <c r="E366" s="54"/>
+      <c r="F366" s="54"/>
+      <c r="G366" s="54"/>
+      <c r="H366" s="54"/>
+      <c r="I366" s="54"/>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="41"/>
       <c r="B367" s="41"/>
-      <c r="C367" s="55"/>
-      <c r="D367" s="55"/>
-      <c r="E367" s="55"/>
-      <c r="F367" s="55"/>
-      <c r="G367" s="55"/>
-      <c r="H367" s="55"/>
-      <c r="I367" s="55"/>
+      <c r="C367" s="54"/>
+      <c r="D367" s="54"/>
+      <c r="E367" s="54"/>
+      <c r="F367" s="54"/>
+      <c r="G367" s="54"/>
+      <c r="H367" s="54"/>
+      <c r="I367" s="54"/>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="41"/>
       <c r="B368" s="41"/>
-      <c r="C368" s="55"/>
-      <c r="D368" s="55"/>
-      <c r="E368" s="55"/>
-      <c r="F368" s="55"/>
-      <c r="G368" s="55"/>
-      <c r="H368" s="55"/>
-      <c r="I368" s="55"/>
+      <c r="C368" s="54"/>
+      <c r="D368" s="54"/>
+      <c r="E368" s="54"/>
+      <c r="F368" s="54"/>
+      <c r="G368" s="54"/>
+      <c r="H368" s="54"/>
+      <c r="I368" s="54"/>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="41"/>
       <c r="B369" s="41"/>
-      <c r="C369" s="55"/>
-      <c r="D369" s="55"/>
-      <c r="E369" s="55"/>
-      <c r="F369" s="55"/>
-      <c r="G369" s="55"/>
-      <c r="H369" s="55"/>
-      <c r="I369" s="55"/>
+      <c r="C369" s="54"/>
+      <c r="D369" s="54"/>
+      <c r="E369" s="54"/>
+      <c r="F369" s="54"/>
+      <c r="G369" s="54"/>
+      <c r="H369" s="54"/>
+      <c r="I369" s="54"/>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="41"/>
       <c r="B370" s="41"/>
-      <c r="C370" s="55"/>
-      <c r="D370" s="55"/>
-      <c r="E370" s="55"/>
-      <c r="F370" s="55"/>
-      <c r="G370" s="55"/>
-      <c r="H370" s="55"/>
-      <c r="I370" s="55"/>
+      <c r="C370" s="54"/>
+      <c r="D370" s="54"/>
+      <c r="E370" s="54"/>
+      <c r="F370" s="54"/>
+      <c r="G370" s="54"/>
+      <c r="H370" s="54"/>
+      <c r="I370" s="54"/>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="41"/>
       <c r="B371" s="41"/>
-      <c r="C371" s="55"/>
-      <c r="D371" s="55"/>
-      <c r="E371" s="55"/>
-      <c r="F371" s="55"/>
-      <c r="G371" s="55"/>
-      <c r="H371" s="55"/>
-      <c r="I371" s="55"/>
+      <c r="C371" s="54"/>
+      <c r="D371" s="54"/>
+      <c r="E371" s="54"/>
+      <c r="F371" s="54"/>
+      <c r="G371" s="54"/>
+      <c r="H371" s="54"/>
+      <c r="I371" s="54"/>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="41"/>
       <c r="B372" s="41"/>
-      <c r="C372" s="55"/>
-      <c r="D372" s="55"/>
-      <c r="E372" s="55"/>
-      <c r="F372" s="55"/>
-      <c r="G372" s="55"/>
-      <c r="H372" s="55"/>
-      <c r="I372" s="55"/>
+      <c r="C372" s="54"/>
+      <c r="D372" s="54"/>
+      <c r="E372" s="54"/>
+      <c r="F372" s="54"/>
+      <c r="G372" s="54"/>
+      <c r="H372" s="54"/>
+      <c r="I372" s="54"/>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="41"/>
       <c r="B373" s="41"/>
-      <c r="C373" s="55"/>
-      <c r="D373" s="55"/>
-      <c r="E373" s="55"/>
-      <c r="F373" s="55"/>
-      <c r="G373" s="55"/>
-      <c r="H373" s="55"/>
-      <c r="I373" s="55"/>
+      <c r="C373" s="54"/>
+      <c r="D373" s="54"/>
+      <c r="E373" s="54"/>
+      <c r="F373" s="54"/>
+      <c r="G373" s="54"/>
+      <c r="H373" s="54"/>
+      <c r="I373" s="54"/>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="41"/>
       <c r="B374" s="41"/>
-      <c r="C374" s="55"/>
-      <c r="D374" s="55"/>
-      <c r="E374" s="55"/>
-      <c r="F374" s="55"/>
-      <c r="G374" s="55"/>
-      <c r="H374" s="55"/>
-      <c r="I374" s="55"/>
+      <c r="C374" s="54"/>
+      <c r="D374" s="54"/>
+      <c r="E374" s="54"/>
+      <c r="F374" s="54"/>
+      <c r="G374" s="54"/>
+      <c r="H374" s="54"/>
+      <c r="I374" s="54"/>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="41"/>
       <c r="B375" s="41"/>
-      <c r="C375" s="55"/>
-      <c r="D375" s="55"/>
-      <c r="E375" s="55"/>
-      <c r="F375" s="55"/>
-      <c r="G375" s="55"/>
-      <c r="H375" s="55"/>
-      <c r="I375" s="55"/>
+      <c r="C375" s="54"/>
+      <c r="D375" s="54"/>
+      <c r="E375" s="54"/>
+      <c r="F375" s="54"/>
+      <c r="G375" s="54"/>
+      <c r="H375" s="54"/>
+      <c r="I375" s="54"/>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="41"/>
       <c r="B376" s="41"/>
-      <c r="C376" s="55"/>
-      <c r="D376" s="55"/>
-      <c r="E376" s="55"/>
-      <c r="F376" s="55"/>
-      <c r="G376" s="55"/>
-      <c r="H376" s="55"/>
-      <c r="I376" s="55"/>
+      <c r="C376" s="54"/>
+      <c r="D376" s="54"/>
+      <c r="E376" s="54"/>
+      <c r="F376" s="54"/>
+      <c r="G376" s="54"/>
+      <c r="H376" s="54"/>
+      <c r="I376" s="54"/>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="41"/>
       <c r="B377" s="41"/>
-      <c r="C377" s="55"/>
-      <c r="D377" s="55"/>
-      <c r="E377" s="55"/>
-      <c r="F377" s="55"/>
-      <c r="G377" s="55"/>
-      <c r="H377" s="55"/>
-      <c r="I377" s="55"/>
+      <c r="C377" s="54"/>
+      <c r="D377" s="54"/>
+      <c r="E377" s="54"/>
+      <c r="F377" s="54"/>
+      <c r="G377" s="54"/>
+      <c r="H377" s="54"/>
+      <c r="I377" s="54"/>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="41"/>
       <c r="B378" s="41"/>
-      <c r="C378" s="55"/>
-      <c r="D378" s="55"/>
-      <c r="E378" s="55"/>
-      <c r="F378" s="55"/>
-      <c r="G378" s="55"/>
-      <c r="H378" s="55"/>
-      <c r="I378" s="55"/>
+      <c r="C378" s="54"/>
+      <c r="D378" s="54"/>
+      <c r="E378" s="54"/>
+      <c r="F378" s="54"/>
+      <c r="G378" s="54"/>
+      <c r="H378" s="54"/>
+      <c r="I378" s="54"/>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="41"/>
       <c r="B379" s="41"/>
-      <c r="C379" s="55"/>
-      <c r="D379" s="55"/>
-      <c r="E379" s="55"/>
-      <c r="F379" s="55"/>
-      <c r="G379" s="55"/>
-      <c r="H379" s="55"/>
-      <c r="I379" s="55"/>
+      <c r="C379" s="54"/>
+      <c r="D379" s="54"/>
+      <c r="E379" s="54"/>
+      <c r="F379" s="54"/>
+      <c r="G379" s="54"/>
+      <c r="H379" s="54"/>
+      <c r="I379" s="54"/>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="41"/>
       <c r="B380" s="41"/>
-      <c r="C380" s="55"/>
-      <c r="D380" s="55"/>
-      <c r="E380" s="55"/>
-      <c r="F380" s="55"/>
-      <c r="G380" s="55"/>
-      <c r="H380" s="55"/>
-      <c r="I380" s="55"/>
+      <c r="C380" s="54"/>
+      <c r="D380" s="54"/>
+      <c r="E380" s="54"/>
+      <c r="F380" s="54"/>
+      <c r="G380" s="54"/>
+      <c r="H380" s="54"/>
+      <c r="I380" s="54"/>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="41"/>
       <c r="B381" s="41"/>
-      <c r="C381" s="55"/>
-      <c r="D381" s="55"/>
-      <c r="E381" s="55"/>
-      <c r="F381" s="55"/>
-      <c r="G381" s="55"/>
-      <c r="H381" s="55"/>
-      <c r="I381" s="55"/>
+      <c r="C381" s="54"/>
+      <c r="D381" s="54"/>
+      <c r="E381" s="54"/>
+      <c r="F381" s="54"/>
+      <c r="G381" s="54"/>
+      <c r="H381" s="54"/>
+      <c r="I381" s="54"/>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="41"/>
       <c r="B382" s="41"/>
-      <c r="C382" s="55"/>
-      <c r="D382" s="55"/>
-      <c r="E382" s="55"/>
-      <c r="F382" s="55"/>
-      <c r="G382" s="55"/>
-      <c r="H382" s="55"/>
-      <c r="I382" s="55"/>
+      <c r="C382" s="54"/>
+      <c r="D382" s="54"/>
+      <c r="E382" s="54"/>
+      <c r="F382" s="54"/>
+      <c r="G382" s="54"/>
+      <c r="H382" s="54"/>
+      <c r="I382" s="54"/>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="41"/>
       <c r="B383" s="41"/>
-      <c r="C383" s="55"/>
-      <c r="D383" s="55"/>
-      <c r="E383" s="55"/>
-      <c r="F383" s="55"/>
-      <c r="G383" s="55"/>
-      <c r="H383" s="55"/>
-      <c r="I383" s="55"/>
+      <c r="C383" s="54"/>
+      <c r="D383" s="54"/>
+      <c r="E383" s="54"/>
+      <c r="F383" s="54"/>
+      <c r="G383" s="54"/>
+      <c r="H383" s="54"/>
+      <c r="I383" s="54"/>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="41"/>
       <c r="B384" s="41"/>
-      <c r="C384" s="55"/>
-      <c r="D384" s="55"/>
-      <c r="E384" s="55"/>
-      <c r="F384" s="55"/>
-      <c r="G384" s="55"/>
-      <c r="H384" s="55"/>
-      <c r="I384" s="55"/>
+      <c r="C384" s="54"/>
+      <c r="D384" s="54"/>
+      <c r="E384" s="54"/>
+      <c r="F384" s="54"/>
+      <c r="G384" s="54"/>
+      <c r="H384" s="54"/>
+      <c r="I384" s="54"/>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="41"/>
       <c r="B385" s="41"/>
-      <c r="C385" s="55"/>
-      <c r="D385" s="55"/>
-      <c r="E385" s="55"/>
-      <c r="F385" s="55"/>
-      <c r="G385" s="55"/>
-      <c r="H385" s="55"/>
-      <c r="I385" s="55"/>
+      <c r="C385" s="54"/>
+      <c r="D385" s="54"/>
+      <c r="E385" s="54"/>
+      <c r="F385" s="54"/>
+      <c r="G385" s="54"/>
+      <c r="H385" s="54"/>
+      <c r="I385" s="54"/>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="41"/>
       <c r="B386" s="41"/>
-      <c r="C386" s="55"/>
-      <c r="D386" s="55"/>
-      <c r="E386" s="55"/>
-      <c r="F386" s="55"/>
-      <c r="G386" s="55"/>
-      <c r="H386" s="55"/>
-      <c r="I386" s="55"/>
+      <c r="C386" s="54"/>
+      <c r="D386" s="54"/>
+      <c r="E386" s="54"/>
+      <c r="F386" s="54"/>
+      <c r="G386" s="54"/>
+      <c r="H386" s="54"/>
+      <c r="I386" s="54"/>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="41"/>
       <c r="B387" s="41"/>
-      <c r="C387" s="55"/>
-      <c r="D387" s="55"/>
-      <c r="E387" s="55"/>
-      <c r="F387" s="55"/>
-      <c r="G387" s="55"/>
-      <c r="H387" s="55"/>
-      <c r="I387" s="55"/>
+      <c r="C387" s="54"/>
+      <c r="D387" s="54"/>
+      <c r="E387" s="54"/>
+      <c r="F387" s="54"/>
+      <c r="G387" s="54"/>
+      <c r="H387" s="54"/>
+      <c r="I387" s="54"/>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="41"/>
       <c r="B388" s="41"/>
-      <c r="C388" s="55"/>
-      <c r="D388" s="55"/>
-      <c r="E388" s="55"/>
-      <c r="F388" s="55"/>
-      <c r="G388" s="55"/>
-      <c r="H388" s="55"/>
-      <c r="I388" s="55"/>
+      <c r="C388" s="54"/>
+      <c r="D388" s="54"/>
+      <c r="E388" s="54"/>
+      <c r="F388" s="54"/>
+      <c r="G388" s="54"/>
+      <c r="H388" s="54"/>
+      <c r="I388" s="54"/>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="41"/>
       <c r="B389" s="41"/>
-      <c r="C389" s="55"/>
-      <c r="D389" s="55"/>
-      <c r="E389" s="55"/>
-      <c r="F389" s="55"/>
-      <c r="G389" s="55"/>
-      <c r="H389" s="55"/>
-      <c r="I389" s="55"/>
+      <c r="C389" s="54"/>
+      <c r="D389" s="54"/>
+      <c r="E389" s="54"/>
+      <c r="F389" s="54"/>
+      <c r="G389" s="54"/>
+      <c r="H389" s="54"/>
+      <c r="I389" s="54"/>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="41"/>
       <c r="B390" s="41"/>
-      <c r="C390" s="55"/>
-      <c r="D390" s="55"/>
-      <c r="E390" s="55"/>
-      <c r="F390" s="55"/>
-      <c r="G390" s="55"/>
-      <c r="H390" s="55"/>
-      <c r="I390" s="55"/>
+      <c r="C390" s="54"/>
+      <c r="D390" s="54"/>
+      <c r="E390" s="54"/>
+      <c r="F390" s="54"/>
+      <c r="G390" s="54"/>
+      <c r="H390" s="54"/>
+      <c r="I390" s="54"/>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="41"/>
       <c r="B391" s="41"/>
-      <c r="C391" s="55"/>
-      <c r="D391" s="55"/>
-      <c r="E391" s="55"/>
-      <c r="F391" s="55"/>
-      <c r="G391" s="55"/>
-      <c r="H391" s="55"/>
-      <c r="I391" s="55"/>
+      <c r="C391" s="54"/>
+      <c r="D391" s="54"/>
+      <c r="E391" s="54"/>
+      <c r="F391" s="54"/>
+      <c r="G391" s="54"/>
+      <c r="H391" s="54"/>
+      <c r="I391" s="54"/>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="41"/>
       <c r="B392" s="41"/>
-      <c r="C392" s="55"/>
-      <c r="D392" s="55"/>
-      <c r="E392" s="55"/>
-      <c r="F392" s="55"/>
-      <c r="G392" s="55"/>
-      <c r="H392" s="55"/>
-      <c r="I392" s="55"/>
+      <c r="C392" s="54"/>
+      <c r="D392" s="54"/>
+      <c r="E392" s="54"/>
+      <c r="F392" s="54"/>
+      <c r="G392" s="54"/>
+      <c r="H392" s="54"/>
+      <c r="I392" s="54"/>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="41"/>
       <c r="B393" s="41"/>
-      <c r="C393" s="55"/>
-      <c r="D393" s="55"/>
-      <c r="E393" s="55"/>
-      <c r="F393" s="55"/>
-      <c r="G393" s="55"/>
-      <c r="H393" s="55"/>
-      <c r="I393" s="55"/>
+      <c r="C393" s="54"/>
+      <c r="D393" s="54"/>
+      <c r="E393" s="54"/>
+      <c r="F393" s="54"/>
+      <c r="G393" s="54"/>
+      <c r="H393" s="54"/>
+      <c r="I393" s="54"/>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="41"/>
       <c r="B394" s="41"/>
-      <c r="C394" s="55"/>
-      <c r="D394" s="55"/>
-      <c r="E394" s="55"/>
-      <c r="F394" s="55"/>
-      <c r="G394" s="55"/>
-      <c r="H394" s="55"/>
-      <c r="I394" s="55"/>
+      <c r="C394" s="54"/>
+      <c r="D394" s="54"/>
+      <c r="E394" s="54"/>
+      <c r="F394" s="54"/>
+      <c r="G394" s="54"/>
+      <c r="H394" s="54"/>
+      <c r="I394" s="54"/>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="41"/>
       <c r="B395" s="41"/>
-      <c r="C395" s="55"/>
-      <c r="D395" s="55"/>
-      <c r="E395" s="55"/>
-      <c r="F395" s="55"/>
-      <c r="G395" s="55"/>
-      <c r="H395" s="55"/>
-      <c r="I395" s="55"/>
+      <c r="C395" s="54"/>
+      <c r="D395" s="54"/>
+      <c r="E395" s="54"/>
+      <c r="F395" s="54"/>
+      <c r="G395" s="54"/>
+      <c r="H395" s="54"/>
+      <c r="I395" s="54"/>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="41"/>
       <c r="B396" s="41"/>
-      <c r="C396" s="55"/>
-      <c r="D396" s="55"/>
-      <c r="E396" s="55"/>
-      <c r="F396" s="55"/>
-      <c r="G396" s="55"/>
-      <c r="H396" s="55"/>
-      <c r="I396" s="55"/>
+      <c r="C396" s="54"/>
+      <c r="D396" s="54"/>
+      <c r="E396" s="54"/>
+      <c r="F396" s="54"/>
+      <c r="G396" s="54"/>
+      <c r="H396" s="54"/>
+      <c r="I396" s="54"/>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="41"/>
       <c r="B397" s="41"/>
-      <c r="C397" s="55"/>
-      <c r="D397" s="55"/>
-      <c r="E397" s="55"/>
-      <c r="F397" s="55"/>
-      <c r="G397" s="55"/>
-      <c r="H397" s="55"/>
-      <c r="I397" s="55"/>
+      <c r="C397" s="54"/>
+      <c r="D397" s="54"/>
+      <c r="E397" s="54"/>
+      <c r="F397" s="54"/>
+      <c r="G397" s="54"/>
+      <c r="H397" s="54"/>
+      <c r="I397" s="54"/>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="41"/>
       <c r="B398" s="41"/>
-      <c r="C398" s="55"/>
-      <c r="D398" s="55"/>
-      <c r="E398" s="55"/>
-      <c r="F398" s="55"/>
-      <c r="G398" s="55"/>
-      <c r="H398" s="55"/>
-      <c r="I398" s="55"/>
+      <c r="C398" s="54"/>
+      <c r="D398" s="54"/>
+      <c r="E398" s="54"/>
+      <c r="F398" s="54"/>
+      <c r="G398" s="54"/>
+      <c r="H398" s="54"/>
+      <c r="I398" s="54"/>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="41"/>
       <c r="B399" s="41"/>
-      <c r="C399" s="55"/>
-      <c r="D399" s="55"/>
-      <c r="E399" s="55"/>
-      <c r="F399" s="55"/>
-      <c r="G399" s="55"/>
-      <c r="H399" s="55"/>
-      <c r="I399" s="55"/>
+      <c r="C399" s="54"/>
+      <c r="D399" s="54"/>
+      <c r="E399" s="54"/>
+      <c r="F399" s="54"/>
+      <c r="G399" s="54"/>
+      <c r="H399" s="54"/>
+      <c r="I399" s="54"/>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="41"/>
       <c r="B400" s="41"/>
-      <c r="C400" s="55"/>
-      <c r="D400" s="55"/>
-      <c r="E400" s="55"/>
-      <c r="F400" s="55"/>
-      <c r="G400" s="55"/>
-      <c r="H400" s="55"/>
-      <c r="I400" s="55"/>
+      <c r="C400" s="54"/>
+      <c r="D400" s="54"/>
+      <c r="E400" s="54"/>
+      <c r="F400" s="54"/>
+      <c r="G400" s="54"/>
+      <c r="H400" s="54"/>
+      <c r="I400" s="54"/>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="41"/>
       <c r="B401" s="41"/>
-      <c r="C401" s="55"/>
-      <c r="D401" s="55"/>
-      <c r="E401" s="55"/>
-      <c r="F401" s="55"/>
-      <c r="G401" s="55"/>
-      <c r="H401" s="55"/>
-      <c r="I401" s="55"/>
+      <c r="C401" s="54"/>
+      <c r="D401" s="54"/>
+      <c r="E401" s="54"/>
+      <c r="F401" s="54"/>
+      <c r="G401" s="54"/>
+      <c r="H401" s="54"/>
+      <c r="I401" s="54"/>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="41"/>
       <c r="B402" s="41"/>
-      <c r="C402" s="55"/>
-      <c r="D402" s="55"/>
-      <c r="E402" s="55"/>
-      <c r="F402" s="55"/>
-      <c r="G402" s="55"/>
-      <c r="H402" s="55"/>
-      <c r="I402" s="55"/>
+      <c r="C402" s="54"/>
+      <c r="D402" s="54"/>
+      <c r="E402" s="54"/>
+      <c r="F402" s="54"/>
+      <c r="G402" s="54"/>
+      <c r="H402" s="54"/>
+      <c r="I402" s="54"/>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="41"/>
       <c r="B403" s="41"/>
-      <c r="C403" s="55"/>
-      <c r="D403" s="55"/>
-      <c r="E403" s="55"/>
-      <c r="F403" s="55"/>
-      <c r="G403" s="55"/>
-      <c r="H403" s="55"/>
-      <c r="I403" s="55"/>
+      <c r="C403" s="54"/>
+      <c r="D403" s="54"/>
+      <c r="E403" s="54"/>
+      <c r="F403" s="54"/>
+      <c r="G403" s="54"/>
+      <c r="H403" s="54"/>
+      <c r="I403" s="54"/>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="41"/>
       <c r="B404" s="41"/>
-      <c r="C404" s="55"/>
-      <c r="D404" s="55"/>
-      <c r="E404" s="55"/>
-      <c r="F404" s="55"/>
-      <c r="G404" s="55"/>
-      <c r="H404" s="55"/>
-      <c r="I404" s="55"/>
+      <c r="C404" s="54"/>
+      <c r="D404" s="54"/>
+      <c r="E404" s="54"/>
+      <c r="F404" s="54"/>
+      <c r="G404" s="54"/>
+      <c r="H404" s="54"/>
+      <c r="I404" s="54"/>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="41"/>
       <c r="B405" s="41"/>
-      <c r="C405" s="55"/>
-      <c r="D405" s="55"/>
-      <c r="E405" s="55"/>
-      <c r="F405" s="55"/>
-      <c r="G405" s="55"/>
-      <c r="H405" s="55"/>
-      <c r="I405" s="55"/>
+      <c r="C405" s="54"/>
+      <c r="D405" s="54"/>
+      <c r="E405" s="54"/>
+      <c r="F405" s="54"/>
+      <c r="G405" s="54"/>
+      <c r="H405" s="54"/>
+      <c r="I405" s="54"/>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="41"/>
       <c r="B406" s="41"/>
-      <c r="C406" s="55"/>
-      <c r="D406" s="55"/>
-      <c r="E406" s="55"/>
-      <c r="F406" s="55"/>
-      <c r="G406" s="55"/>
-      <c r="H406" s="55"/>
-      <c r="I406" s="55"/>
+      <c r="C406" s="54"/>
+      <c r="D406" s="54"/>
+      <c r="E406" s="54"/>
+      <c r="F406" s="54"/>
+      <c r="G406" s="54"/>
+      <c r="H406" s="54"/>
+      <c r="I406" s="54"/>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="41"/>
       <c r="B407" s="41"/>
-      <c r="C407" s="55"/>
-      <c r="D407" s="55"/>
-      <c r="E407" s="55"/>
-      <c r="F407" s="55"/>
-      <c r="G407" s="55"/>
-      <c r="H407" s="55"/>
-      <c r="I407" s="55"/>
+      <c r="C407" s="54"/>
+      <c r="D407" s="54"/>
+      <c r="E407" s="54"/>
+      <c r="F407" s="54"/>
+      <c r="G407" s="54"/>
+      <c r="H407" s="54"/>
+      <c r="I407" s="54"/>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="41"/>
       <c r="B408" s="41"/>
-      <c r="C408" s="55"/>
-      <c r="D408" s="55"/>
-      <c r="E408" s="55"/>
-      <c r="F408" s="55"/>
-      <c r="G408" s="55"/>
-      <c r="H408" s="55"/>
-      <c r="I408" s="55"/>
+      <c r="C408" s="54"/>
+      <c r="D408" s="54"/>
+      <c r="E408" s="54"/>
+      <c r="F408" s="54"/>
+      <c r="G408" s="54"/>
+      <c r="H408" s="54"/>
+      <c r="I408" s="54"/>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="41"/>
       <c r="B409" s="41"/>
-      <c r="C409" s="55"/>
-      <c r="D409" s="55"/>
-      <c r="E409" s="55"/>
-      <c r="F409" s="55"/>
-      <c r="G409" s="55"/>
-      <c r="H409" s="55"/>
-      <c r="I409" s="55"/>
+      <c r="C409" s="54"/>
+      <c r="D409" s="54"/>
+      <c r="E409" s="54"/>
+      <c r="F409" s="54"/>
+      <c r="G409" s="54"/>
+      <c r="H409" s="54"/>
+      <c r="I409" s="54"/>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="41"/>
       <c r="B410" s="41"/>
-      <c r="C410" s="55"/>
-      <c r="D410" s="55"/>
-      <c r="E410" s="55"/>
-      <c r="F410" s="55"/>
-      <c r="G410" s="55"/>
-      <c r="H410" s="55"/>
-      <c r="I410" s="55"/>
+      <c r="C410" s="54"/>
+      <c r="D410" s="54"/>
+      <c r="E410" s="54"/>
+      <c r="F410" s="54"/>
+      <c r="G410" s="54"/>
+      <c r="H410" s="54"/>
+      <c r="I410" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3004C8E2-8327-4524-9427-6D95AF7B9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D860B124-7750-4C88-8B2D-28AD119A6ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57600" yWindow="0" windowWidth="36750" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -901,9 +901,6 @@
     <t>vd-чр</t>
   </si>
   <si>
-    <t>vd-чс</t>
-  </si>
-  <si>
     <t>vd-р</t>
   </si>
   <si>
@@ -1217,6 +1214,9 @@
   </si>
   <si>
     <t>Число рождений "для Европейской России" напечатано 4,702,629, с учётом предыдущей поправки = 4,703,088</t>
+  </si>
+  <si>
+    <t>vd-чу</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1650,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="41" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -1785,7 +1785,7 @@
         <v>287</v>
       </c>
       <c r="AJ1" s="33" t="s">
-        <v>288</v>
+        <v>393</v>
       </c>
       <c r="AL1" s="33" t="s">
         <v>284</v>
@@ -1795,28 +1795,28 @@
       </c>
       <c r="AN1" s="42"/>
       <c r="AO1" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="AP1" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="AP1" s="33" t="s">
+      <c r="AR1" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="AR1" s="43" t="s">
+      <c r="AS1" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="AS1" s="43" t="s">
+      <c r="AT1" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="AT1" s="43" t="s">
+      <c r="AV1" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="AV1" s="43" t="s">
+      <c r="AW1" s="43" t="s">
         <v>294</v>
       </c>
-      <c r="AW1" s="43" t="s">
+      <c r="AX1" s="43" t="s">
         <v>295</v>
-      </c>
-      <c r="AX1" s="43" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.55000000000000004">
@@ -2026,7 +2026,7 @@
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B5" s="12">
         <f>885846-B8</f>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="37"/>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="37"/>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B8" s="19">
         <f>SUM(N8:O8)</f>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B11" s="6">
         <f>SUM(B5:B10)</f>
@@ -23441,28 +23441,28 @@
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="E1" s="53" t="s">
         <v>305</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>306</v>
       </c>
       <c r="F1" s="53"/>
       <c r="G1" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="I1" s="53" t="s">
         <v>308</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="54">
@@ -23487,7 +23487,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="54">
@@ -23512,7 +23512,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B4" s="41"/>
       <c r="C4" s="54">
@@ -23537,7 +23537,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="54">
@@ -23562,7 +23562,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B6" s="41"/>
       <c r="C6" s="54">
@@ -23587,7 +23587,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B7" s="41"/>
       <c r="C7" s="54">
@@ -23612,7 +23612,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="54">
@@ -23662,7 +23662,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10" s="41"/>
       <c r="C10" s="54">
@@ -23687,7 +23687,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="54">
@@ -23737,7 +23737,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" s="54">
@@ -23762,7 +23762,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B14" s="41"/>
       <c r="C14" s="54">
@@ -23787,7 +23787,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="54">
@@ -23812,7 +23812,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B16" s="41"/>
       <c r="C16" s="54">
@@ -23837,7 +23837,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="54">
@@ -23862,7 +23862,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="54">
@@ -23887,7 +23887,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="54">
@@ -23962,7 +23962,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="54">
@@ -24037,7 +24037,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="54">
@@ -24062,7 +24062,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B26" s="41"/>
       <c r="C26" s="54">
@@ -24087,7 +24087,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B27" s="41"/>
       <c r="C27" s="54">
@@ -24137,7 +24137,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B29" s="41"/>
       <c r="C29" s="54">
@@ -24162,7 +24162,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="54">
@@ -24187,7 +24187,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="54">
@@ -24212,7 +24212,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="41" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B32" s="41"/>
       <c r="C32" s="54">
@@ -24237,7 +24237,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="41" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B33" s="41"/>
       <c r="C33" s="54">
@@ -24262,7 +24262,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="41" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B34" s="41"/>
       <c r="C34" s="54">
@@ -24312,7 +24312,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B36" s="41"/>
       <c r="C36" s="54">
@@ -24337,7 +24337,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" s="41"/>
       <c r="C37" s="54">
@@ -24362,7 +24362,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B38" s="41"/>
       <c r="C38" s="54">
@@ -24387,7 +24387,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="54">
@@ -24412,7 +24412,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B40" s="41"/>
       <c r="C40" s="54">
@@ -24437,7 +24437,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="41" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B41" s="41"/>
       <c r="C41" s="54">
@@ -24462,7 +24462,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B42" s="41"/>
       <c r="C42" s="54">
@@ -24487,7 +24487,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="54">
@@ -24512,7 +24512,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B44" s="41"/>
       <c r="C44" s="54">
@@ -24537,7 +24537,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="54">
@@ -24637,7 +24637,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B49" s="41"/>
       <c r="C49" s="54">
@@ -24662,7 +24662,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B50" s="41"/>
       <c r="C50" s="54">
@@ -24687,7 +24687,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="54">
@@ -24712,7 +24712,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="54">
@@ -24737,7 +24737,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B53" s="41"/>
       <c r="C53" s="54">
@@ -24762,7 +24762,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B54" s="41"/>
       <c r="C54" s="54">
@@ -24912,7 +24912,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="41" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B60" s="41"/>
       <c r="C60" s="54">
@@ -25012,7 +25012,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B64" s="41"/>
       <c r="C64" s="54">
@@ -25037,7 +25037,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="54">
@@ -25062,7 +25062,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B66" s="41"/>
       <c r="C66" s="54">
@@ -25087,7 +25087,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="41" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="54">
@@ -25137,7 +25137,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="54">
@@ -25162,7 +25162,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="41" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="54">
@@ -25187,7 +25187,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="54">
@@ -25212,7 +25212,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B72" s="41"/>
       <c r="C72" s="54">
@@ -25237,32 +25237,32 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B73" s="41"/>
       <c r="C73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F73" s="56"/>
       <c r="G73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I73" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B74" s="41"/>
       <c r="C74" s="54">
@@ -25287,32 +25287,32 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B75" s="41"/>
       <c r="C75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F75" s="56"/>
       <c r="G75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I75" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B76" s="41"/>
       <c r="C76" s="54">
@@ -25337,7 +25337,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B77" s="41"/>
       <c r="C77" s="54">
@@ -25362,7 +25362,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="41" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="54">
@@ -25387,7 +25387,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="41" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B79" s="41"/>
       <c r="C79" s="54">
@@ -25412,7 +25412,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B80" s="41"/>
       <c r="C80" s="54">
@@ -25437,7 +25437,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B81" s="41"/>
       <c r="C81" s="54">
@@ -25462,7 +25462,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B82" s="41"/>
       <c r="C82" s="54">
@@ -25487,32 +25487,32 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B83" s="41"/>
       <c r="C83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F83" s="56"/>
       <c r="G83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I83" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B84" s="41"/>
       <c r="C84" s="54">
@@ -25537,7 +25537,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B85" s="41"/>
       <c r="C85" s="54">
@@ -25562,7 +25562,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="41" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B86" s="41"/>
       <c r="C86" s="54">
@@ -25587,24 +25587,24 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="41" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D87" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E87" s="54">
         <v>34.1</v>
       </c>
       <c r="F87" s="54"/>
       <c r="G87" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H87" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I87" s="54">
         <v>21.8</v>
@@ -25612,7 +25612,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="54">
@@ -25637,7 +25637,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B89" s="41"/>
       <c r="C89" s="54">
@@ -25662,7 +25662,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B90" s="41"/>
       <c r="C90" s="54">
@@ -25687,7 +25687,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B91" s="41"/>
       <c r="C91" s="54">
@@ -25712,7 +25712,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B92" s="41"/>
       <c r="C92" s="54">
@@ -25737,7 +25737,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B93" s="41"/>
       <c r="C93" s="54">
@@ -25762,27 +25762,27 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B94" s="41"/>
       <c r="C94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F94" s="56"/>
       <c r="G94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I94" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -25791,13 +25791,13 @@
       </c>
       <c r="B95" s="41"/>
       <c r="C95" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D95" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E95" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F95" s="56"/>
       <c r="G95" s="56"/>
@@ -25806,132 +25806,132 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="41" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B96" s="41"/>
       <c r="C96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F96" s="56"/>
       <c r="G96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I96" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="41" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F97" s="56"/>
       <c r="G97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I97" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="41" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I98" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="41" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B99" s="41"/>
       <c r="C99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I99" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="41" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B100" s="41"/>
       <c r="C100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I100" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="41" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B101" s="41"/>
       <c r="C101" s="54">
@@ -25941,7 +25941,7 @@
         <v>59.8</v>
       </c>
       <c r="E101" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F101" s="54"/>
       <c r="G101" s="54">
@@ -25951,12 +25951,12 @@
         <v>48.8</v>
       </c>
       <c r="I101" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="41" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B102" s="41"/>
       <c r="C102" s="54">
@@ -25966,7 +25966,7 @@
         <v>47.9</v>
       </c>
       <c r="E102" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F102" s="54"/>
       <c r="G102" s="54">
@@ -25976,12 +25976,12 @@
         <v>35</v>
       </c>
       <c r="I102" s="56" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="41" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B103" s="41"/>
       <c r="C103" s="54">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D860B124-7750-4C88-8B2D-28AD119A6ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EFFDBB-C25C-4F50-9895-72D534A65BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57600" yWindow="0" windowWidth="36750" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1296,6 +1296,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1316,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1478,6 +1484,15 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4074,7 +4089,7 @@
       </c>
       <c r="AF33" s="12">
         <f>SUM(N35:AB35)</f>
-        <v>42000</v>
+        <v>43587</v>
       </c>
       <c r="AG33" s="2"/>
       <c r="AH33" s="12">
@@ -4087,7 +4102,7 @@
       </c>
       <c r="AJ33" s="12">
         <f>AF33-D33</f>
-        <v>-1587</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="47">
         <f>C33/B33*1000</f>
@@ -4179,8 +4194,8 @@
       <c r="N35" s="2">
         <v>3690</v>
       </c>
-      <c r="O35" s="2">
-        <v>1626</v>
+      <c r="O35" s="59">
+        <v>3213</v>
       </c>
       <c r="P35" s="2">
         <v>7775</v>
@@ -4711,7 +4726,7 @@
       </c>
       <c r="AF42" s="23">
         <f>SUM(AF2:AF40)</f>
-        <v>576722</v>
+        <v>578309</v>
       </c>
       <c r="AG42" s="2"/>
       <c r="AH42" s="23">
@@ -4724,7 +4739,7 @@
       </c>
       <c r="AJ42" s="23">
         <f>AF42-D42</f>
-        <v>-1590</v>
+        <v>-3</v>
       </c>
       <c r="AL42" s="49">
         <f>C42/B42*1000</f>
@@ -8233,11 +8248,11 @@
       </c>
       <c r="AE88" s="12">
         <f>SUM(N89:AB89)</f>
-        <v>75911</v>
+        <v>77940</v>
       </c>
       <c r="AF88" s="12">
         <f>SUM(N90:AB90)</f>
-        <v>56493</v>
+        <v>58306</v>
       </c>
       <c r="AG88" s="2"/>
       <c r="AH88" s="12">
@@ -8246,11 +8261,11 @@
       </c>
       <c r="AI88" s="12">
         <f>AE88-C88</f>
-        <v>-2029</v>
+        <v>0</v>
       </c>
       <c r="AJ88" s="12">
         <f>AF88-D88</f>
-        <v>-1813</v>
+        <v>0</v>
       </c>
       <c r="AL88" s="47">
         <f>C88/B88*1000</f>
@@ -8324,8 +8339,8 @@
       <c r="V89" s="8">
         <v>7386</v>
       </c>
-      <c r="W89" s="8">
-        <v>2729</v>
+      <c r="W89" s="60">
+        <v>4758</v>
       </c>
       <c r="X89" s="8">
         <v>6218</v>
@@ -8390,8 +8405,8 @@
       <c r="V90" s="8">
         <v>6300</v>
       </c>
-      <c r="W90" s="8">
-        <v>1925</v>
+      <c r="W90" s="60">
+        <v>3738</v>
       </c>
       <c r="X90" s="8">
         <v>4423</v>
@@ -9675,8 +9690,8 @@
       <c r="C106" s="17">
         <v>57604</v>
       </c>
-      <c r="D106" s="17">
-        <v>48687</v>
+      <c r="D106" s="58">
+        <v>51846</v>
       </c>
       <c r="E106" s="17">
         <v>97057</v>
@@ -9764,7 +9779,7 @@
       </c>
       <c r="AJ106" s="12">
         <f>AF106-D106</f>
-        <v>3159</v>
+        <v>0</v>
       </c>
       <c r="AL106" s="47">
         <f>C106/B106*1000</f>
@@ -9772,7 +9787,7 @@
       </c>
       <c r="AM106" s="47">
         <f>D106/B106*1000</f>
-        <v>38.858360569383088</v>
+        <v>41.379640603862129</v>
       </c>
       <c r="AO106" s="47">
         <f>AL106-K106</f>
@@ -9780,7 +9795,7 @@
       </c>
       <c r="AP106" s="47">
         <f>AM106-L106</f>
-        <v>-4.1639430616911E-2</v>
+        <v>2.4796406038621299</v>
       </c>
       <c r="AR106" s="12">
         <f t="shared" ref="AR106" si="96">H106</f>
@@ -12753,8 +12768,8 @@
       <c r="C142" s="17">
         <v>92266</v>
       </c>
-      <c r="D142" s="17">
-        <v>66132</v>
+      <c r="D142" s="58">
+        <v>75420</v>
       </c>
       <c r="E142" s="17">
         <v>96679</v>
@@ -12827,11 +12842,11 @@
       </c>
       <c r="AE142" s="12">
         <f>SUM(N143:AB143)</f>
-        <v>87635</v>
+        <v>92266</v>
       </c>
       <c r="AF142" s="12">
         <f>SUM(N144:AB144)</f>
-        <v>70719</v>
+        <v>75420</v>
       </c>
       <c r="AG142" s="2"/>
       <c r="AH142" s="12">
@@ -12840,11 +12855,11 @@
       </c>
       <c r="AI142" s="12">
         <f>AE142-C142</f>
-        <v>-4631</v>
+        <v>0</v>
       </c>
       <c r="AJ142" s="12">
         <f>AF142-D142</f>
-        <v>4587</v>
+        <v>0</v>
       </c>
       <c r="AL142" s="47">
         <f>C142/B142*1000</f>
@@ -12852,7 +12867,7 @@
       </c>
       <c r="AM142" s="47">
         <f>D142/B142*1000</f>
-        <v>33.828494260634706</v>
+        <v>38.579583819286725</v>
       </c>
       <c r="AO142" s="47">
         <f>AL142-K142</f>
@@ -12860,7 +12875,7 @@
       </c>
       <c r="AP142" s="47">
         <f>AM142-L142</f>
-        <v>2.8494260634708724E-2</v>
+        <v>4.7795838192867279</v>
       </c>
       <c r="AR142" s="12">
         <f t="shared" ref="AR142" si="132">H142</f>
@@ -12924,8 +12939,8 @@
       <c r="X143" s="9">
         <v>9054</v>
       </c>
-      <c r="Y143" s="9">
-        <v>2524</v>
+      <c r="Y143" s="58">
+        <v>7155</v>
       </c>
       <c r="Z143" s="9"/>
       <c r="AA143" s="9"/>
@@ -12988,8 +13003,8 @@
       <c r="X144" s="9">
         <v>8565</v>
       </c>
-      <c r="Y144" s="9">
-        <v>1686</v>
+      <c r="Y144" s="58">
+        <v>6387</v>
       </c>
       <c r="Z144" s="9"/>
       <c r="AA144" s="9"/>
@@ -13737,7 +13752,7 @@
       </c>
       <c r="AF153" s="12">
         <f>SUM(N155:AB155)</f>
-        <v>91273</v>
+        <v>104926</v>
       </c>
       <c r="AG153" s="2"/>
       <c r="AH153" s="12">
@@ -13750,7 +13765,7 @@
       </c>
       <c r="AJ153" s="12">
         <f>AF153-D153</f>
-        <v>-13653</v>
+        <v>0</v>
       </c>
       <c r="AL153" s="47">
         <f>C153/B153*1000</f>
@@ -13860,8 +13875,8 @@
       <c r="N155" s="9">
         <v>13905</v>
       </c>
-      <c r="O155" s="9">
-        <v>1647</v>
+      <c r="O155" s="58">
+        <v>15300</v>
       </c>
       <c r="P155" s="9">
         <v>13571</v>
@@ -16870,11 +16885,11 @@
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
-        <v>3204543</v>
+        <v>3211203</v>
       </c>
       <c r="AF191" s="23">
         <f>SUM(AF85:AF190)</f>
-        <v>2358640</v>
+        <v>2378807</v>
       </c>
       <c r="AG191" s="2"/>
       <c r="AH191" s="23">
@@ -16883,11 +16898,11 @@
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="181"/>
-        <v>-7516</v>
+        <v>-856</v>
       </c>
       <c r="AJ191" s="23">
         <f t="shared" si="181"/>
-        <v>-10115</v>
+        <v>10052</v>
       </c>
       <c r="AL191" s="49">
         <f>C191/B191*1000</f>
@@ -17225,11 +17240,11 @@
       </c>
       <c r="AE195" s="23">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
-        <v>4695338</v>
+        <v>4701998</v>
       </c>
       <c r="AF195" s="23">
         <f>SUM(AF42, AF74, AF84, AF191, AF192)</f>
-        <v>3251564</v>
+        <v>3273318</v>
       </c>
       <c r="AG195" s="2"/>
       <c r="AH195" s="23">
@@ -17238,11 +17253,11 @@
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="186"/>
-        <v>-7291</v>
+        <v>-631</v>
       </c>
       <c r="AJ195" s="23">
         <f t="shared" si="186"/>
-        <v>-32244</v>
+        <v>-10490</v>
       </c>
       <c r="AL195" s="49">
         <f>C195/B195*1000</f>
@@ -23356,11 +23371,11 @@
       </c>
       <c r="AE275" s="23">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
-        <v>5341312</v>
+        <v>5347972</v>
       </c>
       <c r="AF275" s="23">
         <f>SUM(AF195, AF224, AF250, AF274)</f>
-        <v>3710870</v>
+        <v>3732624</v>
       </c>
       <c r="AG275" s="2"/>
       <c r="AH275" s="23">
@@ -23369,11 +23384,11 @@
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="246"/>
-        <v>-27897</v>
+        <v>-21237</v>
       </c>
       <c r="AJ275" s="23">
         <f t="shared" si="246"/>
-        <v>-46550</v>
+        <v>-24796</v>
       </c>
       <c r="AL275" s="49">
         <f>C275/B275*1000</f>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EFFDBB-C25C-4F50-9895-72D534A65BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85DD7F7-8E1A-4831-8C81-7189656BB7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -880,9 +880,6 @@
     <t>v-чр</t>
   </si>
   <si>
-    <t>v-чс</t>
-  </si>
-  <si>
     <t>р YY</t>
   </si>
   <si>
@@ -1217,6 +1214,9 @@
   </si>
   <si>
     <t>vd-чу</t>
+  </si>
+  <si>
+    <t>v-чу</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1482,9 +1482,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1493,6 +1490,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1665,7 +1668,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="41" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1673,7 +1676,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -1761,29 +1764,29 @@
         <v>9</v>
       </c>
       <c r="K1" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="L1" s="35" t="s">
-        <v>283</v>
-      </c>
       <c r="M1" s="26"/>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
       <c r="AD1" s="33" t="s">
         <v>279</v>
       </c>
@@ -1791,47 +1794,47 @@
         <v>280</v>
       </c>
       <c r="AF1" s="33" t="s">
-        <v>281</v>
+        <v>393</v>
       </c>
       <c r="AH1" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="AI1" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="AI1" s="34" t="s">
-        <v>287</v>
-      </c>
       <c r="AJ1" s="33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AL1" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="AM1" s="33" t="s">
         <v>284</v>
-      </c>
-      <c r="AM1" s="33" t="s">
-        <v>285</v>
       </c>
       <c r="AN1" s="42"/>
       <c r="AO1" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP1" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="AP1" s="33" t="s">
+      <c r="AR1" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="AR1" s="43" t="s">
+      <c r="AS1" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="AS1" s="43" t="s">
+      <c r="AT1" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="AT1" s="43" t="s">
+      <c r="AV1" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="AV1" s="43" t="s">
+      <c r="AW1" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="AW1" s="43" t="s">
+      <c r="AX1" s="43" t="s">
         <v>294</v>
-      </c>
-      <c r="AX1" s="43" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.55000000000000004">
@@ -2041,7 +2044,7 @@
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B5" s="12">
         <f>885846-B8</f>
@@ -2159,7 +2162,7 @@
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="37"/>
@@ -2197,7 +2200,7 @@
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="37"/>
@@ -2235,7 +2238,7 @@
     </row>
     <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B8" s="19">
         <f>SUM(N8:O8)</f>
@@ -2306,7 +2309,7 @@
     </row>
     <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -2350,7 +2353,7 @@
     </row>
     <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -2394,7 +2397,7 @@
     </row>
     <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B11" s="6">
         <f>SUM(B5:B10)</f>
@@ -4194,7 +4197,7 @@
       <c r="N35" s="2">
         <v>3690</v>
       </c>
-      <c r="O35" s="59">
+      <c r="O35" s="58">
         <v>3213</v>
       </c>
       <c r="P35" s="2">
@@ -4962,7 +4965,7 @@
       </c>
       <c r="AF44" s="12">
         <f>SUM(N46:AB46)</f>
-        <v>27120</v>
+        <v>26121</v>
       </c>
       <c r="AG44" s="2"/>
       <c r="AH44" s="12">
@@ -4975,7 +4978,7 @@
       </c>
       <c r="AJ44" s="12">
         <f>AF44-D44</f>
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="AL44" s="47">
         <f>C44/B44*1000</f>
@@ -5078,8 +5081,8 @@
       <c r="Q46" s="2">
         <v>2551</v>
       </c>
-      <c r="R46" s="2">
-        <v>2712</v>
+      <c r="R46" s="58">
+        <v>1713</v>
       </c>
       <c r="S46" s="2">
         <v>2146</v>
@@ -5828,7 +5831,7 @@
       </c>
       <c r="AF56" s="12">
         <f>SUM(N58:AB58)</f>
-        <v>24884</v>
+        <v>25884</v>
       </c>
       <c r="AG56" s="2"/>
       <c r="AH56" s="12">
@@ -5841,7 +5844,7 @@
       </c>
       <c r="AJ56" s="12">
         <f>AF56-D56</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AL56" s="47">
         <f>C56/B56*1000</f>
@@ -5949,8 +5952,8 @@
       <c r="T58" s="2">
         <v>2782</v>
       </c>
-      <c r="U58" s="2">
-        <v>1683</v>
+      <c r="U58" s="58">
+        <v>2683</v>
       </c>
       <c r="V58" s="2">
         <v>2796</v>
@@ -5982,8 +5985,8 @@
       <c r="C59" s="3">
         <v>51391</v>
       </c>
-      <c r="D59" s="3">
-        <v>28596</v>
+      <c r="D59" s="58">
+        <v>26596</v>
       </c>
       <c r="E59" s="4">
         <v>248086</v>
@@ -6064,7 +6067,7 @@
       </c>
       <c r="AJ59" s="12">
         <f>AF59-D59</f>
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AL59" s="47">
         <f>C59/B59*1000</f>
@@ -6072,7 +6075,7 @@
       </c>
       <c r="AM59" s="47">
         <f>D59/B59*1000</f>
-        <v>22.949246180342104</v>
+        <v>21.344179305230753</v>
       </c>
       <c r="AO59" s="47">
         <f>AL59-K59</f>
@@ -6080,7 +6083,7 @@
       </c>
       <c r="AP59" s="47">
         <f>AM59-L59</f>
-        <v>1.5492461803421058</v>
+        <v>-5.5820694769245449E-2</v>
       </c>
       <c r="AR59" s="12">
         <f t="shared" ref="AR59" si="50">H59</f>
@@ -7080,7 +7083,7 @@
       </c>
       <c r="AF74" s="23">
         <f>SUM(AF43:AF73)</f>
-        <v>208959</v>
+        <v>208960</v>
       </c>
       <c r="AG74" s="2"/>
       <c r="AH74" s="23">
@@ -7093,7 +7096,7 @@
       </c>
       <c r="AJ74" s="23">
         <f t="shared" si="65"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL74" s="49">
         <f>C74/B74*1000</f>
@@ -8339,7 +8342,7 @@
       <c r="V89" s="8">
         <v>7386</v>
       </c>
-      <c r="W89" s="60">
+      <c r="W89" s="59">
         <v>4758</v>
       </c>
       <c r="X89" s="8">
@@ -8405,7 +8408,7 @@
       <c r="V90" s="8">
         <v>6300</v>
       </c>
-      <c r="W90" s="60">
+      <c r="W90" s="59">
         <v>3738</v>
       </c>
       <c r="X90" s="8">
@@ -8758,7 +8761,7 @@
       </c>
       <c r="AF94" s="12">
         <f>SUM(N96:AB96)</f>
-        <v>117774</v>
+        <v>118774</v>
       </c>
       <c r="AG94" s="2"/>
       <c r="AH94" s="12">
@@ -8771,7 +8774,7 @@
       </c>
       <c r="AJ94" s="12">
         <f>AF94-D94</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AL94" s="47">
         <f>C94/B94*1000</f>
@@ -8888,8 +8891,8 @@
       <c r="O96" s="8">
         <v>8921</v>
       </c>
-      <c r="P96" s="8">
-        <v>12785</v>
+      <c r="P96" s="59">
+        <v>13785</v>
       </c>
       <c r="Q96" s="8">
         <v>16040</v>
@@ -9690,7 +9693,7 @@
       <c r="C106" s="17">
         <v>57604</v>
       </c>
-      <c r="D106" s="58">
+      <c r="D106" s="57">
         <v>51846</v>
       </c>
       <c r="E106" s="17">
@@ -10288,7 +10291,7 @@
       </c>
       <c r="AF112" s="12">
         <f>SUM(N114:AB114)</f>
-        <v>89881</v>
+        <v>90306</v>
       </c>
       <c r="AG112" s="2"/>
       <c r="AH112" s="12">
@@ -10301,7 +10304,7 @@
       </c>
       <c r="AJ112" s="12">
         <f>AF112-D112</f>
-        <v>-425</v>
+        <v>0</v>
       </c>
       <c r="AL112" s="47">
         <f>C112/B112*1000</f>
@@ -10427,8 +10430,8 @@
       <c r="P114" s="9">
         <v>6741</v>
       </c>
-      <c r="Q114" s="9">
-        <v>4659</v>
+      <c r="Q114" s="57">
+        <v>5084</v>
       </c>
       <c r="R114" s="9">
         <v>6375</v>
@@ -10824,7 +10827,7 @@
       </c>
       <c r="AF118" s="12">
         <f>SUM(N120:AB120)</f>
-        <v>68783</v>
+        <v>67714</v>
       </c>
       <c r="AG118" s="2"/>
       <c r="AH118" s="12">
@@ -10837,7 +10840,7 @@
       </c>
       <c r="AJ118" s="12">
         <f>AF118-D118</f>
-        <v>1069</v>
+        <v>0</v>
       </c>
       <c r="AL118" s="47">
         <f>C118/B118*1000</f>
@@ -10967,8 +10970,8 @@
       <c r="T120" s="9">
         <v>5309</v>
       </c>
-      <c r="U120" s="9">
-        <v>11122</v>
+      <c r="U120" s="57">
+        <v>10053</v>
       </c>
       <c r="V120" s="9">
         <v>4008</v>
@@ -12768,7 +12771,7 @@
       <c r="C142" s="17">
         <v>92266</v>
       </c>
-      <c r="D142" s="58">
+      <c r="D142" s="57">
         <v>75420</v>
       </c>
       <c r="E142" s="17">
@@ -12939,7 +12942,7 @@
       <c r="X143" s="9">
         <v>9054</v>
       </c>
-      <c r="Y143" s="58">
+      <c r="Y143" s="57">
         <v>7155</v>
       </c>
       <c r="Z143" s="9"/>
@@ -13003,7 +13006,7 @@
       <c r="X144" s="9">
         <v>8565</v>
       </c>
-      <c r="Y144" s="58">
+      <c r="Y144" s="57">
         <v>6387</v>
       </c>
       <c r="Z144" s="9"/>
@@ -13875,7 +13878,7 @@
       <c r="N155" s="9">
         <v>13905</v>
       </c>
-      <c r="O155" s="58">
+      <c r="O155" s="57">
         <v>15300</v>
       </c>
       <c r="P155" s="9">
@@ -14474,7 +14477,9 @@
       <c r="U162" s="17">
         <v>47178</v>
       </c>
-      <c r="V162" s="17"/>
+      <c r="V162" s="17">
+        <v>32167</v>
+      </c>
       <c r="W162" s="17"/>
       <c r="X162" s="17"/>
       <c r="Y162" s="17"/>
@@ -14484,28 +14489,28 @@
       <c r="AC162" s="2"/>
       <c r="AD162" s="12">
         <f>SUM(N162:AB162)</f>
-        <v>1136479</v>
+        <v>1168646</v>
       </c>
       <c r="AE162" s="12">
         <f>SUM(N163:AB163)</f>
-        <v>60920</v>
+        <v>62887</v>
       </c>
       <c r="AF162" s="12">
         <f>SUM(N164:AB164)</f>
-        <v>34186</v>
+        <v>35405</v>
       </c>
       <c r="AG162" s="2"/>
       <c r="AH162" s="12">
         <f>AD162-B162</f>
-        <v>-44690</v>
+        <v>-12523</v>
       </c>
       <c r="AI162" s="12">
         <f>AE162-C162</f>
-        <v>3033</v>
+        <v>5000</v>
       </c>
       <c r="AJ162" s="12">
         <f>AF162-D162</f>
-        <v>-1219</v>
+        <v>0</v>
       </c>
       <c r="AL162" s="47">
         <f>C162/B162*1000</f>
@@ -14576,7 +14581,9 @@
       <c r="U163" s="9">
         <v>2200</v>
       </c>
-      <c r="V163" s="9"/>
+      <c r="V163" s="9">
+        <v>1967</v>
+      </c>
       <c r="W163" s="9"/>
       <c r="X163" s="9"/>
       <c r="Y163" s="9"/>
@@ -14632,7 +14639,9 @@
       <c r="U164" s="9">
         <v>1455</v>
       </c>
-      <c r="V164" s="9"/>
+      <c r="V164" s="9">
+        <v>1219</v>
+      </c>
       <c r="W164" s="9"/>
       <c r="X164" s="9"/>
       <c r="Y164" s="9"/>
@@ -14735,7 +14744,7 @@
       </c>
       <c r="AF165" s="12">
         <f>SUM(N167:AB167)</f>
-        <v>114406</v>
+        <v>114659</v>
       </c>
       <c r="AG165" s="2"/>
       <c r="AH165" s="12">
@@ -14748,7 +14757,7 @@
       </c>
       <c r="AJ165" s="12">
         <f>AF165-D165</f>
-        <v>-253</v>
+        <v>0</v>
       </c>
       <c r="AL165" s="47">
         <f>C165/B165*1000</f>
@@ -14865,8 +14874,8 @@
       <c r="O167" s="6">
         <v>12215</v>
       </c>
-      <c r="P167" s="6">
-        <v>5275</v>
+      <c r="P167" s="61">
+        <v>5528</v>
       </c>
       <c r="Q167" s="6">
         <v>13075</v>
@@ -15500,7 +15509,7 @@
       </c>
       <c r="AF174" s="12">
         <f>SUM(N176:AB176)</f>
-        <v>67408</v>
+        <v>67708</v>
       </c>
       <c r="AG174" s="2"/>
       <c r="AH174" s="12">
@@ -15513,7 +15522,7 @@
       </c>
       <c r="AJ174" s="12">
         <f>AF174-D174</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AL174" s="47">
         <f>C174/B174*1000</f>
@@ -15621,8 +15630,8 @@
       <c r="P176" s="6">
         <v>15944</v>
       </c>
-      <c r="Q176" s="6">
-        <v>6139</v>
+      <c r="Q176" s="61">
+        <v>6439</v>
       </c>
       <c r="R176" s="6">
         <v>12245</v>
@@ -16881,28 +16890,28 @@
       <c r="AC191" s="2"/>
       <c r="AD191" s="23">
         <f>SUM(AD85:AD190)</f>
-        <v>65165942</v>
+        <v>65198109</v>
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
-        <v>3211203</v>
+        <v>3213170</v>
       </c>
       <c r="AF191" s="23">
         <f>SUM(AF85:AF190)</f>
-        <v>2378807</v>
+        <v>2380935</v>
       </c>
       <c r="AG191" s="2"/>
       <c r="AH191" s="23">
         <f t="shared" ref="AH191:AJ192" si="181">AD191-B191</f>
-        <v>-193405</v>
+        <v>-161238</v>
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="181"/>
-        <v>-856</v>
+        <v>1111</v>
       </c>
       <c r="AJ191" s="23">
         <f t="shared" si="181"/>
-        <v>10052</v>
+        <v>12180</v>
       </c>
       <c r="AL191" s="49">
         <f>C191/B191*1000</f>
@@ -17236,28 +17245,28 @@
       <c r="AC195" s="2"/>
       <c r="AD195" s="23">
         <f>SUM(AD42, AD74, AD84, AD191, AD192)</f>
-        <v>98932071</v>
+        <v>98964238</v>
       </c>
       <c r="AE195" s="23">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
-        <v>4701998</v>
+        <v>4703965</v>
       </c>
       <c r="AF195" s="23">
         <f>SUM(AF42, AF74, AF84, AF191, AF192)</f>
-        <v>3273318</v>
+        <v>3275447</v>
       </c>
       <c r="AG195" s="2"/>
       <c r="AH195" s="23">
         <f t="shared" ref="AH195:AJ196" si="186">AD195-B195</f>
-        <v>-171284</v>
+        <v>-139117</v>
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="186"/>
-        <v>-631</v>
+        <v>1336</v>
       </c>
       <c r="AJ195" s="23">
         <f t="shared" si="186"/>
-        <v>-10490</v>
+        <v>-8361</v>
       </c>
       <c r="AL195" s="49">
         <f>C195/B195*1000</f>
@@ -18164,11 +18173,11 @@
       </c>
       <c r="AE206" s="12">
         <f>SUM(N207:AB207)</f>
-        <v>91403</v>
+        <v>91303</v>
       </c>
       <c r="AF206" s="12">
         <f>SUM(N208:AB208)</f>
-        <v>65553</v>
+        <v>65550</v>
       </c>
       <c r="AG206" s="2"/>
       <c r="AH206" s="12">
@@ -18177,11 +18186,11 @@
       </c>
       <c r="AI206" s="12">
         <f>AE206-C206</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ206" s="12">
         <f>AF206-D206</f>
-        <v>-1041</v>
+        <v>-1044</v>
       </c>
       <c r="AL206" s="47">
         <f>C206/B206*1000</f>
@@ -18244,7 +18253,7 @@
         <v>15797</v>
       </c>
       <c r="S207" s="6">
-        <v>10443</v>
+        <v>10343</v>
       </c>
       <c r="T207" s="6">
         <v>14820</v>
@@ -18306,7 +18315,7 @@
         <v>8778</v>
       </c>
       <c r="U208" s="6">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="V208" s="6"/>
       <c r="W208" s="6"/>
@@ -19534,11 +19543,11 @@
       </c>
       <c r="AE224" s="23">
         <f>SUM(AE196:AE223)</f>
-        <v>283752</v>
+        <v>283652</v>
       </c>
       <c r="AF224" s="23">
         <f>SUM(AF196:AF223)</f>
-        <v>205659</v>
+        <v>205656</v>
       </c>
       <c r="AG224" s="2"/>
       <c r="AH224" s="23">
@@ -19547,11 +19556,11 @@
       </c>
       <c r="AI224" s="23">
         <f>AE224-C224</f>
-        <v>-20569</v>
+        <v>-20669</v>
       </c>
       <c r="AJ224" s="23">
         <f>AF224-D224</f>
-        <v>-14349</v>
+        <v>-14352</v>
       </c>
       <c r="AL224" s="49">
         <f>C224/B224*1000</f>
@@ -20665,7 +20674,7 @@
       </c>
       <c r="AF238" s="12">
         <f>SUM(N240:AB240)</f>
-        <v>61475</v>
+        <v>61275</v>
       </c>
       <c r="AG238" s="2"/>
       <c r="AH238" s="12">
@@ -20678,7 +20687,7 @@
       </c>
       <c r="AJ238" s="12">
         <f>AF238-D238</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AL238" s="47">
         <f>C238/B238*1000</f>
@@ -20790,8 +20799,8 @@
       <c r="Q240" s="6">
         <v>10542</v>
       </c>
-      <c r="R240" s="6">
-        <v>624</v>
+      <c r="R240" s="61">
+        <v>424</v>
       </c>
       <c r="S240" s="6">
         <v>5698</v>
@@ -21524,7 +21533,7 @@
       </c>
       <c r="AF250" s="23">
         <f>SUM(AF225:AF249)</f>
-        <v>150286</v>
+        <v>150086</v>
       </c>
       <c r="AG250" s="2"/>
       <c r="AH250" s="23">
@@ -21537,7 +21546,7 @@
       </c>
       <c r="AJ250" s="23">
         <f>AF250-D250</f>
-        <v>112</v>
+        <v>-88</v>
       </c>
       <c r="AL250" s="49">
         <f>C250/B250*1000</f>
@@ -23367,28 +23376,28 @@
       <c r="AC275" s="2"/>
       <c r="AD275" s="23">
         <f>SUM(AD195, AD224, AD250, AD274)</f>
-        <v>117957347</v>
+        <v>117989514</v>
       </c>
       <c r="AE275" s="23">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
-        <v>5347972</v>
+        <v>5349839</v>
       </c>
       <c r="AF275" s="23">
         <f>SUM(AF195, AF224, AF250, AF274)</f>
-        <v>3732624</v>
+        <v>3734550</v>
       </c>
       <c r="AG275" s="2"/>
       <c r="AH275" s="23">
         <f t="shared" si="246"/>
-        <v>-420803</v>
+        <v>-388636</v>
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="246"/>
-        <v>-21237</v>
+        <v>-19370</v>
       </c>
       <c r="AJ275" s="23">
         <f t="shared" si="246"/>
-        <v>-24796</v>
+        <v>-22870</v>
       </c>
       <c r="AL275" s="49">
         <f>C275/B275*1000</f>
@@ -23456,28 +23465,28 @@
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" s="53" t="s">
         <v>303</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="E1" s="53" t="s">
         <v>304</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>305</v>
       </c>
       <c r="F1" s="53"/>
       <c r="G1" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="H1" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="I1" s="53" t="s">
         <v>307</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="54">
@@ -23502,7 +23511,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="54">
@@ -23527,7 +23536,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B4" s="41"/>
       <c r="C4" s="54">
@@ -23552,7 +23561,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="54">
@@ -23577,7 +23586,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B6" s="41"/>
       <c r="C6" s="54">
@@ -23602,7 +23611,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B7" s="41"/>
       <c r="C7" s="54">
@@ -23627,7 +23636,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="54">
@@ -23677,7 +23686,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B10" s="41"/>
       <c r="C10" s="54">
@@ -23702,7 +23711,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="54">
@@ -23752,7 +23761,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" s="54">
@@ -23777,7 +23786,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B14" s="41"/>
       <c r="C14" s="54">
@@ -23802,7 +23811,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="54">
@@ -23827,7 +23836,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B16" s="41"/>
       <c r="C16" s="54">
@@ -23852,7 +23861,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="54">
@@ -23877,7 +23886,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="54">
@@ -23902,7 +23911,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="54">
@@ -23977,7 +23986,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="54">
@@ -24052,7 +24061,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="54">
@@ -24077,7 +24086,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B26" s="41"/>
       <c r="C26" s="54">
@@ -24102,7 +24111,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B27" s="41"/>
       <c r="C27" s="54">
@@ -24152,7 +24161,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B29" s="41"/>
       <c r="C29" s="54">
@@ -24177,7 +24186,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="54">
@@ -24202,7 +24211,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="54">
@@ -24227,7 +24236,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B32" s="41"/>
       <c r="C32" s="54">
@@ -24252,7 +24261,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="41" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B33" s="41"/>
       <c r="C33" s="54">
@@ -24277,7 +24286,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="41" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B34" s="41"/>
       <c r="C34" s="54">
@@ -24327,7 +24336,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="41" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B36" s="41"/>
       <c r="C36" s="54">
@@ -24352,7 +24361,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37" s="41"/>
       <c r="C37" s="54">
@@ -24377,7 +24386,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B38" s="41"/>
       <c r="C38" s="54">
@@ -24402,7 +24411,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B39" s="41"/>
       <c r="C39" s="54">
@@ -24427,7 +24436,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B40" s="41"/>
       <c r="C40" s="54">
@@ -24452,7 +24461,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B41" s="41"/>
       <c r="C41" s="54">
@@ -24477,7 +24486,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="41" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B42" s="41"/>
       <c r="C42" s="54">
@@ -24502,7 +24511,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="54">
@@ -24527,7 +24536,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B44" s="41"/>
       <c r="C44" s="54">
@@ -24552,7 +24561,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="54">
@@ -24652,7 +24661,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B49" s="41"/>
       <c r="C49" s="54">
@@ -24677,7 +24686,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B50" s="41"/>
       <c r="C50" s="54">
@@ -24702,7 +24711,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="54">
@@ -24727,7 +24736,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="54">
@@ -24752,7 +24761,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B53" s="41"/>
       <c r="C53" s="54">
@@ -24777,7 +24786,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B54" s="41"/>
       <c r="C54" s="54">
@@ -24927,7 +24936,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B60" s="41"/>
       <c r="C60" s="54">
@@ -25027,7 +25036,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="41" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B64" s="41"/>
       <c r="C64" s="54">
@@ -25052,7 +25061,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="54">
@@ -25077,7 +25086,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B66" s="41"/>
       <c r="C66" s="54">
@@ -25102,7 +25111,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="54">
@@ -25152,7 +25161,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="41" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="54">
@@ -25177,7 +25186,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="54">
@@ -25202,7 +25211,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="41" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="54">
@@ -25227,7 +25236,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B72" s="41"/>
       <c r="C72" s="54">
@@ -25252,32 +25261,32 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B73" s="41"/>
       <c r="C73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F73" s="56"/>
       <c r="G73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I73" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="41" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B74" s="41"/>
       <c r="C74" s="54">
@@ -25302,32 +25311,32 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B75" s="41"/>
       <c r="C75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F75" s="56"/>
       <c r="G75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I75" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B76" s="41"/>
       <c r="C76" s="54">
@@ -25352,7 +25361,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B77" s="41"/>
       <c r="C77" s="54">
@@ -25377,7 +25386,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="54">
@@ -25402,7 +25411,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="41" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B79" s="41"/>
       <c r="C79" s="54">
@@ -25427,7 +25436,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="41" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B80" s="41"/>
       <c r="C80" s="54">
@@ -25452,7 +25461,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B81" s="41"/>
       <c r="C81" s="54">
@@ -25477,7 +25486,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B82" s="41"/>
       <c r="C82" s="54">
@@ -25502,32 +25511,32 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B83" s="41"/>
       <c r="C83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F83" s="56"/>
       <c r="G83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I83" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B84" s="41"/>
       <c r="C84" s="54">
@@ -25552,7 +25561,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B85" s="41"/>
       <c r="C85" s="54">
@@ -25577,7 +25586,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="41" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B86" s="41"/>
       <c r="C86" s="54">
@@ -25602,24 +25611,24 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="41" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D87" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E87" s="54">
         <v>34.1</v>
       </c>
       <c r="F87" s="54"/>
       <c r="G87" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H87" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I87" s="54">
         <v>21.8</v>
@@ -25627,7 +25636,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="41" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="54">
@@ -25652,7 +25661,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B89" s="41"/>
       <c r="C89" s="54">
@@ -25677,7 +25686,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B90" s="41"/>
       <c r="C90" s="54">
@@ -25702,7 +25711,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B91" s="41"/>
       <c r="C91" s="54">
@@ -25727,7 +25736,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B92" s="41"/>
       <c r="C92" s="54">
@@ -25752,7 +25761,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B93" s="41"/>
       <c r="C93" s="54">
@@ -25777,27 +25786,27 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B94" s="41"/>
       <c r="C94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F94" s="56"/>
       <c r="G94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I94" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -25806,13 +25815,13 @@
       </c>
       <c r="B95" s="41"/>
       <c r="C95" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D95" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E95" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F95" s="56"/>
       <c r="G95" s="56"/>
@@ -25821,132 +25830,132 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B96" s="41"/>
       <c r="C96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F96" s="56"/>
       <c r="G96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I96" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="41" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F97" s="56"/>
       <c r="G97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I97" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="41" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I98" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="41" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B99" s="41"/>
       <c r="C99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I99" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="41" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B100" s="41"/>
       <c r="C100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I100" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="41" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B101" s="41"/>
       <c r="C101" s="54">
@@ -25956,7 +25965,7 @@
         <v>59.8</v>
       </c>
       <c r="E101" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F101" s="54"/>
       <c r="G101" s="54">
@@ -25966,12 +25975,12 @@
         <v>48.8</v>
       </c>
       <c r="I101" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="41" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B102" s="41"/>
       <c r="C102" s="54">
@@ -25981,7 +25990,7 @@
         <v>47.9</v>
       </c>
       <c r="E102" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F102" s="54"/>
       <c r="G102" s="54">
@@ -25991,12 +26000,12 @@
         <v>35</v>
       </c>
       <c r="I102" s="56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="41" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B103" s="41"/>
       <c r="C103" s="54">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85DD7F7-8E1A-4831-8C81-7189656BB7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D6CA16-755A-4A18-AE30-8C13CBF67D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -1491,11 +1491,11 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1664,17 +1664,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317E8D20-6275-41B8-982F-8FFD4E68F4B1}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="41"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>391</v>
       </c>
@@ -1687,52 +1687,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEW275"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.83984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.62890625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.62890625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.47265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.62890625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.15625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.05078125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.41796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.15625" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.578125" style="6" customWidth="1"/>
-    <col min="14" max="15" width="7.15625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.15625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.15625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.15625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="7.15625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="7.15625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.15625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.68359375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="10.62890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="8.62890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.26171875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="7.734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="6.734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.62890625" style="1" customWidth="1"/>
-    <col min="38" max="39" width="4.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.62890625" style="1" customWidth="1"/>
-    <col min="41" max="42" width="4.7890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.15625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="16.05078125" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="15.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5703125" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.5703125" style="6" customWidth="1"/>
+    <col min="14" max="15" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.7109375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.28515625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.5703125" style="1" customWidth="1"/>
+    <col min="38" max="39" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.5703125" style="1" customWidth="1"/>
+    <col min="41" max="42" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.140625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="5" style="1" customWidth="1"/>
-    <col min="48" max="48" width="17.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="16.7890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="16.62890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="16376" width="12" style="1"/>
-    <col min="16377" max="16377" width="1.7890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16378" max="16384" width="1.7890625" style="1" customWidth="1"/>
+    <col min="16377" max="16377" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="16378" max="16384" width="1.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1770,23 +1770,23 @@
         <v>282</v>
       </c>
       <c r="M1" s="26"/>
-      <c r="N1" s="60" t="s">
+      <c r="N1" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="60"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
       <c r="AD1" s="33" t="s">
         <v>279</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>8792</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>12</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
@@ -2042,7 +2042,7 @@
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>295</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>19821</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>296</v>
       </c>
@@ -2198,7 +2198,7 @@
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>297</v>
       </c>
@@ -2236,7 +2236,7 @@
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2"/>
     </row>
-    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>298</v>
       </c>
@@ -2307,7 +2307,7 @@
       <c r="AS8" s="52"/>
       <c r="AT8" s="52"/>
     </row>
-    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
         <v>299</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="AI9" s="6"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
         <v>300</v>
       </c>
@@ -2395,7 +2395,7 @@
       <c r="AI10" s="6"/>
       <c r="AJ10" s="6"/>
     </row>
-    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
         <v>301</v>
       </c>
@@ -2444,7 +2444,7 @@
       <c r="AI11" s="6"/>
       <c r="AJ11" s="6"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>15</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>44088</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>16</v>
       </c>
@@ -2607,7 +2607,7 @@
       <c r="AI13" s="2"/>
       <c r="AJ13" s="2"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>17</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>18</v>
       </c>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AE15" s="12">
         <f>SUM(N16:AB16)</f>
-        <v>58977</v>
+        <v>59877</v>
       </c>
       <c r="AF15" s="12">
         <f>SUM(N17:AB17)</f>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AI15" s="12">
         <f>AE15-C15</f>
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="12">
         <f>AF15-D15</f>
@@ -2778,14 +2778,14 @@
         <v>33167</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="37"/>
       <c r="L16" s="37"/>
-      <c r="N16" s="2">
-        <v>5712</v>
+      <c r="N16" s="58">
+        <v>6612</v>
       </c>
       <c r="O16" s="2">
         <v>5229</v>
@@ -2830,7 +2830,7 @@
       <c r="AI16" s="2"/>
       <c r="AJ16" s="2"/>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>20</v>
       </c>
@@ -2882,7 +2882,7 @@
       <c r="AI17" s="2"/>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>21</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>76684</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>22</v>
       </c>
@@ -3067,7 +3067,7 @@
       <c r="AI19" s="2"/>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
         <v>24</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>38321</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>25</v>
       </c>
@@ -3294,7 +3294,7 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>26</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="AI23" s="2"/>
       <c r="AJ23" s="2"/>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
         <v>27</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>99899</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>28</v>
       </c>
@@ -3527,7 +3527,7 @@
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>29</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
         <v>30</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>36336</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>31</v>
       </c>
@@ -3744,7 +3744,7 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>32</v>
       </c>
@@ -3786,7 +3786,7 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>34</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
         <v>35</v>
       </c>
@@ -4007,7 +4007,7 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>36280</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
         <v>37</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
         <v>38</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
         <v>39</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>55174</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>40</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>41</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
         <v>42</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>77982</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
         <v>43</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
         <v>44</v>
       </c>
@@ -4672,7 +4672,7 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A42" s="30" t="s">
         <v>45</v>
       </c>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AE42" s="23">
         <f>SUM(AE2:AE40)</f>
-        <v>943129</v>
+        <v>944029</v>
       </c>
       <c r="AF42" s="23">
         <f>SUM(AF2:AF40)</f>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AI42" s="23">
         <f>AE42-C42</f>
-        <v>-808</v>
+        <v>92</v>
       </c>
       <c r="AJ42" s="23">
         <f>AF42-D42</f>
@@ -4786,7 +4786,7 @@
         <v>-9503</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
         <v>46</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>12531</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>47</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>25499</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
         <v>48</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
         <v>49</v>
       </c>
@@ -5117,7 +5117,7 @@
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>50</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>20432</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
         <v>51</v>
       </c>
@@ -5285,7 +5285,7 @@
       <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
     </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
         <v>52</v>
       </c>
@@ -5330,7 +5330,7 @@
       <c r="AI49" s="2"/>
       <c r="AJ49" s="2"/>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
         <v>53</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>15551</v>
       </c>
     </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
         <v>54</v>
       </c>
@@ -5493,7 +5493,7 @@
       <c r="AI51" s="2"/>
       <c r="AJ51" s="2"/>
     </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
         <v>55</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="AI52" s="2"/>
       <c r="AJ52" s="2"/>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
         <v>56</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>17783</v>
       </c>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
         <v>57</v>
       </c>
@@ -5703,7 +5703,7 @@
       <c r="AI54" s="2"/>
       <c r="AJ54" s="2"/>
     </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
         <v>58</v>
       </c>
@@ -5748,7 +5748,7 @@
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
     </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
         <v>59</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>25432</v>
       </c>
     </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
         <v>60</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="AI57" s="2"/>
       <c r="AJ57" s="2"/>
     </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
         <v>61</v>
       </c>
@@ -5975,7 +5975,7 @@
       <c r="AI58" s="2"/>
       <c r="AJ58" s="2"/>
     </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
         <v>62</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>24399</v>
       </c>
     </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
         <v>63</v>
       </c>
@@ -6143,7 +6143,7 @@
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
     </row>
-    <row r="61" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
         <v>64</v>
       </c>
@@ -6188,7 +6188,7 @@
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
     </row>
-    <row r="62" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
         <v>65</v>
       </c>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AE62" s="12">
         <f>SUM(N63:AB63)</f>
-        <v>26107</v>
+        <v>25107</v>
       </c>
       <c r="AF62" s="12">
         <f>SUM(N64:AB64)</f>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="AI62" s="12">
         <f>AE62-C62</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ62" s="12">
         <f>AF62-D62</f>
@@ -6305,14 +6305,14 @@
         <v>15757</v>
       </c>
     </row>
-    <row r="63" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
         <v>66</v>
       </c>
       <c r="K63" s="37"/>
       <c r="L63" s="37"/>
-      <c r="N63" s="2">
-        <v>5536</v>
+      <c r="N63" s="58">
+        <v>4536</v>
       </c>
       <c r="O63" s="2">
         <v>3658</v>
@@ -6350,7 +6350,7 @@
       <c r="AI63" s="2"/>
       <c r="AJ63" s="2"/>
     </row>
-    <row r="64" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
         <v>67</v>
       </c>
@@ -6395,7 +6395,7 @@
       <c r="AI64" s="2"/>
       <c r="AJ64" s="2"/>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A65" s="29" t="s">
         <v>68</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>17247</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>69</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="AI66" s="2"/>
       <c r="AJ66" s="2"/>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
         <v>70</v>
       </c>
@@ -6600,7 +6600,7 @@
       <c r="AI67" s="2"/>
       <c r="AJ67" s="2"/>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
         <v>71</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A69" s="28" t="s">
         <v>72</v>
       </c>
@@ -6763,7 +6763,7 @@
       <c r="AI69" s="2"/>
       <c r="AJ69" s="2"/>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
         <v>73</v>
       </c>
@@ -6805,7 +6805,7 @@
       <c r="AI70" s="2"/>
       <c r="AJ70" s="2"/>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A71" s="29" t="s">
         <v>74</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>17010</v>
       </c>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
         <v>75</v>
       </c>
@@ -6978,7 +6978,7 @@
       <c r="AI72" s="2"/>
       <c r="AJ72" s="2"/>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
         <v>76</v>
       </c>
@@ -7026,7 +7026,7 @@
       <c r="AI73" s="2"/>
       <c r="AJ73" s="2"/>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
         <v>77</v>
       </c>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AE74" s="23">
         <f>SUM(AE43:AE73)</f>
-        <v>357847</v>
+        <v>356847</v>
       </c>
       <c r="AF74" s="23">
         <f>SUM(AF43:AF73)</f>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AI74" s="23">
         <f t="shared" si="65"/>
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="AJ74" s="23">
         <f t="shared" si="65"/>
@@ -7140,7 +7140,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>78</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>12183</v>
       </c>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>79</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="AI76" s="2"/>
       <c r="AJ76" s="2"/>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>80</v>
       </c>
@@ -7388,7 +7388,7 @@
       <c r="AI77" s="2"/>
       <c r="AJ77" s="2"/>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>81</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>26309</v>
       </c>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>82</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="AI79" s="2"/>
       <c r="AJ79" s="2"/>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>83</v>
       </c>
@@ -7630,7 +7630,7 @@
       <c r="AI80" s="2"/>
       <c r="AJ80" s="2"/>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
         <v>84</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>85</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="AI82" s="2"/>
       <c r="AJ82" s="2"/>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>86</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="AI83" s="2"/>
       <c r="AJ83" s="2"/>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A84" s="44" t="s">
         <v>87</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>8257</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>88</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>44683</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>89</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>90</v>
       </c>
@@ -8165,7 +8165,7 @@
       <c r="AI87" s="2"/>
       <c r="AJ87" s="2"/>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>91</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>60082</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>92</v>
       </c>
@@ -8365,7 +8365,7 @@
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>93</v>
       </c>
@@ -8431,7 +8431,7 @@
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>94</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>40347</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>95</v>
       </c>
@@ -8613,7 +8613,7 @@
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>96</v>
       </c>
@@ -8673,7 +8673,7 @@
       <c r="AI93" s="2"/>
       <c r="AJ93" s="2"/>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
         <v>97</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>98935</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>98</v>
       </c>
@@ -8869,7 +8869,7 @@
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>99</v>
       </c>
@@ -8933,7 +8933,7 @@
       <c r="AI96" s="2"/>
       <c r="AJ96" s="2"/>
     </row>
-    <row r="97" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
         <v>100</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>120135</v>
       </c>
     </row>
-    <row r="98" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>101</v>
       </c>
@@ -9125,7 +9125,7 @@
       <c r="AI98" s="2"/>
       <c r="AJ98" s="2"/>
     </row>
-    <row r="99" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>102</v>
       </c>
@@ -9187,7 +9187,7 @@
       <c r="AI99" s="2"/>
       <c r="AJ99" s="2"/>
     </row>
-    <row r="100" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
         <v>103</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>59074</v>
       </c>
     </row>
-    <row r="101" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>104</v>
       </c>
@@ -9367,7 +9367,7 @@
       <c r="AI101" s="2"/>
       <c r="AJ101" s="2"/>
     </row>
-    <row r="102" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>105</v>
       </c>
@@ -9423,7 +9423,7 @@
       <c r="AI102" s="2"/>
       <c r="AJ102" s="2"/>
     </row>
-    <row r="103" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A103" s="18" t="s">
         <v>106</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>72188</v>
       </c>
     </row>
-    <row r="104" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>107</v>
       </c>
@@ -9619,7 +9619,7 @@
       <c r="AI104" s="2"/>
       <c r="AJ104" s="2"/>
     </row>
-    <row r="105" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>108</v>
       </c>
@@ -9683,7 +9683,7 @@
       <c r="AI105" s="2"/>
       <c r="AJ105" s="2"/>
     </row>
-    <row r="106" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A106" s="18" t="s">
         <v>109</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>44326</v>
       </c>
     </row>
-    <row r="107" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>110</v>
       </c>
@@ -9875,7 +9875,7 @@
       <c r="AI107" s="2"/>
       <c r="AJ107" s="2"/>
     </row>
-    <row r="108" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>111</v>
       </c>
@@ -9937,7 +9937,7 @@
       <c r="AI108" s="2"/>
       <c r="AJ108" s="2"/>
     </row>
-    <row r="109" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
         <v>112</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>51040</v>
       </c>
     </row>
-    <row r="110" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>113</v>
       </c>
@@ -10133,7 +10133,7 @@
       <c r="AI110" s="2"/>
       <c r="AJ110" s="2"/>
     </row>
-    <row r="111" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>114</v>
       </c>
@@ -10197,7 +10197,7 @@
       <c r="AI111" s="2"/>
       <c r="AJ111" s="2"/>
     </row>
-    <row r="112" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
         <v>115</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>78783</v>
       </c>
     </row>
-    <row r="113" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>116</v>
       </c>
@@ -10405,7 +10405,7 @@
       <c r="AI113" s="2"/>
       <c r="AJ113" s="2"/>
     </row>
-    <row r="114" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>117</v>
       </c>
@@ -10475,7 +10475,7 @@
       <c r="AI114" s="2"/>
       <c r="AJ114" s="2"/>
     </row>
-    <row r="115" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A115" s="18" t="s">
         <v>118</v>
       </c>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="AE115" s="12">
         <f>SUM(N116:AB116)</f>
-        <v>67246</v>
+        <v>72581</v>
       </c>
       <c r="AF115" s="12">
         <f>SUM(N117:AB117)</f>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="AI115" s="12">
         <f>AE115-C115</f>
-        <v>-5335</v>
+        <v>0</v>
       </c>
       <c r="AJ115" s="12">
         <f>AF115-D115</f>
@@ -10609,7 +10609,7 @@
         <v>58051</v>
       </c>
     </row>
-    <row r="116" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>119</v>
       </c>
@@ -10628,8 +10628,8 @@
       <c r="N116" s="9">
         <v>9566</v>
       </c>
-      <c r="O116" s="9">
-        <v>5298</v>
+      <c r="O116" s="57">
+        <v>10633</v>
       </c>
       <c r="P116" s="9">
         <v>7077</v>
@@ -10675,7 +10675,7 @@
       <c r="AI116" s="2"/>
       <c r="AJ116" s="2"/>
     </row>
-    <row r="117" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>120</v>
       </c>
@@ -10741,7 +10741,7 @@
       <c r="AI117" s="2"/>
       <c r="AJ117" s="2"/>
     </row>
-    <row r="118" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
         <v>121</v>
       </c>
@@ -10871,7 +10871,7 @@
         <v>65761</v>
       </c>
     </row>
-    <row r="119" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>122</v>
       </c>
@@ -10933,7 +10933,7 @@
       <c r="AI119" s="2"/>
       <c r="AJ119" s="2"/>
     </row>
-    <row r="120" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>123</v>
       </c>
@@ -10995,7 +10995,7 @@
       <c r="AI120" s="2"/>
       <c r="AJ120" s="2"/>
     </row>
-    <row r="121" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
         <v>124</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>39804</v>
       </c>
     </row>
-    <row r="122" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>125</v>
       </c>
@@ -11187,7 +11187,7 @@
       <c r="AI122" s="2"/>
       <c r="AJ122" s="2"/>
     </row>
-    <row r="123" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>126</v>
       </c>
@@ -11249,7 +11249,7 @@
       <c r="AI123" s="2"/>
       <c r="AJ123" s="2"/>
     </row>
-    <row r="124" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
         <v>127</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="125" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>128</v>
       </c>
@@ -11425,7 +11425,7 @@
       <c r="AI125" s="2"/>
       <c r="AJ125" s="2"/>
     </row>
-    <row r="126" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>129</v>
       </c>
@@ -11479,7 +11479,7 @@
       <c r="AI126" s="2"/>
       <c r="AJ126" s="2"/>
     </row>
-    <row r="127" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>130</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>75183</v>
       </c>
     </row>
-    <row r="128" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>131</v>
       </c>
@@ -11675,7 +11675,7 @@
       <c r="AI128" s="2"/>
       <c r="AJ128" s="2"/>
     </row>
-    <row r="129" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>132</v>
       </c>
@@ -11739,7 +11739,7 @@
       <c r="AI129" s="2"/>
       <c r="AJ129" s="2"/>
     </row>
-    <row r="130" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A130" s="18" t="s">
         <v>133</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>60505</v>
       </c>
     </row>
-    <row r="131" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>134</v>
       </c>
@@ -11927,7 +11927,7 @@
       <c r="AI131" s="2"/>
       <c r="AJ131" s="2"/>
     </row>
-    <row r="132" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>135</v>
       </c>
@@ -11987,15 +11987,15 @@
       <c r="AI132" s="2"/>
       <c r="AJ132" s="2"/>
     </row>
-    <row r="133" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>136</v>
       </c>
       <c r="B133" s="17">
         <v>2806879</v>
       </c>
-      <c r="C133" s="17">
-        <v>156712</v>
+      <c r="C133" s="57">
+        <v>156022</v>
       </c>
       <c r="D133" s="17">
         <v>117028</v>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AI133" s="12">
         <f>AE133-C133</f>
-        <v>-690</v>
+        <v>0</v>
       </c>
       <c r="AJ133" s="12">
         <f>AF133-D133</f>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AL133" s="47">
         <f>C133/B133*1000</f>
-        <v>55.831405628814061</v>
+        <v>55.585580995832025</v>
       </c>
       <c r="AM133" s="47">
         <f>D133/B133*1000</f>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="AO133" s="47">
         <f>AL133-K133</f>
-        <v>3.1405628814063391E-2</v>
+        <v>-0.2144190041679721</v>
       </c>
       <c r="AP133" s="47">
         <f>AM133-L133</f>
@@ -12119,7 +12119,7 @@
         <v>121495</v>
       </c>
     </row>
-    <row r="134" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>137</v>
       </c>
@@ -12183,7 +12183,7 @@
       <c r="AI134" s="2"/>
       <c r="AJ134" s="2"/>
     </row>
-    <row r="135" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>138</v>
       </c>
@@ -12247,7 +12247,7 @@
       <c r="AI135" s="2"/>
       <c r="AJ135" s="2"/>
     </row>
-    <row r="136" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>139</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>82146</v>
       </c>
     </row>
-    <row r="137" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>140</v>
       </c>
@@ -12455,7 +12455,7 @@
       <c r="AI137" s="2"/>
       <c r="AJ137" s="2"/>
     </row>
-    <row r="138" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>141</v>
       </c>
@@ -12525,7 +12525,7 @@
       <c r="AI138" s="2"/>
       <c r="AJ138" s="2"/>
     </row>
-    <row r="139" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>142</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>34066</v>
       </c>
     </row>
-    <row r="140" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>143</v>
       </c>
@@ -12705,7 +12705,7 @@
       <c r="AI140" s="2"/>
       <c r="AJ140" s="2"/>
     </row>
-    <row r="141" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
         <v>144</v>
       </c>
@@ -12761,7 +12761,7 @@
       <c r="AI141" s="2"/>
       <c r="AJ141" s="2"/>
     </row>
-    <row r="142" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>145</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>62602</v>
       </c>
     </row>
-    <row r="143" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>146</v>
       </c>
@@ -12957,7 +12957,7 @@
       <c r="AI143" s="2"/>
       <c r="AJ143" s="2"/>
     </row>
-    <row r="144" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
         <v>147</v>
       </c>
@@ -13021,7 +13021,7 @@
       <c r="AI144" s="2"/>
       <c r="AJ144" s="2"/>
     </row>
-    <row r="145" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A145" s="18" t="s">
         <v>148</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>102581</v>
       </c>
     </row>
-    <row r="146" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>149</v>
       </c>
@@ -13197,7 +13197,7 @@
       <c r="AI146" s="2"/>
       <c r="AJ146" s="2"/>
     </row>
-    <row r="147" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>150</v>
       </c>
@@ -13251,7 +13251,7 @@
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
     </row>
-    <row r="148" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="s">
         <v>151</v>
       </c>
@@ -13343,7 +13343,7 @@
         <v>28401</v>
       </c>
     </row>
-    <row r="149" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A149" s="20" t="s">
         <v>152</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>26234</v>
       </c>
     </row>
-    <row r="150" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
         <v>153</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>25550</v>
       </c>
     </row>
-    <row r="151" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
         <v>154</v>
       </c>
@@ -13615,7 +13615,7 @@
       <c r="AI151" s="2"/>
       <c r="AJ151" s="2"/>
     </row>
-    <row r="152" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
         <v>155</v>
       </c>
@@ -13671,7 +13671,7 @@
       <c r="AI152" s="2"/>
       <c r="AJ152" s="2"/>
     </row>
-    <row r="153" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>156</v>
       </c>
@@ -13736,8 +13736,8 @@
       <c r="V153" s="17">
         <v>214957</v>
       </c>
-      <c r="W153" s="17">
-        <v>123557</v>
+      <c r="W153" s="57">
+        <v>138743</v>
       </c>
       <c r="X153" s="17"/>
       <c r="Y153" s="17"/>
@@ -13747,11 +13747,11 @@
       <c r="AC153" s="2"/>
       <c r="AD153" s="12">
         <f>SUM(N153:AB153)</f>
-        <v>2423385</v>
+        <v>2438571</v>
       </c>
       <c r="AE153" s="12">
         <f>SUM(N154:AB154)</f>
-        <v>125671</v>
+        <v>126373</v>
       </c>
       <c r="AF153" s="12">
         <f>SUM(N155:AB155)</f>
@@ -13760,11 +13760,11 @@
       <c r="AG153" s="2"/>
       <c r="AH153" s="12">
         <f>AD153-B153</f>
-        <v>-15186</v>
+        <v>0</v>
       </c>
       <c r="AI153" s="12">
         <f>AE153-C153</f>
-        <v>-702</v>
+        <v>0</v>
       </c>
       <c r="AJ153" s="12">
         <f>AF153-D153</f>
@@ -13799,7 +13799,7 @@
         <v>86961</v>
       </c>
     </row>
-    <row r="154" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
         <v>157</v>
       </c>
@@ -13842,8 +13842,8 @@
       <c r="V154" s="9">
         <v>9261</v>
       </c>
-      <c r="W154" s="9">
-        <v>7231</v>
+      <c r="W154" s="57">
+        <v>7933</v>
       </c>
       <c r="X154" s="9"/>
       <c r="Y154" s="9"/>
@@ -13859,7 +13859,7 @@
       <c r="AI154" s="2"/>
       <c r="AJ154" s="2"/>
     </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>158</v>
       </c>
@@ -13919,7 +13919,7 @@
       <c r="AI155" s="2"/>
       <c r="AJ155" s="2"/>
     </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
         <v>159</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>56268</v>
       </c>
     </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>160</v>
       </c>
@@ -14099,7 +14099,7 @@
       <c r="AI157" s="2"/>
       <c r="AJ157" s="2"/>
     </row>
-    <row r="158" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>161</v>
       </c>
@@ -14155,7 +14155,7 @@
       <c r="AI158" s="2"/>
       <c r="AJ158" s="2"/>
     </row>
-    <row r="159" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
         <v>162</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>53594</v>
       </c>
     </row>
-    <row r="160" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>163</v>
       </c>
@@ -14351,7 +14351,7 @@
       <c r="AI160" s="2"/>
       <c r="AJ160" s="2"/>
     </row>
-    <row r="161" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
         <v>164</v>
       </c>
@@ -14415,7 +14415,7 @@
       <c r="AI161" s="2"/>
       <c r="AJ161" s="2"/>
     </row>
-    <row r="162" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
         <v>165</v>
       </c>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="AE162" s="12">
         <f>SUM(N163:AB163)</f>
-        <v>62887</v>
+        <v>57887</v>
       </c>
       <c r="AF162" s="12">
         <f>SUM(N164:AB164)</f>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="AI162" s="12">
         <f>AE162-C162</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AJ162" s="12">
         <f>AF162-D162</f>
@@ -14541,7 +14541,7 @@
         <v>34141</v>
       </c>
     </row>
-    <row r="163" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>166</v>
       </c>
@@ -14575,8 +14575,8 @@
       <c r="S163" s="9">
         <v>823</v>
       </c>
-      <c r="T163" s="9">
-        <v>8376</v>
+      <c r="T163" s="57">
+        <v>3376</v>
       </c>
       <c r="U163" s="9">
         <v>2200</v>
@@ -14599,7 +14599,7 @@
       <c r="AI163" s="2"/>
       <c r="AJ163" s="2"/>
     </row>
-    <row r="164" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>167</v>
       </c>
@@ -14657,15 +14657,15 @@
       <c r="AI164" s="2"/>
       <c r="AJ164" s="2"/>
     </row>
-    <row r="165" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
         <v>168</v>
       </c>
       <c r="B165" s="19">
         <v>2907014</v>
       </c>
-      <c r="C165" s="19">
-        <v>139796</v>
+      <c r="C165" s="60">
+        <v>139346</v>
       </c>
       <c r="D165" s="19">
         <v>114659</v>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="AI165" s="12">
         <f>AE165-C165</f>
-        <v>-450</v>
+        <v>0</v>
       </c>
       <c r="AJ165" s="12">
         <f>AF165-D165</f>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="AL165" s="47">
         <f>C165/B165*1000</f>
-        <v>48.089207688714261</v>
+        <v>47.934409672605632</v>
       </c>
       <c r="AM165" s="47">
         <f>D165/B165*1000</f>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="AO165" s="47">
         <f>AL165-K165</f>
-        <v>0.18920768871426219</v>
+        <v>3.4409672605633546E-2</v>
       </c>
       <c r="AP165" s="47">
         <f>AM165-L165</f>
@@ -14788,7 +14788,7 @@
         <v>94346</v>
       </c>
     </row>
-    <row r="166" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>169</v>
       </c>
@@ -14852,7 +14852,7 @@
       <c r="AI166" s="2"/>
       <c r="AJ166" s="2"/>
     </row>
-    <row r="167" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>170</v>
       </c>
@@ -14874,7 +14874,7 @@
       <c r="O167" s="6">
         <v>12215</v>
       </c>
-      <c r="P167" s="61">
+      <c r="P167" s="60">
         <v>5528</v>
       </c>
       <c r="Q167" s="6">
@@ -14916,7 +14916,7 @@
       <c r="AI167" s="2"/>
       <c r="AJ167" s="2"/>
     </row>
-    <row r="168" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
         <v>171</v>
       </c>
@@ -14986,37 +14986,39 @@
       <c r="X168" s="19">
         <v>160408</v>
       </c>
-      <c r="Y168" s="19">
-        <v>268864</v>
-      </c>
-      <c r="Z168" s="17"/>
+      <c r="Y168" s="60">
+        <v>168864</v>
+      </c>
+      <c r="Z168" s="57">
+        <v>5916</v>
+      </c>
       <c r="AA168" s="17"/>
       <c r="AB168" s="17"/>
       <c r="AC168" s="2"/>
       <c r="AD168" s="12">
         <f>SUM(N168:AB168)</f>
-        <v>1976302</v>
+        <v>1882218</v>
       </c>
       <c r="AE168" s="12">
         <f>SUM(N169:AB169)</f>
-        <v>87822</v>
+        <v>88071</v>
       </c>
       <c r="AF168" s="12">
         <f>SUM(N170:AB170)</f>
-        <v>56836</v>
+        <v>57003</v>
       </c>
       <c r="AG168" s="2"/>
       <c r="AH168" s="12">
         <f>AD168-B168</f>
-        <v>94084</v>
+        <v>0</v>
       </c>
       <c r="AI168" s="12">
         <f>AE168-C168</f>
-        <v>-249</v>
+        <v>0</v>
       </c>
       <c r="AJ168" s="12">
         <f>AF168-D168</f>
-        <v>-167</v>
+        <v>0</v>
       </c>
       <c r="AL168" s="47">
         <f>C168/B168*1000</f>
@@ -15047,7 +15049,7 @@
         <v>59944</v>
       </c>
     </row>
-    <row r="169" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>172</v>
       </c>
@@ -15099,7 +15101,9 @@
       <c r="Y169" s="6">
         <v>6728</v>
       </c>
-      <c r="Z169" s="9"/>
+      <c r="Z169" s="57">
+        <v>249</v>
+      </c>
       <c r="AA169" s="9"/>
       <c r="AB169" s="9"/>
       <c r="AC169" s="2"/>
@@ -15111,7 +15115,7 @@
       <c r="AI169" s="2"/>
       <c r="AJ169" s="2"/>
     </row>
-    <row r="170" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>173</v>
       </c>
@@ -15163,7 +15167,9 @@
       <c r="Y170" s="6">
         <v>4429</v>
       </c>
-      <c r="Z170" s="9"/>
+      <c r="Z170" s="57">
+        <v>167</v>
+      </c>
       <c r="AA170" s="9"/>
       <c r="AB170" s="9"/>
       <c r="AC170" s="2"/>
@@ -15175,7 +15181,7 @@
       <c r="AI170" s="2"/>
       <c r="AJ170" s="2"/>
     </row>
-    <row r="171" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
         <v>174</v>
       </c>
@@ -15306,7 +15312,7 @@
         <v>56895</v>
       </c>
     </row>
-    <row r="172" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
         <v>175</v>
       </c>
@@ -15370,7 +15376,7 @@
       <c r="AI172" s="2"/>
       <c r="AJ172" s="2"/>
     </row>
-    <row r="173" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
         <v>176</v>
       </c>
@@ -15434,7 +15440,7 @@
       <c r="AI173" s="2"/>
       <c r="AJ173" s="2"/>
     </row>
-    <row r="174" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
         <v>177</v>
       </c>
@@ -15553,7 +15559,7 @@
         <v>63824</v>
       </c>
     </row>
-    <row r="175" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
         <v>178</v>
       </c>
@@ -15605,7 +15611,7 @@
       <c r="AI175" s="2"/>
       <c r="AJ175" s="2"/>
     </row>
-    <row r="176" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
         <v>179</v>
       </c>
@@ -15630,7 +15636,7 @@
       <c r="P176" s="6">
         <v>15944</v>
       </c>
-      <c r="Q176" s="61">
+      <c r="Q176" s="60">
         <v>6439</v>
       </c>
       <c r="R176" s="6">
@@ -15657,7 +15663,7 @@
       <c r="AI176" s="2"/>
       <c r="AJ176" s="2"/>
     </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A177" s="18" t="s">
         <v>180</v>
       </c>
@@ -15786,7 +15792,7 @@
         <v>85859</v>
       </c>
     </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>181</v>
       </c>
@@ -15848,7 +15854,7 @@
       <c r="AI178" s="2"/>
       <c r="AJ178" s="2"/>
     </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>182</v>
       </c>
@@ -15910,7 +15916,7 @@
       <c r="AI179" s="2"/>
       <c r="AJ179" s="2"/>
     </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A180" s="18" t="s">
         <v>183</v>
       </c>
@@ -16029,7 +16035,7 @@
         <v>57290</v>
       </c>
     </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>184</v>
       </c>
@@ -16081,7 +16087,7 @@
       <c r="AI181" s="2"/>
       <c r="AJ181" s="2"/>
     </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
         <v>185</v>
       </c>
@@ -16133,7 +16139,7 @@
       <c r="AI182" s="2"/>
       <c r="AJ182" s="2"/>
     </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A183" s="20" t="s">
         <v>186</v>
       </c>
@@ -16225,7 +16231,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A184" s="20" t="s">
         <v>187</v>
       </c>
@@ -16317,7 +16323,7 @@
         <v>7737</v>
       </c>
     </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A185" s="18" t="s">
         <v>188</v>
       </c>
@@ -16454,7 +16460,7 @@
         <v>69619</v>
       </c>
     </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
         <v>189</v>
       </c>
@@ -16524,7 +16530,7 @@
       <c r="AI186" s="2"/>
       <c r="AJ186" s="2"/>
     </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>190</v>
       </c>
@@ -16594,7 +16600,7 @@
       <c r="AI187" s="2"/>
       <c r="AJ187" s="2"/>
     </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A188" s="18" t="s">
         <v>191</v>
       </c>
@@ -16721,7 +16727,7 @@
         <v>36205</v>
       </c>
     </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>192</v>
       </c>
@@ -16781,7 +16787,7 @@
       <c r="AI189" s="2"/>
       <c r="AJ189" s="2"/>
     </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>193</v>
       </c>
@@ -16841,7 +16847,7 @@
       <c r="AI190" s="2"/>
       <c r="AJ190" s="2"/>
     </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A191" s="45" t="s">
         <v>194</v>
       </c>
@@ -16890,28 +16896,28 @@
       <c r="AC191" s="2"/>
       <c r="AD191" s="23">
         <f>SUM(AD85:AD190)</f>
-        <v>65198109</v>
+        <v>65119211</v>
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
-        <v>3213170</v>
+        <v>3214456</v>
       </c>
       <c r="AF191" s="23">
         <f>SUM(AF85:AF190)</f>
-        <v>2380935</v>
+        <v>2381102</v>
       </c>
       <c r="AG191" s="2"/>
       <c r="AH191" s="23">
         <f t="shared" ref="AH191:AJ192" si="181">AD191-B191</f>
-        <v>-161238</v>
+        <v>-240136</v>
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="181"/>
-        <v>1111</v>
+        <v>2397</v>
       </c>
       <c r="AJ191" s="23">
         <f t="shared" si="181"/>
-        <v>12180</v>
+        <v>12347</v>
       </c>
       <c r="AL191" s="49">
         <f>C191/B191*1000</f>
@@ -16955,7 +16961,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A192" s="18" t="s">
         <v>195</v>
       </c>
@@ -17080,7 +17086,7 @@
         <v>68890</v>
       </c>
     </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
         <v>196</v>
       </c>
@@ -17138,7 +17144,7 @@
       <c r="AI193" s="2"/>
       <c r="AJ193" s="2"/>
     </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
         <v>197</v>
       </c>
@@ -17196,7 +17202,7 @@
       <c r="AI194" s="2"/>
       <c r="AJ194" s="2"/>
     </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A195" s="45" t="s">
         <v>198</v>
       </c>
@@ -17245,28 +17251,28 @@
       <c r="AC195" s="2"/>
       <c r="AD195" s="23">
         <f>SUM(AD42, AD74, AD84, AD191, AD192)</f>
-        <v>98964238</v>
+        <v>98885340</v>
       </c>
       <c r="AE195" s="23">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
-        <v>4703965</v>
+        <v>4705151</v>
       </c>
       <c r="AF195" s="23">
         <f>SUM(AF42, AF74, AF84, AF191, AF192)</f>
-        <v>3275447</v>
+        <v>3275614</v>
       </c>
       <c r="AG195" s="2"/>
       <c r="AH195" s="23">
         <f t="shared" ref="AH195:AJ196" si="186">AD195-B195</f>
-        <v>-139117</v>
+        <v>-218015</v>
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="186"/>
-        <v>1336</v>
+        <v>2522</v>
       </c>
       <c r="AJ195" s="23">
         <f t="shared" si="186"/>
-        <v>-8361</v>
+        <v>-8194</v>
       </c>
       <c r="AL195" s="49">
         <f>C195/B195*1000</f>
@@ -17310,7 +17316,7 @@
         <v>-252189</v>
       </c>
     </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A196" s="18" t="s">
         <v>199</v>
       </c>
@@ -17431,7 +17437,7 @@
         <v>15719</v>
       </c>
     </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>200</v>
       </c>
@@ -17485,7 +17491,7 @@
       <c r="AI197" s="2"/>
       <c r="AJ197" s="2"/>
     </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>201</v>
       </c>
@@ -17539,7 +17545,7 @@
       <c r="AI198" s="2"/>
       <c r="AJ198" s="2"/>
     </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A199" s="18" t="s">
         <v>202</v>
       </c>
@@ -17660,7 +17666,7 @@
         <v>12320</v>
       </c>
     </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>203</v>
       </c>
@@ -17720,7 +17726,7 @@
       <c r="AI200" s="2"/>
       <c r="AJ200" s="2"/>
     </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
         <v>204</v>
       </c>
@@ -17780,7 +17786,7 @@
       <c r="AI201" s="2"/>
       <c r="AJ201" s="2"/>
     </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A202" s="18" t="s">
         <v>205</v>
       </c>
@@ -17903,7 +17909,7 @@
         <v>13860</v>
       </c>
     </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A203" s="11" t="s">
         <v>206</v>
       </c>
@@ -17959,7 +17965,7 @@
       <c r="AI203" s="2"/>
       <c r="AJ203" s="2"/>
     </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
         <v>207</v>
       </c>
@@ -18015,7 +18021,7 @@
       <c r="AI204" s="2"/>
       <c r="AJ204" s="2"/>
     </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A205" s="20" t="s">
         <v>208</v>
       </c>
@@ -18098,7 +18104,7 @@
       <c r="AS205" s="12"/>
       <c r="AT205" s="12"/>
     </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A206" s="18" t="s">
         <v>209</v>
       </c>
@@ -18221,7 +18227,7 @@
         <v>57139</v>
       </c>
     </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>210</v>
       </c>
@@ -18277,7 +18283,7 @@
       <c r="AI207" s="2"/>
       <c r="AJ207" s="2"/>
     </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>211</v>
       </c>
@@ -18333,7 +18339,7 @@
       <c r="AI208" s="2"/>
       <c r="AJ208" s="2"/>
     </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A209" s="18" t="s">
         <v>212</v>
       </c>
@@ -18460,7 +18466,7 @@
         <v>14579</v>
       </c>
     </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>213</v>
       </c>
@@ -18520,7 +18526,7 @@
       <c r="AI210" s="2"/>
       <c r="AJ210" s="2"/>
     </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>214</v>
       </c>
@@ -18580,7 +18586,7 @@
       <c r="AI211" s="2"/>
       <c r="AJ211" s="2"/>
     </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A212" s="18" t="s">
         <v>215</v>
       </c>
@@ -18697,7 +18703,7 @@
         <v>28752</v>
       </c>
     </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>216</v>
       </c>
@@ -18747,7 +18753,7 @@
       <c r="AI213" s="2"/>
       <c r="AJ213" s="2"/>
     </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>217</v>
       </c>
@@ -18797,7 +18803,7 @@
       <c r="AI214" s="2"/>
       <c r="AJ214" s="2"/>
     </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A215" s="18" t="s">
         <v>218</v>
       </c>
@@ -18918,7 +18924,7 @@
         <v>16626</v>
       </c>
     </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>219</v>
       </c>
@@ -18972,7 +18978,7 @@
       <c r="AI216" s="2"/>
       <c r="AJ216" s="2"/>
     </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>220</v>
       </c>
@@ -19026,7 +19032,7 @@
       <c r="AI217" s="2"/>
       <c r="AJ217" s="2"/>
     </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A218" s="18" t="s">
         <v>221</v>
       </c>
@@ -19103,7 +19109,7 @@
       </c>
       <c r="AE218" s="12">
         <f>SUM(N219:AB219)</f>
-        <v>31534</v>
+        <v>30534</v>
       </c>
       <c r="AF218" s="12">
         <f>SUM(N220:AB220)</f>
@@ -19116,7 +19122,7 @@
       </c>
       <c r="AI218" s="12">
         <f>AE218-C218</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ218" s="12">
         <f>AF218-D218</f>
@@ -19151,7 +19157,7 @@
         <v>17424</v>
       </c>
     </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>222</v>
       </c>
@@ -19179,8 +19185,8 @@
       <c r="Q219" s="6">
         <v>2886</v>
       </c>
-      <c r="R219" s="6">
-        <v>6698</v>
+      <c r="R219" s="60">
+        <v>5698</v>
       </c>
       <c r="S219" s="6">
         <v>2312</v>
@@ -19209,7 +19215,7 @@
       <c r="AI219" s="2"/>
       <c r="AJ219" s="2"/>
     </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>223</v>
       </c>
@@ -19267,7 +19273,7 @@
       <c r="AI220" s="2"/>
       <c r="AJ220" s="2"/>
     </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A221" s="18" t="s">
         <v>224</v>
       </c>
@@ -19382,7 +19388,7 @@
         <v>14815</v>
       </c>
     </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
         <v>225</v>
       </c>
@@ -19436,7 +19442,7 @@
       <c r="AI222" s="2"/>
       <c r="AJ222" s="2"/>
     </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
         <v>226</v>
       </c>
@@ -19490,7 +19496,7 @@
       <c r="AI223" s="2"/>
       <c r="AJ223" s="2"/>
     </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A224" s="45" t="s">
         <v>227</v>
       </c>
@@ -19543,7 +19549,7 @@
       </c>
       <c r="AE224" s="23">
         <f>SUM(AE196:AE223)</f>
-        <v>283652</v>
+        <v>282652</v>
       </c>
       <c r="AF224" s="23">
         <f>SUM(AF196:AF223)</f>
@@ -19556,7 +19562,7 @@
       </c>
       <c r="AI224" s="23">
         <f>AE224-C224</f>
-        <v>-20669</v>
+        <v>-21669</v>
       </c>
       <c r="AJ224" s="23">
         <f>AF224-D224</f>
@@ -19604,7 +19610,7 @@
         <v>-2679</v>
       </c>
     </row>
-    <row r="225" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A225" s="18" t="s">
         <v>228</v>
       </c>
@@ -19681,7 +19687,7 @@
       <c r="AS225" s="12"/>
       <c r="AT225" s="12"/>
     </row>
-    <row r="226" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A226" s="18" t="s">
         <v>229</v>
       </c>
@@ -19800,7 +19806,7 @@
         <v>17487</v>
       </c>
     </row>
-    <row r="227" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>230</v>
       </c>
@@ -19852,7 +19858,7 @@
       <c r="AI227" s="2"/>
       <c r="AJ227" s="2"/>
     </row>
-    <row r="228" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>231</v>
       </c>
@@ -19904,7 +19910,7 @@
       <c r="AI228" s="2"/>
       <c r="AJ228" s="2"/>
     </row>
-    <row r="229" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A229" s="18" t="s">
         <v>232</v>
       </c>
@@ -20027,7 +20033,7 @@
         <v>12724</v>
       </c>
     </row>
-    <row r="230" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>233</v>
       </c>
@@ -20083,7 +20089,7 @@
       <c r="AI230" s="2"/>
       <c r="AJ230" s="2"/>
     </row>
-    <row r="231" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
         <v>234</v>
       </c>
@@ -20139,7 +20145,7 @@
       <c r="AI231" s="2"/>
       <c r="AJ231" s="2"/>
     </row>
-    <row r="232" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A232" s="18" t="s">
         <v>235</v>
       </c>
@@ -20256,7 +20262,7 @@
         <v>16324</v>
       </c>
     </row>
-    <row r="233" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>236</v>
       </c>
@@ -20306,7 +20312,7 @@
       <c r="AI233" s="2"/>
       <c r="AJ233" s="2"/>
     </row>
-    <row r="234" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
         <v>237</v>
       </c>
@@ -20356,7 +20362,7 @@
       <c r="AI234" s="2"/>
       <c r="AJ234" s="2"/>
     </row>
-    <row r="235" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A235" s="18" t="s">
         <v>238</v>
       </c>
@@ -20475,7 +20481,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="236" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
         <v>239</v>
       </c>
@@ -20533,7 +20539,7 @@
       <c r="AI236" s="2"/>
       <c r="AJ236" s="2"/>
     </row>
-    <row r="237" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>240</v>
       </c>
@@ -20591,7 +20597,7 @@
       <c r="AI237" s="2"/>
       <c r="AJ237" s="2"/>
     </row>
-    <row r="238" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A238" s="18" t="s">
         <v>241</v>
       </c>
@@ -20718,7 +20724,7 @@
         <v>60357</v>
       </c>
     </row>
-    <row r="239" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>242</v>
       </c>
@@ -20771,7 +20777,7 @@
       <c r="AB239" s="9"/>
       <c r="AC239" s="2"/>
     </row>
-    <row r="240" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>243</v>
       </c>
@@ -20799,7 +20805,7 @@
       <c r="Q240" s="6">
         <v>10542</v>
       </c>
-      <c r="R240" s="61">
+      <c r="R240" s="60">
         <v>424</v>
       </c>
       <c r="S240" s="6">
@@ -20831,7 +20837,7 @@
       <c r="AI240" s="2"/>
       <c r="AJ240" s="2"/>
     </row>
-    <row r="241" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A241" s="18" t="s">
         <v>244</v>
       </c>
@@ -20950,7 +20956,7 @@
         <v>36016</v>
       </c>
     </row>
-    <row r="242" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
         <v>245</v>
       </c>
@@ -21002,7 +21008,7 @@
       <c r="AI242" s="2"/>
       <c r="AJ242" s="2"/>
     </row>
-    <row r="243" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A243" s="11" t="s">
         <v>246</v>
       </c>
@@ -21054,7 +21060,7 @@
       <c r="AI243" s="2"/>
       <c r="AJ243" s="2"/>
     </row>
-    <row r="244" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A244" s="18" t="s">
         <v>247</v>
       </c>
@@ -21171,7 +21177,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="245" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
         <v>248</v>
       </c>
@@ -21221,7 +21227,7 @@
       <c r="AI245" s="2"/>
       <c r="AJ245" s="2"/>
     </row>
-    <row r="246" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
         <v>249</v>
       </c>
@@ -21271,7 +21277,7 @@
       <c r="AI246" s="2"/>
       <c r="AJ246" s="2"/>
     </row>
-    <row r="247" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A247" s="18" t="s">
         <v>250</v>
       </c>
@@ -21384,7 +21390,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="248" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>251</v>
       </c>
@@ -21430,7 +21436,7 @@
       <c r="AI248" s="2"/>
       <c r="AJ248" s="2"/>
     </row>
-    <row r="249" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>252</v>
       </c>
@@ -21476,7 +21482,7 @@
       <c r="AI249" s="2"/>
       <c r="AJ249" s="2"/>
     </row>
-    <row r="250" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A250" s="45" t="s">
         <v>253</v>
       </c>
@@ -21590,7 +21596,7 @@
         <v>-5324</v>
       </c>
     </row>
-    <row r="251" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A251" s="14" t="s">
         <v>254</v>
       </c>
@@ -21689,7 +21695,7 @@
         <v>10239</v>
       </c>
     </row>
-    <row r="252" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A252" s="14" t="s">
         <v>255</v>
       </c>
@@ -21767,7 +21773,7 @@
       <c r="AS252" s="12"/>
       <c r="AT252" s="12"/>
     </row>
-    <row r="253" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A253" s="14" t="s">
         <v>256</v>
       </c>
@@ -21863,7 +21869,7 @@
         <v>18.045821337734392</v>
       </c>
     </row>
-    <row r="254" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -21911,7 +21917,7 @@
       <c r="AI254" s="2"/>
       <c r="AJ254" s="2"/>
     </row>
-    <row r="255" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -21959,7 +21965,7 @@
       <c r="AI255" s="2"/>
       <c r="AJ255" s="2"/>
     </row>
-    <row r="256" spans="1:50" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A256" s="14" t="s">
         <v>259</v>
       </c>
@@ -22065,7 +22071,7 @@
       <c r="AS256" s="12"/>
       <c r="AT256" s="12"/>
     </row>
-    <row r="257" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -22115,7 +22121,7 @@
       <c r="AI257" s="2"/>
       <c r="AJ257" s="2"/>
     </row>
-    <row r="258" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>261</v>
       </c>
@@ -22165,7 +22171,7 @@
       <c r="AI258" s="2"/>
       <c r="AJ258" s="2"/>
     </row>
-    <row r="259" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A259" s="14" t="s">
         <v>262</v>
       </c>
@@ -22279,7 +22285,7 @@
         <v>9335</v>
       </c>
     </row>
-    <row r="260" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>263</v>
       </c>
@@ -22331,7 +22337,7 @@
       <c r="AI260" s="2"/>
       <c r="AJ260" s="2"/>
     </row>
-    <row r="261" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>264</v>
       </c>
@@ -22383,7 +22389,7 @@
       <c r="AI261" s="2"/>
       <c r="AJ261" s="2"/>
     </row>
-    <row r="262" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A262" s="14" t="s">
         <v>265</v>
       </c>
@@ -22491,7 +22497,7 @@
       <c r="AS262" s="12"/>
       <c r="AT262" s="12"/>
     </row>
-    <row r="263" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -22543,7 +22549,7 @@
       <c r="AI263" s="2"/>
       <c r="AJ263" s="2"/>
     </row>
-    <row r="264" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>267</v>
       </c>
@@ -22595,7 +22601,7 @@
       <c r="AI264" s="2"/>
       <c r="AJ264" s="2"/>
     </row>
-    <row r="265" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A265" s="14" t="s">
         <v>268</v>
       </c>
@@ -22699,7 +22705,7 @@
       <c r="AS265" s="12"/>
       <c r="AT265" s="12"/>
     </row>
-    <row r="266" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -22747,7 +22753,7 @@
       <c r="AI266" s="2"/>
       <c r="AJ266" s="2"/>
     </row>
-    <row r="267" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>270</v>
       </c>
@@ -22795,7 +22801,7 @@
       <c r="AI267" s="2"/>
       <c r="AJ267" s="2"/>
     </row>
-    <row r="268" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A268" s="14" t="s">
         <v>271</v>
       </c>
@@ -22905,7 +22911,7 @@
         <v>4397</v>
       </c>
     </row>
-    <row r="269" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>272</v>
       </c>
@@ -22953,7 +22959,7 @@
       <c r="AI269" s="2"/>
       <c r="AJ269" s="2"/>
     </row>
-    <row r="270" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>273</v>
       </c>
@@ -23001,7 +23007,7 @@
       <c r="AI270" s="2"/>
       <c r="AJ270" s="2"/>
     </row>
-    <row r="271" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A271" s="14" t="s">
         <v>274</v>
       </c>
@@ -23113,7 +23119,7 @@
       <c r="AS271" s="12"/>
       <c r="AT271" s="12"/>
     </row>
-    <row r="272" spans="1:46" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>275</v>
       </c>
@@ -23163,7 +23169,7 @@
       <c r="AI272" s="2"/>
       <c r="AJ272" s="2"/>
     </row>
-    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>276</v>
       </c>
@@ -23213,7 +23219,7 @@
       <c r="AI273" s="2"/>
       <c r="AJ273" s="2"/>
     </row>
-    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
       <c r="A274" s="21" t="s">
         <v>277</v>
       </c>
@@ -23326,7 +23332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
       <c r="A275" s="21" t="s">
         <v>278</v>
       </c>
@@ -23376,28 +23382,28 @@
       <c r="AC275" s="2"/>
       <c r="AD275" s="23">
         <f>SUM(AD195, AD224, AD250, AD274)</f>
-        <v>117989514</v>
+        <v>117910616</v>
       </c>
       <c r="AE275" s="23">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
-        <v>5349839</v>
+        <v>5350025</v>
       </c>
       <c r="AF275" s="23">
         <f>SUM(AF195, AF224, AF250, AF274)</f>
-        <v>3734550</v>
+        <v>3734717</v>
       </c>
       <c r="AG275" s="2"/>
       <c r="AH275" s="23">
         <f t="shared" si="246"/>
-        <v>-388636</v>
+        <v>-467534</v>
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="246"/>
-        <v>-19370</v>
+        <v>-19184</v>
       </c>
       <c r="AJ275" s="23">
         <f t="shared" si="246"/>
-        <v>-22870</v>
+        <v>-22703</v>
       </c>
       <c r="AL275" s="49">
         <f>C275/B275*1000</f>
@@ -23452,14 +23458,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C75BB2-12A9-42A6-B34F-FED52308A84D}">
   <dimension ref="A1:I410"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.15625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="5.89453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -23484,7 +23490,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
         <v>308</v>
       </c>
@@ -23509,7 +23515,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>309</v>
       </c>
@@ -23534,7 +23540,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>310</v>
       </c>
@@ -23559,7 +23565,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>311</v>
       </c>
@@ -23584,7 +23590,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>312</v>
       </c>
@@ -23609,7 +23615,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>313</v>
       </c>
@@ -23634,7 +23640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>314</v>
       </c>
@@ -23659,7 +23665,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
         <v>30</v>
       </c>
@@ -23684,7 +23690,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>315</v>
       </c>
@@ -23709,7 +23715,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="55" t="s">
         <v>316</v>
       </c>
@@ -23734,7 +23740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
         <v>39</v>
       </c>
@@ -23759,7 +23765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
         <v>317</v>
       </c>
@@ -23784,7 +23790,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>318</v>
       </c>
@@ -23809,7 +23815,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>319</v>
       </c>
@@ -23834,7 +23840,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
         <v>320</v>
       </c>
@@ -23859,7 +23865,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
         <v>321</v>
       </c>
@@ -23884,7 +23890,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>322</v>
       </c>
@@ -23909,7 +23915,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>323</v>
       </c>
@@ -23934,7 +23940,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>59</v>
       </c>
@@ -23959,7 +23965,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>62</v>
       </c>
@@ -23984,7 +23990,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>324</v>
       </c>
@@ -24009,7 +24015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
         <v>68</v>
       </c>
@@ -24034,7 +24040,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
         <v>71</v>
       </c>
@@ -24059,7 +24065,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="s">
         <v>325</v>
       </c>
@@ -24084,7 +24090,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>326</v>
       </c>
@@ -24109,7 +24115,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
         <v>327</v>
       </c>
@@ -24134,7 +24140,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>81</v>
       </c>
@@ -24159,7 +24165,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
         <v>328</v>
       </c>
@@ -24184,7 +24190,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="41" t="s">
         <v>329</v>
       </c>
@@ -24209,7 +24215,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="41" t="s">
         <v>330</v>
       </c>
@@ -24234,7 +24240,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="41" t="s">
         <v>331</v>
       </c>
@@ -24259,7 +24265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="s">
         <v>332</v>
       </c>
@@ -24284,7 +24290,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="41" t="s">
         <v>333</v>
       </c>
@@ -24309,7 +24315,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="41" t="s">
         <v>100</v>
       </c>
@@ -24334,7 +24340,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="41" t="s">
         <v>334</v>
       </c>
@@ -24359,7 +24365,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="41" t="s">
         <v>335</v>
       </c>
@@ -24384,7 +24390,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="41" t="s">
         <v>336</v>
       </c>
@@ -24409,7 +24415,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="41" t="s">
         <v>337</v>
       </c>
@@ -24434,7 +24440,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="41" t="s">
         <v>338</v>
       </c>
@@ -24459,7 +24465,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="41" t="s">
         <v>339</v>
       </c>
@@ -24484,7 +24490,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="41" t="s">
         <v>340</v>
       </c>
@@ -24509,7 +24515,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
         <v>341</v>
       </c>
@@ -24534,7 +24540,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
         <v>342</v>
       </c>
@@ -24559,7 +24565,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="41" t="s">
         <v>343</v>
       </c>
@@ -24584,7 +24590,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="41" t="s">
         <v>130</v>
       </c>
@@ -24609,7 +24615,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="41" t="s">
         <v>133</v>
       </c>
@@ -24634,7 +24640,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="41" t="s">
         <v>136</v>
       </c>
@@ -24659,7 +24665,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="41" t="s">
         <v>344</v>
       </c>
@@ -24684,7 +24690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="41" t="s">
         <v>345</v>
       </c>
@@ -24709,7 +24715,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
         <v>346</v>
       </c>
@@ -24734,7 +24740,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="41" t="s">
         <v>347</v>
       </c>
@@ -24759,7 +24765,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="41" t="s">
         <v>348</v>
       </c>
@@ -24784,7 +24790,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="41" t="s">
         <v>349</v>
       </c>
@@ -24809,7 +24815,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="41" t="s">
         <v>156</v>
       </c>
@@ -24834,7 +24840,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
         <v>159</v>
       </c>
@@ -24859,7 +24865,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
         <v>162</v>
       </c>
@@ -24884,7 +24890,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
         <v>165</v>
       </c>
@@ -24909,7 +24915,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
         <v>168</v>
       </c>
@@ -24934,7 +24940,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
         <v>350</v>
       </c>
@@ -24959,7 +24965,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
         <v>174</v>
       </c>
@@ -24984,7 +24990,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="41" t="s">
         <v>177</v>
       </c>
@@ -25009,7 +25015,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="41" t="s">
         <v>180</v>
       </c>
@@ -25034,7 +25040,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="41" t="s">
         <v>351</v>
       </c>
@@ -25059,7 +25065,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
         <v>352</v>
       </c>
@@ -25084,7 +25090,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
         <v>353</v>
       </c>
@@ -25109,7 +25115,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="41" t="s">
         <v>354</v>
       </c>
@@ -25134,7 +25140,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="41" t="s">
         <v>191</v>
       </c>
@@ -25159,7 +25165,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="41" t="s">
         <v>355</v>
       </c>
@@ -25184,7 +25190,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="41" t="s">
         <v>356</v>
       </c>
@@ -25209,7 +25215,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="41" t="s">
         <v>357</v>
       </c>
@@ -25234,7 +25240,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
         <v>358</v>
       </c>
@@ -25259,7 +25265,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
         <v>359</v>
       </c>
@@ -25284,7 +25290,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
         <v>361</v>
       </c>
@@ -25309,7 +25315,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="41" t="s">
         <v>362</v>
       </c>
@@ -25334,7 +25340,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
         <v>363</v>
       </c>
@@ -25359,7 +25365,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="41" t="s">
         <v>364</v>
       </c>
@@ -25384,7 +25390,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
         <v>365</v>
       </c>
@@ -25409,7 +25415,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
         <v>366</v>
       </c>
@@ -25434,7 +25440,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
         <v>367</v>
       </c>
@@ -25459,7 +25465,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="41" t="s">
         <v>368</v>
       </c>
@@ -25484,7 +25490,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
         <v>369</v>
       </c>
@@ -25509,7 +25515,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="41" t="s">
         <v>370</v>
       </c>
@@ -25534,7 +25540,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="41" t="s">
         <v>371</v>
       </c>
@@ -25559,7 +25565,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="41" t="s">
         <v>372</v>
       </c>
@@ -25584,7 +25590,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
         <v>373</v>
       </c>
@@ -25609,7 +25615,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
         <v>374</v>
       </c>
@@ -25634,7 +25640,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="41" t="s">
         <v>375</v>
       </c>
@@ -25659,7 +25665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="41" t="s">
         <v>376</v>
       </c>
@@ -25684,7 +25690,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="41" t="s">
         <v>377</v>
       </c>
@@ -25709,7 +25715,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="41" t="s">
         <v>378</v>
       </c>
@@ -25734,7 +25740,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="41" t="s">
         <v>379</v>
       </c>
@@ -25759,7 +25765,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
         <v>380</v>
       </c>
@@ -25784,7 +25790,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="41" t="s">
         <v>381</v>
       </c>
@@ -25809,7 +25815,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="41" t="s">
         <v>256</v>
       </c>
@@ -25828,7 +25834,7 @@
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="41" t="s">
         <v>382</v>
       </c>
@@ -25853,7 +25859,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="41" t="s">
         <v>383</v>
       </c>
@@ -25878,7 +25884,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="41" t="s">
         <v>384</v>
       </c>
@@ -25903,7 +25909,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="41" t="s">
         <v>385</v>
       </c>
@@ -25928,7 +25934,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="41" t="s">
         <v>386</v>
       </c>
@@ -25953,7 +25959,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="41" t="s">
         <v>387</v>
       </c>
@@ -25978,7 +25984,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="41" t="s">
         <v>388</v>
       </c>
@@ -26003,7 +26009,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="41" t="s">
         <v>389</v>
       </c>
@@ -26028,7 +26034,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="41"/>
       <c r="B104" s="41"/>
       <c r="C104" s="54"/>
@@ -26039,7 +26045,7 @@
       <c r="H104" s="54"/>
       <c r="I104" s="54"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="41"/>
       <c r="B105" s="41"/>
       <c r="C105" s="54"/>
@@ -26050,7 +26056,7 @@
       <c r="H105" s="54"/>
       <c r="I105" s="54"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="41"/>
       <c r="B106" s="41"/>
       <c r="C106" s="54"/>
@@ -26061,7 +26067,7 @@
       <c r="H106" s="54"/>
       <c r="I106" s="54"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="41"/>
       <c r="B107" s="41"/>
       <c r="C107" s="54"/>
@@ -26072,7 +26078,7 @@
       <c r="H107" s="54"/>
       <c r="I107" s="54"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="41"/>
       <c r="B108" s="41"/>
       <c r="C108" s="54"/>
@@ -26083,7 +26089,7 @@
       <c r="H108" s="54"/>
       <c r="I108" s="54"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="41"/>
       <c r="B109" s="41"/>
       <c r="C109" s="54"/>
@@ -26094,7 +26100,7 @@
       <c r="H109" s="54"/>
       <c r="I109" s="54"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
       <c r="C110" s="54"/>
@@ -26105,7 +26111,7 @@
       <c r="H110" s="54"/>
       <c r="I110" s="54"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="41"/>
       <c r="B111" s="41"/>
       <c r="C111" s="54"/>
@@ -26116,7 +26122,7 @@
       <c r="H111" s="54"/>
       <c r="I111" s="54"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="41"/>
       <c r="B112" s="41"/>
       <c r="C112" s="54"/>
@@ -26127,7 +26133,7 @@
       <c r="H112" s="54"/>
       <c r="I112" s="54"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="41"/>
       <c r="B113" s="41"/>
       <c r="C113" s="54"/>
@@ -26138,7 +26144,7 @@
       <c r="H113" s="54"/>
       <c r="I113" s="54"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="41"/>
       <c r="B114" s="41"/>
       <c r="C114" s="54"/>
@@ -26149,7 +26155,7 @@
       <c r="H114" s="54"/>
       <c r="I114" s="54"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="41"/>
       <c r="B115" s="41"/>
       <c r="C115" s="54"/>
@@ -26160,7 +26166,7 @@
       <c r="H115" s="54"/>
       <c r="I115" s="54"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="41"/>
       <c r="B116" s="41"/>
       <c r="C116" s="54"/>
@@ -26171,7 +26177,7 @@
       <c r="H116" s="54"/>
       <c r="I116" s="54"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="41"/>
       <c r="B117" s="41"/>
       <c r="C117" s="54"/>
@@ -26182,7 +26188,7 @@
       <c r="H117" s="54"/>
       <c r="I117" s="54"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
       <c r="C118" s="54"/>
@@ -26193,7 +26199,7 @@
       <c r="H118" s="54"/>
       <c r="I118" s="54"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
       <c r="C119" s="54"/>
@@ -26204,7 +26210,7 @@
       <c r="H119" s="54"/>
       <c r="I119" s="54"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
       <c r="C120" s="54"/>
@@ -26215,7 +26221,7 @@
       <c r="H120" s="54"/>
       <c r="I120" s="54"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
       <c r="C121" s="54"/>
@@ -26226,7 +26232,7 @@
       <c r="H121" s="54"/>
       <c r="I121" s="54"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
       <c r="C122" s="54"/>
@@ -26237,7 +26243,7 @@
       <c r="H122" s="54"/>
       <c r="I122" s="54"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
       <c r="C123" s="54"/>
@@ -26248,7 +26254,7 @@
       <c r="H123" s="54"/>
       <c r="I123" s="54"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
       <c r="C124" s="54"/>
@@ -26259,7 +26265,7 @@
       <c r="H124" s="54"/>
       <c r="I124" s="54"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
       <c r="C125" s="54"/>
@@ -26270,7 +26276,7 @@
       <c r="H125" s="54"/>
       <c r="I125" s="54"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="54"/>
@@ -26281,7 +26287,7 @@
       <c r="H126" s="54"/>
       <c r="I126" s="54"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
       <c r="C127" s="54"/>
@@ -26292,7 +26298,7 @@
       <c r="H127" s="54"/>
       <c r="I127" s="54"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
       <c r="C128" s="54"/>
@@ -26303,7 +26309,7 @@
       <c r="H128" s="54"/>
       <c r="I128" s="54"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
       <c r="C129" s="54"/>
@@ -26314,7 +26320,7 @@
       <c r="H129" s="54"/>
       <c r="I129" s="54"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
       <c r="C130" s="54"/>
@@ -26325,7 +26331,7 @@
       <c r="H130" s="54"/>
       <c r="I130" s="54"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
       <c r="C131" s="54"/>
@@ -26336,7 +26342,7 @@
       <c r="H131" s="54"/>
       <c r="I131" s="54"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
       <c r="C132" s="54"/>
@@ -26347,7 +26353,7 @@
       <c r="H132" s="54"/>
       <c r="I132" s="54"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
       <c r="C133" s="54"/>
@@ -26358,7 +26364,7 @@
       <c r="H133" s="54"/>
       <c r="I133" s="54"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
       <c r="C134" s="54"/>
@@ -26369,7 +26375,7 @@
       <c r="H134" s="54"/>
       <c r="I134" s="54"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
       <c r="C135" s="54"/>
@@ -26380,7 +26386,7 @@
       <c r="H135" s="54"/>
       <c r="I135" s="54"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
       <c r="C136" s="54"/>
@@ -26391,7 +26397,7 @@
       <c r="H136" s="54"/>
       <c r="I136" s="54"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="41"/>
       <c r="B137" s="41"/>
       <c r="C137" s="54"/>
@@ -26402,7 +26408,7 @@
       <c r="H137" s="54"/>
       <c r="I137" s="54"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="41"/>
       <c r="B138" s="41"/>
       <c r="C138" s="54"/>
@@ -26413,7 +26419,7 @@
       <c r="H138" s="54"/>
       <c r="I138" s="54"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="41"/>
       <c r="B139" s="41"/>
       <c r="C139" s="54"/>
@@ -26424,7 +26430,7 @@
       <c r="H139" s="54"/>
       <c r="I139" s="54"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="41"/>
       <c r="B140" s="41"/>
       <c r="C140" s="54"/>
@@ -26435,7 +26441,7 @@
       <c r="H140" s="54"/>
       <c r="I140" s="54"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="41"/>
       <c r="B141" s="41"/>
       <c r="C141" s="54"/>
@@ -26446,7 +26452,7 @@
       <c r="H141" s="54"/>
       <c r="I141" s="54"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="41"/>
       <c r="B142" s="41"/>
       <c r="C142" s="54"/>
@@ -26457,7 +26463,7 @@
       <c r="H142" s="54"/>
       <c r="I142" s="54"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="41"/>
       <c r="B143" s="41"/>
       <c r="C143" s="54"/>
@@ -26468,7 +26474,7 @@
       <c r="H143" s="54"/>
       <c r="I143" s="54"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="41"/>
       <c r="B144" s="41"/>
       <c r="C144" s="54"/>
@@ -26479,7 +26485,7 @@
       <c r="H144" s="54"/>
       <c r="I144" s="54"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="41"/>
       <c r="B145" s="41"/>
       <c r="C145" s="54"/>
@@ -26490,7 +26496,7 @@
       <c r="H145" s="54"/>
       <c r="I145" s="54"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="41"/>
       <c r="B146" s="41"/>
       <c r="C146" s="54"/>
@@ -26501,7 +26507,7 @@
       <c r="H146" s="54"/>
       <c r="I146" s="54"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="41"/>
       <c r="B147" s="41"/>
       <c r="C147" s="54"/>
@@ -26512,7 +26518,7 @@
       <c r="H147" s="54"/>
       <c r="I147" s="54"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="41"/>
       <c r="B148" s="41"/>
       <c r="C148" s="54"/>
@@ -26523,7 +26529,7 @@
       <c r="H148" s="54"/>
       <c r="I148" s="54"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="41"/>
       <c r="B149" s="41"/>
       <c r="C149" s="54"/>
@@ -26534,7 +26540,7 @@
       <c r="H149" s="54"/>
       <c r="I149" s="54"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="41"/>
       <c r="B150" s="41"/>
       <c r="C150" s="54"/>
@@ -26545,7 +26551,7 @@
       <c r="H150" s="54"/>
       <c r="I150" s="54"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
       <c r="C151" s="54"/>
@@ -26556,7 +26562,7 @@
       <c r="H151" s="54"/>
       <c r="I151" s="54"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="41"/>
       <c r="B152" s="41"/>
       <c r="C152" s="54"/>
@@ -26567,7 +26573,7 @@
       <c r="H152" s="54"/>
       <c r="I152" s="54"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="41"/>
       <c r="B153" s="41"/>
       <c r="C153" s="54"/>
@@ -26578,7 +26584,7 @@
       <c r="H153" s="54"/>
       <c r="I153" s="54"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="41"/>
       <c r="B154" s="41"/>
       <c r="C154" s="54"/>
@@ -26589,7 +26595,7 @@
       <c r="H154" s="54"/>
       <c r="I154" s="54"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="41"/>
       <c r="B155" s="41"/>
       <c r="C155" s="54"/>
@@ -26600,7 +26606,7 @@
       <c r="H155" s="54"/>
       <c r="I155" s="54"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="41"/>
       <c r="B156" s="41"/>
       <c r="C156" s="54"/>
@@ -26611,7 +26617,7 @@
       <c r="H156" s="54"/>
       <c r="I156" s="54"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="41"/>
       <c r="B157" s="41"/>
       <c r="C157" s="54"/>
@@ -26622,7 +26628,7 @@
       <c r="H157" s="54"/>
       <c r="I157" s="54"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="41"/>
       <c r="B158" s="41"/>
       <c r="C158" s="54"/>
@@ -26633,7 +26639,7 @@
       <c r="H158" s="54"/>
       <c r="I158" s="54"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="41"/>
       <c r="B159" s="41"/>
       <c r="C159" s="54"/>
@@ -26644,7 +26650,7 @@
       <c r="H159" s="54"/>
       <c r="I159" s="54"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="41"/>
       <c r="B160" s="41"/>
       <c r="C160" s="54"/>
@@ -26655,7 +26661,7 @@
       <c r="H160" s="54"/>
       <c r="I160" s="54"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="41"/>
       <c r="B161" s="41"/>
       <c r="C161" s="54"/>
@@ -26666,7 +26672,7 @@
       <c r="H161" s="54"/>
       <c r="I161" s="54"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="41"/>
       <c r="B162" s="41"/>
       <c r="C162" s="54"/>
@@ -26677,7 +26683,7 @@
       <c r="H162" s="54"/>
       <c r="I162" s="54"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="41"/>
       <c r="B163" s="41"/>
       <c r="C163" s="54"/>
@@ -26688,7 +26694,7 @@
       <c r="H163" s="54"/>
       <c r="I163" s="54"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="41"/>
       <c r="B164" s="41"/>
       <c r="C164" s="54"/>
@@ -26699,7 +26705,7 @@
       <c r="H164" s="54"/>
       <c r="I164" s="54"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="41"/>
       <c r="B165" s="41"/>
       <c r="C165" s="54"/>
@@ -26710,7 +26716,7 @@
       <c r="H165" s="54"/>
       <c r="I165" s="54"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="41"/>
       <c r="B166" s="41"/>
       <c r="C166" s="54"/>
@@ -26721,7 +26727,7 @@
       <c r="H166" s="54"/>
       <c r="I166" s="54"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="41"/>
       <c r="B167" s="41"/>
       <c r="C167" s="54"/>
@@ -26732,7 +26738,7 @@
       <c r="H167" s="54"/>
       <c r="I167" s="54"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="41"/>
       <c r="B168" s="41"/>
       <c r="C168" s="54"/>
@@ -26743,7 +26749,7 @@
       <c r="H168" s="54"/>
       <c r="I168" s="54"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="41"/>
       <c r="B169" s="41"/>
       <c r="C169" s="54"/>
@@ -26754,7 +26760,7 @@
       <c r="H169" s="54"/>
       <c r="I169" s="54"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="41"/>
       <c r="B170" s="41"/>
       <c r="C170" s="54"/>
@@ -26765,7 +26771,7 @@
       <c r="H170" s="54"/>
       <c r="I170" s="54"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="41"/>
       <c r="B171" s="41"/>
       <c r="C171" s="54"/>
@@ -26776,7 +26782,7 @@
       <c r="H171" s="54"/>
       <c r="I171" s="54"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="41"/>
       <c r="B172" s="41"/>
       <c r="C172" s="54"/>
@@ -26787,7 +26793,7 @@
       <c r="H172" s="54"/>
       <c r="I172" s="54"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="41"/>
       <c r="B173" s="41"/>
       <c r="C173" s="54"/>
@@ -26798,7 +26804,7 @@
       <c r="H173" s="54"/>
       <c r="I173" s="54"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="41"/>
       <c r="B174" s="41"/>
       <c r="C174" s="54"/>
@@ -26809,7 +26815,7 @@
       <c r="H174" s="54"/>
       <c r="I174" s="54"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
       <c r="C175" s="54"/>
@@ -26820,7 +26826,7 @@
       <c r="H175" s="54"/>
       <c r="I175" s="54"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="41"/>
       <c r="B176" s="41"/>
       <c r="C176" s="54"/>
@@ -26831,7 +26837,7 @@
       <c r="H176" s="54"/>
       <c r="I176" s="54"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="41"/>
       <c r="B177" s="41"/>
       <c r="C177" s="54"/>
@@ -26842,7 +26848,7 @@
       <c r="H177" s="54"/>
       <c r="I177" s="54"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="41"/>
       <c r="B178" s="41"/>
       <c r="C178" s="54"/>
@@ -26853,7 +26859,7 @@
       <c r="H178" s="54"/>
       <c r="I178" s="54"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="41"/>
       <c r="B179" s="41"/>
       <c r="C179" s="54"/>
@@ -26864,7 +26870,7 @@
       <c r="H179" s="54"/>
       <c r="I179" s="54"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="41"/>
       <c r="B180" s="41"/>
       <c r="C180" s="54"/>
@@ -26875,7 +26881,7 @@
       <c r="H180" s="54"/>
       <c r="I180" s="54"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="41"/>
       <c r="B181" s="41"/>
       <c r="C181" s="54"/>
@@ -26886,7 +26892,7 @@
       <c r="H181" s="54"/>
       <c r="I181" s="54"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="41"/>
       <c r="B182" s="41"/>
       <c r="C182" s="54"/>
@@ -26897,7 +26903,7 @@
       <c r="H182" s="54"/>
       <c r="I182" s="54"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="41"/>
       <c r="B183" s="41"/>
       <c r="C183" s="54"/>
@@ -26908,7 +26914,7 @@
       <c r="H183" s="54"/>
       <c r="I183" s="54"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="41"/>
       <c r="B184" s="41"/>
       <c r="C184" s="54"/>
@@ -26919,7 +26925,7 @@
       <c r="H184" s="54"/>
       <c r="I184" s="54"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="41"/>
       <c r="B185" s="41"/>
       <c r="C185" s="54"/>
@@ -26930,7 +26936,7 @@
       <c r="H185" s="54"/>
       <c r="I185" s="54"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="41"/>
       <c r="B186" s="41"/>
       <c r="C186" s="54"/>
@@ -26941,7 +26947,7 @@
       <c r="H186" s="54"/>
       <c r="I186" s="54"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="41"/>
       <c r="B187" s="41"/>
       <c r="C187" s="54"/>
@@ -26952,7 +26958,7 @@
       <c r="H187" s="54"/>
       <c r="I187" s="54"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="41"/>
       <c r="B188" s="41"/>
       <c r="C188" s="54"/>
@@ -26963,7 +26969,7 @@
       <c r="H188" s="54"/>
       <c r="I188" s="54"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="41"/>
       <c r="B189" s="41"/>
       <c r="C189" s="54"/>
@@ -26974,7 +26980,7 @@
       <c r="H189" s="54"/>
       <c r="I189" s="54"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="41"/>
       <c r="B190" s="41"/>
       <c r="C190" s="54"/>
@@ -26985,7 +26991,7 @@
       <c r="H190" s="54"/>
       <c r="I190" s="54"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="41"/>
       <c r="B191" s="41"/>
       <c r="C191" s="54"/>
@@ -26996,7 +27002,7 @@
       <c r="H191" s="54"/>
       <c r="I191" s="54"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="41"/>
       <c r="B192" s="41"/>
       <c r="C192" s="54"/>
@@ -27007,7 +27013,7 @@
       <c r="H192" s="54"/>
       <c r="I192" s="54"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="41"/>
       <c r="B193" s="41"/>
       <c r="C193" s="54"/>
@@ -27018,7 +27024,7 @@
       <c r="H193" s="54"/>
       <c r="I193" s="54"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="41"/>
       <c r="B194" s="41"/>
       <c r="C194" s="54"/>
@@ -27029,7 +27035,7 @@
       <c r="H194" s="54"/>
       <c r="I194" s="54"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="41"/>
       <c r="B195" s="41"/>
       <c r="C195" s="54"/>
@@ -27040,7 +27046,7 @@
       <c r="H195" s="54"/>
       <c r="I195" s="54"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="41"/>
       <c r="B196" s="41"/>
       <c r="C196" s="54"/>
@@ -27051,7 +27057,7 @@
       <c r="H196" s="54"/>
       <c r="I196" s="54"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="41"/>
       <c r="B197" s="41"/>
       <c r="C197" s="54"/>
@@ -27062,7 +27068,7 @@
       <c r="H197" s="54"/>
       <c r="I197" s="54"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="41"/>
       <c r="B198" s="41"/>
       <c r="C198" s="54"/>
@@ -27073,7 +27079,7 @@
       <c r="H198" s="54"/>
       <c r="I198" s="54"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="41"/>
       <c r="B199" s="41"/>
       <c r="C199" s="54"/>
@@ -27084,7 +27090,7 @@
       <c r="H199" s="54"/>
       <c r="I199" s="54"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="41"/>
       <c r="B200" s="41"/>
       <c r="C200" s="54"/>
@@ -27095,7 +27101,7 @@
       <c r="H200" s="54"/>
       <c r="I200" s="54"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="41"/>
       <c r="B201" s="41"/>
       <c r="C201" s="54"/>
@@ -27106,7 +27112,7 @@
       <c r="H201" s="54"/>
       <c r="I201" s="54"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="41"/>
       <c r="B202" s="41"/>
       <c r="C202" s="54"/>
@@ -27117,7 +27123,7 @@
       <c r="H202" s="54"/>
       <c r="I202" s="54"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="41"/>
       <c r="B203" s="41"/>
       <c r="C203" s="54"/>
@@ -27128,7 +27134,7 @@
       <c r="H203" s="54"/>
       <c r="I203" s="54"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="41"/>
       <c r="B204" s="41"/>
       <c r="C204" s="54"/>
@@ -27139,7 +27145,7 @@
       <c r="H204" s="54"/>
       <c r="I204" s="54"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="41"/>
       <c r="B205" s="41"/>
       <c r="C205" s="54"/>
@@ -27150,7 +27156,7 @@
       <c r="H205" s="54"/>
       <c r="I205" s="54"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="41"/>
       <c r="B206" s="41"/>
       <c r="C206" s="54"/>
@@ -27161,7 +27167,7 @@
       <c r="H206" s="54"/>
       <c r="I206" s="54"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="41"/>
       <c r="B207" s="41"/>
       <c r="C207" s="54"/>
@@ -27172,7 +27178,7 @@
       <c r="H207" s="54"/>
       <c r="I207" s="54"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="41"/>
       <c r="B208" s="41"/>
       <c r="C208" s="54"/>
@@ -27183,7 +27189,7 @@
       <c r="H208" s="54"/>
       <c r="I208" s="54"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="41"/>
       <c r="B209" s="41"/>
       <c r="C209" s="54"/>
@@ -27194,7 +27200,7 @@
       <c r="H209" s="54"/>
       <c r="I209" s="54"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="41"/>
       <c r="B210" s="41"/>
       <c r="C210" s="54"/>
@@ -27205,7 +27211,7 @@
       <c r="H210" s="54"/>
       <c r="I210" s="54"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="41"/>
       <c r="B211" s="41"/>
       <c r="C211" s="54"/>
@@ -27216,7 +27222,7 @@
       <c r="H211" s="54"/>
       <c r="I211" s="54"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="41"/>
       <c r="B212" s="41"/>
       <c r="C212" s="54"/>
@@ -27227,7 +27233,7 @@
       <c r="H212" s="54"/>
       <c r="I212" s="54"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="41"/>
       <c r="B213" s="41"/>
       <c r="C213" s="54"/>
@@ -27238,7 +27244,7 @@
       <c r="H213" s="54"/>
       <c r="I213" s="54"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="41"/>
       <c r="B214" s="41"/>
       <c r="C214" s="54"/>
@@ -27249,7 +27255,7 @@
       <c r="H214" s="54"/>
       <c r="I214" s="54"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="41"/>
       <c r="B215" s="41"/>
       <c r="C215" s="54"/>
@@ -27260,7 +27266,7 @@
       <c r="H215" s="54"/>
       <c r="I215" s="54"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="41"/>
       <c r="B216" s="41"/>
       <c r="C216" s="54"/>
@@ -27271,7 +27277,7 @@
       <c r="H216" s="54"/>
       <c r="I216" s="54"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="41"/>
       <c r="B217" s="41"/>
       <c r="C217" s="54"/>
@@ -27282,7 +27288,7 @@
       <c r="H217" s="54"/>
       <c r="I217" s="54"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="41"/>
       <c r="B218" s="41"/>
       <c r="C218" s="54"/>
@@ -27293,7 +27299,7 @@
       <c r="H218" s="54"/>
       <c r="I218" s="54"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="41"/>
       <c r="B219" s="41"/>
       <c r="C219" s="54"/>
@@ -27304,7 +27310,7 @@
       <c r="H219" s="54"/>
       <c r="I219" s="54"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="41"/>
       <c r="B220" s="41"/>
       <c r="C220" s="54"/>
@@ -27315,7 +27321,7 @@
       <c r="H220" s="54"/>
       <c r="I220" s="54"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="41"/>
       <c r="B221" s="41"/>
       <c r="C221" s="54"/>
@@ -27326,7 +27332,7 @@
       <c r="H221" s="54"/>
       <c r="I221" s="54"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="41"/>
       <c r="B222" s="41"/>
       <c r="C222" s="54"/>
@@ -27337,7 +27343,7 @@
       <c r="H222" s="54"/>
       <c r="I222" s="54"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="41"/>
       <c r="B223" s="41"/>
       <c r="C223" s="54"/>
@@ -27348,7 +27354,7 @@
       <c r="H223" s="54"/>
       <c r="I223" s="54"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="41"/>
       <c r="B224" s="41"/>
       <c r="C224" s="54"/>
@@ -27359,7 +27365,7 @@
       <c r="H224" s="54"/>
       <c r="I224" s="54"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="41"/>
       <c r="B225" s="41"/>
       <c r="C225" s="54"/>
@@ -27370,7 +27376,7 @@
       <c r="H225" s="54"/>
       <c r="I225" s="54"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="41"/>
       <c r="B226" s="41"/>
       <c r="C226" s="54"/>
@@ -27381,7 +27387,7 @@
       <c r="H226" s="54"/>
       <c r="I226" s="54"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="41"/>
       <c r="B227" s="41"/>
       <c r="C227" s="54"/>
@@ -27392,7 +27398,7 @@
       <c r="H227" s="54"/>
       <c r="I227" s="54"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="41"/>
       <c r="B228" s="41"/>
       <c r="C228" s="54"/>
@@ -27403,7 +27409,7 @@
       <c r="H228" s="54"/>
       <c r="I228" s="54"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="41"/>
       <c r="B229" s="41"/>
       <c r="C229" s="54"/>
@@ -27414,7 +27420,7 @@
       <c r="H229" s="54"/>
       <c r="I229" s="54"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="41"/>
       <c r="B230" s="41"/>
       <c r="C230" s="54"/>
@@ -27425,7 +27431,7 @@
       <c r="H230" s="54"/>
       <c r="I230" s="54"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="41"/>
       <c r="B231" s="41"/>
       <c r="C231" s="54"/>
@@ -27436,7 +27442,7 @@
       <c r="H231" s="54"/>
       <c r="I231" s="54"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="41"/>
       <c r="B232" s="41"/>
       <c r="C232" s="54"/>
@@ -27447,7 +27453,7 @@
       <c r="H232" s="54"/>
       <c r="I232" s="54"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="41"/>
       <c r="B233" s="41"/>
       <c r="C233" s="54"/>
@@ -27458,7 +27464,7 @@
       <c r="H233" s="54"/>
       <c r="I233" s="54"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="41"/>
       <c r="B234" s="41"/>
       <c r="C234" s="54"/>
@@ -27469,7 +27475,7 @@
       <c r="H234" s="54"/>
       <c r="I234" s="54"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="41"/>
       <c r="B235" s="41"/>
       <c r="C235" s="54"/>
@@ -27480,7 +27486,7 @@
       <c r="H235" s="54"/>
       <c r="I235" s="54"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="41"/>
       <c r="B236" s="41"/>
       <c r="C236" s="54"/>
@@ -27491,7 +27497,7 @@
       <c r="H236" s="54"/>
       <c r="I236" s="54"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="41"/>
       <c r="B237" s="41"/>
       <c r="C237" s="54"/>
@@ -27502,7 +27508,7 @@
       <c r="H237" s="54"/>
       <c r="I237" s="54"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="41"/>
       <c r="B238" s="41"/>
       <c r="C238" s="54"/>
@@ -27513,7 +27519,7 @@
       <c r="H238" s="54"/>
       <c r="I238" s="54"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="41"/>
       <c r="B239" s="41"/>
       <c r="C239" s="54"/>
@@ -27524,7 +27530,7 @@
       <c r="H239" s="54"/>
       <c r="I239" s="54"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="41"/>
       <c r="B240" s="41"/>
       <c r="C240" s="54"/>
@@ -27535,7 +27541,7 @@
       <c r="H240" s="54"/>
       <c r="I240" s="54"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="41"/>
       <c r="B241" s="41"/>
       <c r="C241" s="54"/>
@@ -27546,7 +27552,7 @@
       <c r="H241" s="54"/>
       <c r="I241" s="54"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="41"/>
       <c r="B242" s="41"/>
       <c r="C242" s="54"/>
@@ -27557,7 +27563,7 @@
       <c r="H242" s="54"/>
       <c r="I242" s="54"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="41"/>
       <c r="B243" s="41"/>
       <c r="C243" s="54"/>
@@ -27568,7 +27574,7 @@
       <c r="H243" s="54"/>
       <c r="I243" s="54"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="41"/>
       <c r="B244" s="41"/>
       <c r="C244" s="54"/>
@@ -27579,7 +27585,7 @@
       <c r="H244" s="54"/>
       <c r="I244" s="54"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="41"/>
       <c r="B245" s="41"/>
       <c r="C245" s="54"/>
@@ -27590,7 +27596,7 @@
       <c r="H245" s="54"/>
       <c r="I245" s="54"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="41"/>
       <c r="B246" s="41"/>
       <c r="C246" s="54"/>
@@ -27601,7 +27607,7 @@
       <c r="H246" s="54"/>
       <c r="I246" s="54"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="41"/>
       <c r="B247" s="41"/>
       <c r="C247" s="54"/>
@@ -27612,7 +27618,7 @@
       <c r="H247" s="54"/>
       <c r="I247" s="54"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="41"/>
       <c r="B248" s="41"/>
       <c r="C248" s="54"/>
@@ -27623,7 +27629,7 @@
       <c r="H248" s="54"/>
       <c r="I248" s="54"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="41"/>
       <c r="B249" s="41"/>
       <c r="C249" s="54"/>
@@ -27634,7 +27640,7 @@
       <c r="H249" s="54"/>
       <c r="I249" s="54"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="41"/>
       <c r="B250" s="41"/>
       <c r="C250" s="54"/>
@@ -27645,7 +27651,7 @@
       <c r="H250" s="54"/>
       <c r="I250" s="54"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="41"/>
       <c r="B251" s="41"/>
       <c r="C251" s="54"/>
@@ -27656,7 +27662,7 @@
       <c r="H251" s="54"/>
       <c r="I251" s="54"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="41"/>
       <c r="B252" s="41"/>
       <c r="C252" s="54"/>
@@ -27667,7 +27673,7 @@
       <c r="H252" s="54"/>
       <c r="I252" s="54"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="41"/>
       <c r="B253" s="41"/>
       <c r="C253" s="54"/>
@@ -27678,7 +27684,7 @@
       <c r="H253" s="54"/>
       <c r="I253" s="54"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="41"/>
       <c r="B254" s="41"/>
       <c r="C254" s="54"/>
@@ -27689,7 +27695,7 @@
       <c r="H254" s="54"/>
       <c r="I254" s="54"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="41"/>
       <c r="B255" s="41"/>
       <c r="C255" s="54"/>
@@ -27700,7 +27706,7 @@
       <c r="H255" s="54"/>
       <c r="I255" s="54"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="41"/>
       <c r="B256" s="41"/>
       <c r="C256" s="54"/>
@@ -27711,7 +27717,7 @@
       <c r="H256" s="54"/>
       <c r="I256" s="54"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="41"/>
       <c r="B257" s="41"/>
       <c r="C257" s="54"/>
@@ -27722,7 +27728,7 @@
       <c r="H257" s="54"/>
       <c r="I257" s="54"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="41"/>
       <c r="B258" s="41"/>
       <c r="C258" s="54"/>
@@ -27733,7 +27739,7 @@
       <c r="H258" s="54"/>
       <c r="I258" s="54"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="41"/>
       <c r="B259" s="41"/>
       <c r="C259" s="54"/>
@@ -27744,7 +27750,7 @@
       <c r="H259" s="54"/>
       <c r="I259" s="54"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="41"/>
       <c r="B260" s="41"/>
       <c r="C260" s="54"/>
@@ -27755,7 +27761,7 @@
       <c r="H260" s="54"/>
       <c r="I260" s="54"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="41"/>
       <c r="B261" s="41"/>
       <c r="C261" s="54"/>
@@ -27766,7 +27772,7 @@
       <c r="H261" s="54"/>
       <c r="I261" s="54"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="41"/>
       <c r="B262" s="41"/>
       <c r="C262" s="54"/>
@@ -27777,7 +27783,7 @@
       <c r="H262" s="54"/>
       <c r="I262" s="54"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="41"/>
       <c r="B263" s="41"/>
       <c r="C263" s="54"/>
@@ -27788,7 +27794,7 @@
       <c r="H263" s="54"/>
       <c r="I263" s="54"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="41"/>
       <c r="B264" s="41"/>
       <c r="C264" s="54"/>
@@ -27799,7 +27805,7 @@
       <c r="H264" s="54"/>
       <c r="I264" s="54"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="41"/>
       <c r="B265" s="41"/>
       <c r="C265" s="54"/>
@@ -27810,7 +27816,7 @@
       <c r="H265" s="54"/>
       <c r="I265" s="54"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="41"/>
       <c r="B266" s="41"/>
       <c r="C266" s="54"/>
@@ -27821,7 +27827,7 @@
       <c r="H266" s="54"/>
       <c r="I266" s="54"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="41"/>
       <c r="B267" s="41"/>
       <c r="C267" s="54"/>
@@ -27832,7 +27838,7 @@
       <c r="H267" s="54"/>
       <c r="I267" s="54"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="41"/>
       <c r="B268" s="41"/>
       <c r="C268" s="54"/>
@@ -27843,7 +27849,7 @@
       <c r="H268" s="54"/>
       <c r="I268" s="54"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="41"/>
       <c r="B269" s="41"/>
       <c r="C269" s="54"/>
@@ -27854,7 +27860,7 @@
       <c r="H269" s="54"/>
       <c r="I269" s="54"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="41"/>
       <c r="B270" s="41"/>
       <c r="C270" s="54"/>
@@ -27865,7 +27871,7 @@
       <c r="H270" s="54"/>
       <c r="I270" s="54"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="41"/>
       <c r="B271" s="41"/>
       <c r="C271" s="54"/>
@@ -27876,7 +27882,7 @@
       <c r="H271" s="54"/>
       <c r="I271" s="54"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="41"/>
       <c r="B272" s="41"/>
       <c r="C272" s="54"/>
@@ -27887,7 +27893,7 @@
       <c r="H272" s="54"/>
       <c r="I272" s="54"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="41"/>
       <c r="B273" s="41"/>
       <c r="C273" s="54"/>
@@ -27898,7 +27904,7 @@
       <c r="H273" s="54"/>
       <c r="I273" s="54"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="41"/>
       <c r="B274" s="41"/>
       <c r="C274" s="54"/>
@@ -27909,7 +27915,7 @@
       <c r="H274" s="54"/>
       <c r="I274" s="54"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="41"/>
       <c r="B275" s="41"/>
       <c r="C275" s="54"/>
@@ -27920,7 +27926,7 @@
       <c r="H275" s="54"/>
       <c r="I275" s="54"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="41"/>
       <c r="B276" s="41"/>
       <c r="C276" s="54"/>
@@ -27931,7 +27937,7 @@
       <c r="H276" s="54"/>
       <c r="I276" s="54"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="41"/>
       <c r="B277" s="41"/>
       <c r="C277" s="54"/>
@@ -27942,7 +27948,7 @@
       <c r="H277" s="54"/>
       <c r="I277" s="54"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="41"/>
       <c r="B278" s="41"/>
       <c r="C278" s="54"/>
@@ -27953,7 +27959,7 @@
       <c r="H278" s="54"/>
       <c r="I278" s="54"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="41"/>
       <c r="B279" s="41"/>
       <c r="C279" s="54"/>
@@ -27964,7 +27970,7 @@
       <c r="H279" s="54"/>
       <c r="I279" s="54"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="41"/>
       <c r="B280" s="41"/>
       <c r="C280" s="54"/>
@@ -27975,7 +27981,7 @@
       <c r="H280" s="54"/>
       <c r="I280" s="54"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="41"/>
       <c r="B281" s="41"/>
       <c r="C281" s="54"/>
@@ -27986,7 +27992,7 @@
       <c r="H281" s="54"/>
       <c r="I281" s="54"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="41"/>
       <c r="B282" s="41"/>
       <c r="C282" s="54"/>
@@ -27997,7 +28003,7 @@
       <c r="H282" s="54"/>
       <c r="I282" s="54"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="41"/>
       <c r="B283" s="41"/>
       <c r="C283" s="54"/>
@@ -28008,7 +28014,7 @@
       <c r="H283" s="54"/>
       <c r="I283" s="54"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="41"/>
       <c r="B284" s="41"/>
       <c r="C284" s="54"/>
@@ -28019,7 +28025,7 @@
       <c r="H284" s="54"/>
       <c r="I284" s="54"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="41"/>
       <c r="B285" s="41"/>
       <c r="C285" s="54"/>
@@ -28030,7 +28036,7 @@
       <c r="H285" s="54"/>
       <c r="I285" s="54"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="41"/>
       <c r="B286" s="41"/>
       <c r="C286" s="54"/>
@@ -28041,7 +28047,7 @@
       <c r="H286" s="54"/>
       <c r="I286" s="54"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="41"/>
       <c r="B287" s="41"/>
       <c r="C287" s="54"/>
@@ -28052,7 +28058,7 @@
       <c r="H287" s="54"/>
       <c r="I287" s="54"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="41"/>
       <c r="B288" s="41"/>
       <c r="C288" s="54"/>
@@ -28063,7 +28069,7 @@
       <c r="H288" s="54"/>
       <c r="I288" s="54"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="41"/>
       <c r="B289" s="41"/>
       <c r="C289" s="54"/>
@@ -28074,7 +28080,7 @@
       <c r="H289" s="54"/>
       <c r="I289" s="54"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="41"/>
       <c r="B290" s="41"/>
       <c r="C290" s="54"/>
@@ -28085,7 +28091,7 @@
       <c r="H290" s="54"/>
       <c r="I290" s="54"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="41"/>
       <c r="B291" s="41"/>
       <c r="C291" s="54"/>
@@ -28096,7 +28102,7 @@
       <c r="H291" s="54"/>
       <c r="I291" s="54"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="41"/>
       <c r="B292" s="41"/>
       <c r="C292" s="54"/>
@@ -28107,7 +28113,7 @@
       <c r="H292" s="54"/>
       <c r="I292" s="54"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="41"/>
       <c r="B293" s="41"/>
       <c r="C293" s="54"/>
@@ -28118,7 +28124,7 @@
       <c r="H293" s="54"/>
       <c r="I293" s="54"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="41"/>
       <c r="B294" s="41"/>
       <c r="C294" s="54"/>
@@ -28129,7 +28135,7 @@
       <c r="H294" s="54"/>
       <c r="I294" s="54"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="41"/>
       <c r="B295" s="41"/>
       <c r="C295" s="54"/>
@@ -28140,7 +28146,7 @@
       <c r="H295" s="54"/>
       <c r="I295" s="54"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="41"/>
       <c r="B296" s="41"/>
       <c r="C296" s="54"/>
@@ -28151,7 +28157,7 @@
       <c r="H296" s="54"/>
       <c r="I296" s="54"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="41"/>
       <c r="B297" s="41"/>
       <c r="C297" s="54"/>
@@ -28162,7 +28168,7 @@
       <c r="H297" s="54"/>
       <c r="I297" s="54"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="41"/>
       <c r="B298" s="41"/>
       <c r="C298" s="54"/>
@@ -28173,7 +28179,7 @@
       <c r="H298" s="54"/>
       <c r="I298" s="54"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="41"/>
       <c r="B299" s="41"/>
       <c r="C299" s="54"/>
@@ -28184,7 +28190,7 @@
       <c r="H299" s="54"/>
       <c r="I299" s="54"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="41"/>
       <c r="B300" s="41"/>
       <c r="C300" s="54"/>
@@ -28195,7 +28201,7 @@
       <c r="H300" s="54"/>
       <c r="I300" s="54"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="41"/>
       <c r="B301" s="41"/>
       <c r="C301" s="54"/>
@@ -28206,7 +28212,7 @@
       <c r="H301" s="54"/>
       <c r="I301" s="54"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="41"/>
       <c r="B302" s="41"/>
       <c r="C302" s="54"/>
@@ -28217,7 +28223,7 @@
       <c r="H302" s="54"/>
       <c r="I302" s="54"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="41"/>
       <c r="B303" s="41"/>
       <c r="C303" s="54"/>
@@ -28228,7 +28234,7 @@
       <c r="H303" s="54"/>
       <c r="I303" s="54"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="41"/>
       <c r="B304" s="41"/>
       <c r="C304" s="54"/>
@@ -28239,7 +28245,7 @@
       <c r="H304" s="54"/>
       <c r="I304" s="54"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="41"/>
       <c r="B305" s="41"/>
       <c r="C305" s="54"/>
@@ -28250,7 +28256,7 @@
       <c r="H305" s="54"/>
       <c r="I305" s="54"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="41"/>
       <c r="B306" s="41"/>
       <c r="C306" s="54"/>
@@ -28261,7 +28267,7 @@
       <c r="H306" s="54"/>
       <c r="I306" s="54"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="41"/>
       <c r="B307" s="41"/>
       <c r="C307" s="54"/>
@@ -28272,7 +28278,7 @@
       <c r="H307" s="54"/>
       <c r="I307" s="54"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="41"/>
       <c r="B308" s="41"/>
       <c r="C308" s="54"/>
@@ -28283,7 +28289,7 @@
       <c r="H308" s="54"/>
       <c r="I308" s="54"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="41"/>
       <c r="B309" s="41"/>
       <c r="C309" s="54"/>
@@ -28294,7 +28300,7 @@
       <c r="H309" s="54"/>
       <c r="I309" s="54"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="41"/>
       <c r="B310" s="41"/>
       <c r="C310" s="54"/>
@@ -28305,7 +28311,7 @@
       <c r="H310" s="54"/>
       <c r="I310" s="54"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="41"/>
       <c r="B311" s="41"/>
       <c r="C311" s="54"/>
@@ -28316,7 +28322,7 @@
       <c r="H311" s="54"/>
       <c r="I311" s="54"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="41"/>
       <c r="B312" s="41"/>
       <c r="C312" s="54"/>
@@ -28327,7 +28333,7 @@
       <c r="H312" s="54"/>
       <c r="I312" s="54"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="41"/>
       <c r="B313" s="41"/>
       <c r="C313" s="54"/>
@@ -28338,7 +28344,7 @@
       <c r="H313" s="54"/>
       <c r="I313" s="54"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="41"/>
       <c r="B314" s="41"/>
       <c r="C314" s="54"/>
@@ -28349,7 +28355,7 @@
       <c r="H314" s="54"/>
       <c r="I314" s="54"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="41"/>
       <c r="B315" s="41"/>
       <c r="C315" s="54"/>
@@ -28360,7 +28366,7 @@
       <c r="H315" s="54"/>
       <c r="I315" s="54"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="41"/>
       <c r="B316" s="41"/>
       <c r="C316" s="54"/>
@@ -28371,7 +28377,7 @@
       <c r="H316" s="54"/>
       <c r="I316" s="54"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="41"/>
       <c r="B317" s="41"/>
       <c r="C317" s="54"/>
@@ -28382,7 +28388,7 @@
       <c r="H317" s="54"/>
       <c r="I317" s="54"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="41"/>
       <c r="B318" s="41"/>
       <c r="C318" s="54"/>
@@ -28393,7 +28399,7 @@
       <c r="H318" s="54"/>
       <c r="I318" s="54"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="41"/>
       <c r="B319" s="41"/>
       <c r="C319" s="54"/>
@@ -28404,7 +28410,7 @@
       <c r="H319" s="54"/>
       <c r="I319" s="54"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="41"/>
       <c r="B320" s="41"/>
       <c r="C320" s="54"/>
@@ -28415,7 +28421,7 @@
       <c r="H320" s="54"/>
       <c r="I320" s="54"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="41"/>
       <c r="B321" s="41"/>
       <c r="C321" s="54"/>
@@ -28426,7 +28432,7 @@
       <c r="H321" s="54"/>
       <c r="I321" s="54"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="41"/>
       <c r="B322" s="41"/>
       <c r="C322" s="54"/>
@@ -28437,7 +28443,7 @@
       <c r="H322" s="54"/>
       <c r="I322" s="54"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="41"/>
       <c r="B323" s="41"/>
       <c r="C323" s="54"/>
@@ -28448,7 +28454,7 @@
       <c r="H323" s="54"/>
       <c r="I323" s="54"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="41"/>
       <c r="B324" s="41"/>
       <c r="C324" s="54"/>
@@ -28459,7 +28465,7 @@
       <c r="H324" s="54"/>
       <c r="I324" s="54"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="41"/>
       <c r="B325" s="41"/>
       <c r="C325" s="54"/>
@@ -28470,7 +28476,7 @@
       <c r="H325" s="54"/>
       <c r="I325" s="54"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="41"/>
       <c r="B326" s="41"/>
       <c r="C326" s="54"/>
@@ -28481,7 +28487,7 @@
       <c r="H326" s="54"/>
       <c r="I326" s="54"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="41"/>
       <c r="B327" s="41"/>
       <c r="C327" s="54"/>
@@ -28492,7 +28498,7 @@
       <c r="H327" s="54"/>
       <c r="I327" s="54"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="41"/>
       <c r="B328" s="41"/>
       <c r="C328" s="54"/>
@@ -28503,7 +28509,7 @@
       <c r="H328" s="54"/>
       <c r="I328" s="54"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="41"/>
       <c r="B329" s="41"/>
       <c r="C329" s="54"/>
@@ -28514,7 +28520,7 @@
       <c r="H329" s="54"/>
       <c r="I329" s="54"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="41"/>
       <c r="B330" s="41"/>
       <c r="C330" s="54"/>
@@ -28525,7 +28531,7 @@
       <c r="H330" s="54"/>
       <c r="I330" s="54"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="41"/>
       <c r="B331" s="41"/>
       <c r="C331" s="54"/>
@@ -28536,7 +28542,7 @@
       <c r="H331" s="54"/>
       <c r="I331" s="54"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="41"/>
       <c r="B332" s="41"/>
       <c r="C332" s="54"/>
@@ -28547,7 +28553,7 @@
       <c r="H332" s="54"/>
       <c r="I332" s="54"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="41"/>
       <c r="B333" s="41"/>
       <c r="C333" s="54"/>
@@ -28558,7 +28564,7 @@
       <c r="H333" s="54"/>
       <c r="I333" s="54"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="41"/>
       <c r="B334" s="41"/>
       <c r="C334" s="54"/>
@@ -28569,7 +28575,7 @@
       <c r="H334" s="54"/>
       <c r="I334" s="54"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="41"/>
       <c r="B335" s="41"/>
       <c r="C335" s="54"/>
@@ -28580,7 +28586,7 @@
       <c r="H335" s="54"/>
       <c r="I335" s="54"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="41"/>
       <c r="B336" s="41"/>
       <c r="C336" s="54"/>
@@ -28591,7 +28597,7 @@
       <c r="H336" s="54"/>
       <c r="I336" s="54"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="41"/>
       <c r="B337" s="41"/>
       <c r="C337" s="54"/>
@@ -28602,7 +28608,7 @@
       <c r="H337" s="54"/>
       <c r="I337" s="54"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="41"/>
       <c r="B338" s="41"/>
       <c r="C338" s="54"/>
@@ -28613,7 +28619,7 @@
       <c r="H338" s="54"/>
       <c r="I338" s="54"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="41"/>
       <c r="B339" s="41"/>
       <c r="C339" s="54"/>
@@ -28624,7 +28630,7 @@
       <c r="H339" s="54"/>
       <c r="I339" s="54"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="41"/>
       <c r="B340" s="41"/>
       <c r="C340" s="54"/>
@@ -28635,7 +28641,7 @@
       <c r="H340" s="54"/>
       <c r="I340" s="54"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="41"/>
       <c r="B341" s="41"/>
       <c r="C341" s="54"/>
@@ -28646,7 +28652,7 @@
       <c r="H341" s="54"/>
       <c r="I341" s="54"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="41"/>
       <c r="B342" s="41"/>
       <c r="C342" s="54"/>
@@ -28657,7 +28663,7 @@
       <c r="H342" s="54"/>
       <c r="I342" s="54"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="41"/>
       <c r="B343" s="41"/>
       <c r="C343" s="54"/>
@@ -28668,7 +28674,7 @@
       <c r="H343" s="54"/>
       <c r="I343" s="54"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="41"/>
       <c r="B344" s="41"/>
       <c r="C344" s="54"/>
@@ -28679,7 +28685,7 @@
       <c r="H344" s="54"/>
       <c r="I344" s="54"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="41"/>
       <c r="B345" s="41"/>
       <c r="C345" s="54"/>
@@ -28690,7 +28696,7 @@
       <c r="H345" s="54"/>
       <c r="I345" s="54"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="41"/>
       <c r="B346" s="41"/>
       <c r="C346" s="54"/>
@@ -28701,7 +28707,7 @@
       <c r="H346" s="54"/>
       <c r="I346" s="54"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="41"/>
       <c r="B347" s="41"/>
       <c r="C347" s="54"/>
@@ -28712,7 +28718,7 @@
       <c r="H347" s="54"/>
       <c r="I347" s="54"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="41"/>
       <c r="B348" s="41"/>
       <c r="C348" s="54"/>
@@ -28723,7 +28729,7 @@
       <c r="H348" s="54"/>
       <c r="I348" s="54"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="41"/>
       <c r="B349" s="41"/>
       <c r="C349" s="54"/>
@@ -28734,7 +28740,7 @@
       <c r="H349" s="54"/>
       <c r="I349" s="54"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="41"/>
       <c r="B350" s="41"/>
       <c r="C350" s="54"/>
@@ -28745,7 +28751,7 @@
       <c r="H350" s="54"/>
       <c r="I350" s="54"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="41"/>
       <c r="B351" s="41"/>
       <c r="C351" s="54"/>
@@ -28756,7 +28762,7 @@
       <c r="H351" s="54"/>
       <c r="I351" s="54"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="41"/>
       <c r="B352" s="41"/>
       <c r="C352" s="54"/>
@@ -28767,7 +28773,7 @@
       <c r="H352" s="54"/>
       <c r="I352" s="54"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="41"/>
       <c r="B353" s="41"/>
       <c r="C353" s="54"/>
@@ -28778,7 +28784,7 @@
       <c r="H353" s="54"/>
       <c r="I353" s="54"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="41"/>
       <c r="B354" s="41"/>
       <c r="C354" s="54"/>
@@ -28789,7 +28795,7 @@
       <c r="H354" s="54"/>
       <c r="I354" s="54"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="41"/>
       <c r="B355" s="41"/>
       <c r="C355" s="54"/>
@@ -28800,7 +28806,7 @@
       <c r="H355" s="54"/>
       <c r="I355" s="54"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="41"/>
       <c r="B356" s="41"/>
       <c r="C356" s="54"/>
@@ -28811,7 +28817,7 @@
       <c r="H356" s="54"/>
       <c r="I356" s="54"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="41"/>
       <c r="B357" s="41"/>
       <c r="C357" s="54"/>
@@ -28822,7 +28828,7 @@
       <c r="H357" s="54"/>
       <c r="I357" s="54"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="41"/>
       <c r="B358" s="41"/>
       <c r="C358" s="54"/>
@@ -28833,7 +28839,7 @@
       <c r="H358" s="54"/>
       <c r="I358" s="54"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="41"/>
       <c r="B359" s="41"/>
       <c r="C359" s="54"/>
@@ -28844,7 +28850,7 @@
       <c r="H359" s="54"/>
       <c r="I359" s="54"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="41"/>
       <c r="B360" s="41"/>
       <c r="C360" s="54"/>
@@ -28855,7 +28861,7 @@
       <c r="H360" s="54"/>
       <c r="I360" s="54"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="41"/>
       <c r="B361" s="41"/>
       <c r="C361" s="54"/>
@@ -28866,7 +28872,7 @@
       <c r="H361" s="54"/>
       <c r="I361" s="54"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="41"/>
       <c r="B362" s="41"/>
       <c r="C362" s="54"/>
@@ -28877,7 +28883,7 @@
       <c r="H362" s="54"/>
       <c r="I362" s="54"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="41"/>
       <c r="B363" s="41"/>
       <c r="C363" s="54"/>
@@ -28888,7 +28894,7 @@
       <c r="H363" s="54"/>
       <c r="I363" s="54"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="41"/>
       <c r="B364" s="41"/>
       <c r="C364" s="54"/>
@@ -28899,7 +28905,7 @@
       <c r="H364" s="54"/>
       <c r="I364" s="54"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="41"/>
       <c r="B365" s="41"/>
       <c r="C365" s="54"/>
@@ -28910,7 +28916,7 @@
       <c r="H365" s="54"/>
       <c r="I365" s="54"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="41"/>
       <c r="B366" s="41"/>
       <c r="C366" s="54"/>
@@ -28921,7 +28927,7 @@
       <c r="H366" s="54"/>
       <c r="I366" s="54"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="41"/>
       <c r="B367" s="41"/>
       <c r="C367" s="54"/>
@@ -28932,7 +28938,7 @@
       <c r="H367" s="54"/>
       <c r="I367" s="54"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="41"/>
       <c r="B368" s="41"/>
       <c r="C368" s="54"/>
@@ -28943,7 +28949,7 @@
       <c r="H368" s="54"/>
       <c r="I368" s="54"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="41"/>
       <c r="B369" s="41"/>
       <c r="C369" s="54"/>
@@ -28954,7 +28960,7 @@
       <c r="H369" s="54"/>
       <c r="I369" s="54"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="41"/>
       <c r="B370" s="41"/>
       <c r="C370" s="54"/>
@@ -28965,7 +28971,7 @@
       <c r="H370" s="54"/>
       <c r="I370" s="54"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="41"/>
       <c r="B371" s="41"/>
       <c r="C371" s="54"/>
@@ -28976,7 +28982,7 @@
       <c r="H371" s="54"/>
       <c r="I371" s="54"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="41"/>
       <c r="B372" s="41"/>
       <c r="C372" s="54"/>
@@ -28987,7 +28993,7 @@
       <c r="H372" s="54"/>
       <c r="I372" s="54"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="41"/>
       <c r="B373" s="41"/>
       <c r="C373" s="54"/>
@@ -28998,7 +29004,7 @@
       <c r="H373" s="54"/>
       <c r="I373" s="54"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="41"/>
       <c r="B374" s="41"/>
       <c r="C374" s="54"/>
@@ -29009,7 +29015,7 @@
       <c r="H374" s="54"/>
       <c r="I374" s="54"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="41"/>
       <c r="B375" s="41"/>
       <c r="C375" s="54"/>
@@ -29020,7 +29026,7 @@
       <c r="H375" s="54"/>
       <c r="I375" s="54"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="41"/>
       <c r="B376" s="41"/>
       <c r="C376" s="54"/>
@@ -29031,7 +29037,7 @@
       <c r="H376" s="54"/>
       <c r="I376" s="54"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" s="41"/>
       <c r="B377" s="41"/>
       <c r="C377" s="54"/>
@@ -29042,7 +29048,7 @@
       <c r="H377" s="54"/>
       <c r="I377" s="54"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" s="41"/>
       <c r="B378" s="41"/>
       <c r="C378" s="54"/>
@@ -29053,7 +29059,7 @@
       <c r="H378" s="54"/>
       <c r="I378" s="54"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" s="41"/>
       <c r="B379" s="41"/>
       <c r="C379" s="54"/>
@@ -29064,7 +29070,7 @@
       <c r="H379" s="54"/>
       <c r="I379" s="54"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" s="41"/>
       <c r="B380" s="41"/>
       <c r="C380" s="54"/>
@@ -29075,7 +29081,7 @@
       <c r="H380" s="54"/>
       <c r="I380" s="54"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" s="41"/>
       <c r="B381" s="41"/>
       <c r="C381" s="54"/>
@@ -29086,7 +29092,7 @@
       <c r="H381" s="54"/>
       <c r="I381" s="54"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" s="41"/>
       <c r="B382" s="41"/>
       <c r="C382" s="54"/>
@@ -29097,7 +29103,7 @@
       <c r="H382" s="54"/>
       <c r="I382" s="54"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" s="41"/>
       <c r="B383" s="41"/>
       <c r="C383" s="54"/>
@@ -29108,7 +29114,7 @@
       <c r="H383" s="54"/>
       <c r="I383" s="54"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" s="41"/>
       <c r="B384" s="41"/>
       <c r="C384" s="54"/>
@@ -29119,7 +29125,7 @@
       <c r="H384" s="54"/>
       <c r="I384" s="54"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" s="41"/>
       <c r="B385" s="41"/>
       <c r="C385" s="54"/>
@@ -29130,7 +29136,7 @@
       <c r="H385" s="54"/>
       <c r="I385" s="54"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" s="41"/>
       <c r="B386" s="41"/>
       <c r="C386" s="54"/>
@@ -29141,7 +29147,7 @@
       <c r="H386" s="54"/>
       <c r="I386" s="54"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" s="41"/>
       <c r="B387" s="41"/>
       <c r="C387" s="54"/>
@@ -29152,7 +29158,7 @@
       <c r="H387" s="54"/>
       <c r="I387" s="54"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" s="41"/>
       <c r="B388" s="41"/>
       <c r="C388" s="54"/>
@@ -29163,7 +29169,7 @@
       <c r="H388" s="54"/>
       <c r="I388" s="54"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" s="41"/>
       <c r="B389" s="41"/>
       <c r="C389" s="54"/>
@@ -29174,7 +29180,7 @@
       <c r="H389" s="54"/>
       <c r="I389" s="54"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" s="41"/>
       <c r="B390" s="41"/>
       <c r="C390" s="54"/>
@@ -29185,7 +29191,7 @@
       <c r="H390" s="54"/>
       <c r="I390" s="54"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" s="41"/>
       <c r="B391" s="41"/>
       <c r="C391" s="54"/>
@@ -29196,7 +29202,7 @@
       <c r="H391" s="54"/>
       <c r="I391" s="54"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" s="41"/>
       <c r="B392" s="41"/>
       <c r="C392" s="54"/>
@@ -29207,7 +29213,7 @@
       <c r="H392" s="54"/>
       <c r="I392" s="54"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" s="41"/>
       <c r="B393" s="41"/>
       <c r="C393" s="54"/>
@@ -29218,7 +29224,7 @@
       <c r="H393" s="54"/>
       <c r="I393" s="54"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" s="41"/>
       <c r="B394" s="41"/>
       <c r="C394" s="54"/>
@@ -29229,7 +29235,7 @@
       <c r="H394" s="54"/>
       <c r="I394" s="54"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" s="41"/>
       <c r="B395" s="41"/>
       <c r="C395" s="54"/>
@@ -29240,7 +29246,7 @@
       <c r="H395" s="54"/>
       <c r="I395" s="54"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" s="41"/>
       <c r="B396" s="41"/>
       <c r="C396" s="54"/>
@@ -29251,7 +29257,7 @@
       <c r="H396" s="54"/>
       <c r="I396" s="54"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" s="41"/>
       <c r="B397" s="41"/>
       <c r="C397" s="54"/>
@@ -29262,7 +29268,7 @@
       <c r="H397" s="54"/>
       <c r="I397" s="54"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" s="41"/>
       <c r="B398" s="41"/>
       <c r="C398" s="54"/>
@@ -29273,7 +29279,7 @@
       <c r="H398" s="54"/>
       <c r="I398" s="54"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" s="41"/>
       <c r="B399" s="41"/>
       <c r="C399" s="54"/>
@@ -29284,7 +29290,7 @@
       <c r="H399" s="54"/>
       <c r="I399" s="54"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" s="41"/>
       <c r="B400" s="41"/>
       <c r="C400" s="54"/>
@@ -29295,7 +29301,7 @@
       <c r="H400" s="54"/>
       <c r="I400" s="54"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" s="41"/>
       <c r="B401" s="41"/>
       <c r="C401" s="54"/>
@@ -29306,7 +29312,7 @@
       <c r="H401" s="54"/>
       <c r="I401" s="54"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" s="41"/>
       <c r="B402" s="41"/>
       <c r="C402" s="54"/>
@@ -29317,7 +29323,7 @@
       <c r="H402" s="54"/>
       <c r="I402" s="54"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" s="41"/>
       <c r="B403" s="41"/>
       <c r="C403" s="54"/>
@@ -29328,7 +29334,7 @@
       <c r="H403" s="54"/>
       <c r="I403" s="54"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" s="41"/>
       <c r="B404" s="41"/>
       <c r="C404" s="54"/>
@@ -29339,7 +29345,7 @@
       <c r="H404" s="54"/>
       <c r="I404" s="54"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" s="41"/>
       <c r="B405" s="41"/>
       <c r="C405" s="54"/>
@@ -29350,7 +29356,7 @@
       <c r="H405" s="54"/>
       <c r="I405" s="54"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" s="41"/>
       <c r="B406" s="41"/>
       <c r="C406" s="54"/>
@@ -29361,7 +29367,7 @@
       <c r="H406" s="54"/>
       <c r="I406" s="54"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" s="41"/>
       <c r="B407" s="41"/>
       <c r="C407" s="54"/>
@@ -29372,7 +29378,7 @@
       <c r="H407" s="54"/>
       <c r="I407" s="54"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" s="41"/>
       <c r="B408" s="41"/>
       <c r="C408" s="54"/>
@@ -29383,7 +29389,7 @@
       <c r="H408" s="54"/>
       <c r="I408" s="54"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" s="41"/>
       <c r="B409" s="41"/>
       <c r="C409" s="54"/>
@@ -29394,7 +29400,7 @@
       <c r="H409" s="54"/>
       <c r="I409" s="54"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" s="41"/>
       <c r="B410" s="41"/>
       <c r="C410" s="54"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D6CA16-755A-4A18-AE30-8C13CBF67D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AD1BC-1234-43AE-8205-453AD24AC6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4515" yWindow="1590" windowWidth="32910" windowHeight="20220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AD1BC-1234-43AE-8205-453AD24AC6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260B522E-8721-442F-A0DA-D3BC7A25B21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4515" yWindow="1590" windowWidth="32910" windowHeight="20220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17325" yWindow="525" windowWidth="20610" windowHeight="20220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="394">
   <si>
     <t>губ</t>
   </si>
@@ -1322,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1497,6 +1497,12 @@
     <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10244,14 +10250,14 @@
       <c r="P112" s="17">
         <v>199366</v>
       </c>
-      <c r="Q112" s="17">
-        <v>223019</v>
+      <c r="Q112" s="57">
+        <v>123019</v>
       </c>
       <c r="R112" s="17">
         <v>188494</v>
       </c>
-      <c r="S112" s="17">
-        <v>122556</v>
+      <c r="S112" s="57">
+        <v>131426</v>
       </c>
       <c r="T112" s="17">
         <v>185448</v>
@@ -10283,7 +10289,7 @@
       <c r="AC112" s="2"/>
       <c r="AD112" s="12">
         <f>SUM(N112:AB112)</f>
-        <v>2675331</v>
+        <v>2584201</v>
       </c>
       <c r="AE112" s="12">
         <f>SUM(N113:AB113)</f>
@@ -10296,7 +10302,7 @@
       <c r="AG112" s="2"/>
       <c r="AH112" s="12">
         <f>AD112-B112</f>
-        <v>91130</v>
+        <v>0</v>
       </c>
       <c r="AI112" s="12">
         <f>AE112-C112</f>
@@ -10519,8 +10525,8 @@
       <c r="O115" s="17">
         <v>184023</v>
       </c>
-      <c r="P115" s="17">
-        <v>216815</v>
+      <c r="P115" s="57">
+        <v>151715</v>
       </c>
       <c r="Q115" s="17">
         <v>59413</v>
@@ -10557,7 +10563,7 @@
       <c r="AC115" s="2"/>
       <c r="AD115" s="12">
         <f>SUM(N115:AB115)</f>
-        <v>1584225</v>
+        <v>1519125</v>
       </c>
       <c r="AE115" s="12">
         <f>SUM(N116:AB116)</f>
@@ -10570,7 +10576,7 @@
       <c r="AG115" s="2"/>
       <c r="AH115" s="12">
         <f>AD115-B115</f>
-        <v>65100</v>
+        <v>0</v>
       </c>
       <c r="AI115" s="12">
         <f>AE115-C115</f>
@@ -11066,14 +11072,16 @@
       <c r="X121" s="17">
         <v>146413</v>
       </c>
-      <c r="Y121" s="17"/>
+      <c r="Y121" s="57">
+        <v>23294</v>
+      </c>
       <c r="Z121" s="17"/>
       <c r="AA121" s="17"/>
       <c r="AB121" s="17"/>
       <c r="AC121" s="2"/>
       <c r="AD121" s="12">
         <f>SUM(N121:AB121)</f>
-        <v>1287835</v>
+        <v>1311129</v>
       </c>
       <c r="AE121" s="12">
         <f>SUM(N122:AB122)</f>
@@ -11086,7 +11094,7 @@
       <c r="AG121" s="2"/>
       <c r="AH121" s="12">
         <f>AD121-B121</f>
-        <v>-23294</v>
+        <v>0</v>
       </c>
       <c r="AI121" s="12">
         <f>AE121-C121</f>
@@ -11174,7 +11182,9 @@
       <c r="X122" s="9">
         <v>7155</v>
       </c>
-      <c r="Y122" s="9"/>
+      <c r="Y122" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Z122" s="9"/>
       <c r="AA122" s="9"/>
       <c r="AB122" s="9"/>
@@ -11236,7 +11246,9 @@
       <c r="X123" s="9">
         <v>5195</v>
       </c>
-      <c r="Y123" s="9"/>
+      <c r="Y123" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Z123" s="9"/>
       <c r="AA123" s="9"/>
       <c r="AB123" s="9"/>
@@ -11807,7 +11819,9 @@
       <c r="W130" s="17">
         <v>156990</v>
       </c>
-      <c r="X130" s="17"/>
+      <c r="X130" s="57">
+        <v>14506</v>
+      </c>
       <c r="Y130" s="17"/>
       <c r="Z130" s="17"/>
       <c r="AA130" s="17"/>
@@ -11815,7 +11829,7 @@
       <c r="AC130" s="2"/>
       <c r="AD130" s="12">
         <f>SUM(N130:AB130)</f>
-        <v>1591507</v>
+        <v>1606013</v>
       </c>
       <c r="AE130" s="12">
         <f>SUM(N131:AB131)</f>
@@ -11828,7 +11842,7 @@
       <c r="AG130" s="2"/>
       <c r="AH130" s="12">
         <f>AD130-B130</f>
-        <v>-14506</v>
+        <v>0</v>
       </c>
       <c r="AI130" s="12">
         <f>AE130-C130</f>
@@ -11913,7 +11927,9 @@
       <c r="W131" s="9">
         <v>8493</v>
       </c>
-      <c r="X131" s="9"/>
+      <c r="X131" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Y131" s="9"/>
       <c r="Z131" s="9"/>
       <c r="AA131" s="9"/>
@@ -11973,7 +11989,9 @@
       <c r="W132" s="9">
         <v>7891</v>
       </c>
-      <c r="X132" s="9"/>
+      <c r="X132" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Y132" s="9"/>
       <c r="Z132" s="9"/>
       <c r="AA132" s="9"/>
@@ -12538,13 +12556,13 @@
       <c r="D139" s="17">
         <v>29690</v>
       </c>
-      <c r="E139" s="17" t="s">
+      <c r="E139" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="F139" s="17" t="s">
+      <c r="F139" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="G139" s="17" t="s">
+      <c r="G139" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H139" s="17">
@@ -12835,13 +12853,15 @@
       <c r="Y142" s="17">
         <v>168976</v>
       </c>
-      <c r="Z142" s="17"/>
+      <c r="Z142" s="57">
+        <v>4218</v>
+      </c>
       <c r="AA142" s="17"/>
       <c r="AB142" s="17"/>
       <c r="AC142" s="2"/>
       <c r="AD142" s="12">
         <f>SUM(N142:AB142)</f>
-        <v>1950702</v>
+        <v>1954920</v>
       </c>
       <c r="AE142" s="12">
         <f>SUM(N143:AB143)</f>
@@ -12854,7 +12874,7 @@
       <c r="AG142" s="2"/>
       <c r="AH142" s="12">
         <f>AD142-B142</f>
-        <v>-4218</v>
+        <v>0</v>
       </c>
       <c r="AI142" s="12">
         <f>AE142-C142</f>
@@ -12945,7 +12965,9 @@
       <c r="Y143" s="57">
         <v>7155</v>
       </c>
-      <c r="Z143" s="9"/>
+      <c r="Z143" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="AA143" s="9"/>
       <c r="AB143" s="9"/>
       <c r="AC143" s="2"/>
@@ -13009,7 +13031,9 @@
       <c r="Y144" s="57">
         <v>6387</v>
       </c>
-      <c r="Z144" s="9"/>
+      <c r="Z144" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="AA144" s="9"/>
       <c r="AB144" s="9"/>
       <c r="AC144" s="2"/>
@@ -13448,13 +13472,13 @@
       <c r="D150" s="17">
         <v>23152</v>
       </c>
-      <c r="E150" s="17" t="s">
+      <c r="E150" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="F150" s="17" t="s">
+      <c r="F150" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="G150" s="17" t="s">
+      <c r="G150" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H150" s="17">
@@ -13497,7 +13521,9 @@
       <c r="U150" s="17">
         <v>92575</v>
       </c>
-      <c r="V150" s="17"/>
+      <c r="V150" s="57">
+        <v>85810</v>
+      </c>
       <c r="W150" s="17"/>
       <c r="X150" s="17"/>
       <c r="Y150" s="17"/>
@@ -13507,7 +13533,7 @@
       <c r="AC150" s="2"/>
       <c r="AD150" s="12">
         <f>SUM(N150:AB150)</f>
-        <v>755507</v>
+        <v>841317</v>
       </c>
       <c r="AE150" s="12">
         <f>SUM(N151:AB151)</f>
@@ -13520,7 +13546,7 @@
       <c r="AG150" s="2"/>
       <c r="AH150" s="12">
         <f>AD150-B150</f>
-        <v>-85810</v>
+        <v>0</v>
       </c>
       <c r="AI150" s="12">
         <f>AE150-C150</f>
@@ -13599,7 +13625,9 @@
       <c r="U151" s="9">
         <v>3046</v>
       </c>
-      <c r="V151" s="9"/>
+      <c r="V151" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="W151" s="9"/>
       <c r="X151" s="9"/>
       <c r="Y151" s="9"/>
@@ -13655,7 +13683,9 @@
       <c r="U152" s="9">
         <v>2680</v>
       </c>
-      <c r="V152" s="9"/>
+      <c r="V152" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="W152" s="9"/>
       <c r="X152" s="9"/>
       <c r="Y152" s="9"/>
@@ -13932,13 +13962,13 @@
       <c r="D156" s="17">
         <v>62764</v>
       </c>
-      <c r="E156" s="17" t="s">
+      <c r="E156" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="F156" s="17" t="s">
+      <c r="F156" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="G156" s="17" t="s">
+      <c r="G156" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H156" s="17">
@@ -13981,7 +14011,9 @@
       <c r="U156" s="17">
         <v>228580</v>
       </c>
-      <c r="V156" s="17"/>
+      <c r="V156" s="57">
+        <v>121987</v>
+      </c>
       <c r="W156" s="17"/>
       <c r="X156" s="17"/>
       <c r="Y156" s="17"/>
@@ -13991,7 +14023,7 @@
       <c r="AC156" s="2"/>
       <c r="AD156" s="12">
         <f>SUM(N156:AB156)</f>
-        <v>1529749</v>
+        <v>1651736</v>
       </c>
       <c r="AE156" s="12">
         <f>SUM(N157:AB157)</f>
@@ -14004,7 +14036,7 @@
       <c r="AG156" s="2"/>
       <c r="AH156" s="12">
         <f>AD156-B156</f>
-        <v>-121987</v>
+        <v>0</v>
       </c>
       <c r="AI156" s="12">
         <f>AE156-C156</f>
@@ -14083,7 +14115,9 @@
       <c r="U157" s="9">
         <v>12925</v>
       </c>
-      <c r="V157" s="9"/>
+      <c r="V157" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="W157" s="9"/>
       <c r="X157" s="9"/>
       <c r="Y157" s="9"/>
@@ -14139,7 +14173,9 @@
       <c r="U158" s="9">
         <v>9699</v>
       </c>
-      <c r="V158" s="9"/>
+      <c r="V158" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="W158" s="9"/>
       <c r="X158" s="9"/>
       <c r="Y158" s="9"/>
@@ -14229,13 +14265,15 @@
       <c r="Y159" s="17">
         <v>115885</v>
       </c>
-      <c r="Z159" s="17"/>
+      <c r="Z159" s="57">
+        <v>42622</v>
+      </c>
       <c r="AA159" s="17"/>
       <c r="AB159" s="17"/>
       <c r="AC159" s="2"/>
       <c r="AD159" s="12">
         <f>SUM(N159:AB159)</f>
-        <v>1412165</v>
+        <v>1454787</v>
       </c>
       <c r="AE159" s="12">
         <f>SUM(N160:AB160)</f>
@@ -14248,7 +14286,7 @@
       <c r="AG159" s="2"/>
       <c r="AH159" s="12">
         <f>AD159-B159</f>
-        <v>-42622</v>
+        <v>0</v>
       </c>
       <c r="AI159" s="12">
         <f>AE159-C159</f>
@@ -14339,7 +14377,9 @@
       <c r="Y160" s="9">
         <v>6677</v>
       </c>
-      <c r="Z160" s="9"/>
+      <c r="Z160" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="AA160" s="9"/>
       <c r="AB160" s="9"/>
       <c r="AC160" s="2"/>
@@ -14403,7 +14443,9 @@
       <c r="Y161" s="9">
         <v>5050</v>
       </c>
-      <c r="Z161" s="9"/>
+      <c r="Z161" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="AA161" s="9"/>
       <c r="AB161" s="9"/>
       <c r="AC161" s="2"/>
@@ -16667,7 +16709,9 @@
       <c r="W188" s="19">
         <v>110903</v>
       </c>
-      <c r="X188" s="17"/>
+      <c r="X188" s="57">
+        <v>39445</v>
+      </c>
       <c r="Y188" s="17"/>
       <c r="Z188" s="17"/>
       <c r="AA188" s="17"/>
@@ -16675,7 +16719,7 @@
       <c r="AC188" s="2"/>
       <c r="AD188" s="12">
         <f>SUM(N188:AB188)</f>
-        <v>1172771</v>
+        <v>1212216</v>
       </c>
       <c r="AE188" s="12">
         <f>SUM(N189:AB189)</f>
@@ -16688,7 +16732,7 @@
       <c r="AG188" s="2"/>
       <c r="AH188" s="12">
         <f>AD188-B188</f>
-        <v>-39445</v>
+        <v>0</v>
       </c>
       <c r="AI188" s="12">
         <f>AE188-C188</f>
@@ -16773,7 +16817,9 @@
       <c r="W189" s="6">
         <v>4130</v>
       </c>
-      <c r="X189" s="9"/>
+      <c r="X189" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Y189" s="9"/>
       <c r="Z189" s="9"/>
       <c r="AA189" s="9"/>
@@ -16833,7 +16879,9 @@
       <c r="W190" s="6">
         <v>2849</v>
       </c>
-      <c r="X190" s="9"/>
+      <c r="X190" s="63" t="s">
+        <v>14</v>
+      </c>
       <c r="Y190" s="9"/>
       <c r="Z190" s="9"/>
       <c r="AA190" s="9"/>
@@ -16896,7 +16944,7 @@
       <c r="AC191" s="2"/>
       <c r="AD191" s="23">
         <f>SUM(AD85:AD190)</f>
-        <v>65119211</v>
+        <v>65294863</v>
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
@@ -16909,7 +16957,7 @@
       <c r="AG191" s="2"/>
       <c r="AH191" s="23">
         <f t="shared" ref="AH191:AJ192" si="181">AD191-B191</f>
-        <v>-240136</v>
+        <v>-64484</v>
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="181"/>
@@ -17251,7 +17299,7 @@
       <c r="AC195" s="2"/>
       <c r="AD195" s="23">
         <f>SUM(AD42, AD74, AD84, AD191, AD192)</f>
-        <v>98885340</v>
+        <v>99060992</v>
       </c>
       <c r="AE195" s="23">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
@@ -17264,7 +17312,7 @@
       <c r="AG195" s="2"/>
       <c r="AH195" s="23">
         <f t="shared" ref="AH195:AJ196" si="186">AD195-B195</f>
-        <v>-218015</v>
+        <v>-42363</v>
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="186"/>
@@ -17374,7 +17422,9 @@
       <c r="T196" s="19">
         <v>14682</v>
       </c>
-      <c r="U196" s="19"/>
+      <c r="U196" s="60">
+        <v>101431</v>
+      </c>
       <c r="V196" s="19"/>
       <c r="W196" s="19"/>
       <c r="X196" s="19"/>
@@ -17385,7 +17435,7 @@
       <c r="AC196" s="2"/>
       <c r="AD196" s="12">
         <f>SUM(N196:AB196)</f>
-        <v>780495</v>
+        <v>881926</v>
       </c>
       <c r="AE196" s="12">
         <f>SUM(N197:AB197)</f>
@@ -17398,7 +17448,7 @@
       <c r="AG196" s="2"/>
       <c r="AH196" s="12">
         <f t="shared" si="186"/>
-        <v>-101431</v>
+        <v>0</v>
       </c>
       <c r="AI196" s="12">
         <f t="shared" si="186"/>
@@ -17474,7 +17524,9 @@
       <c r="T197" s="6">
         <v>339</v>
       </c>
-      <c r="U197" s="6"/>
+      <c r="U197" s="37" t="s">
+        <v>14</v>
+      </c>
       <c r="V197" s="6"/>
       <c r="W197" s="6"/>
       <c r="X197" s="6"/>
@@ -17528,7 +17580,9 @@
       <c r="T198" s="6">
         <v>272</v>
       </c>
-      <c r="U198" s="6"/>
+      <c r="U198" s="37" t="s">
+        <v>14</v>
+      </c>
       <c r="V198" s="6"/>
       <c r="W198" s="6"/>
       <c r="X198" s="6"/>
@@ -19545,7 +19599,7 @@
       <c r="AC224" s="2"/>
       <c r="AD224" s="23">
         <f>SUM(AD196:AD223)</f>
-        <v>7979988</v>
+        <v>8081419</v>
       </c>
       <c r="AE224" s="23">
         <f>SUM(AE196:AE223)</f>
@@ -19558,7 +19612,7 @@
       <c r="AG224" s="2"/>
       <c r="AH224" s="23">
         <f>AD224-B224</f>
-        <v>-105419</v>
+        <v>-3988</v>
       </c>
       <c r="AI224" s="23">
         <f>AE224-C224</f>
@@ -23382,7 +23436,7 @@
       <c r="AC275" s="2"/>
       <c r="AD275" s="23">
         <f>SUM(AD195, AD224, AD250, AD274)</f>
-        <v>117910616</v>
+        <v>118187699</v>
       </c>
       <c r="AE275" s="23">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
@@ -23395,7 +23449,7 @@
       <c r="AG275" s="2"/>
       <c r="AH275" s="23">
         <f t="shared" si="246"/>
-        <v>-467534</v>
+        <v>-190451</v>
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="246"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260B522E-8721-442F-A0DA-D3BC7A25B21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4A6761-0126-423F-9B4C-CCA6487748A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17325" yWindow="525" windowWidth="20610" windowHeight="20220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="394">
   <si>
     <t>губ</t>
   </si>
@@ -1322,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1494,13 +1494,19 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1670,17 +1676,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317E8D20-6275-41B8-982F-8FFD4E68F4B1}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="41" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
         <v>391</v>
       </c>
@@ -1693,52 +1699,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEW275"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.15625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.15625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.41796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.41796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.15625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.5703125" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="6" customWidth="1"/>
-    <col min="14" max="15" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.7109375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.28515625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.5703125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.5703125" style="1" customWidth="1"/>
-    <col min="41" max="42" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.140625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.83984375" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.578125" style="6" customWidth="1"/>
+    <col min="14" max="15" width="7.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.62890625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="7.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.68359375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="11.15625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="9.15625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.26171875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="8.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="7.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.578125" style="1" customWidth="1"/>
+    <col min="38" max="39" width="4.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.578125" style="1" customWidth="1"/>
+    <col min="41" max="42" width="5.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.15625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="17.41796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.83984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.68359375" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="5" style="1" customWidth="1"/>
-    <col min="48" max="48" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.15625" style="1" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="16376" width="12" style="1"/>
     <col min="16377" max="16377" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="16378" max="16384" width="1.85546875" style="1" customWidth="1"/>
+    <col min="16378" max="16384" width="1.83984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1776,23 +1782,23 @@
         <v>282</v>
       </c>
       <c r="M1" s="26"/>
-      <c r="N1" s="61" t="s">
+      <c r="N1" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
-      <c r="AB1" s="61"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
       <c r="AD1" s="33" t="s">
         <v>279</v>
       </c>
@@ -1843,7 +1849,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
@@ -1964,7 +1970,7 @@
         <v>8792</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="28" t="s">
         <v>12</v>
       </c>
@@ -2006,7 +2012,7 @@
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
@@ -2048,7 +2054,7 @@
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="27" t="s">
         <v>295</v>
       </c>
@@ -2166,7 +2172,7 @@
         <v>19821</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="28" t="s">
         <v>296</v>
       </c>
@@ -2204,7 +2210,7 @@
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="28" t="s">
         <v>297</v>
       </c>
@@ -2242,7 +2248,7 @@
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2"/>
     </row>
-    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="20" t="s">
         <v>298</v>
       </c>
@@ -2313,7 +2319,7 @@
       <c r="AS8" s="52"/>
       <c r="AT8" s="52"/>
     </row>
-    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="50" t="s">
         <v>299</v>
       </c>
@@ -2357,7 +2363,7 @@
       <c r="AI9" s="6"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="50" t="s">
         <v>300</v>
       </c>
@@ -2401,7 +2407,7 @@
       <c r="AI10" s="6"/>
       <c r="AJ10" s="6"/>
     </row>
-    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="50" t="s">
         <v>301</v>
       </c>
@@ -2450,7 +2456,7 @@
       <c r="AI11" s="6"/>
       <c r="AJ11" s="6"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="27" t="s">
         <v>15</v>
       </c>
@@ -2571,7 +2577,7 @@
         <v>44088</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="28" t="s">
         <v>16</v>
       </c>
@@ -2613,7 +2619,7 @@
       <c r="AI13" s="2"/>
       <c r="AJ13" s="2"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="28" t="s">
         <v>17</v>
       </c>
@@ -2655,7 +2661,7 @@
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="27" t="s">
         <v>18</v>
       </c>
@@ -2784,7 +2790,7 @@
         <v>33167</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
         <v>19</v>
       </c>
@@ -2836,7 +2842,7 @@
       <c r="AI16" s="2"/>
       <c r="AJ16" s="2"/>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="28" t="s">
         <v>20</v>
       </c>
@@ -2888,7 +2894,7 @@
       <c r="AI17" s="2"/>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="27" t="s">
         <v>21</v>
       </c>
@@ -3019,7 +3025,7 @@
         <v>76684</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="28" t="s">
         <v>22</v>
       </c>
@@ -3073,7 +3079,7 @@
       <c r="AI19" s="2"/>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
@@ -3127,7 +3133,7 @@
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="29" t="s">
         <v>24</v>
       </c>
@@ -3252,7 +3258,7 @@
         <v>38321</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="28" t="s">
         <v>25</v>
       </c>
@@ -3300,7 +3306,7 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="28" t="s">
         <v>26</v>
       </c>
@@ -3348,7 +3354,7 @@
       <c r="AI23" s="2"/>
       <c r="AJ23" s="2"/>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="29" t="s">
         <v>27</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>99899</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="28" t="s">
         <v>28</v>
       </c>
@@ -3533,7 +3539,7 @@
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="28" t="s">
         <v>29</v>
       </c>
@@ -3587,7 +3593,7 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="29" t="s">
         <v>30</v>
       </c>
@@ -3708,7 +3714,7 @@
         <v>36336</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="28" t="s">
         <v>31</v>
       </c>
@@ -3750,7 +3756,7 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="28" t="s">
         <v>32</v>
       </c>
@@ -3792,7 +3798,7 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
@@ -3917,7 +3923,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="28" t="s">
         <v>34</v>
       </c>
@@ -3965,7 +3971,7 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="28" t="s">
         <v>35</v>
       </c>
@@ -4013,12 +4019,12 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3">
-        <v>1415341</v>
+      <c r="B33" s="58">
+        <v>1418690</v>
       </c>
       <c r="C33" s="3">
         <v>73348</v>
@@ -4103,7 +4109,7 @@
       <c r="AG33" s="2"/>
       <c r="AH33" s="12">
         <f>AD33-B33</f>
-        <v>3349</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="12">
         <f>AE33-C33</f>
@@ -4115,19 +4121,19 @@
       </c>
       <c r="AL33" s="47">
         <f>C33/B33*1000</f>
-        <v>51.823553475805483</v>
+        <v>51.701217320203853</v>
       </c>
       <c r="AM33" s="47">
         <f>D33/B33*1000</f>
-        <v>30.796112032365343</v>
+        <v>30.72341385362553</v>
       </c>
       <c r="AO33" s="47">
         <f>AL33-K33</f>
-        <v>1.1235534758054797</v>
+        <v>1.0012173202038497</v>
       </c>
       <c r="AP33" s="47">
         <f>AM33-L33</f>
-        <v>0.59611203236534394</v>
+        <v>0.52341385362553083</v>
       </c>
       <c r="AR33" s="12">
         <f t="shared" ref="AR33" si="24">H33</f>
@@ -4142,7 +4148,7 @@
         <v>36280</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="28" t="s">
         <v>37</v>
       </c>
@@ -4194,7 +4200,7 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="28" t="s">
         <v>38</v>
       </c>
@@ -4246,7 +4252,7 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="29" t="s">
         <v>39</v>
       </c>
@@ -4363,7 +4369,7 @@
         <v>55174</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="28" t="s">
         <v>40</v>
       </c>
@@ -4401,7 +4407,7 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="28" t="s">
         <v>41</v>
       </c>
@@ -4439,7 +4445,7 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="29" t="s">
         <v>42</v>
       </c>
@@ -4570,7 +4576,7 @@
         <v>77982</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="28" t="s">
         <v>43</v>
       </c>
@@ -4624,7 +4630,7 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="28" t="s">
         <v>44</v>
       </c>
@@ -4678,7 +4684,7 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="30" t="s">
         <v>45</v>
       </c>
@@ -4792,7 +4798,7 @@
         <v>-9503</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="29" t="s">
         <v>46</v>
       </c>
@@ -4884,7 +4890,7 @@
         <v>12531</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="29" t="s">
         <v>47</v>
       </c>
@@ -5015,7 +5021,7 @@
         <v>25499</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="28" t="s">
         <v>48</v>
       </c>
@@ -5069,7 +5075,7 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="28" t="s">
         <v>49</v>
       </c>
@@ -5123,7 +5129,7 @@
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="29" t="s">
         <v>50</v>
       </c>
@@ -5172,8 +5178,8 @@
       <c r="Q47" s="3">
         <v>90662</v>
       </c>
-      <c r="R47" s="3">
-        <v>110320</v>
+      <c r="R47" s="58">
+        <v>117238</v>
       </c>
       <c r="S47" s="3">
         <v>86950</v>
@@ -5194,7 +5200,7 @@
       <c r="AC47" s="2"/>
       <c r="AD47" s="12">
         <f>SUM(N47:AB47)</f>
-        <v>889591</v>
+        <v>896509</v>
       </c>
       <c r="AE47" s="12">
         <f>SUM(N48:AB48)</f>
@@ -5207,7 +5213,7 @@
       <c r="AG47" s="2"/>
       <c r="AH47" s="12">
         <f>AD47-B47</f>
-        <v>-6918</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="12">
         <f>AE47-C47</f>
@@ -5246,7 +5252,7 @@
         <v>20432</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="28" t="s">
         <v>51</v>
       </c>
@@ -5291,7 +5297,7 @@
       <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
     </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="28" t="s">
         <v>52</v>
       </c>
@@ -5336,7 +5342,7 @@
       <c r="AI49" s="2"/>
       <c r="AJ49" s="2"/>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="29" t="s">
         <v>53</v>
       </c>
@@ -5379,17 +5385,17 @@
       <c r="O50" s="3">
         <v>77020</v>
       </c>
-      <c r="P50" s="3">
-        <v>74810</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>105839</v>
+      <c r="P50" s="58">
+        <v>86270</v>
+      </c>
+      <c r="Q50" s="58">
+        <v>111407</v>
       </c>
       <c r="R50" s="3">
         <v>113785</v>
       </c>
-      <c r="S50" s="3">
-        <v>103350</v>
+      <c r="S50" s="58">
+        <v>109447</v>
       </c>
       <c r="T50" s="12">
         <v>125748</v>
@@ -5405,7 +5411,7 @@
       <c r="AC50" s="2"/>
       <c r="AD50" s="12">
         <f>SUM(N50:AB50)</f>
-        <v>728834</v>
+        <v>751959</v>
       </c>
       <c r="AE50" s="12">
         <f>SUM(N51:AB51)</f>
@@ -5418,7 +5424,7 @@
       <c r="AG50" s="2"/>
       <c r="AH50" s="12">
         <f>AD50-B50</f>
-        <v>-23125</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="12">
         <f>AE50-C50</f>
@@ -5457,7 +5463,7 @@
         <v>15551</v>
       </c>
     </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="28" t="s">
         <v>54</v>
       </c>
@@ -5499,7 +5505,7 @@
       <c r="AI51" s="2"/>
       <c r="AJ51" s="2"/>
     </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="28" t="s">
         <v>55</v>
       </c>
@@ -5541,7 +5547,7 @@
       <c r="AI52" s="2"/>
       <c r="AJ52" s="2"/>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="29" t="s">
         <v>56</v>
       </c>
@@ -5664,7 +5670,7 @@
         <v>17783</v>
       </c>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="28" t="s">
         <v>57</v>
       </c>
@@ -5709,7 +5715,7 @@
       <c r="AI54" s="2"/>
       <c r="AJ54" s="2"/>
     </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="28" t="s">
         <v>58</v>
       </c>
@@ -5754,7 +5760,7 @@
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
     </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="29" t="s">
         <v>59</v>
       </c>
@@ -5881,7 +5887,7 @@
         <v>25432</v>
       </c>
     </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="28" t="s">
         <v>60</v>
       </c>
@@ -5931,7 +5937,7 @@
       <c r="AI57" s="2"/>
       <c r="AJ57" s="2"/>
     </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="28" t="s">
         <v>61</v>
       </c>
@@ -5981,7 +5987,7 @@
       <c r="AI58" s="2"/>
       <c r="AJ58" s="2"/>
     </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="29" t="s">
         <v>62</v>
       </c>
@@ -6104,7 +6110,7 @@
         <v>24399</v>
       </c>
     </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="28" t="s">
         <v>63</v>
       </c>
@@ -6149,7 +6155,7 @@
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
     </row>
-    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="28" t="s">
         <v>64</v>
       </c>
@@ -6194,7 +6200,7 @@
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
     </row>
-    <row r="62" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="29" t="s">
         <v>65</v>
       </c>
@@ -6231,8 +6237,8 @@
       <c r="O62" s="3">
         <v>92871</v>
       </c>
-      <c r="P62" s="3">
-        <v>83130</v>
+      <c r="P62" s="58">
+        <v>88665</v>
       </c>
       <c r="Q62" s="3">
         <v>86428</v>
@@ -6259,7 +6265,7 @@
       <c r="AC62" s="2"/>
       <c r="AD62" s="12">
         <f>SUM(N62:AB62)</f>
-        <v>648453</v>
+        <v>653988</v>
       </c>
       <c r="AE62" s="12">
         <f>SUM(N63:AB63)</f>
@@ -6272,7 +6278,7 @@
       <c r="AG62" s="2"/>
       <c r="AH62" s="12">
         <f>AD62-B62</f>
-        <v>-5535</v>
+        <v>0</v>
       </c>
       <c r="AI62" s="12">
         <f>AE62-C62</f>
@@ -6311,7 +6317,7 @@
         <v>15757</v>
       </c>
     </row>
-    <row r="63" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="28" t="s">
         <v>66</v>
       </c>
@@ -6356,7 +6362,7 @@
       <c r="AI63" s="2"/>
       <c r="AJ63" s="2"/>
     </row>
-    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="28" t="s">
         <v>67</v>
       </c>
@@ -6401,7 +6407,7 @@
       <c r="AI64" s="2"/>
       <c r="AJ64" s="2"/>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="29" t="s">
         <v>68</v>
       </c>
@@ -6522,7 +6528,7 @@
         <v>17247</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="28" t="s">
         <v>69</v>
       </c>
@@ -6564,7 +6570,7 @@
       <c r="AI66" s="2"/>
       <c r="AJ66" s="2"/>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="28" t="s">
         <v>70</v>
       </c>
@@ -6606,7 +6612,7 @@
       <c r="AI67" s="2"/>
       <c r="AJ67" s="2"/>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="29" t="s">
         <v>71</v>
       </c>
@@ -6646,8 +6652,8 @@
       <c r="N68" s="3">
         <v>107785</v>
       </c>
-      <c r="O68" s="3">
-        <v>196721</v>
+      <c r="O68" s="58">
+        <v>96721</v>
       </c>
       <c r="P68" s="3">
         <v>85886</v>
@@ -6655,8 +6661,8 @@
       <c r="Q68" s="3">
         <v>96098</v>
       </c>
-      <c r="R68" s="3">
-        <v>191094</v>
+      <c r="R68" s="58">
+        <v>91094</v>
       </c>
       <c r="S68" s="3">
         <v>124767</v>
@@ -6675,7 +6681,7 @@
       <c r="AC68" s="2"/>
       <c r="AD68" s="12">
         <f>SUM(N68:AB68)</f>
-        <v>906453</v>
+        <v>706453</v>
       </c>
       <c r="AE68" s="12">
         <f>SUM(N69:AB69)</f>
@@ -6688,7 +6694,7 @@
       <c r="AG68" s="2"/>
       <c r="AH68" s="12">
         <f>AD68-B68</f>
-        <v>198000</v>
+        <v>-2000</v>
       </c>
       <c r="AI68" s="12">
         <f>AE68-C68</f>
@@ -6727,7 +6733,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="28" t="s">
         <v>72</v>
       </c>
@@ -6769,7 +6775,7 @@
       <c r="AI69" s="2"/>
       <c r="AJ69" s="2"/>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="28" t="s">
         <v>73</v>
       </c>
@@ -6811,7 +6817,7 @@
       <c r="AI70" s="2"/>
       <c r="AJ70" s="2"/>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="29" t="s">
         <v>74</v>
       </c>
@@ -6936,7 +6942,7 @@
         <v>17010</v>
       </c>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="28" t="s">
         <v>75</v>
       </c>
@@ -6984,7 +6990,7 @@
       <c r="AI72" s="2"/>
       <c r="AJ72" s="2"/>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="28" t="s">
         <v>76</v>
       </c>
@@ -7032,7 +7038,7 @@
       <c r="AI73" s="2"/>
       <c r="AJ73" s="2"/>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="30" t="s">
         <v>77</v>
       </c>
@@ -7081,7 +7087,7 @@
       <c r="AC74" s="2"/>
       <c r="AD74" s="23">
         <f>SUM(AD43:AD73)</f>
-        <v>9190534</v>
+        <v>9026112</v>
       </c>
       <c r="AE74" s="23">
         <f>SUM(AE43:AE73)</f>
@@ -7094,7 +7100,7 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="23">
         <f t="shared" ref="AH74:AJ75" si="65">AD74-B74</f>
-        <v>76051</v>
+        <v>-88371</v>
       </c>
       <c r="AI74" s="23">
         <f t="shared" si="65"/>
@@ -7146,7 +7152,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="16" t="s">
         <v>78</v>
       </c>
@@ -7211,8 +7217,8 @@
       <c r="V75" s="15">
         <v>53000</v>
       </c>
-      <c r="W75" s="15">
-        <v>64600</v>
+      <c r="W75" s="59">
+        <v>70000</v>
       </c>
       <c r="X75" s="15"/>
       <c r="Y75" s="15"/>
@@ -7222,7 +7228,7 @@
       <c r="AC75" s="2"/>
       <c r="AD75" s="12">
         <f>SUM(N75:AB75)</f>
-        <v>706500</v>
+        <v>711900</v>
       </c>
       <c r="AE75" s="12">
         <f>SUM(N76:AB76)</f>
@@ -7235,7 +7241,7 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="12">
         <f t="shared" si="65"/>
-        <v>-5400</v>
+        <v>0</v>
       </c>
       <c r="AI75" s="12">
         <f t="shared" si="65"/>
@@ -7274,7 +7280,7 @@
         <v>12183</v>
       </c>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="10" t="s">
         <v>79</v>
       </c>
@@ -7334,7 +7340,7 @@
       <c r="AI76" s="2"/>
       <c r="AJ76" s="2"/>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="10" t="s">
         <v>80</v>
       </c>
@@ -7394,7 +7400,7 @@
       <c r="AI77" s="2"/>
       <c r="AJ77" s="2"/>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="16" t="s">
         <v>81</v>
       </c>
@@ -7520,7 +7526,7 @@
         <v>26309</v>
       </c>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="10" t="s">
         <v>82</v>
       </c>
@@ -7578,7 +7584,7 @@
       <c r="AI79" s="2"/>
       <c r="AJ79" s="2"/>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="10" t="s">
         <v>83</v>
       </c>
@@ -7636,7 +7642,7 @@
       <c r="AI80" s="2"/>
       <c r="AJ80" s="2"/>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="16" t="s">
         <v>84</v>
       </c>
@@ -7724,7 +7730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="10" t="s">
         <v>85</v>
       </c>
@@ -7772,7 +7778,7 @@
       <c r="AI82" s="2"/>
       <c r="AJ82" s="2"/>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="10" t="s">
         <v>86</v>
       </c>
@@ -7820,7 +7826,7 @@
       <c r="AI83" s="2"/>
       <c r="AJ83" s="2"/>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="44" t="s">
         <v>87</v>
       </c>
@@ -7870,7 +7876,7 @@
       <c r="AC84" s="2"/>
       <c r="AD84" s="23">
         <f>SUM(AD75:AD83)</f>
-        <v>2397298</v>
+        <v>2402698</v>
       </c>
       <c r="AE84" s="23">
         <f>SUM(AE75:AE83)</f>
@@ -7883,7 +7889,7 @@
       <c r="AG84" s="23"/>
       <c r="AH84" s="23">
         <f t="shared" ref="AH84:AJ85" si="73">AD84-B84</f>
-        <v>-13364</v>
+        <v>-7964</v>
       </c>
       <c r="AI84" s="23">
         <f t="shared" si="73"/>
@@ -7935,7 +7941,7 @@
         <v>8257</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="16" t="s">
         <v>88</v>
       </c>
@@ -8059,7 +8065,7 @@
         <v>44683</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="10" t="s">
         <v>89</v>
       </c>
@@ -8115,7 +8121,7 @@
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="10" t="s">
         <v>90</v>
       </c>
@@ -8171,7 +8177,7 @@
       <c r="AI87" s="2"/>
       <c r="AJ87" s="2"/>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="16" t="s">
         <v>91</v>
       </c>
@@ -8248,12 +8254,14 @@
       <c r="Z88" s="15">
         <v>107686</v>
       </c>
-      <c r="AA88" s="12"/>
+      <c r="AA88" s="58">
+        <v>25065</v>
+      </c>
       <c r="AB88" s="15"/>
       <c r="AC88" s="2"/>
       <c r="AD88" s="12">
         <f>SUM(N88:AB88)</f>
-        <v>1500035</v>
+        <v>1525100</v>
       </c>
       <c r="AE88" s="12">
         <f>SUM(N89:AB89)</f>
@@ -8266,7 +8274,7 @@
       <c r="AG88" s="2"/>
       <c r="AH88" s="12">
         <f>AD88-B88</f>
-        <v>-25065</v>
+        <v>0</v>
       </c>
       <c r="AI88" s="12">
         <f>AE88-C88</f>
@@ -8305,7 +8313,7 @@
         <v>60082</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="10" t="s">
         <v>92</v>
       </c>
@@ -8348,8 +8356,8 @@
       <c r="V89" s="8">
         <v>7386</v>
       </c>
-      <c r="W89" s="59">
-        <v>4758</v>
+      <c r="W89" s="64">
+        <v>2729</v>
       </c>
       <c r="X89" s="8">
         <v>6218</v>
@@ -8360,7 +8368,9 @@
       <c r="Z89" s="8">
         <v>5718</v>
       </c>
-      <c r="AA89" s="2"/>
+      <c r="AA89" s="58">
+        <v>2029</v>
+      </c>
       <c r="AB89" s="8"/>
       <c r="AC89" s="2"/>
       <c r="AD89" s="2"/>
@@ -8371,7 +8381,7 @@
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="10" t="s">
         <v>93</v>
       </c>
@@ -8414,8 +8424,8 @@
       <c r="V90" s="8">
         <v>6300</v>
       </c>
-      <c r="W90" s="59">
-        <v>3738</v>
+      <c r="W90" s="64">
+        <v>1925</v>
       </c>
       <c r="X90" s="8">
         <v>4423</v>
@@ -8426,7 +8436,9 @@
       <c r="Z90" s="8">
         <v>4449</v>
       </c>
-      <c r="AA90" s="2"/>
+      <c r="AA90" s="58">
+        <v>1813</v>
+      </c>
       <c r="AB90" s="8"/>
       <c r="AC90" s="2"/>
       <c r="AD90" s="2"/>
@@ -8437,7 +8449,7 @@
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="16" t="s">
         <v>94</v>
       </c>
@@ -8559,7 +8571,7 @@
         <v>40347</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="10" t="s">
         <v>95</v>
       </c>
@@ -8619,7 +8631,7 @@
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="10" t="s">
         <v>96</v>
       </c>
@@ -8679,7 +8691,7 @@
       <c r="AI93" s="2"/>
       <c r="AJ93" s="2"/>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="16" t="s">
         <v>97</v>
       </c>
@@ -8744,8 +8756,8 @@
       <c r="V94" s="15">
         <v>178573</v>
       </c>
-      <c r="W94" s="15">
-        <v>170198</v>
+      <c r="W94" s="59">
+        <v>190198</v>
       </c>
       <c r="X94" s="15">
         <v>280961</v>
@@ -8759,7 +8771,7 @@
       <c r="AC94" s="2"/>
       <c r="AD94" s="12">
         <f>SUM(N94:AB94)</f>
-        <v>2692268</v>
+        <v>2712268</v>
       </c>
       <c r="AE94" s="12">
         <f>SUM(N95:AB95)</f>
@@ -8772,7 +8784,7 @@
       <c r="AG94" s="2"/>
       <c r="AH94" s="12">
         <f>AD94-B94</f>
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="AI94" s="12">
         <f>AE94-C94</f>
@@ -8811,7 +8823,7 @@
         <v>98935</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="10" t="s">
         <v>98</v>
       </c>
@@ -8875,7 +8887,7 @@
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="10" t="s">
         <v>99</v>
       </c>
@@ -8939,7 +8951,7 @@
       <c r="AI96" s="2"/>
       <c r="AJ96" s="2"/>
     </row>
-    <row r="97" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="16" t="s">
         <v>100</v>
       </c>
@@ -9069,7 +9081,7 @@
         <v>120135</v>
       </c>
     </row>
-    <row r="98" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="10" t="s">
         <v>101</v>
       </c>
@@ -9131,7 +9143,7 @@
       <c r="AI98" s="2"/>
       <c r="AJ98" s="2"/>
     </row>
-    <row r="99" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="10" t="s">
         <v>102</v>
       </c>
@@ -9193,7 +9205,7 @@
       <c r="AI99" s="2"/>
       <c r="AJ99" s="2"/>
     </row>
-    <row r="100" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="16" t="s">
         <v>103</v>
       </c>
@@ -9317,7 +9329,7 @@
         <v>59074</v>
       </c>
     </row>
-    <row r="101" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="10" t="s">
         <v>104</v>
       </c>
@@ -9373,7 +9385,7 @@
       <c r="AI101" s="2"/>
       <c r="AJ101" s="2"/>
     </row>
-    <row r="102" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="10" t="s">
         <v>105</v>
       </c>
@@ -9429,7 +9441,7 @@
       <c r="AI102" s="2"/>
       <c r="AJ102" s="2"/>
     </row>
-    <row r="103" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="18" t="s">
         <v>106</v>
       </c>
@@ -9561,7 +9573,7 @@
         <v>72188</v>
       </c>
     </row>
-    <row r="104" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="11" t="s">
         <v>107</v>
       </c>
@@ -9625,7 +9637,7 @@
       <c r="AI104" s="2"/>
       <c r="AJ104" s="2"/>
     </row>
-    <row r="105" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="11" t="s">
         <v>108</v>
       </c>
@@ -9689,7 +9701,7 @@
       <c r="AI105" s="2"/>
       <c r="AJ105" s="2"/>
     </row>
-    <row r="106" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="18" t="s">
         <v>109</v>
       </c>
@@ -9819,7 +9831,7 @@
         <v>44326</v>
       </c>
     </row>
-    <row r="107" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="11" t="s">
         <v>110</v>
       </c>
@@ -9881,7 +9893,7 @@
       <c r="AI107" s="2"/>
       <c r="AJ107" s="2"/>
     </row>
-    <row r="108" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="11" t="s">
         <v>111</v>
       </c>
@@ -9943,7 +9955,7 @@
       <c r="AI108" s="2"/>
       <c r="AJ108" s="2"/>
     </row>
-    <row r="109" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="18" t="s">
         <v>112</v>
       </c>
@@ -10075,7 +10087,7 @@
         <v>51040</v>
       </c>
     </row>
-    <row r="110" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="11" t="s">
         <v>113</v>
       </c>
@@ -10139,7 +10151,7 @@
       <c r="AI110" s="2"/>
       <c r="AJ110" s="2"/>
     </row>
-    <row r="111" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="11" t="s">
         <v>114</v>
       </c>
@@ -10203,7 +10215,7 @@
       <c r="AI111" s="2"/>
       <c r="AJ111" s="2"/>
     </row>
-    <row r="112" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="18" t="s">
         <v>115</v>
       </c>
@@ -10341,7 +10353,7 @@
         <v>78783</v>
       </c>
     </row>
-    <row r="113" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="11" t="s">
         <v>116</v>
       </c>
@@ -10411,7 +10423,7 @@
       <c r="AI113" s="2"/>
       <c r="AJ113" s="2"/>
     </row>
-    <row r="114" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="11" t="s">
         <v>117</v>
       </c>
@@ -10481,7 +10493,7 @@
       <c r="AI114" s="2"/>
       <c r="AJ114" s="2"/>
     </row>
-    <row r="115" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="18" t="s">
         <v>118</v>
       </c>
@@ -10615,7 +10627,7 @@
         <v>58051</v>
       </c>
     </row>
-    <row r="116" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="11" t="s">
         <v>119</v>
       </c>
@@ -10681,7 +10693,7 @@
       <c r="AI116" s="2"/>
       <c r="AJ116" s="2"/>
     </row>
-    <row r="117" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="11" t="s">
         <v>120</v>
       </c>
@@ -10747,7 +10759,7 @@
       <c r="AI117" s="2"/>
       <c r="AJ117" s="2"/>
     </row>
-    <row r="118" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="18" t="s">
         <v>121</v>
       </c>
@@ -10877,7 +10889,7 @@
         <v>65761</v>
       </c>
     </row>
-    <row r="119" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="11" t="s">
         <v>122</v>
       </c>
@@ -10939,7 +10951,7 @@
       <c r="AI119" s="2"/>
       <c r="AJ119" s="2"/>
     </row>
-    <row r="120" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="11" t="s">
         <v>123</v>
       </c>
@@ -11001,7 +11013,7 @@
       <c r="AI120" s="2"/>
       <c r="AJ120" s="2"/>
     </row>
-    <row r="121" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="18" t="s">
         <v>124</v>
       </c>
@@ -11133,7 +11145,7 @@
         <v>39804</v>
       </c>
     </row>
-    <row r="122" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="11" t="s">
         <v>125</v>
       </c>
@@ -11182,7 +11194,7 @@
       <c r="X122" s="9">
         <v>7155</v>
       </c>
-      <c r="Y122" s="63" t="s">
+      <c r="Y122" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Z122" s="9"/>
@@ -11197,7 +11209,7 @@
       <c r="AI122" s="2"/>
       <c r="AJ122" s="2"/>
     </row>
-    <row r="123" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="11" t="s">
         <v>126</v>
       </c>
@@ -11246,7 +11258,7 @@
       <c r="X123" s="9">
         <v>5195</v>
       </c>
-      <c r="Y123" s="63" t="s">
+      <c r="Y123" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Z123" s="9"/>
@@ -11261,7 +11273,7 @@
       <c r="AI123" s="2"/>
       <c r="AJ123" s="2"/>
     </row>
-    <row r="124" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="18" t="s">
         <v>127</v>
       </c>
@@ -11383,7 +11395,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="125" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="11" t="s">
         <v>128</v>
       </c>
@@ -11437,7 +11449,7 @@
       <c r="AI125" s="2"/>
       <c r="AJ125" s="2"/>
     </row>
-    <row r="126" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="11" t="s">
         <v>129</v>
       </c>
@@ -11491,7 +11503,7 @@
       <c r="AI126" s="2"/>
       <c r="AJ126" s="2"/>
     </row>
-    <row r="127" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="18" t="s">
         <v>130</v>
       </c>
@@ -11623,7 +11635,7 @@
         <v>75183</v>
       </c>
     </row>
-    <row r="128" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="11" t="s">
         <v>131</v>
       </c>
@@ -11687,7 +11699,7 @@
       <c r="AI128" s="2"/>
       <c r="AJ128" s="2"/>
     </row>
-    <row r="129" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="11" t="s">
         <v>132</v>
       </c>
@@ -11751,7 +11763,7 @@
       <c r="AI129" s="2"/>
       <c r="AJ129" s="2"/>
     </row>
-    <row r="130" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="18" t="s">
         <v>133</v>
       </c>
@@ -11881,7 +11893,7 @@
         <v>60505</v>
       </c>
     </row>
-    <row r="131" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="11" t="s">
         <v>134</v>
       </c>
@@ -11927,7 +11939,7 @@
       <c r="W131" s="9">
         <v>8493</v>
       </c>
-      <c r="X131" s="63" t="s">
+      <c r="X131" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Y131" s="9"/>
@@ -11943,7 +11955,7 @@
       <c r="AI131" s="2"/>
       <c r="AJ131" s="2"/>
     </row>
-    <row r="132" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="11" t="s">
         <v>135</v>
       </c>
@@ -11989,7 +12001,7 @@
       <c r="W132" s="9">
         <v>7891</v>
       </c>
-      <c r="X132" s="63" t="s">
+      <c r="X132" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Y132" s="9"/>
@@ -12005,12 +12017,12 @@
       <c r="AI132" s="2"/>
       <c r="AJ132" s="2"/>
     </row>
-    <row r="133" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B133" s="17">
-        <v>2806879</v>
+      <c r="B133" s="57">
+        <v>2805285</v>
       </c>
       <c r="C133" s="57">
         <v>156022</v>
@@ -12098,7 +12110,7 @@
       <c r="AG133" s="2"/>
       <c r="AH133" s="12">
         <f>AD133-B133</f>
-        <v>-1594</v>
+        <v>0</v>
       </c>
       <c r="AI133" s="12">
         <f>AE133-C133</f>
@@ -12110,19 +12122,19 @@
       </c>
       <c r="AL133" s="47">
         <f>C133/B133*1000</f>
-        <v>55.585580995832025</v>
+        <v>55.617165457342125</v>
       </c>
       <c r="AM133" s="47">
         <f>D133/B133*1000</f>
-        <v>41.693282824090382</v>
+        <v>41.716973498236364</v>
       </c>
       <c r="AO133" s="47">
         <f>AL133-K133</f>
-        <v>-0.2144190041679721</v>
+        <v>-0.18283454265787213</v>
       </c>
       <c r="AP133" s="47">
         <f>AM133-L133</f>
-        <v>-6.7171759096211758E-3</v>
+        <v>1.697349823636074E-2</v>
       </c>
       <c r="AR133" s="12">
         <f t="shared" ref="AR133" si="123">H133</f>
@@ -12137,7 +12149,7 @@
         <v>121495</v>
       </c>
     </row>
-    <row r="134" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="11" t="s">
         <v>137</v>
       </c>
@@ -12201,7 +12213,7 @@
       <c r="AI134" s="2"/>
       <c r="AJ134" s="2"/>
     </row>
-    <row r="135" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="11" t="s">
         <v>138</v>
       </c>
@@ -12265,7 +12277,7 @@
       <c r="AI135" s="2"/>
       <c r="AJ135" s="2"/>
     </row>
-    <row r="136" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="18" t="s">
         <v>139</v>
       </c>
@@ -12345,13 +12357,13 @@
       <c r="AA136" s="17">
         <v>212588</v>
       </c>
-      <c r="AB136" s="17">
-        <v>175776</v>
+      <c r="AB136" s="57">
+        <v>174776</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" s="12">
         <f>SUM(N136:AB136)</f>
-        <v>2946338</v>
+        <v>2945338</v>
       </c>
       <c r="AE136" s="12">
         <f>SUM(N137:AB137)</f>
@@ -12364,7 +12376,7 @@
       <c r="AG136" s="2"/>
       <c r="AH136" s="12">
         <f>AD136-B136</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI136" s="12">
         <f>AE136-C136</f>
@@ -12403,7 +12415,7 @@
         <v>82146</v>
       </c>
     </row>
-    <row r="137" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="11" t="s">
         <v>140</v>
       </c>
@@ -12473,7 +12485,7 @@
       <c r="AI137" s="2"/>
       <c r="AJ137" s="2"/>
     </row>
-    <row r="138" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="11" t="s">
         <v>141</v>
       </c>
@@ -12543,7 +12555,7 @@
       <c r="AI138" s="2"/>
       <c r="AJ138" s="2"/>
     </row>
-    <row r="139" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="18" t="s">
         <v>142</v>
       </c>
@@ -12556,13 +12568,13 @@
       <c r="D139" s="17">
         <v>29690</v>
       </c>
-      <c r="E139" s="62" t="s">
+      <c r="E139" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="F139" s="62" t="s">
+      <c r="F139" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="G139" s="62" t="s">
+      <c r="G139" s="61" t="s">
         <v>14</v>
       </c>
       <c r="H139" s="17">
@@ -12667,7 +12679,7 @@
         <v>34066</v>
       </c>
     </row>
-    <row r="140" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="11" t="s">
         <v>143</v>
       </c>
@@ -12723,7 +12735,7 @@
       <c r="AI140" s="2"/>
       <c r="AJ140" s="2"/>
     </row>
-    <row r="141" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="11" t="s">
         <v>144</v>
       </c>
@@ -12779,7 +12791,7 @@
       <c r="AI141" s="2"/>
       <c r="AJ141" s="2"/>
     </row>
-    <row r="142" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="18" t="s">
         <v>145</v>
       </c>
@@ -12913,7 +12925,7 @@
         <v>62602</v>
       </c>
     </row>
-    <row r="143" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="11" t="s">
         <v>146</v>
       </c>
@@ -12965,7 +12977,7 @@
       <c r="Y143" s="57">
         <v>7155</v>
       </c>
-      <c r="Z143" s="63" t="s">
+      <c r="Z143" s="62" t="s">
         <v>14</v>
       </c>
       <c r="AA143" s="9"/>
@@ -12979,7 +12991,7 @@
       <c r="AI143" s="2"/>
       <c r="AJ143" s="2"/>
     </row>
-    <row r="144" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="11" t="s">
         <v>147</v>
       </c>
@@ -13031,7 +13043,7 @@
       <c r="Y144" s="57">
         <v>6387</v>
       </c>
-      <c r="Z144" s="63" t="s">
+      <c r="Z144" s="62" t="s">
         <v>14</v>
       </c>
       <c r="AA144" s="9"/>
@@ -13045,7 +13057,7 @@
       <c r="AI144" s="2"/>
       <c r="AJ144" s="2"/>
     </row>
-    <row r="145" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="18" t="s">
         <v>148</v>
       </c>
@@ -13167,7 +13179,7 @@
         <v>102581</v>
       </c>
     </row>
-    <row r="146" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="11" t="s">
         <v>149</v>
       </c>
@@ -13221,7 +13233,7 @@
       <c r="AI146" s="2"/>
       <c r="AJ146" s="2"/>
     </row>
-    <row r="147" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="11" t="s">
         <v>150</v>
       </c>
@@ -13275,7 +13287,7 @@
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
     </row>
-    <row r="148" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="20" t="s">
         <v>151</v>
       </c>
@@ -13367,7 +13379,7 @@
         <v>28401</v>
       </c>
     </row>
-    <row r="149" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="20" t="s">
         <v>152</v>
       </c>
@@ -13459,7 +13471,7 @@
         <v>26234</v>
       </c>
     </row>
-    <row r="150" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="18" t="s">
         <v>153</v>
       </c>
@@ -13472,13 +13484,13 @@
       <c r="D150" s="17">
         <v>23152</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="F150" s="62" t="s">
+      <c r="F150" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="61" t="s">
         <v>14</v>
       </c>
       <c r="H150" s="17">
@@ -13585,7 +13597,7 @@
         <v>25550</v>
       </c>
     </row>
-    <row r="151" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="11" t="s">
         <v>154</v>
       </c>
@@ -13625,7 +13637,7 @@
       <c r="U151" s="9">
         <v>3046</v>
       </c>
-      <c r="V151" s="63" t="s">
+      <c r="V151" s="62" t="s">
         <v>14</v>
       </c>
       <c r="W151" s="9"/>
@@ -13643,7 +13655,7 @@
       <c r="AI151" s="2"/>
       <c r="AJ151" s="2"/>
     </row>
-    <row r="152" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="11" t="s">
         <v>155</v>
       </c>
@@ -13683,7 +13695,7 @@
       <c r="U152" s="9">
         <v>2680</v>
       </c>
-      <c r="V152" s="63" t="s">
+      <c r="V152" s="62" t="s">
         <v>14</v>
       </c>
       <c r="W152" s="9"/>
@@ -13701,7 +13713,7 @@
       <c r="AI152" s="2"/>
       <c r="AJ152" s="2"/>
     </row>
-    <row r="153" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="18" t="s">
         <v>156</v>
       </c>
@@ -13829,7 +13841,7 @@
         <v>86961</v>
       </c>
     </row>
-    <row r="154" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="11" t="s">
         <v>157</v>
       </c>
@@ -13889,7 +13901,7 @@
       <c r="AI154" s="2"/>
       <c r="AJ154" s="2"/>
     </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="11" t="s">
         <v>158</v>
       </c>
@@ -13949,7 +13961,7 @@
       <c r="AI155" s="2"/>
       <c r="AJ155" s="2"/>
     </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="18" t="s">
         <v>159</v>
       </c>
@@ -13962,13 +13974,13 @@
       <c r="D156" s="17">
         <v>62764</v>
       </c>
-      <c r="E156" s="62" t="s">
+      <c r="E156" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="F156" s="62" t="s">
+      <c r="F156" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="G156" s="62" t="s">
+      <c r="G156" s="61" t="s">
         <v>14</v>
       </c>
       <c r="H156" s="17">
@@ -14075,7 +14087,7 @@
         <v>56268</v>
       </c>
     </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="11" t="s">
         <v>160</v>
       </c>
@@ -14115,7 +14127,7 @@
       <c r="U157" s="9">
         <v>12925</v>
       </c>
-      <c r="V157" s="63" t="s">
+      <c r="V157" s="62" t="s">
         <v>14</v>
       </c>
       <c r="W157" s="9"/>
@@ -14133,7 +14145,7 @@
       <c r="AI157" s="2"/>
       <c r="AJ157" s="2"/>
     </row>
-    <row r="158" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="11" t="s">
         <v>161</v>
       </c>
@@ -14173,7 +14185,7 @@
       <c r="U158" s="9">
         <v>9699</v>
       </c>
-      <c r="V158" s="63" t="s">
+      <c r="V158" s="62" t="s">
         <v>14</v>
       </c>
       <c r="W158" s="9"/>
@@ -14191,7 +14203,7 @@
       <c r="AI158" s="2"/>
       <c r="AJ158" s="2"/>
     </row>
-    <row r="159" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="18" t="s">
         <v>162</v>
       </c>
@@ -14325,7 +14337,7 @@
         <v>53594</v>
       </c>
     </row>
-    <row r="160" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="11" t="s">
         <v>163</v>
       </c>
@@ -14377,7 +14389,7 @@
       <c r="Y160" s="9">
         <v>6677</v>
       </c>
-      <c r="Z160" s="63" t="s">
+      <c r="Z160" s="62" t="s">
         <v>14</v>
       </c>
       <c r="AA160" s="9"/>
@@ -14391,7 +14403,7 @@
       <c r="AI160" s="2"/>
       <c r="AJ160" s="2"/>
     </row>
-    <row r="161" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="11" t="s">
         <v>164</v>
       </c>
@@ -14443,7 +14455,7 @@
       <c r="Y161" s="9">
         <v>5050</v>
       </c>
-      <c r="Z161" s="63" t="s">
+      <c r="Z161" s="62" t="s">
         <v>14</v>
       </c>
       <c r="AA161" s="9"/>
@@ -14457,7 +14469,7 @@
       <c r="AI161" s="2"/>
       <c r="AJ161" s="2"/>
     </row>
-    <row r="162" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="18" t="s">
         <v>165</v>
       </c>
@@ -14495,8 +14507,8 @@
         <v>30</v>
       </c>
       <c r="M162" s="9"/>
-      <c r="N162" s="17">
-        <v>110934</v>
+      <c r="N162" s="57">
+        <v>123457</v>
       </c>
       <c r="O162" s="17">
         <v>294690</v>
@@ -14531,7 +14543,7 @@
       <c r="AC162" s="2"/>
       <c r="AD162" s="12">
         <f>SUM(N162:AB162)</f>
-        <v>1168646</v>
+        <v>1181169</v>
       </c>
       <c r="AE162" s="12">
         <f>SUM(N163:AB163)</f>
@@ -14544,7 +14556,7 @@
       <c r="AG162" s="2"/>
       <c r="AH162" s="12">
         <f>AD162-B162</f>
-        <v>-12523</v>
+        <v>0</v>
       </c>
       <c r="AI162" s="12">
         <f>AE162-C162</f>
@@ -14583,7 +14595,7 @@
         <v>34141</v>
       </c>
     </row>
-    <row r="163" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="11" t="s">
         <v>166</v>
       </c>
@@ -14641,7 +14653,7 @@
       <c r="AI163" s="2"/>
       <c r="AJ163" s="2"/>
     </row>
-    <row r="164" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="11" t="s">
         <v>167</v>
       </c>
@@ -14699,7 +14711,7 @@
       <c r="AI164" s="2"/>
       <c r="AJ164" s="2"/>
     </row>
-    <row r="165" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="18" t="s">
         <v>168</v>
       </c>
@@ -14830,7 +14842,7 @@
         <v>94346</v>
       </c>
     </row>
-    <row r="166" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="11" t="s">
         <v>169</v>
       </c>
@@ -14894,7 +14906,7 @@
       <c r="AI166" s="2"/>
       <c r="AJ166" s="2"/>
     </row>
-    <row r="167" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="11" t="s">
         <v>170</v>
       </c>
@@ -14958,7 +14970,7 @@
       <c r="AI167" s="2"/>
       <c r="AJ167" s="2"/>
     </row>
-    <row r="168" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="18" t="s">
         <v>171</v>
       </c>
@@ -15091,7 +15103,7 @@
         <v>59944</v>
       </c>
     </row>
-    <row r="169" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="11" t="s">
         <v>172</v>
       </c>
@@ -15157,7 +15169,7 @@
       <c r="AI169" s="2"/>
       <c r="AJ169" s="2"/>
     </row>
-    <row r="170" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="11" t="s">
         <v>173</v>
       </c>
@@ -15223,7 +15235,7 @@
       <c r="AI170" s="2"/>
       <c r="AJ170" s="2"/>
     </row>
-    <row r="171" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="18" t="s">
         <v>174</v>
       </c>
@@ -15354,7 +15366,7 @@
         <v>56895</v>
       </c>
     </row>
-    <row r="172" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="11" t="s">
         <v>175</v>
       </c>
@@ -15418,7 +15430,7 @@
       <c r="AI172" s="2"/>
       <c r="AJ172" s="2"/>
     </row>
-    <row r="173" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="11" t="s">
         <v>176</v>
       </c>
@@ -15482,7 +15494,7 @@
       <c r="AI173" s="2"/>
       <c r="AJ173" s="2"/>
     </row>
-    <row r="174" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="18" t="s">
         <v>177</v>
       </c>
@@ -15601,7 +15613,7 @@
         <v>63824</v>
       </c>
     </row>
-    <row r="175" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="11" t="s">
         <v>178</v>
       </c>
@@ -15653,7 +15665,7 @@
       <c r="AI175" s="2"/>
       <c r="AJ175" s="2"/>
     </row>
-    <row r="176" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="11" t="s">
         <v>179</v>
       </c>
@@ -15705,7 +15717,7 @@
       <c r="AI176" s="2"/>
       <c r="AJ176" s="2"/>
     </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="18" t="s">
         <v>180</v>
       </c>
@@ -15834,7 +15846,7 @@
         <v>85859</v>
       </c>
     </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="11" t="s">
         <v>181</v>
       </c>
@@ -15896,7 +15908,7 @@
       <c r="AI178" s="2"/>
       <c r="AJ178" s="2"/>
     </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="11" t="s">
         <v>182</v>
       </c>
@@ -15958,7 +15970,7 @@
       <c r="AI179" s="2"/>
       <c r="AJ179" s="2"/>
     </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="18" t="s">
         <v>183</v>
       </c>
@@ -15998,8 +16010,8 @@
       <c r="N180" s="19">
         <v>425817</v>
       </c>
-      <c r="O180" s="19">
-        <v>562976</v>
+      <c r="O180" s="60">
+        <v>362976</v>
       </c>
       <c r="P180" s="19">
         <v>501681</v>
@@ -16007,11 +16019,11 @@
       <c r="Q180" s="19">
         <v>195781</v>
       </c>
-      <c r="R180" s="19">
-        <v>26483</v>
-      </c>
-      <c r="S180" s="19">
-        <v>166296</v>
+      <c r="R180" s="60">
+        <v>166483</v>
+      </c>
+      <c r="S180" s="60">
+        <v>206296</v>
       </c>
       <c r="T180" s="17"/>
       <c r="U180" s="17"/>
@@ -16025,7 +16037,7 @@
       <c r="AC180" s="2"/>
       <c r="AD180" s="12">
         <f>SUM(N180:AB180)</f>
-        <v>1879034</v>
+        <v>1859034</v>
       </c>
       <c r="AE180" s="12">
         <f>SUM(N181:AB181)</f>
@@ -16038,7 +16050,7 @@
       <c r="AG180" s="2"/>
       <c r="AH180" s="12">
         <f>AD180-B180</f>
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AI180" s="12">
         <f>AE180-C180</f>
@@ -16077,7 +16089,7 @@
         <v>57290</v>
       </c>
     </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="11" t="s">
         <v>184</v>
       </c>
@@ -16129,7 +16141,7 @@
       <c r="AI181" s="2"/>
       <c r="AJ181" s="2"/>
     </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="11" t="s">
         <v>185</v>
       </c>
@@ -16181,7 +16193,7 @@
       <c r="AI182" s="2"/>
       <c r="AJ182" s="2"/>
     </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="20" t="s">
         <v>186</v>
       </c>
@@ -16273,7 +16285,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="20" t="s">
         <v>187</v>
       </c>
@@ -16365,7 +16377,7 @@
         <v>7737</v>
       </c>
     </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="18" t="s">
         <v>188</v>
       </c>
@@ -16502,7 +16514,7 @@
         <v>69619</v>
       </c>
     </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="11" t="s">
         <v>189</v>
       </c>
@@ -16572,7 +16584,7 @@
       <c r="AI186" s="2"/>
       <c r="AJ186" s="2"/>
     </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="11" t="s">
         <v>190</v>
       </c>
@@ -16642,7 +16654,7 @@
       <c r="AI187" s="2"/>
       <c r="AJ187" s="2"/>
     </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="18" t="s">
         <v>191</v>
       </c>
@@ -16771,7 +16783,7 @@
         <v>36205</v>
       </c>
     </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="11" t="s">
         <v>192</v>
       </c>
@@ -16817,7 +16829,7 @@
       <c r="W189" s="6">
         <v>4130</v>
       </c>
-      <c r="X189" s="63" t="s">
+      <c r="X189" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Y189" s="9"/>
@@ -16833,7 +16845,7 @@
       <c r="AI189" s="2"/>
       <c r="AJ189" s="2"/>
     </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="11" t="s">
         <v>193</v>
       </c>
@@ -16879,7 +16891,7 @@
       <c r="W190" s="6">
         <v>2849</v>
       </c>
-      <c r="X190" s="63" t="s">
+      <c r="X190" s="62" t="s">
         <v>14</v>
       </c>
       <c r="Y190" s="9"/>
@@ -16895,7 +16907,7 @@
       <c r="AI190" s="2"/>
       <c r="AJ190" s="2"/>
     </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="45" t="s">
         <v>194</v>
       </c>
@@ -16944,7 +16956,7 @@
       <c r="AC191" s="2"/>
       <c r="AD191" s="23">
         <f>SUM(AD85:AD190)</f>
-        <v>65294863</v>
+        <v>65331451</v>
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
@@ -16957,7 +16969,7 @@
       <c r="AG191" s="2"/>
       <c r="AH191" s="23">
         <f t="shared" ref="AH191:AJ192" si="181">AD191-B191</f>
-        <v>-64484</v>
+        <v>-27896</v>
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="181"/>
@@ -17009,7 +17021,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="18" t="s">
         <v>195</v>
       </c>
@@ -17134,7 +17146,7 @@
         <v>68890</v>
       </c>
     </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="11" t="s">
         <v>196</v>
       </c>
@@ -17192,7 +17204,7 @@
       <c r="AI193" s="2"/>
       <c r="AJ193" s="2"/>
     </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="11" t="s">
         <v>197</v>
       </c>
@@ -17250,7 +17262,7 @@
       <c r="AI194" s="2"/>
       <c r="AJ194" s="2"/>
     </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="45" t="s">
         <v>198</v>
       </c>
@@ -17299,7 +17311,7 @@
       <c r="AC195" s="2"/>
       <c r="AD195" s="23">
         <f>SUM(AD42, AD74, AD84, AD191, AD192)</f>
-        <v>99060992</v>
+        <v>98938558</v>
       </c>
       <c r="AE195" s="23">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
@@ -17312,7 +17324,7 @@
       <c r="AG195" s="2"/>
       <c r="AH195" s="23">
         <f t="shared" ref="AH195:AJ196" si="186">AD195-B195</f>
-        <v>-42363</v>
+        <v>-164797</v>
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="186"/>
@@ -17364,7 +17376,7 @@
         <v>-252189</v>
       </c>
     </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="18" t="s">
         <v>199</v>
       </c>
@@ -17487,7 +17499,7 @@
         <v>15719</v>
       </c>
     </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="11" t="s">
         <v>200</v>
       </c>
@@ -17543,7 +17555,7 @@
       <c r="AI197" s="2"/>
       <c r="AJ197" s="2"/>
     </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="11" t="s">
         <v>201</v>
       </c>
@@ -17599,7 +17611,7 @@
       <c r="AI198" s="2"/>
       <c r="AJ198" s="2"/>
     </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="18" t="s">
         <v>202</v>
       </c>
@@ -17720,7 +17732,7 @@
         <v>12320</v>
       </c>
     </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="11" t="s">
         <v>203</v>
       </c>
@@ -17780,7 +17792,7 @@
       <c r="AI200" s="2"/>
       <c r="AJ200" s="2"/>
     </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="11" t="s">
         <v>204</v>
       </c>
@@ -17840,7 +17852,7 @@
       <c r="AI201" s="2"/>
       <c r="AJ201" s="2"/>
     </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="18" t="s">
         <v>205</v>
       </c>
@@ -17963,7 +17975,7 @@
         <v>13860</v>
       </c>
     </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="11" t="s">
         <v>206</v>
       </c>
@@ -18019,7 +18031,7 @@
       <c r="AI203" s="2"/>
       <c r="AJ203" s="2"/>
     </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="11" t="s">
         <v>207</v>
       </c>
@@ -18075,7 +18087,7 @@
       <c r="AI204" s="2"/>
       <c r="AJ204" s="2"/>
     </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="20" t="s">
         <v>208</v>
       </c>
@@ -18158,7 +18170,7 @@
       <c r="AS205" s="12"/>
       <c r="AT205" s="12"/>
     </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="18" t="s">
         <v>209</v>
       </c>
@@ -18281,7 +18293,7 @@
         <v>57139</v>
       </c>
     </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="11" t="s">
         <v>210</v>
       </c>
@@ -18337,7 +18349,7 @@
       <c r="AI207" s="2"/>
       <c r="AJ207" s="2"/>
     </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="11" t="s">
         <v>211</v>
       </c>
@@ -18393,7 +18405,7 @@
       <c r="AI208" s="2"/>
       <c r="AJ208" s="2"/>
     </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="18" t="s">
         <v>212</v>
       </c>
@@ -18520,7 +18532,7 @@
         <v>14579</v>
       </c>
     </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="11" t="s">
         <v>213</v>
       </c>
@@ -18580,7 +18592,7 @@
       <c r="AI210" s="2"/>
       <c r="AJ210" s="2"/>
     </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="11" t="s">
         <v>214</v>
       </c>
@@ -18640,7 +18652,7 @@
       <c r="AI211" s="2"/>
       <c r="AJ211" s="2"/>
     </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="18" t="s">
         <v>215</v>
       </c>
@@ -18757,7 +18769,7 @@
         <v>28752</v>
       </c>
     </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="11" t="s">
         <v>216</v>
       </c>
@@ -18807,7 +18819,7 @@
       <c r="AI213" s="2"/>
       <c r="AJ213" s="2"/>
     </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="11" t="s">
         <v>217</v>
       </c>
@@ -18857,7 +18869,7 @@
       <c r="AI214" s="2"/>
       <c r="AJ214" s="2"/>
     </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="18" t="s">
         <v>218</v>
       </c>
@@ -18978,7 +18990,7 @@
         <v>16626</v>
       </c>
     </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="11" t="s">
         <v>219</v>
       </c>
@@ -19032,7 +19044,7 @@
       <c r="AI216" s="2"/>
       <c r="AJ216" s="2"/>
     </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="11" t="s">
         <v>220</v>
       </c>
@@ -19086,7 +19098,7 @@
       <c r="AI217" s="2"/>
       <c r="AJ217" s="2"/>
     </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="18" t="s">
         <v>221</v>
       </c>
@@ -19211,7 +19223,7 @@
         <v>17424</v>
       </c>
     </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="11" t="s">
         <v>222</v>
       </c>
@@ -19269,7 +19281,7 @@
       <c r="AI219" s="2"/>
       <c r="AJ219" s="2"/>
     </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="11" t="s">
         <v>223</v>
       </c>
@@ -19327,7 +19339,7 @@
       <c r="AI220" s="2"/>
       <c r="AJ220" s="2"/>
     </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="18" t="s">
         <v>224</v>
       </c>
@@ -19385,7 +19397,9 @@
       <c r="T221" s="19">
         <v>98853</v>
       </c>
-      <c r="U221" s="19"/>
+      <c r="U221" s="39">
+        <v>4028</v>
+      </c>
       <c r="V221" s="19"/>
       <c r="W221" s="19"/>
       <c r="X221" s="19"/>
@@ -19396,7 +19410,7 @@
       <c r="AC221" s="2"/>
       <c r="AD221" s="12">
         <f>SUM(N221:AB221)</f>
-        <v>686500</v>
+        <v>690528</v>
       </c>
       <c r="AE221" s="12">
         <f>SUM(N222:AB222)</f>
@@ -19409,7 +19423,7 @@
       <c r="AG221" s="2"/>
       <c r="AH221" s="12">
         <f>AD221-B221</f>
-        <v>-4028</v>
+        <v>0</v>
       </c>
       <c r="AI221" s="12"/>
       <c r="AJ221" s="12"/>
@@ -19442,7 +19456,7 @@
         <v>14815</v>
       </c>
     </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="11" t="s">
         <v>225</v>
       </c>
@@ -19458,28 +19472,30 @@
       <c r="K222" s="37"/>
       <c r="L222" s="37"/>
       <c r="M222" s="9"/>
-      <c r="N222" s="6" t="s">
+      <c r="N222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="O222" s="6" t="s">
+      <c r="O222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="P222" s="6" t="s">
+      <c r="P222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="Q222" s="6" t="s">
+      <c r="Q222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="R222" s="6" t="s">
+      <c r="R222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="S222" s="6" t="s">
+      <c r="S222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="T222" s="6" t="s">
+      <c r="T222" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="U222" s="6"/>
+      <c r="U222" s="37" t="s">
+        <v>14</v>
+      </c>
       <c r="V222" s="6"/>
       <c r="W222" s="6"/>
       <c r="X222" s="6"/>
@@ -19496,7 +19512,7 @@
       <c r="AI222" s="2"/>
       <c r="AJ222" s="2"/>
     </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="11" t="s">
         <v>226</v>
       </c>
@@ -19512,28 +19528,30 @@
       <c r="K223" s="37"/>
       <c r="L223" s="37"/>
       <c r="M223" s="9"/>
-      <c r="N223" s="6" t="s">
+      <c r="N223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="O223" s="6" t="s">
+      <c r="O223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="P223" s="6" t="s">
+      <c r="P223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="Q223" s="6" t="s">
+      <c r="Q223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="R223" s="6" t="s">
+      <c r="R223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="S223" s="6" t="s">
+      <c r="S223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="T223" s="6" t="s">
+      <c r="T223" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="U223" s="6"/>
+      <c r="U223" s="37" t="s">
+        <v>14</v>
+      </c>
       <c r="V223" s="6"/>
       <c r="W223" s="6"/>
       <c r="X223" s="6"/>
@@ -19550,7 +19568,7 @@
       <c r="AI223" s="2"/>
       <c r="AJ223" s="2"/>
     </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="45" t="s">
         <v>227</v>
       </c>
@@ -19599,7 +19617,7 @@
       <c r="AC224" s="2"/>
       <c r="AD224" s="23">
         <f>SUM(AD196:AD223)</f>
-        <v>8081419</v>
+        <v>8085447</v>
       </c>
       <c r="AE224" s="23">
         <f>SUM(AE196:AE223)</f>
@@ -19612,7 +19630,7 @@
       <c r="AG224" s="2"/>
       <c r="AH224" s="23">
         <f>AD224-B224</f>
-        <v>-3988</v>
+        <v>40</v>
       </c>
       <c r="AI224" s="23">
         <f>AE224-C224</f>
@@ -19664,7 +19682,7 @@
         <v>-2679</v>
       </c>
     </row>
-    <row r="225" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="18" t="s">
         <v>228</v>
       </c>
@@ -19741,7 +19759,7 @@
       <c r="AS225" s="12"/>
       <c r="AT225" s="12"/>
     </row>
-    <row r="226" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="18" t="s">
         <v>229</v>
       </c>
@@ -19860,7 +19878,7 @@
         <v>17487</v>
       </c>
     </row>
-    <row r="227" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="11" t="s">
         <v>230</v>
       </c>
@@ -19912,7 +19930,7 @@
       <c r="AI227" s="2"/>
       <c r="AJ227" s="2"/>
     </row>
-    <row r="228" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="11" t="s">
         <v>231</v>
       </c>
@@ -19964,12 +19982,12 @@
       <c r="AI228" s="2"/>
       <c r="AJ228" s="2"/>
     </row>
-    <row r="229" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="18" t="s">
         <v>232</v>
       </c>
       <c r="B229" s="19">
-        <v>586002</v>
+        <v>576002</v>
       </c>
       <c r="C229" s="19">
         <v>20933</v>
@@ -20048,7 +20066,7 @@
       <c r="AG229" s="2"/>
       <c r="AH229" s="12">
         <f>AD229-B229</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="AI229" s="12">
         <f>AE229-C229</f>
@@ -20060,19 +20078,19 @@
       </c>
       <c r="AL229" s="47">
         <f>C229/B229*1000</f>
-        <v>35.721721086276155</v>
+        <v>36.341887701778809</v>
       </c>
       <c r="AM229" s="47">
         <f>D229/B229*1000</f>
-        <v>20.680816789021197</v>
+        <v>21.03985750049479</v>
       </c>
       <c r="AO229" s="47">
         <f>AL229-K229</f>
-        <v>-0.57827891372384244</v>
+        <v>4.1887701778811959E-2</v>
       </c>
       <c r="AP229" s="47">
         <f>AM229-L229</f>
-        <v>-0.41918321097880451</v>
+        <v>-6.0142499505211333E-2</v>
       </c>
       <c r="AR229" s="12">
         <f t="shared" ref="AR229" si="213">H229</f>
@@ -20087,7 +20105,7 @@
         <v>12724</v>
       </c>
     </row>
-    <row r="230" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="11" t="s">
         <v>233</v>
       </c>
@@ -20143,7 +20161,7 @@
       <c r="AI230" s="2"/>
       <c r="AJ230" s="2"/>
     </row>
-    <row r="231" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="11" t="s">
         <v>234</v>
       </c>
@@ -20199,7 +20217,7 @@
       <c r="AI231" s="2"/>
       <c r="AJ231" s="2"/>
     </row>
-    <row r="232" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="18" t="s">
         <v>235</v>
       </c>
@@ -20316,7 +20334,7 @@
         <v>16324</v>
       </c>
     </row>
-    <row r="233" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="11" t="s">
         <v>236</v>
       </c>
@@ -20366,7 +20384,7 @@
       <c r="AI233" s="2"/>
       <c r="AJ233" s="2"/>
     </row>
-    <row r="234" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="11" t="s">
         <v>237</v>
       </c>
@@ -20416,7 +20434,7 @@
       <c r="AI234" s="2"/>
       <c r="AJ234" s="2"/>
     </row>
-    <row r="235" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="18" t="s">
         <v>238</v>
       </c>
@@ -20535,7 +20553,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="236" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="11" t="s">
         <v>239</v>
       </c>
@@ -20593,7 +20611,7 @@
       <c r="AI236" s="2"/>
       <c r="AJ236" s="2"/>
     </row>
-    <row r="237" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="11" t="s">
         <v>240</v>
       </c>
@@ -20651,7 +20669,7 @@
       <c r="AI237" s="2"/>
       <c r="AJ237" s="2"/>
     </row>
-    <row r="238" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="18" t="s">
         <v>241</v>
       </c>
@@ -20778,7 +20796,7 @@
         <v>60357</v>
       </c>
     </row>
-    <row r="239" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="11" t="s">
         <v>242</v>
       </c>
@@ -20831,7 +20849,7 @@
       <c r="AB239" s="9"/>
       <c r="AC239" s="2"/>
     </row>
-    <row r="240" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="11" t="s">
         <v>243</v>
       </c>
@@ -20891,7 +20909,7 @@
       <c r="AI240" s="2"/>
       <c r="AJ240" s="2"/>
     </row>
-    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="18" t="s">
         <v>244</v>
       </c>
@@ -21010,7 +21028,7 @@
         <v>36016</v>
       </c>
     </row>
-    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="11" t="s">
         <v>245</v>
       </c>
@@ -21062,7 +21080,7 @@
       <c r="AI242" s="2"/>
       <c r="AJ242" s="2"/>
     </row>
-    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="11" t="s">
         <v>246</v>
       </c>
@@ -21114,7 +21132,7 @@
       <c r="AI243" s="2"/>
       <c r="AJ243" s="2"/>
     </row>
-    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="18" t="s">
         <v>247</v>
       </c>
@@ -21231,7 +21249,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="11" t="s">
         <v>248</v>
       </c>
@@ -21281,7 +21299,7 @@
       <c r="AI245" s="2"/>
       <c r="AJ245" s="2"/>
     </row>
-    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="11" t="s">
         <v>249</v>
       </c>
@@ -21331,7 +21349,7 @@
       <c r="AI246" s="2"/>
       <c r="AJ246" s="2"/>
     </row>
-    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="18" t="s">
         <v>250</v>
       </c>
@@ -21444,7 +21462,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="11" t="s">
         <v>251</v>
       </c>
@@ -21490,7 +21508,7 @@
       <c r="AI248" s="2"/>
       <c r="AJ248" s="2"/>
     </row>
-    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="11" t="s">
         <v>252</v>
       </c>
@@ -21536,7 +21554,7 @@
       <c r="AI249" s="2"/>
       <c r="AJ249" s="2"/>
     </row>
-    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="45" t="s">
         <v>253</v>
       </c>
@@ -21650,7 +21668,7 @@
         <v>-5324</v>
       </c>
     </row>
-    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="14" t="s">
         <v>254</v>
       </c>
@@ -21749,7 +21767,7 @@
         <v>10239</v>
       </c>
     </row>
-    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="14" t="s">
         <v>255</v>
       </c>
@@ -21827,7 +21845,7 @@
       <c r="AS252" s="12"/>
       <c r="AT252" s="12"/>
     </row>
-    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="14" t="s">
         <v>256</v>
       </c>
@@ -21923,7 +21941,7 @@
         <v>18.045821337734392</v>
       </c>
     </row>
-    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -21971,7 +21989,7 @@
       <c r="AI254" s="2"/>
       <c r="AJ254" s="2"/>
     </row>
-    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -22019,7 +22037,7 @@
       <c r="AI255" s="2"/>
       <c r="AJ255" s="2"/>
     </row>
-    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="14" t="s">
         <v>259</v>
       </c>
@@ -22072,7 +22090,9 @@
       <c r="R256" s="15">
         <v>94474</v>
       </c>
-      <c r="S256" s="15"/>
+      <c r="S256" s="59">
+        <v>22913</v>
+      </c>
       <c r="T256" s="15"/>
       <c r="U256" s="15"/>
       <c r="V256" s="15"/>
@@ -22085,11 +22105,11 @@
       <c r="AC256" s="2"/>
       <c r="AD256" s="12">
         <f>SUM(N256:AB256)</f>
-        <v>572341</v>
+        <v>595254</v>
       </c>
       <c r="AE256" s="12">
         <f>SUM(N257:AB257)</f>
-        <v>9605</v>
+        <v>10055</v>
       </c>
       <c r="AF256" s="12">
         <f>SUM(N258:AB258)</f>
@@ -22098,11 +22118,11 @@
       <c r="AG256" s="2"/>
       <c r="AH256" s="12">
         <f>AD256-B256</f>
-        <v>-22913</v>
+        <v>0</v>
       </c>
       <c r="AI256" s="12">
         <f>AE256-C256</f>
-        <v>-450</v>
+        <v>0</v>
       </c>
       <c r="AJ256" s="12">
         <f>AF256-D256</f>
@@ -22125,7 +22145,7 @@
       <c r="AS256" s="12"/>
       <c r="AT256" s="12"/>
     </row>
-    <row r="257" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -22156,7 +22176,9 @@
       <c r="R257" s="8">
         <v>2302</v>
       </c>
-      <c r="S257" s="8"/>
+      <c r="S257" s="59">
+        <v>450</v>
+      </c>
       <c r="T257" s="8"/>
       <c r="U257" s="8"/>
       <c r="V257" s="8"/>
@@ -22175,7 +22197,7 @@
       <c r="AI257" s="2"/>
       <c r="AJ257" s="2"/>
     </row>
-    <row r="258" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
         <v>261</v>
       </c>
@@ -22206,7 +22228,9 @@
       <c r="R258" s="8">
         <v>2002</v>
       </c>
-      <c r="S258" s="8"/>
+      <c r="S258" s="59" t="s">
+        <v>14</v>
+      </c>
       <c r="T258" s="8"/>
       <c r="U258" s="8"/>
       <c r="V258" s="8"/>
@@ -22225,7 +22249,7 @@
       <c r="AI258" s="2"/>
       <c r="AJ258" s="2"/>
     </row>
-    <row r="259" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="14" t="s">
         <v>262</v>
       </c>
@@ -22263,8 +22287,8 @@
         <v>14</v>
       </c>
       <c r="M259" s="9"/>
-      <c r="N259" s="15">
-        <v>179646</v>
+      <c r="N259" s="59">
+        <v>203138</v>
       </c>
       <c r="O259" s="15">
         <v>79531</v>
@@ -22293,7 +22317,7 @@
       <c r="AC259" s="2"/>
       <c r="AD259" s="12">
         <f>SUM(N259:AB259)</f>
-        <v>657942</v>
+        <v>681434</v>
       </c>
       <c r="AE259" s="12">
         <f>SUM(N260:AB260)</f>
@@ -22306,7 +22330,7 @@
       <c r="AG259" s="2"/>
       <c r="AH259" s="12">
         <f>AD259-B259</f>
-        <v>-23492</v>
+        <v>0</v>
       </c>
       <c r="AI259" s="12">
         <f>AE259-C259</f>
@@ -22339,7 +22363,7 @@
         <v>9335</v>
       </c>
     </row>
-    <row r="260" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
         <v>263</v>
       </c>
@@ -22391,7 +22415,7 @@
       <c r="AI260" s="2"/>
       <c r="AJ260" s="2"/>
     </row>
-    <row r="261" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
         <v>264</v>
       </c>
@@ -22443,7 +22467,7 @@
       <c r="AI261" s="2"/>
       <c r="AJ261" s="2"/>
     </row>
-    <row r="262" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="14" t="s">
         <v>265</v>
       </c>
@@ -22481,8 +22505,8 @@
         <v>14</v>
       </c>
       <c r="M262" s="9"/>
-      <c r="N262" s="15">
-        <v>360430</v>
+      <c r="N262" s="59">
+        <v>370430</v>
       </c>
       <c r="O262" s="15">
         <v>186999</v>
@@ -22511,7 +22535,7 @@
       <c r="AC262" s="2"/>
       <c r="AD262" s="12">
         <f>SUM(N262:AB262)</f>
-        <v>1154507</v>
+        <v>1164507</v>
       </c>
       <c r="AE262" s="12">
         <f>SUM(N263:AB263)</f>
@@ -22524,7 +22548,7 @@
       <c r="AG262" s="2"/>
       <c r="AH262" s="12">
         <f>AD262-B262</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="AI262" s="12">
         <f>AE262-C262</f>
@@ -22551,7 +22575,7 @@
       <c r="AS262" s="12"/>
       <c r="AT262" s="12"/>
     </row>
-    <row r="263" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -22603,7 +22627,7 @@
       <c r="AI263" s="2"/>
       <c r="AJ263" s="2"/>
     </row>
-    <row r="264" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
         <v>267</v>
       </c>
@@ -22655,12 +22679,12 @@
       <c r="AI264" s="2"/>
       <c r="AJ264" s="2"/>
     </row>
-    <row r="265" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="B265" s="15">
-        <v>397959</v>
+      <c r="B265" s="59">
+        <v>387959</v>
       </c>
       <c r="C265" s="15">
         <v>10456</v>
@@ -22696,8 +22720,8 @@
       <c r="N265" s="15">
         <v>71339</v>
       </c>
-      <c r="O265" s="15">
-        <v>46394</v>
+      <c r="O265" s="59">
+        <v>86394</v>
       </c>
       <c r="P265" s="15">
         <v>84625</v>
@@ -22705,7 +22729,9 @@
       <c r="Q265" s="15">
         <v>138286</v>
       </c>
-      <c r="R265" s="15"/>
+      <c r="R265" s="59">
+        <v>7315</v>
+      </c>
       <c r="S265" s="15"/>
       <c r="T265" s="15"/>
       <c r="U265" s="15"/>
@@ -22719,7 +22745,7 @@
       <c r="AC265" s="2"/>
       <c r="AD265" s="12">
         <f>SUM(N265:AB265)</f>
-        <v>340644</v>
+        <v>387959</v>
       </c>
       <c r="AE265" s="12">
         <f>SUM(N266:AB266)</f>
@@ -22732,7 +22758,7 @@
       <c r="AG265" s="2"/>
       <c r="AH265" s="12">
         <f>AD265-B265</f>
-        <v>-57315</v>
+        <v>0</v>
       </c>
       <c r="AI265" s="12">
         <f>AE265-C265</f>
@@ -22744,11 +22770,11 @@
       </c>
       <c r="AL265" s="47">
         <f>C265/B265*1000</f>
-        <v>26.274063408542087</v>
+        <v>26.951301555061232</v>
       </c>
       <c r="AM265" s="47">
         <f>D265/B265*1000</f>
-        <v>16.662520510906905</v>
+        <v>17.092012300268841</v>
       </c>
       <c r="AO265" s="47"/>
       <c r="AP265" s="47"/>
@@ -22759,7 +22785,7 @@
       <c r="AS265" s="12"/>
       <c r="AT265" s="12"/>
     </row>
-    <row r="266" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -22787,7 +22813,9 @@
       <c r="Q266" s="8">
         <v>6065</v>
       </c>
-      <c r="R266" s="8"/>
+      <c r="R266" s="65" t="s">
+        <v>14</v>
+      </c>
       <c r="S266" s="8"/>
       <c r="T266" s="8"/>
       <c r="U266" s="8"/>
@@ -22807,7 +22835,7 @@
       <c r="AI266" s="2"/>
       <c r="AJ266" s="2"/>
     </row>
-    <row r="267" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" t="s">
         <v>270</v>
       </c>
@@ -22835,7 +22863,9 @@
       <c r="Q267" s="8">
         <v>3272</v>
       </c>
-      <c r="R267" s="8"/>
+      <c r="R267" s="65" t="s">
+        <v>14</v>
+      </c>
       <c r="S267" s="8"/>
       <c r="T267" s="8"/>
       <c r="U267" s="8"/>
@@ -22855,7 +22885,7 @@
       <c r="AI267" s="2"/>
       <c r="AJ267" s="2"/>
     </row>
-    <row r="268" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="14" t="s">
         <v>271</v>
       </c>
@@ -22905,7 +22935,9 @@
       <c r="Q268" s="15">
         <v>91394</v>
       </c>
-      <c r="R268" s="15"/>
+      <c r="R268" s="59">
+        <v>30000</v>
+      </c>
       <c r="S268" s="15"/>
       <c r="T268" s="15"/>
       <c r="U268" s="15"/>
@@ -22919,7 +22951,7 @@
       <c r="AC268" s="2"/>
       <c r="AD268" s="12">
         <f>SUM(N268:AB268)</f>
-        <v>554903</v>
+        <v>584903</v>
       </c>
       <c r="AE268" s="12">
         <f>SUM(N269:AB269)</f>
@@ -22932,7 +22964,7 @@
       <c r="AG268" s="2"/>
       <c r="AH268" s="12">
         <f>AD268-B268</f>
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="AI268" s="12">
         <f>AE268-C268</f>
@@ -22965,7 +22997,7 @@
         <v>4397</v>
       </c>
     </row>
-    <row r="269" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" t="s">
         <v>272</v>
       </c>
@@ -22993,7 +23025,9 @@
       <c r="Q269" s="8">
         <v>37</v>
       </c>
-      <c r="R269" s="8"/>
+      <c r="R269" s="65" t="s">
+        <v>14</v>
+      </c>
       <c r="S269" s="8"/>
       <c r="T269" s="8"/>
       <c r="U269" s="8"/>
@@ -23013,7 +23047,7 @@
       <c r="AI269" s="2"/>
       <c r="AJ269" s="2"/>
     </row>
-    <row r="270" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" t="s">
         <v>273</v>
       </c>
@@ -23041,7 +23075,9 @@
       <c r="Q270" s="8">
         <v>20</v>
       </c>
-      <c r="R270" s="8"/>
+      <c r="R270" s="65" t="s">
+        <v>14</v>
+      </c>
       <c r="S270" s="8"/>
       <c r="T270" s="8"/>
       <c r="U270" s="8"/>
@@ -23061,7 +23097,7 @@
       <c r="AI270" s="2"/>
       <c r="AJ270" s="2"/>
     </row>
-    <row r="271" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="14" t="s">
         <v>274</v>
       </c>
@@ -23173,7 +23209,7 @@
       <c r="AS271" s="12"/>
       <c r="AT271" s="12"/>
     </row>
-    <row r="272" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
         <v>275</v>
       </c>
@@ -23223,7 +23259,7 @@
       <c r="AI272" s="2"/>
       <c r="AJ272" s="2"/>
     </row>
-    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>276</v>
       </c>
@@ -23273,7 +23309,7 @@
       <c r="AI273" s="2"/>
       <c r="AJ273" s="2"/>
     </row>
-    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="21" t="s">
         <v>277</v>
       </c>
@@ -23323,11 +23359,11 @@
       <c r="AC274" s="2"/>
       <c r="AD274" s="23">
         <f>SUM(AD251:AD273)</f>
-        <v>6228690</v>
+        <v>6362410</v>
       </c>
       <c r="AE274" s="23">
         <f>SUM(AE251:AE273)</f>
-        <v>147180</v>
+        <v>147630</v>
       </c>
       <c r="AF274" s="23">
         <f>SUM(AF251:AF273)</f>
@@ -23336,11 +23372,11 @@
       <c r="AG274" s="2"/>
       <c r="AH274" s="23">
         <f t="shared" ref="AH274:AJ275" si="246">AD274-B274</f>
-        <v>-143600</v>
+        <v>-9880</v>
       </c>
       <c r="AI274" s="23">
         <f t="shared" si="246"/>
-        <v>-37</v>
+        <v>413</v>
       </c>
       <c r="AJ274" s="23">
         <f t="shared" si="246"/>
@@ -23386,7 +23422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="21" t="s">
         <v>278</v>
       </c>
@@ -23436,11 +23472,11 @@
       <c r="AC275" s="2"/>
       <c r="AD275" s="23">
         <f>SUM(AD195, AD224, AD250, AD274)</f>
-        <v>118187699</v>
+        <v>118203013</v>
       </c>
       <c r="AE275" s="23">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
-        <v>5350025</v>
+        <v>5350475</v>
       </c>
       <c r="AF275" s="23">
         <f>SUM(AF195, AF224, AF250, AF274)</f>
@@ -23449,11 +23485,11 @@
       <c r="AG275" s="2"/>
       <c r="AH275" s="23">
         <f t="shared" si="246"/>
-        <v>-190451</v>
+        <v>-175137</v>
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="246"/>
-        <v>-19184</v>
+        <v>-18734</v>
       </c>
       <c r="AJ275" s="23">
         <f t="shared" si="246"/>
@@ -23512,14 +23548,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C75BB2-12A9-42A6-B34F-FED52308A84D}">
   <dimension ref="A1:I410"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.83984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -23544,7 +23580,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41" t="s">
         <v>308</v>
       </c>
@@ -23569,7 +23605,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
         <v>309</v>
       </c>
@@ -23594,7 +23630,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="41" t="s">
         <v>310</v>
       </c>
@@ -23619,7 +23655,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41" t="s">
         <v>311</v>
       </c>
@@ -23644,7 +23680,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="41" t="s">
         <v>312</v>
       </c>
@@ -23669,7 +23705,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="41" t="s">
         <v>313</v>
       </c>
@@ -23694,7 +23730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="41" t="s">
         <v>314</v>
       </c>
@@ -23719,7 +23755,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="41" t="s">
         <v>30</v>
       </c>
@@ -23744,7 +23780,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="41" t="s">
         <v>315</v>
       </c>
@@ -23769,7 +23805,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="55" t="s">
         <v>316</v>
       </c>
@@ -23794,7 +23830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="55" t="s">
         <v>39</v>
       </c>
@@ -23819,7 +23855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="41" t="s">
         <v>317</v>
       </c>
@@ -23844,7 +23880,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="41" t="s">
         <v>318</v>
       </c>
@@ -23869,7 +23905,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="41" t="s">
         <v>319</v>
       </c>
@@ -23894,7 +23930,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="41" t="s">
         <v>320</v>
       </c>
@@ -23919,7 +23955,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="41" t="s">
         <v>321</v>
       </c>
@@ -23944,7 +23980,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
         <v>322</v>
       </c>
@@ -23969,7 +24005,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="41" t="s">
         <v>323</v>
       </c>
@@ -23994,7 +24030,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="41" t="s">
         <v>59</v>
       </c>
@@ -24019,7 +24055,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="41" t="s">
         <v>62</v>
       </c>
@@ -24044,7 +24080,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="41" t="s">
         <v>324</v>
       </c>
@@ -24069,7 +24105,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="41" t="s">
         <v>68</v>
       </c>
@@ -24094,7 +24130,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="41" t="s">
         <v>71</v>
       </c>
@@ -24119,7 +24155,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="41" t="s">
         <v>325</v>
       </c>
@@ -24144,7 +24180,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="41" t="s">
         <v>326</v>
       </c>
@@ -24169,7 +24205,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="41" t="s">
         <v>327</v>
       </c>
@@ -24194,7 +24230,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="41" t="s">
         <v>81</v>
       </c>
@@ -24219,7 +24255,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="41" t="s">
         <v>328</v>
       </c>
@@ -24244,7 +24280,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="41" t="s">
         <v>329</v>
       </c>
@@ -24269,7 +24305,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="41" t="s">
         <v>330</v>
       </c>
@@ -24294,7 +24330,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="41" t="s">
         <v>331</v>
       </c>
@@ -24319,7 +24355,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="41" t="s">
         <v>332</v>
       </c>
@@ -24344,7 +24380,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="41" t="s">
         <v>333</v>
       </c>
@@ -24369,7 +24405,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="41" t="s">
         <v>100</v>
       </c>
@@ -24394,7 +24430,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="41" t="s">
         <v>334</v>
       </c>
@@ -24419,7 +24455,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="41" t="s">
         <v>335</v>
       </c>
@@ -24444,7 +24480,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="41" t="s">
         <v>336</v>
       </c>
@@ -24469,7 +24505,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="41" t="s">
         <v>337</v>
       </c>
@@ -24494,7 +24530,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="41" t="s">
         <v>338</v>
       </c>
@@ -24519,7 +24555,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="41" t="s">
         <v>339</v>
       </c>
@@ -24544,7 +24580,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="41" t="s">
         <v>340</v>
       </c>
@@ -24569,7 +24605,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="41" t="s">
         <v>341</v>
       </c>
@@ -24594,7 +24630,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="41" t="s">
         <v>342</v>
       </c>
@@ -24619,7 +24655,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="41" t="s">
         <v>343</v>
       </c>
@@ -24644,7 +24680,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="41" t="s">
         <v>130</v>
       </c>
@@ -24669,7 +24705,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="41" t="s">
         <v>133</v>
       </c>
@@ -24694,7 +24730,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="41" t="s">
         <v>136</v>
       </c>
@@ -24719,7 +24755,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="41" t="s">
         <v>344</v>
       </c>
@@ -24744,7 +24780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="41" t="s">
         <v>345</v>
       </c>
@@ -24769,7 +24805,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="41" t="s">
         <v>346</v>
       </c>
@@ -24794,7 +24830,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="41" t="s">
         <v>347</v>
       </c>
@@ -24819,7 +24855,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="41" t="s">
         <v>348</v>
       </c>
@@ -24844,7 +24880,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="41" t="s">
         <v>349</v>
       </c>
@@ -24869,7 +24905,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="41" t="s">
         <v>156</v>
       </c>
@@ -24894,7 +24930,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="41" t="s">
         <v>159</v>
       </c>
@@ -24919,7 +24955,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="41" t="s">
         <v>162</v>
       </c>
@@ -24944,7 +24980,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="41" t="s">
         <v>165</v>
       </c>
@@ -24969,7 +25005,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="41" t="s">
         <v>168</v>
       </c>
@@ -24994,7 +25030,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="41" t="s">
         <v>350</v>
       </c>
@@ -25019,7 +25055,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="41" t="s">
         <v>174</v>
       </c>
@@ -25044,7 +25080,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="41" t="s">
         <v>177</v>
       </c>
@@ -25069,7 +25105,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="41" t="s">
         <v>180</v>
       </c>
@@ -25094,7 +25130,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="41" t="s">
         <v>351</v>
       </c>
@@ -25119,7 +25155,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="41" t="s">
         <v>352</v>
       </c>
@@ -25144,7 +25180,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="41" t="s">
         <v>353</v>
       </c>
@@ -25169,7 +25205,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="41" t="s">
         <v>354</v>
       </c>
@@ -25194,7 +25230,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="41" t="s">
         <v>191</v>
       </c>
@@ -25219,7 +25255,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="41" t="s">
         <v>355</v>
       </c>
@@ -25244,7 +25280,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="41" t="s">
         <v>356</v>
       </c>
@@ -25269,7 +25305,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="41" t="s">
         <v>357</v>
       </c>
@@ -25294,7 +25330,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="41" t="s">
         <v>358</v>
       </c>
@@ -25319,7 +25355,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="41" t="s">
         <v>359</v>
       </c>
@@ -25344,7 +25380,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="41" t="s">
         <v>361</v>
       </c>
@@ -25369,7 +25405,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="41" t="s">
         <v>362</v>
       </c>
@@ -25394,7 +25430,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="41" t="s">
         <v>363</v>
       </c>
@@ -25419,7 +25455,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="41" t="s">
         <v>364</v>
       </c>
@@ -25444,7 +25480,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="41" t="s">
         <v>365</v>
       </c>
@@ -25469,7 +25505,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="41" t="s">
         <v>366</v>
       </c>
@@ -25494,7 +25530,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="41" t="s">
         <v>367</v>
       </c>
@@ -25519,7 +25555,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="41" t="s">
         <v>368</v>
       </c>
@@ -25544,7 +25580,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="41" t="s">
         <v>369</v>
       </c>
@@ -25569,7 +25605,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="41" t="s">
         <v>370</v>
       </c>
@@ -25594,7 +25630,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="41" t="s">
         <v>371</v>
       </c>
@@ -25619,7 +25655,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="41" t="s">
         <v>372</v>
       </c>
@@ -25644,7 +25680,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="41" t="s">
         <v>373</v>
       </c>
@@ -25669,7 +25705,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="41" t="s">
         <v>374</v>
       </c>
@@ -25694,7 +25730,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="41" t="s">
         <v>375</v>
       </c>
@@ -25719,7 +25755,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41" t="s">
         <v>376</v>
       </c>
@@ -25744,7 +25780,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="41" t="s">
         <v>377</v>
       </c>
@@ -25769,7 +25805,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="41" t="s">
         <v>378</v>
       </c>
@@ -25794,7 +25830,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="41" t="s">
         <v>379</v>
       </c>
@@ -25819,7 +25855,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="41" t="s">
         <v>380</v>
       </c>
@@ -25844,7 +25880,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="41" t="s">
         <v>381</v>
       </c>
@@ -25869,7 +25905,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="41" t="s">
         <v>256</v>
       </c>
@@ -25888,7 +25924,7 @@
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="41" t="s">
         <v>382</v>
       </c>
@@ -25913,7 +25949,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="41" t="s">
         <v>383</v>
       </c>
@@ -25938,7 +25974,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="41" t="s">
         <v>384</v>
       </c>
@@ -25963,7 +25999,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="41" t="s">
         <v>385</v>
       </c>
@@ -25988,7 +26024,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="41" t="s">
         <v>386</v>
       </c>
@@ -26013,7 +26049,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="41" t="s">
         <v>387</v>
       </c>
@@ -26038,7 +26074,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="41" t="s">
         <v>388</v>
       </c>
@@ -26063,7 +26099,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="41" t="s">
         <v>389</v>
       </c>
@@ -26088,7 +26124,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="41"/>
       <c r="B104" s="41"/>
       <c r="C104" s="54"/>
@@ -26099,7 +26135,7 @@
       <c r="H104" s="54"/>
       <c r="I104" s="54"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="41"/>
       <c r="B105" s="41"/>
       <c r="C105" s="54"/>
@@ -26110,7 +26146,7 @@
       <c r="H105" s="54"/>
       <c r="I105" s="54"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="41"/>
       <c r="B106" s="41"/>
       <c r="C106" s="54"/>
@@ -26121,7 +26157,7 @@
       <c r="H106" s="54"/>
       <c r="I106" s="54"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="41"/>
       <c r="B107" s="41"/>
       <c r="C107" s="54"/>
@@ -26132,7 +26168,7 @@
       <c r="H107" s="54"/>
       <c r="I107" s="54"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="41"/>
       <c r="B108" s="41"/>
       <c r="C108" s="54"/>
@@ -26143,7 +26179,7 @@
       <c r="H108" s="54"/>
       <c r="I108" s="54"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="41"/>
       <c r="B109" s="41"/>
       <c r="C109" s="54"/>
@@ -26154,7 +26190,7 @@
       <c r="H109" s="54"/>
       <c r="I109" s="54"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
       <c r="C110" s="54"/>
@@ -26165,7 +26201,7 @@
       <c r="H110" s="54"/>
       <c r="I110" s="54"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="41"/>
       <c r="B111" s="41"/>
       <c r="C111" s="54"/>
@@ -26176,7 +26212,7 @@
       <c r="H111" s="54"/>
       <c r="I111" s="54"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="41"/>
       <c r="B112" s="41"/>
       <c r="C112" s="54"/>
@@ -26187,7 +26223,7 @@
       <c r="H112" s="54"/>
       <c r="I112" s="54"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="41"/>
       <c r="B113" s="41"/>
       <c r="C113" s="54"/>
@@ -26198,7 +26234,7 @@
       <c r="H113" s="54"/>
       <c r="I113" s="54"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="41"/>
       <c r="B114" s="41"/>
       <c r="C114" s="54"/>
@@ -26209,7 +26245,7 @@
       <c r="H114" s="54"/>
       <c r="I114" s="54"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="41"/>
       <c r="B115" s="41"/>
       <c r="C115" s="54"/>
@@ -26220,7 +26256,7 @@
       <c r="H115" s="54"/>
       <c r="I115" s="54"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="41"/>
       <c r="B116" s="41"/>
       <c r="C116" s="54"/>
@@ -26231,7 +26267,7 @@
       <c r="H116" s="54"/>
       <c r="I116" s="54"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="41"/>
       <c r="B117" s="41"/>
       <c r="C117" s="54"/>
@@ -26242,7 +26278,7 @@
       <c r="H117" s="54"/>
       <c r="I117" s="54"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
       <c r="C118" s="54"/>
@@ -26253,7 +26289,7 @@
       <c r="H118" s="54"/>
       <c r="I118" s="54"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
       <c r="C119" s="54"/>
@@ -26264,7 +26300,7 @@
       <c r="H119" s="54"/>
       <c r="I119" s="54"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
       <c r="C120" s="54"/>
@@ -26275,7 +26311,7 @@
       <c r="H120" s="54"/>
       <c r="I120" s="54"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
       <c r="C121" s="54"/>
@@ -26286,7 +26322,7 @@
       <c r="H121" s="54"/>
       <c r="I121" s="54"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
       <c r="C122" s="54"/>
@@ -26297,7 +26333,7 @@
       <c r="H122" s="54"/>
       <c r="I122" s="54"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
       <c r="C123" s="54"/>
@@ -26308,7 +26344,7 @@
       <c r="H123" s="54"/>
       <c r="I123" s="54"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
       <c r="C124" s="54"/>
@@ -26319,7 +26355,7 @@
       <c r="H124" s="54"/>
       <c r="I124" s="54"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
       <c r="C125" s="54"/>
@@ -26330,7 +26366,7 @@
       <c r="H125" s="54"/>
       <c r="I125" s="54"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="54"/>
@@ -26341,7 +26377,7 @@
       <c r="H126" s="54"/>
       <c r="I126" s="54"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
       <c r="C127" s="54"/>
@@ -26352,7 +26388,7 @@
       <c r="H127" s="54"/>
       <c r="I127" s="54"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
       <c r="C128" s="54"/>
@@ -26363,7 +26399,7 @@
       <c r="H128" s="54"/>
       <c r="I128" s="54"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
       <c r="C129" s="54"/>
@@ -26374,7 +26410,7 @@
       <c r="H129" s="54"/>
       <c r="I129" s="54"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
       <c r="C130" s="54"/>
@@ -26385,7 +26421,7 @@
       <c r="H130" s="54"/>
       <c r="I130" s="54"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
       <c r="C131" s="54"/>
@@ -26396,7 +26432,7 @@
       <c r="H131" s="54"/>
       <c r="I131" s="54"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
       <c r="C132" s="54"/>
@@ -26407,7 +26443,7 @@
       <c r="H132" s="54"/>
       <c r="I132" s="54"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
       <c r="C133" s="54"/>
@@ -26418,7 +26454,7 @@
       <c r="H133" s="54"/>
       <c r="I133" s="54"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
       <c r="C134" s="54"/>
@@ -26429,7 +26465,7 @@
       <c r="H134" s="54"/>
       <c r="I134" s="54"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
       <c r="C135" s="54"/>
@@ -26440,7 +26476,7 @@
       <c r="H135" s="54"/>
       <c r="I135" s="54"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
       <c r="C136" s="54"/>
@@ -26451,7 +26487,7 @@
       <c r="H136" s="54"/>
       <c r="I136" s="54"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="41"/>
       <c r="B137" s="41"/>
       <c r="C137" s="54"/>
@@ -26462,7 +26498,7 @@
       <c r="H137" s="54"/>
       <c r="I137" s="54"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="41"/>
       <c r="B138" s="41"/>
       <c r="C138" s="54"/>
@@ -26473,7 +26509,7 @@
       <c r="H138" s="54"/>
       <c r="I138" s="54"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="41"/>
       <c r="B139" s="41"/>
       <c r="C139" s="54"/>
@@ -26484,7 +26520,7 @@
       <c r="H139" s="54"/>
       <c r="I139" s="54"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="41"/>
       <c r="B140" s="41"/>
       <c r="C140" s="54"/>
@@ -26495,7 +26531,7 @@
       <c r="H140" s="54"/>
       <c r="I140" s="54"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="41"/>
       <c r="B141" s="41"/>
       <c r="C141" s="54"/>
@@ -26506,7 +26542,7 @@
       <c r="H141" s="54"/>
       <c r="I141" s="54"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="41"/>
       <c r="B142" s="41"/>
       <c r="C142" s="54"/>
@@ -26517,7 +26553,7 @@
       <c r="H142" s="54"/>
       <c r="I142" s="54"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="41"/>
       <c r="B143" s="41"/>
       <c r="C143" s="54"/>
@@ -26528,7 +26564,7 @@
       <c r="H143" s="54"/>
       <c r="I143" s="54"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="41"/>
       <c r="B144" s="41"/>
       <c r="C144" s="54"/>
@@ -26539,7 +26575,7 @@
       <c r="H144" s="54"/>
       <c r="I144" s="54"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="41"/>
       <c r="B145" s="41"/>
       <c r="C145" s="54"/>
@@ -26550,7 +26586,7 @@
       <c r="H145" s="54"/>
       <c r="I145" s="54"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="41"/>
       <c r="B146" s="41"/>
       <c r="C146" s="54"/>
@@ -26561,7 +26597,7 @@
       <c r="H146" s="54"/>
       <c r="I146" s="54"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="41"/>
       <c r="B147" s="41"/>
       <c r="C147" s="54"/>
@@ -26572,7 +26608,7 @@
       <c r="H147" s="54"/>
       <c r="I147" s="54"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="41"/>
       <c r="B148" s="41"/>
       <c r="C148" s="54"/>
@@ -26583,7 +26619,7 @@
       <c r="H148" s="54"/>
       <c r="I148" s="54"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="41"/>
       <c r="B149" s="41"/>
       <c r="C149" s="54"/>
@@ -26594,7 +26630,7 @@
       <c r="H149" s="54"/>
       <c r="I149" s="54"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="41"/>
       <c r="B150" s="41"/>
       <c r="C150" s="54"/>
@@ -26605,7 +26641,7 @@
       <c r="H150" s="54"/>
       <c r="I150" s="54"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
       <c r="C151" s="54"/>
@@ -26616,7 +26652,7 @@
       <c r="H151" s="54"/>
       <c r="I151" s="54"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="41"/>
       <c r="B152" s="41"/>
       <c r="C152" s="54"/>
@@ -26627,7 +26663,7 @@
       <c r="H152" s="54"/>
       <c r="I152" s="54"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="41"/>
       <c r="B153" s="41"/>
       <c r="C153" s="54"/>
@@ -26638,7 +26674,7 @@
       <c r="H153" s="54"/>
       <c r="I153" s="54"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="41"/>
       <c r="B154" s="41"/>
       <c r="C154" s="54"/>
@@ -26649,7 +26685,7 @@
       <c r="H154" s="54"/>
       <c r="I154" s="54"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="41"/>
       <c r="B155" s="41"/>
       <c r="C155" s="54"/>
@@ -26660,7 +26696,7 @@
       <c r="H155" s="54"/>
       <c r="I155" s="54"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="41"/>
       <c r="B156" s="41"/>
       <c r="C156" s="54"/>
@@ -26671,7 +26707,7 @@
       <c r="H156" s="54"/>
       <c r="I156" s="54"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="41"/>
       <c r="B157" s="41"/>
       <c r="C157" s="54"/>
@@ -26682,7 +26718,7 @@
       <c r="H157" s="54"/>
       <c r="I157" s="54"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="41"/>
       <c r="B158" s="41"/>
       <c r="C158" s="54"/>
@@ -26693,7 +26729,7 @@
       <c r="H158" s="54"/>
       <c r="I158" s="54"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="41"/>
       <c r="B159" s="41"/>
       <c r="C159" s="54"/>
@@ -26704,7 +26740,7 @@
       <c r="H159" s="54"/>
       <c r="I159" s="54"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="41"/>
       <c r="B160" s="41"/>
       <c r="C160" s="54"/>
@@ -26715,7 +26751,7 @@
       <c r="H160" s="54"/>
       <c r="I160" s="54"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="41"/>
       <c r="B161" s="41"/>
       <c r="C161" s="54"/>
@@ -26726,7 +26762,7 @@
       <c r="H161" s="54"/>
       <c r="I161" s="54"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="41"/>
       <c r="B162" s="41"/>
       <c r="C162" s="54"/>
@@ -26737,7 +26773,7 @@
       <c r="H162" s="54"/>
       <c r="I162" s="54"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="41"/>
       <c r="B163" s="41"/>
       <c r="C163" s="54"/>
@@ -26748,7 +26784,7 @@
       <c r="H163" s="54"/>
       <c r="I163" s="54"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="41"/>
       <c r="B164" s="41"/>
       <c r="C164" s="54"/>
@@ -26759,7 +26795,7 @@
       <c r="H164" s="54"/>
       <c r="I164" s="54"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="41"/>
       <c r="B165" s="41"/>
       <c r="C165" s="54"/>
@@ -26770,7 +26806,7 @@
       <c r="H165" s="54"/>
       <c r="I165" s="54"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="41"/>
       <c r="B166" s="41"/>
       <c r="C166" s="54"/>
@@ -26781,7 +26817,7 @@
       <c r="H166" s="54"/>
       <c r="I166" s="54"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="41"/>
       <c r="B167" s="41"/>
       <c r="C167" s="54"/>
@@ -26792,7 +26828,7 @@
       <c r="H167" s="54"/>
       <c r="I167" s="54"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="41"/>
       <c r="B168" s="41"/>
       <c r="C168" s="54"/>
@@ -26803,7 +26839,7 @@
       <c r="H168" s="54"/>
       <c r="I168" s="54"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="41"/>
       <c r="B169" s="41"/>
       <c r="C169" s="54"/>
@@ -26814,7 +26850,7 @@
       <c r="H169" s="54"/>
       <c r="I169" s="54"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="41"/>
       <c r="B170" s="41"/>
       <c r="C170" s="54"/>
@@ -26825,7 +26861,7 @@
       <c r="H170" s="54"/>
       <c r="I170" s="54"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="41"/>
       <c r="B171" s="41"/>
       <c r="C171" s="54"/>
@@ -26836,7 +26872,7 @@
       <c r="H171" s="54"/>
       <c r="I171" s="54"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="41"/>
       <c r="B172" s="41"/>
       <c r="C172" s="54"/>
@@ -26847,7 +26883,7 @@
       <c r="H172" s="54"/>
       <c r="I172" s="54"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="41"/>
       <c r="B173" s="41"/>
       <c r="C173" s="54"/>
@@ -26858,7 +26894,7 @@
       <c r="H173" s="54"/>
       <c r="I173" s="54"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="41"/>
       <c r="B174" s="41"/>
       <c r="C174" s="54"/>
@@ -26869,7 +26905,7 @@
       <c r="H174" s="54"/>
       <c r="I174" s="54"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
       <c r="C175" s="54"/>
@@ -26880,7 +26916,7 @@
       <c r="H175" s="54"/>
       <c r="I175" s="54"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="41"/>
       <c r="B176" s="41"/>
       <c r="C176" s="54"/>
@@ -26891,7 +26927,7 @@
       <c r="H176" s="54"/>
       <c r="I176" s="54"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="41"/>
       <c r="B177" s="41"/>
       <c r="C177" s="54"/>
@@ -26902,7 +26938,7 @@
       <c r="H177" s="54"/>
       <c r="I177" s="54"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="41"/>
       <c r="B178" s="41"/>
       <c r="C178" s="54"/>
@@ -26913,7 +26949,7 @@
       <c r="H178" s="54"/>
       <c r="I178" s="54"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="41"/>
       <c r="B179" s="41"/>
       <c r="C179" s="54"/>
@@ -26924,7 +26960,7 @@
       <c r="H179" s="54"/>
       <c r="I179" s="54"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="41"/>
       <c r="B180" s="41"/>
       <c r="C180" s="54"/>
@@ -26935,7 +26971,7 @@
       <c r="H180" s="54"/>
       <c r="I180" s="54"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="41"/>
       <c r="B181" s="41"/>
       <c r="C181" s="54"/>
@@ -26946,7 +26982,7 @@
       <c r="H181" s="54"/>
       <c r="I181" s="54"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="41"/>
       <c r="B182" s="41"/>
       <c r="C182" s="54"/>
@@ -26957,7 +26993,7 @@
       <c r="H182" s="54"/>
       <c r="I182" s="54"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="41"/>
       <c r="B183" s="41"/>
       <c r="C183" s="54"/>
@@ -26968,7 +27004,7 @@
       <c r="H183" s="54"/>
       <c r="I183" s="54"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="41"/>
       <c r="B184" s="41"/>
       <c r="C184" s="54"/>
@@ -26979,7 +27015,7 @@
       <c r="H184" s="54"/>
       <c r="I184" s="54"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="41"/>
       <c r="B185" s="41"/>
       <c r="C185" s="54"/>
@@ -26990,7 +27026,7 @@
       <c r="H185" s="54"/>
       <c r="I185" s="54"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="41"/>
       <c r="B186" s="41"/>
       <c r="C186" s="54"/>
@@ -27001,7 +27037,7 @@
       <c r="H186" s="54"/>
       <c r="I186" s="54"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="41"/>
       <c r="B187" s="41"/>
       <c r="C187" s="54"/>
@@ -27012,7 +27048,7 @@
       <c r="H187" s="54"/>
       <c r="I187" s="54"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="41"/>
       <c r="B188" s="41"/>
       <c r="C188" s="54"/>
@@ -27023,7 +27059,7 @@
       <c r="H188" s="54"/>
       <c r="I188" s="54"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="41"/>
       <c r="B189" s="41"/>
       <c r="C189" s="54"/>
@@ -27034,7 +27070,7 @@
       <c r="H189" s="54"/>
       <c r="I189" s="54"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="41"/>
       <c r="B190" s="41"/>
       <c r="C190" s="54"/>
@@ -27045,7 +27081,7 @@
       <c r="H190" s="54"/>
       <c r="I190" s="54"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="41"/>
       <c r="B191" s="41"/>
       <c r="C191" s="54"/>
@@ -27056,7 +27092,7 @@
       <c r="H191" s="54"/>
       <c r="I191" s="54"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="41"/>
       <c r="B192" s="41"/>
       <c r="C192" s="54"/>
@@ -27067,7 +27103,7 @@
       <c r="H192" s="54"/>
       <c r="I192" s="54"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="41"/>
       <c r="B193" s="41"/>
       <c r="C193" s="54"/>
@@ -27078,7 +27114,7 @@
       <c r="H193" s="54"/>
       <c r="I193" s="54"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="41"/>
       <c r="B194" s="41"/>
       <c r="C194" s="54"/>
@@ -27089,7 +27125,7 @@
       <c r="H194" s="54"/>
       <c r="I194" s="54"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="41"/>
       <c r="B195" s="41"/>
       <c r="C195" s="54"/>
@@ -27100,7 +27136,7 @@
       <c r="H195" s="54"/>
       <c r="I195" s="54"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="41"/>
       <c r="B196" s="41"/>
       <c r="C196" s="54"/>
@@ -27111,7 +27147,7 @@
       <c r="H196" s="54"/>
       <c r="I196" s="54"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="41"/>
       <c r="B197" s="41"/>
       <c r="C197" s="54"/>
@@ -27122,7 +27158,7 @@
       <c r="H197" s="54"/>
       <c r="I197" s="54"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="41"/>
       <c r="B198" s="41"/>
       <c r="C198" s="54"/>
@@ -27133,7 +27169,7 @@
       <c r="H198" s="54"/>
       <c r="I198" s="54"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="41"/>
       <c r="B199" s="41"/>
       <c r="C199" s="54"/>
@@ -27144,7 +27180,7 @@
       <c r="H199" s="54"/>
       <c r="I199" s="54"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="41"/>
       <c r="B200" s="41"/>
       <c r="C200" s="54"/>
@@ -27155,7 +27191,7 @@
       <c r="H200" s="54"/>
       <c r="I200" s="54"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="41"/>
       <c r="B201" s="41"/>
       <c r="C201" s="54"/>
@@ -27166,7 +27202,7 @@
       <c r="H201" s="54"/>
       <c r="I201" s="54"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="41"/>
       <c r="B202" s="41"/>
       <c r="C202" s="54"/>
@@ -27177,7 +27213,7 @@
       <c r="H202" s="54"/>
       <c r="I202" s="54"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="41"/>
       <c r="B203" s="41"/>
       <c r="C203" s="54"/>
@@ -27188,7 +27224,7 @@
       <c r="H203" s="54"/>
       <c r="I203" s="54"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="41"/>
       <c r="B204" s="41"/>
       <c r="C204" s="54"/>
@@ -27199,7 +27235,7 @@
       <c r="H204" s="54"/>
       <c r="I204" s="54"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="41"/>
       <c r="B205" s="41"/>
       <c r="C205" s="54"/>
@@ -27210,7 +27246,7 @@
       <c r="H205" s="54"/>
       <c r="I205" s="54"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="41"/>
       <c r="B206" s="41"/>
       <c r="C206" s="54"/>
@@ -27221,7 +27257,7 @@
       <c r="H206" s="54"/>
       <c r="I206" s="54"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="41"/>
       <c r="B207" s="41"/>
       <c r="C207" s="54"/>
@@ -27232,7 +27268,7 @@
       <c r="H207" s="54"/>
       <c r="I207" s="54"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="41"/>
       <c r="B208" s="41"/>
       <c r="C208" s="54"/>
@@ -27243,7 +27279,7 @@
       <c r="H208" s="54"/>
       <c r="I208" s="54"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="41"/>
       <c r="B209" s="41"/>
       <c r="C209" s="54"/>
@@ -27254,7 +27290,7 @@
       <c r="H209" s="54"/>
       <c r="I209" s="54"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="41"/>
       <c r="B210" s="41"/>
       <c r="C210" s="54"/>
@@ -27265,7 +27301,7 @@
       <c r="H210" s="54"/>
       <c r="I210" s="54"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="41"/>
       <c r="B211" s="41"/>
       <c r="C211" s="54"/>
@@ -27276,7 +27312,7 @@
       <c r="H211" s="54"/>
       <c r="I211" s="54"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="41"/>
       <c r="B212" s="41"/>
       <c r="C212" s="54"/>
@@ -27287,7 +27323,7 @@
       <c r="H212" s="54"/>
       <c r="I212" s="54"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="41"/>
       <c r="B213" s="41"/>
       <c r="C213" s="54"/>
@@ -27298,7 +27334,7 @@
       <c r="H213" s="54"/>
       <c r="I213" s="54"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="41"/>
       <c r="B214" s="41"/>
       <c r="C214" s="54"/>
@@ -27309,7 +27345,7 @@
       <c r="H214" s="54"/>
       <c r="I214" s="54"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="41"/>
       <c r="B215" s="41"/>
       <c r="C215" s="54"/>
@@ -27320,7 +27356,7 @@
       <c r="H215" s="54"/>
       <c r="I215" s="54"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="41"/>
       <c r="B216" s="41"/>
       <c r="C216" s="54"/>
@@ -27331,7 +27367,7 @@
       <c r="H216" s="54"/>
       <c r="I216" s="54"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="41"/>
       <c r="B217" s="41"/>
       <c r="C217" s="54"/>
@@ -27342,7 +27378,7 @@
       <c r="H217" s="54"/>
       <c r="I217" s="54"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="41"/>
       <c r="B218" s="41"/>
       <c r="C218" s="54"/>
@@ -27353,7 +27389,7 @@
       <c r="H218" s="54"/>
       <c r="I218" s="54"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="41"/>
       <c r="B219" s="41"/>
       <c r="C219" s="54"/>
@@ -27364,7 +27400,7 @@
       <c r="H219" s="54"/>
       <c r="I219" s="54"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="41"/>
       <c r="B220" s="41"/>
       <c r="C220" s="54"/>
@@ -27375,7 +27411,7 @@
       <c r="H220" s="54"/>
       <c r="I220" s="54"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="41"/>
       <c r="B221" s="41"/>
       <c r="C221" s="54"/>
@@ -27386,7 +27422,7 @@
       <c r="H221" s="54"/>
       <c r="I221" s="54"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="41"/>
       <c r="B222" s="41"/>
       <c r="C222" s="54"/>
@@ -27397,7 +27433,7 @@
       <c r="H222" s="54"/>
       <c r="I222" s="54"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="41"/>
       <c r="B223" s="41"/>
       <c r="C223" s="54"/>
@@ -27408,7 +27444,7 @@
       <c r="H223" s="54"/>
       <c r="I223" s="54"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="41"/>
       <c r="B224" s="41"/>
       <c r="C224" s="54"/>
@@ -27419,7 +27455,7 @@
       <c r="H224" s="54"/>
       <c r="I224" s="54"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="41"/>
       <c r="B225" s="41"/>
       <c r="C225" s="54"/>
@@ -27430,7 +27466,7 @@
       <c r="H225" s="54"/>
       <c r="I225" s="54"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="41"/>
       <c r="B226" s="41"/>
       <c r="C226" s="54"/>
@@ -27441,7 +27477,7 @@
       <c r="H226" s="54"/>
       <c r="I226" s="54"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="41"/>
       <c r="B227" s="41"/>
       <c r="C227" s="54"/>
@@ -27452,7 +27488,7 @@
       <c r="H227" s="54"/>
       <c r="I227" s="54"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="41"/>
       <c r="B228" s="41"/>
       <c r="C228" s="54"/>
@@ -27463,7 +27499,7 @@
       <c r="H228" s="54"/>
       <c r="I228" s="54"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="41"/>
       <c r="B229" s="41"/>
       <c r="C229" s="54"/>
@@ -27474,7 +27510,7 @@
       <c r="H229" s="54"/>
       <c r="I229" s="54"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="41"/>
       <c r="B230" s="41"/>
       <c r="C230" s="54"/>
@@ -27485,7 +27521,7 @@
       <c r="H230" s="54"/>
       <c r="I230" s="54"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="41"/>
       <c r="B231" s="41"/>
       <c r="C231" s="54"/>
@@ -27496,7 +27532,7 @@
       <c r="H231" s="54"/>
       <c r="I231" s="54"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="41"/>
       <c r="B232" s="41"/>
       <c r="C232" s="54"/>
@@ -27507,7 +27543,7 @@
       <c r="H232" s="54"/>
       <c r="I232" s="54"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="41"/>
       <c r="B233" s="41"/>
       <c r="C233" s="54"/>
@@ -27518,7 +27554,7 @@
       <c r="H233" s="54"/>
       <c r="I233" s="54"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="41"/>
       <c r="B234" s="41"/>
       <c r="C234" s="54"/>
@@ -27529,7 +27565,7 @@
       <c r="H234" s="54"/>
       <c r="I234" s="54"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="41"/>
       <c r="B235" s="41"/>
       <c r="C235" s="54"/>
@@ -27540,7 +27576,7 @@
       <c r="H235" s="54"/>
       <c r="I235" s="54"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="41"/>
       <c r="B236" s="41"/>
       <c r="C236" s="54"/>
@@ -27551,7 +27587,7 @@
       <c r="H236" s="54"/>
       <c r="I236" s="54"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="41"/>
       <c r="B237" s="41"/>
       <c r="C237" s="54"/>
@@ -27562,7 +27598,7 @@
       <c r="H237" s="54"/>
       <c r="I237" s="54"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="41"/>
       <c r="B238" s="41"/>
       <c r="C238" s="54"/>
@@ -27573,7 +27609,7 @@
       <c r="H238" s="54"/>
       <c r="I238" s="54"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="41"/>
       <c r="B239" s="41"/>
       <c r="C239" s="54"/>
@@ -27584,7 +27620,7 @@
       <c r="H239" s="54"/>
       <c r="I239" s="54"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="41"/>
       <c r="B240" s="41"/>
       <c r="C240" s="54"/>
@@ -27595,7 +27631,7 @@
       <c r="H240" s="54"/>
       <c r="I240" s="54"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="41"/>
       <c r="B241" s="41"/>
       <c r="C241" s="54"/>
@@ -27606,7 +27642,7 @@
       <c r="H241" s="54"/>
       <c r="I241" s="54"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="41"/>
       <c r="B242" s="41"/>
       <c r="C242" s="54"/>
@@ -27617,7 +27653,7 @@
       <c r="H242" s="54"/>
       <c r="I242" s="54"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="41"/>
       <c r="B243" s="41"/>
       <c r="C243" s="54"/>
@@ -27628,7 +27664,7 @@
       <c r="H243" s="54"/>
       <c r="I243" s="54"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="41"/>
       <c r="B244" s="41"/>
       <c r="C244" s="54"/>
@@ -27639,7 +27675,7 @@
       <c r="H244" s="54"/>
       <c r="I244" s="54"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="41"/>
       <c r="B245" s="41"/>
       <c r="C245" s="54"/>
@@ -27650,7 +27686,7 @@
       <c r="H245" s="54"/>
       <c r="I245" s="54"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="41"/>
       <c r="B246" s="41"/>
       <c r="C246" s="54"/>
@@ -27661,7 +27697,7 @@
       <c r="H246" s="54"/>
       <c r="I246" s="54"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="41"/>
       <c r="B247" s="41"/>
       <c r="C247" s="54"/>
@@ -27672,7 +27708,7 @@
       <c r="H247" s="54"/>
       <c r="I247" s="54"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="41"/>
       <c r="B248" s="41"/>
       <c r="C248" s="54"/>
@@ -27683,7 +27719,7 @@
       <c r="H248" s="54"/>
       <c r="I248" s="54"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="41"/>
       <c r="B249" s="41"/>
       <c r="C249" s="54"/>
@@ -27694,7 +27730,7 @@
       <c r="H249" s="54"/>
       <c r="I249" s="54"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="41"/>
       <c r="B250" s="41"/>
       <c r="C250" s="54"/>
@@ -27705,7 +27741,7 @@
       <c r="H250" s="54"/>
       <c r="I250" s="54"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="41"/>
       <c r="B251" s="41"/>
       <c r="C251" s="54"/>
@@ -27716,7 +27752,7 @@
       <c r="H251" s="54"/>
       <c r="I251" s="54"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="41"/>
       <c r="B252" s="41"/>
       <c r="C252" s="54"/>
@@ -27727,7 +27763,7 @@
       <c r="H252" s="54"/>
       <c r="I252" s="54"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="41"/>
       <c r="B253" s="41"/>
       <c r="C253" s="54"/>
@@ -27738,7 +27774,7 @@
       <c r="H253" s="54"/>
       <c r="I253" s="54"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="41"/>
       <c r="B254" s="41"/>
       <c r="C254" s="54"/>
@@ -27749,7 +27785,7 @@
       <c r="H254" s="54"/>
       <c r="I254" s="54"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="41"/>
       <c r="B255" s="41"/>
       <c r="C255" s="54"/>
@@ -27760,7 +27796,7 @@
       <c r="H255" s="54"/>
       <c r="I255" s="54"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="41"/>
       <c r="B256" s="41"/>
       <c r="C256" s="54"/>
@@ -27771,7 +27807,7 @@
       <c r="H256" s="54"/>
       <c r="I256" s="54"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="41"/>
       <c r="B257" s="41"/>
       <c r="C257" s="54"/>
@@ -27782,7 +27818,7 @@
       <c r="H257" s="54"/>
       <c r="I257" s="54"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="41"/>
       <c r="B258" s="41"/>
       <c r="C258" s="54"/>
@@ -27793,7 +27829,7 @@
       <c r="H258" s="54"/>
       <c r="I258" s="54"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="41"/>
       <c r="B259" s="41"/>
       <c r="C259" s="54"/>
@@ -27804,7 +27840,7 @@
       <c r="H259" s="54"/>
       <c r="I259" s="54"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="41"/>
       <c r="B260" s="41"/>
       <c r="C260" s="54"/>
@@ -27815,7 +27851,7 @@
       <c r="H260" s="54"/>
       <c r="I260" s="54"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="41"/>
       <c r="B261" s="41"/>
       <c r="C261" s="54"/>
@@ -27826,7 +27862,7 @@
       <c r="H261" s="54"/>
       <c r="I261" s="54"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="41"/>
       <c r="B262" s="41"/>
       <c r="C262" s="54"/>
@@ -27837,7 +27873,7 @@
       <c r="H262" s="54"/>
       <c r="I262" s="54"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="41"/>
       <c r="B263" s="41"/>
       <c r="C263" s="54"/>
@@ -27848,7 +27884,7 @@
       <c r="H263" s="54"/>
       <c r="I263" s="54"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="41"/>
       <c r="B264" s="41"/>
       <c r="C264" s="54"/>
@@ -27859,7 +27895,7 @@
       <c r="H264" s="54"/>
       <c r="I264" s="54"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="41"/>
       <c r="B265" s="41"/>
       <c r="C265" s="54"/>
@@ -27870,7 +27906,7 @@
       <c r="H265" s="54"/>
       <c r="I265" s="54"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="41"/>
       <c r="B266" s="41"/>
       <c r="C266" s="54"/>
@@ -27881,7 +27917,7 @@
       <c r="H266" s="54"/>
       <c r="I266" s="54"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="41"/>
       <c r="B267" s="41"/>
       <c r="C267" s="54"/>
@@ -27892,7 +27928,7 @@
       <c r="H267" s="54"/>
       <c r="I267" s="54"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="41"/>
       <c r="B268" s="41"/>
       <c r="C268" s="54"/>
@@ -27903,7 +27939,7 @@
       <c r="H268" s="54"/>
       <c r="I268" s="54"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="41"/>
       <c r="B269" s="41"/>
       <c r="C269" s="54"/>
@@ -27914,7 +27950,7 @@
       <c r="H269" s="54"/>
       <c r="I269" s="54"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="41"/>
       <c r="B270" s="41"/>
       <c r="C270" s="54"/>
@@ -27925,7 +27961,7 @@
       <c r="H270" s="54"/>
       <c r="I270" s="54"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="41"/>
       <c r="B271" s="41"/>
       <c r="C271" s="54"/>
@@ -27936,7 +27972,7 @@
       <c r="H271" s="54"/>
       <c r="I271" s="54"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="41"/>
       <c r="B272" s="41"/>
       <c r="C272" s="54"/>
@@ -27947,7 +27983,7 @@
       <c r="H272" s="54"/>
       <c r="I272" s="54"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="41"/>
       <c r="B273" s="41"/>
       <c r="C273" s="54"/>
@@ -27958,7 +27994,7 @@
       <c r="H273" s="54"/>
       <c r="I273" s="54"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="41"/>
       <c r="B274" s="41"/>
       <c r="C274" s="54"/>
@@ -27969,7 +28005,7 @@
       <c r="H274" s="54"/>
       <c r="I274" s="54"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="41"/>
       <c r="B275" s="41"/>
       <c r="C275" s="54"/>
@@ -27980,7 +28016,7 @@
       <c r="H275" s="54"/>
       <c r="I275" s="54"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="41"/>
       <c r="B276" s="41"/>
       <c r="C276" s="54"/>
@@ -27991,7 +28027,7 @@
       <c r="H276" s="54"/>
       <c r="I276" s="54"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="41"/>
       <c r="B277" s="41"/>
       <c r="C277" s="54"/>
@@ -28002,7 +28038,7 @@
       <c r="H277" s="54"/>
       <c r="I277" s="54"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="41"/>
       <c r="B278" s="41"/>
       <c r="C278" s="54"/>
@@ -28013,7 +28049,7 @@
       <c r="H278" s="54"/>
       <c r="I278" s="54"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="41"/>
       <c r="B279" s="41"/>
       <c r="C279" s="54"/>
@@ -28024,7 +28060,7 @@
       <c r="H279" s="54"/>
       <c r="I279" s="54"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="41"/>
       <c r="B280" s="41"/>
       <c r="C280" s="54"/>
@@ -28035,7 +28071,7 @@
       <c r="H280" s="54"/>
       <c r="I280" s="54"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="41"/>
       <c r="B281" s="41"/>
       <c r="C281" s="54"/>
@@ -28046,7 +28082,7 @@
       <c r="H281" s="54"/>
       <c r="I281" s="54"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="41"/>
       <c r="B282" s="41"/>
       <c r="C282" s="54"/>
@@ -28057,7 +28093,7 @@
       <c r="H282" s="54"/>
       <c r="I282" s="54"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="41"/>
       <c r="B283" s="41"/>
       <c r="C283" s="54"/>
@@ -28068,7 +28104,7 @@
       <c r="H283" s="54"/>
       <c r="I283" s="54"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="41"/>
       <c r="B284" s="41"/>
       <c r="C284" s="54"/>
@@ -28079,7 +28115,7 @@
       <c r="H284" s="54"/>
       <c r="I284" s="54"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="41"/>
       <c r="B285" s="41"/>
       <c r="C285" s="54"/>
@@ -28090,7 +28126,7 @@
       <c r="H285" s="54"/>
       <c r="I285" s="54"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="41"/>
       <c r="B286" s="41"/>
       <c r="C286" s="54"/>
@@ -28101,7 +28137,7 @@
       <c r="H286" s="54"/>
       <c r="I286" s="54"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="41"/>
       <c r="B287" s="41"/>
       <c r="C287" s="54"/>
@@ -28112,7 +28148,7 @@
       <c r="H287" s="54"/>
       <c r="I287" s="54"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="41"/>
       <c r="B288" s="41"/>
       <c r="C288" s="54"/>
@@ -28123,7 +28159,7 @@
       <c r="H288" s="54"/>
       <c r="I288" s="54"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="41"/>
       <c r="B289" s="41"/>
       <c r="C289" s="54"/>
@@ -28134,7 +28170,7 @@
       <c r="H289" s="54"/>
       <c r="I289" s="54"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="41"/>
       <c r="B290" s="41"/>
       <c r="C290" s="54"/>
@@ -28145,7 +28181,7 @@
       <c r="H290" s="54"/>
       <c r="I290" s="54"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="41"/>
       <c r="B291" s="41"/>
       <c r="C291" s="54"/>
@@ -28156,7 +28192,7 @@
       <c r="H291" s="54"/>
       <c r="I291" s="54"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="41"/>
       <c r="B292" s="41"/>
       <c r="C292" s="54"/>
@@ -28167,7 +28203,7 @@
       <c r="H292" s="54"/>
       <c r="I292" s="54"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="41"/>
       <c r="B293" s="41"/>
       <c r="C293" s="54"/>
@@ -28178,7 +28214,7 @@
       <c r="H293" s="54"/>
       <c r="I293" s="54"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="41"/>
       <c r="B294" s="41"/>
       <c r="C294" s="54"/>
@@ -28189,7 +28225,7 @@
       <c r="H294" s="54"/>
       <c r="I294" s="54"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="41"/>
       <c r="B295" s="41"/>
       <c r="C295" s="54"/>
@@ -28200,7 +28236,7 @@
       <c r="H295" s="54"/>
       <c r="I295" s="54"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="41"/>
       <c r="B296" s="41"/>
       <c r="C296" s="54"/>
@@ -28211,7 +28247,7 @@
       <c r="H296" s="54"/>
       <c r="I296" s="54"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="41"/>
       <c r="B297" s="41"/>
       <c r="C297" s="54"/>
@@ -28222,7 +28258,7 @@
       <c r="H297" s="54"/>
       <c r="I297" s="54"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="41"/>
       <c r="B298" s="41"/>
       <c r="C298" s="54"/>
@@ -28233,7 +28269,7 @@
       <c r="H298" s="54"/>
       <c r="I298" s="54"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="41"/>
       <c r="B299" s="41"/>
       <c r="C299" s="54"/>
@@ -28244,7 +28280,7 @@
       <c r="H299" s="54"/>
       <c r="I299" s="54"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="41"/>
       <c r="B300" s="41"/>
       <c r="C300" s="54"/>
@@ -28255,7 +28291,7 @@
       <c r="H300" s="54"/>
       <c r="I300" s="54"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="41"/>
       <c r="B301" s="41"/>
       <c r="C301" s="54"/>
@@ -28266,7 +28302,7 @@
       <c r="H301" s="54"/>
       <c r="I301" s="54"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="41"/>
       <c r="B302" s="41"/>
       <c r="C302" s="54"/>
@@ -28277,7 +28313,7 @@
       <c r="H302" s="54"/>
       <c r="I302" s="54"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="41"/>
       <c r="B303" s="41"/>
       <c r="C303" s="54"/>
@@ -28288,7 +28324,7 @@
       <c r="H303" s="54"/>
       <c r="I303" s="54"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="41"/>
       <c r="B304" s="41"/>
       <c r="C304" s="54"/>
@@ -28299,7 +28335,7 @@
       <c r="H304" s="54"/>
       <c r="I304" s="54"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="41"/>
       <c r="B305" s="41"/>
       <c r="C305" s="54"/>
@@ -28310,7 +28346,7 @@
       <c r="H305" s="54"/>
       <c r="I305" s="54"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="41"/>
       <c r="B306" s="41"/>
       <c r="C306" s="54"/>
@@ -28321,7 +28357,7 @@
       <c r="H306" s="54"/>
       <c r="I306" s="54"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="41"/>
       <c r="B307" s="41"/>
       <c r="C307" s="54"/>
@@ -28332,7 +28368,7 @@
       <c r="H307" s="54"/>
       <c r="I307" s="54"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="41"/>
       <c r="B308" s="41"/>
       <c r="C308" s="54"/>
@@ -28343,7 +28379,7 @@
       <c r="H308" s="54"/>
       <c r="I308" s="54"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="41"/>
       <c r="B309" s="41"/>
       <c r="C309" s="54"/>
@@ -28354,7 +28390,7 @@
       <c r="H309" s="54"/>
       <c r="I309" s="54"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="41"/>
       <c r="B310" s="41"/>
       <c r="C310" s="54"/>
@@ -28365,7 +28401,7 @@
       <c r="H310" s="54"/>
       <c r="I310" s="54"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="41"/>
       <c r="B311" s="41"/>
       <c r="C311" s="54"/>
@@ -28376,7 +28412,7 @@
       <c r="H311" s="54"/>
       <c r="I311" s="54"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="41"/>
       <c r="B312" s="41"/>
       <c r="C312" s="54"/>
@@ -28387,7 +28423,7 @@
       <c r="H312" s="54"/>
       <c r="I312" s="54"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="41"/>
       <c r="B313" s="41"/>
       <c r="C313" s="54"/>
@@ -28398,7 +28434,7 @@
       <c r="H313" s="54"/>
       <c r="I313" s="54"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="41"/>
       <c r="B314" s="41"/>
       <c r="C314" s="54"/>
@@ -28409,7 +28445,7 @@
       <c r="H314" s="54"/>
       <c r="I314" s="54"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="41"/>
       <c r="B315" s="41"/>
       <c r="C315" s="54"/>
@@ -28420,7 +28456,7 @@
       <c r="H315" s="54"/>
       <c r="I315" s="54"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="41"/>
       <c r="B316" s="41"/>
       <c r="C316" s="54"/>
@@ -28431,7 +28467,7 @@
       <c r="H316" s="54"/>
       <c r="I316" s="54"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="41"/>
       <c r="B317" s="41"/>
       <c r="C317" s="54"/>
@@ -28442,7 +28478,7 @@
       <c r="H317" s="54"/>
       <c r="I317" s="54"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="41"/>
       <c r="B318" s="41"/>
       <c r="C318" s="54"/>
@@ -28453,7 +28489,7 @@
       <c r="H318" s="54"/>
       <c r="I318" s="54"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="41"/>
       <c r="B319" s="41"/>
       <c r="C319" s="54"/>
@@ -28464,7 +28500,7 @@
       <c r="H319" s="54"/>
       <c r="I319" s="54"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="41"/>
       <c r="B320" s="41"/>
       <c r="C320" s="54"/>
@@ -28475,7 +28511,7 @@
       <c r="H320" s="54"/>
       <c r="I320" s="54"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="41"/>
       <c r="B321" s="41"/>
       <c r="C321" s="54"/>
@@ -28486,7 +28522,7 @@
       <c r="H321" s="54"/>
       <c r="I321" s="54"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="41"/>
       <c r="B322" s="41"/>
       <c r="C322" s="54"/>
@@ -28497,7 +28533,7 @@
       <c r="H322" s="54"/>
       <c r="I322" s="54"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="41"/>
       <c r="B323" s="41"/>
       <c r="C323" s="54"/>
@@ -28508,7 +28544,7 @@
       <c r="H323" s="54"/>
       <c r="I323" s="54"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="41"/>
       <c r="B324" s="41"/>
       <c r="C324" s="54"/>
@@ -28519,7 +28555,7 @@
       <c r="H324" s="54"/>
       <c r="I324" s="54"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="41"/>
       <c r="B325" s="41"/>
       <c r="C325" s="54"/>
@@ -28530,7 +28566,7 @@
       <c r="H325" s="54"/>
       <c r="I325" s="54"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="41"/>
       <c r="B326" s="41"/>
       <c r="C326" s="54"/>
@@ -28541,7 +28577,7 @@
       <c r="H326" s="54"/>
       <c r="I326" s="54"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="41"/>
       <c r="B327" s="41"/>
       <c r="C327" s="54"/>
@@ -28552,7 +28588,7 @@
       <c r="H327" s="54"/>
       <c r="I327" s="54"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="41"/>
       <c r="B328" s="41"/>
       <c r="C328" s="54"/>
@@ -28563,7 +28599,7 @@
       <c r="H328" s="54"/>
       <c r="I328" s="54"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="41"/>
       <c r="B329" s="41"/>
       <c r="C329" s="54"/>
@@ -28574,7 +28610,7 @@
       <c r="H329" s="54"/>
       <c r="I329" s="54"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="41"/>
       <c r="B330" s="41"/>
       <c r="C330" s="54"/>
@@ -28585,7 +28621,7 @@
       <c r="H330" s="54"/>
       <c r="I330" s="54"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="41"/>
       <c r="B331" s="41"/>
       <c r="C331" s="54"/>
@@ -28596,7 +28632,7 @@
       <c r="H331" s="54"/>
       <c r="I331" s="54"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="41"/>
       <c r="B332" s="41"/>
       <c r="C332" s="54"/>
@@ -28607,7 +28643,7 @@
       <c r="H332" s="54"/>
       <c r="I332" s="54"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="41"/>
       <c r="B333" s="41"/>
       <c r="C333" s="54"/>
@@ -28618,7 +28654,7 @@
       <c r="H333" s="54"/>
       <c r="I333" s="54"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="41"/>
       <c r="B334" s="41"/>
       <c r="C334" s="54"/>
@@ -28629,7 +28665,7 @@
       <c r="H334" s="54"/>
       <c r="I334" s="54"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="41"/>
       <c r="B335" s="41"/>
       <c r="C335" s="54"/>
@@ -28640,7 +28676,7 @@
       <c r="H335" s="54"/>
       <c r="I335" s="54"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="41"/>
       <c r="B336" s="41"/>
       <c r="C336" s="54"/>
@@ -28651,7 +28687,7 @@
       <c r="H336" s="54"/>
       <c r="I336" s="54"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="41"/>
       <c r="B337" s="41"/>
       <c r="C337" s="54"/>
@@ -28662,7 +28698,7 @@
       <c r="H337" s="54"/>
       <c r="I337" s="54"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="41"/>
       <c r="B338" s="41"/>
       <c r="C338" s="54"/>
@@ -28673,7 +28709,7 @@
       <c r="H338" s="54"/>
       <c r="I338" s="54"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="41"/>
       <c r="B339" s="41"/>
       <c r="C339" s="54"/>
@@ -28684,7 +28720,7 @@
       <c r="H339" s="54"/>
       <c r="I339" s="54"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="41"/>
       <c r="B340" s="41"/>
       <c r="C340" s="54"/>
@@ -28695,7 +28731,7 @@
       <c r="H340" s="54"/>
       <c r="I340" s="54"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="41"/>
       <c r="B341" s="41"/>
       <c r="C341" s="54"/>
@@ -28706,7 +28742,7 @@
       <c r="H341" s="54"/>
       <c r="I341" s="54"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="41"/>
       <c r="B342" s="41"/>
       <c r="C342" s="54"/>
@@ -28717,7 +28753,7 @@
       <c r="H342" s="54"/>
       <c r="I342" s="54"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="41"/>
       <c r="B343" s="41"/>
       <c r="C343" s="54"/>
@@ -28728,7 +28764,7 @@
       <c r="H343" s="54"/>
       <c r="I343" s="54"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="41"/>
       <c r="B344" s="41"/>
       <c r="C344" s="54"/>
@@ -28739,7 +28775,7 @@
       <c r="H344" s="54"/>
       <c r="I344" s="54"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="41"/>
       <c r="B345" s="41"/>
       <c r="C345" s="54"/>
@@ -28750,7 +28786,7 @@
       <c r="H345" s="54"/>
       <c r="I345" s="54"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="41"/>
       <c r="B346" s="41"/>
       <c r="C346" s="54"/>
@@ -28761,7 +28797,7 @@
       <c r="H346" s="54"/>
       <c r="I346" s="54"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="41"/>
       <c r="B347" s="41"/>
       <c r="C347" s="54"/>
@@ -28772,7 +28808,7 @@
       <c r="H347" s="54"/>
       <c r="I347" s="54"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="41"/>
       <c r="B348" s="41"/>
       <c r="C348" s="54"/>
@@ -28783,7 +28819,7 @@
       <c r="H348" s="54"/>
       <c r="I348" s="54"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="41"/>
       <c r="B349" s="41"/>
       <c r="C349" s="54"/>
@@ -28794,7 +28830,7 @@
       <c r="H349" s="54"/>
       <c r="I349" s="54"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="41"/>
       <c r="B350" s="41"/>
       <c r="C350" s="54"/>
@@ -28805,7 +28841,7 @@
       <c r="H350" s="54"/>
       <c r="I350" s="54"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="41"/>
       <c r="B351" s="41"/>
       <c r="C351" s="54"/>
@@ -28816,7 +28852,7 @@
       <c r="H351" s="54"/>
       <c r="I351" s="54"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="41"/>
       <c r="B352" s="41"/>
       <c r="C352" s="54"/>
@@ -28827,7 +28863,7 @@
       <c r="H352" s="54"/>
       <c r="I352" s="54"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="41"/>
       <c r="B353" s="41"/>
       <c r="C353" s="54"/>
@@ -28838,7 +28874,7 @@
       <c r="H353" s="54"/>
       <c r="I353" s="54"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="41"/>
       <c r="B354" s="41"/>
       <c r="C354" s="54"/>
@@ -28849,7 +28885,7 @@
       <c r="H354" s="54"/>
       <c r="I354" s="54"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="41"/>
       <c r="B355" s="41"/>
       <c r="C355" s="54"/>
@@ -28860,7 +28896,7 @@
       <c r="H355" s="54"/>
       <c r="I355" s="54"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="41"/>
       <c r="B356" s="41"/>
       <c r="C356" s="54"/>
@@ -28871,7 +28907,7 @@
       <c r="H356" s="54"/>
       <c r="I356" s="54"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="41"/>
       <c r="B357" s="41"/>
       <c r="C357" s="54"/>
@@ -28882,7 +28918,7 @@
       <c r="H357" s="54"/>
       <c r="I357" s="54"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="41"/>
       <c r="B358" s="41"/>
       <c r="C358" s="54"/>
@@ -28893,7 +28929,7 @@
       <c r="H358" s="54"/>
       <c r="I358" s="54"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="41"/>
       <c r="B359" s="41"/>
       <c r="C359" s="54"/>
@@ -28904,7 +28940,7 @@
       <c r="H359" s="54"/>
       <c r="I359" s="54"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="41"/>
       <c r="B360" s="41"/>
       <c r="C360" s="54"/>
@@ -28915,7 +28951,7 @@
       <c r="H360" s="54"/>
       <c r="I360" s="54"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="41"/>
       <c r="B361" s="41"/>
       <c r="C361" s="54"/>
@@ -28926,7 +28962,7 @@
       <c r="H361" s="54"/>
       <c r="I361" s="54"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="41"/>
       <c r="B362" s="41"/>
       <c r="C362" s="54"/>
@@ -28937,7 +28973,7 @@
       <c r="H362" s="54"/>
       <c r="I362" s="54"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="41"/>
       <c r="B363" s="41"/>
       <c r="C363" s="54"/>
@@ -28948,7 +28984,7 @@
       <c r="H363" s="54"/>
       <c r="I363" s="54"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="41"/>
       <c r="B364" s="41"/>
       <c r="C364" s="54"/>
@@ -28959,7 +28995,7 @@
       <c r="H364" s="54"/>
       <c r="I364" s="54"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="41"/>
       <c r="B365" s="41"/>
       <c r="C365" s="54"/>
@@ -28970,7 +29006,7 @@
       <c r="H365" s="54"/>
       <c r="I365" s="54"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="41"/>
       <c r="B366" s="41"/>
       <c r="C366" s="54"/>
@@ -28981,7 +29017,7 @@
       <c r="H366" s="54"/>
       <c r="I366" s="54"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="41"/>
       <c r="B367" s="41"/>
       <c r="C367" s="54"/>
@@ -28992,7 +29028,7 @@
       <c r="H367" s="54"/>
       <c r="I367" s="54"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="41"/>
       <c r="B368" s="41"/>
       <c r="C368" s="54"/>
@@ -29003,7 +29039,7 @@
       <c r="H368" s="54"/>
       <c r="I368" s="54"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="41"/>
       <c r="B369" s="41"/>
       <c r="C369" s="54"/>
@@ -29014,7 +29050,7 @@
       <c r="H369" s="54"/>
       <c r="I369" s="54"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="41"/>
       <c r="B370" s="41"/>
       <c r="C370" s="54"/>
@@ -29025,7 +29061,7 @@
       <c r="H370" s="54"/>
       <c r="I370" s="54"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="41"/>
       <c r="B371" s="41"/>
       <c r="C371" s="54"/>
@@ -29036,7 +29072,7 @@
       <c r="H371" s="54"/>
       <c r="I371" s="54"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="41"/>
       <c r="B372" s="41"/>
       <c r="C372" s="54"/>
@@ -29047,7 +29083,7 @@
       <c r="H372" s="54"/>
       <c r="I372" s="54"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="41"/>
       <c r="B373" s="41"/>
       <c r="C373" s="54"/>
@@ -29058,7 +29094,7 @@
       <c r="H373" s="54"/>
       <c r="I373" s="54"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="41"/>
       <c r="B374" s="41"/>
       <c r="C374" s="54"/>
@@ -29069,7 +29105,7 @@
       <c r="H374" s="54"/>
       <c r="I374" s="54"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="41"/>
       <c r="B375" s="41"/>
       <c r="C375" s="54"/>
@@ -29080,7 +29116,7 @@
       <c r="H375" s="54"/>
       <c r="I375" s="54"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="41"/>
       <c r="B376" s="41"/>
       <c r="C376" s="54"/>
@@ -29091,7 +29127,7 @@
       <c r="H376" s="54"/>
       <c r="I376" s="54"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="41"/>
       <c r="B377" s="41"/>
       <c r="C377" s="54"/>
@@ -29102,7 +29138,7 @@
       <c r="H377" s="54"/>
       <c r="I377" s="54"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="41"/>
       <c r="B378" s="41"/>
       <c r="C378" s="54"/>
@@ -29113,7 +29149,7 @@
       <c r="H378" s="54"/>
       <c r="I378" s="54"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="41"/>
       <c r="B379" s="41"/>
       <c r="C379" s="54"/>
@@ -29124,7 +29160,7 @@
       <c r="H379" s="54"/>
       <c r="I379" s="54"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="41"/>
       <c r="B380" s="41"/>
       <c r="C380" s="54"/>
@@ -29135,7 +29171,7 @@
       <c r="H380" s="54"/>
       <c r="I380" s="54"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="41"/>
       <c r="B381" s="41"/>
       <c r="C381" s="54"/>
@@ -29146,7 +29182,7 @@
       <c r="H381" s="54"/>
       <c r="I381" s="54"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="41"/>
       <c r="B382" s="41"/>
       <c r="C382" s="54"/>
@@ -29157,7 +29193,7 @@
       <c r="H382" s="54"/>
       <c r="I382" s="54"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="41"/>
       <c r="B383" s="41"/>
       <c r="C383" s="54"/>
@@ -29168,7 +29204,7 @@
       <c r="H383" s="54"/>
       <c r="I383" s="54"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="41"/>
       <c r="B384" s="41"/>
       <c r="C384" s="54"/>
@@ -29179,7 +29215,7 @@
       <c r="H384" s="54"/>
       <c r="I384" s="54"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="41"/>
       <c r="B385" s="41"/>
       <c r="C385" s="54"/>
@@ -29190,7 +29226,7 @@
       <c r="H385" s="54"/>
       <c r="I385" s="54"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="41"/>
       <c r="B386" s="41"/>
       <c r="C386" s="54"/>
@@ -29201,7 +29237,7 @@
       <c r="H386" s="54"/>
       <c r="I386" s="54"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="41"/>
       <c r="B387" s="41"/>
       <c r="C387" s="54"/>
@@ -29212,7 +29248,7 @@
       <c r="H387" s="54"/>
       <c r="I387" s="54"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="41"/>
       <c r="B388" s="41"/>
       <c r="C388" s="54"/>
@@ -29223,7 +29259,7 @@
       <c r="H388" s="54"/>
       <c r="I388" s="54"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="41"/>
       <c r="B389" s="41"/>
       <c r="C389" s="54"/>
@@ -29234,7 +29270,7 @@
       <c r="H389" s="54"/>
       <c r="I389" s="54"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="41"/>
       <c r="B390" s="41"/>
       <c r="C390" s="54"/>
@@ -29245,7 +29281,7 @@
       <c r="H390" s="54"/>
       <c r="I390" s="54"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="41"/>
       <c r="B391" s="41"/>
       <c r="C391" s="54"/>
@@ -29256,7 +29292,7 @@
       <c r="H391" s="54"/>
       <c r="I391" s="54"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="41"/>
       <c r="B392" s="41"/>
       <c r="C392" s="54"/>
@@ -29267,7 +29303,7 @@
       <c r="H392" s="54"/>
       <c r="I392" s="54"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="41"/>
       <c r="B393" s="41"/>
       <c r="C393" s="54"/>
@@ -29278,7 +29314,7 @@
       <c r="H393" s="54"/>
       <c r="I393" s="54"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="41"/>
       <c r="B394" s="41"/>
       <c r="C394" s="54"/>
@@ -29289,7 +29325,7 @@
       <c r="H394" s="54"/>
       <c r="I394" s="54"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="41"/>
       <c r="B395" s="41"/>
       <c r="C395" s="54"/>
@@ -29300,7 +29336,7 @@
       <c r="H395" s="54"/>
       <c r="I395" s="54"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="41"/>
       <c r="B396" s="41"/>
       <c r="C396" s="54"/>
@@ -29311,7 +29347,7 @@
       <c r="H396" s="54"/>
       <c r="I396" s="54"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="41"/>
       <c r="B397" s="41"/>
       <c r="C397" s="54"/>
@@ -29322,7 +29358,7 @@
       <c r="H397" s="54"/>
       <c r="I397" s="54"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="41"/>
       <c r="B398" s="41"/>
       <c r="C398" s="54"/>
@@ -29333,7 +29369,7 @@
       <c r="H398" s="54"/>
       <c r="I398" s="54"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="41"/>
       <c r="B399" s="41"/>
       <c r="C399" s="54"/>
@@ -29344,7 +29380,7 @@
       <c r="H399" s="54"/>
       <c r="I399" s="54"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="41"/>
       <c r="B400" s="41"/>
       <c r="C400" s="54"/>
@@ -29355,7 +29391,7 @@
       <c r="H400" s="54"/>
       <c r="I400" s="54"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="41"/>
       <c r="B401" s="41"/>
       <c r="C401" s="54"/>
@@ -29366,7 +29402,7 @@
       <c r="H401" s="54"/>
       <c r="I401" s="54"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="41"/>
       <c r="B402" s="41"/>
       <c r="C402" s="54"/>
@@ -29377,7 +29413,7 @@
       <c r="H402" s="54"/>
       <c r="I402" s="54"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="41"/>
       <c r="B403" s="41"/>
       <c r="C403" s="54"/>
@@ -29388,7 +29424,7 @@
       <c r="H403" s="54"/>
       <c r="I403" s="54"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="41"/>
       <c r="B404" s="41"/>
       <c r="C404" s="54"/>
@@ -29399,7 +29435,7 @@
       <c r="H404" s="54"/>
       <c r="I404" s="54"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="41"/>
       <c r="B405" s="41"/>
       <c r="C405" s="54"/>
@@ -29410,7 +29446,7 @@
       <c r="H405" s="54"/>
       <c r="I405" s="54"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="41"/>
       <c r="B406" s="41"/>
       <c r="C406" s="54"/>
@@ -29421,7 +29457,7 @@
       <c r="H406" s="54"/>
       <c r="I406" s="54"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="41"/>
       <c r="B407" s="41"/>
       <c r="C407" s="54"/>
@@ -29432,7 +29468,7 @@
       <c r="H407" s="54"/>
       <c r="I407" s="54"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="41"/>
       <c r="B408" s="41"/>
       <c r="C408" s="54"/>
@@ -29443,7 +29479,7 @@
       <c r="H408" s="54"/>
       <c r="I408" s="54"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="41"/>
       <c r="B409" s="41"/>
       <c r="C409" s="54"/>
@@ -29454,7 +29490,7 @@
       <c r="H409" s="54"/>
       <c r="I409" s="54"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="41"/>
       <c r="B410" s="41"/>
       <c r="C410" s="54"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1891.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896C3C04-CF94-4C3E-9792-F5B863DFAE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F6C00C-8560-4871-AF03-AFD3277311DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="16905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="3" r:id="rId1"/>
@@ -1259,7 +1259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1302,6 +1302,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1322,7 +1328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1506,6 +1512,9 @@
     <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1673,17 +1682,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317E8D20-6275-41B8-982F-8FFD4E68F4B1}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="41" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
         <v>391</v>
       </c>
@@ -1696,14 +1705,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C75BB2-12A9-42A6-B34F-FED52308A84D}">
   <dimension ref="A1:I410"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.83984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1737,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="41" t="s">
         <v>308</v>
       </c>
@@ -1753,7 +1762,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41" t="s">
         <v>309</v>
       </c>
@@ -1778,7 +1787,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="41" t="s">
         <v>310</v>
       </c>
@@ -1803,7 +1812,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41" t="s">
         <v>311</v>
       </c>
@@ -1828,7 +1837,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="41" t="s">
         <v>312</v>
       </c>
@@ -1853,7 +1862,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="41" t="s">
         <v>313</v>
       </c>
@@ -1878,7 +1887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="41" t="s">
         <v>314</v>
       </c>
@@ -1903,7 +1912,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="41" t="s">
         <v>30</v>
       </c>
@@ -1928,7 +1937,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="41" t="s">
         <v>315</v>
       </c>
@@ -1953,7 +1962,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="55" t="s">
         <v>316</v>
       </c>
@@ -1978,7 +1987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="55" t="s">
         <v>39</v>
       </c>
@@ -2003,7 +2012,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="41" t="s">
         <v>317</v>
       </c>
@@ -2028,7 +2037,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="41" t="s">
         <v>318</v>
       </c>
@@ -2053,7 +2062,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="41" t="s">
         <v>319</v>
       </c>
@@ -2078,7 +2087,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="41" t="s">
         <v>320</v>
       </c>
@@ -2103,7 +2112,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="41" t="s">
         <v>321</v>
       </c>
@@ -2128,7 +2137,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="41" t="s">
         <v>322</v>
       </c>
@@ -2153,7 +2162,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="41" t="s">
         <v>323</v>
       </c>
@@ -2178,7 +2187,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="41" t="s">
         <v>59</v>
       </c>
@@ -2203,7 +2212,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="41" t="s">
         <v>62</v>
       </c>
@@ -2228,7 +2237,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="41" t="s">
         <v>324</v>
       </c>
@@ -2253,7 +2262,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="41" t="s">
         <v>68</v>
       </c>
@@ -2278,7 +2287,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="41" t="s">
         <v>71</v>
       </c>
@@ -2303,7 +2312,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="41" t="s">
         <v>325</v>
       </c>
@@ -2328,7 +2337,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="41" t="s">
         <v>326</v>
       </c>
@@ -2353,7 +2362,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="41" t="s">
         <v>327</v>
       </c>
@@ -2378,7 +2387,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="41" t="s">
         <v>81</v>
       </c>
@@ -2403,7 +2412,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="41" t="s">
         <v>328</v>
       </c>
@@ -2428,7 +2437,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="41" t="s">
         <v>329</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="41" t="s">
         <v>330</v>
       </c>
@@ -2478,7 +2487,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="41" t="s">
         <v>331</v>
       </c>
@@ -2503,7 +2512,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="41" t="s">
         <v>332</v>
       </c>
@@ -2528,7 +2537,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="41" t="s">
         <v>333</v>
       </c>
@@ -2553,7 +2562,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="41" t="s">
         <v>100</v>
       </c>
@@ -2578,7 +2587,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="41" t="s">
         <v>334</v>
       </c>
@@ -2603,7 +2612,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="41" t="s">
         <v>335</v>
       </c>
@@ -2628,7 +2637,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="41" t="s">
         <v>336</v>
       </c>
@@ -2653,7 +2662,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="41" t="s">
         <v>337</v>
       </c>
@@ -2678,7 +2687,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="41" t="s">
         <v>338</v>
       </c>
@@ -2703,7 +2712,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="41" t="s">
         <v>339</v>
       </c>
@@ -2728,7 +2737,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="41" t="s">
         <v>340</v>
       </c>
@@ -2753,7 +2762,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="41" t="s">
         <v>341</v>
       </c>
@@ -2778,7 +2787,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="41" t="s">
         <v>342</v>
       </c>
@@ -2803,7 +2812,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="41" t="s">
         <v>343</v>
       </c>
@@ -2828,7 +2837,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="41" t="s">
         <v>130</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="41" t="s">
         <v>133</v>
       </c>
@@ -2878,7 +2887,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="41" t="s">
         <v>136</v>
       </c>
@@ -2903,7 +2912,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="41" t="s">
         <v>344</v>
       </c>
@@ -2928,7 +2937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="41" t="s">
         <v>345</v>
       </c>
@@ -2953,7 +2962,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="41" t="s">
         <v>346</v>
       </c>
@@ -2978,7 +2987,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="41" t="s">
         <v>347</v>
       </c>
@@ -3003,7 +3012,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="41" t="s">
         <v>348</v>
       </c>
@@ -3028,7 +3037,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="41" t="s">
         <v>349</v>
       </c>
@@ -3053,7 +3062,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="41" t="s">
         <v>156</v>
       </c>
@@ -3078,7 +3087,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="41" t="s">
         <v>159</v>
       </c>
@@ -3103,7 +3112,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="41" t="s">
         <v>162</v>
       </c>
@@ -3128,7 +3137,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="41" t="s">
         <v>165</v>
       </c>
@@ -3153,7 +3162,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="41" t="s">
         <v>168</v>
       </c>
@@ -3178,7 +3187,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="41" t="s">
         <v>350</v>
       </c>
@@ -3203,7 +3212,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="41" t="s">
         <v>174</v>
       </c>
@@ -3228,7 +3237,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="41" t="s">
         <v>177</v>
       </c>
@@ -3253,7 +3262,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="41" t="s">
         <v>180</v>
       </c>
@@ -3278,7 +3287,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="41" t="s">
         <v>351</v>
       </c>
@@ -3303,7 +3312,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="41" t="s">
         <v>352</v>
       </c>
@@ -3328,7 +3337,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="41" t="s">
         <v>353</v>
       </c>
@@ -3353,7 +3362,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="41" t="s">
         <v>354</v>
       </c>
@@ -3378,7 +3387,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="41" t="s">
         <v>191</v>
       </c>
@@ -3403,7 +3412,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="41" t="s">
         <v>355</v>
       </c>
@@ -3428,7 +3437,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="41" t="s">
         <v>356</v>
       </c>
@@ -3453,7 +3462,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="41" t="s">
         <v>357</v>
       </c>
@@ -3478,7 +3487,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="41" t="s">
         <v>358</v>
       </c>
@@ -3503,7 +3512,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="41" t="s">
         <v>359</v>
       </c>
@@ -3528,7 +3537,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="41" t="s">
         <v>361</v>
       </c>
@@ -3553,7 +3562,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="41" t="s">
         <v>362</v>
       </c>
@@ -3578,7 +3587,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="41" t="s">
         <v>363</v>
       </c>
@@ -3603,7 +3612,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="41" t="s">
         <v>364</v>
       </c>
@@ -3628,7 +3637,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="41" t="s">
         <v>365</v>
       </c>
@@ -3653,7 +3662,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="41" t="s">
         <v>366</v>
       </c>
@@ -3678,7 +3687,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="41" t="s">
         <v>367</v>
       </c>
@@ -3703,7 +3712,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="41" t="s">
         <v>368</v>
       </c>
@@ -3728,7 +3737,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="41" t="s">
         <v>369</v>
       </c>
@@ -3753,7 +3762,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="41" t="s">
         <v>370</v>
       </c>
@@ -3778,7 +3787,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="41" t="s">
         <v>371</v>
       </c>
@@ -3803,7 +3812,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="41" t="s">
         <v>372</v>
       </c>
@@ -3828,7 +3837,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="41" t="s">
         <v>373</v>
       </c>
@@ -3853,7 +3862,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="41" t="s">
         <v>374</v>
       </c>
@@ -3878,7 +3887,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="41" t="s">
         <v>375</v>
       </c>
@@ -3903,7 +3912,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41" t="s">
         <v>376</v>
       </c>
@@ -3928,7 +3937,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="41" t="s">
         <v>377</v>
       </c>
@@ -3953,7 +3962,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="41" t="s">
         <v>378</v>
       </c>
@@ -3978,7 +3987,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="41" t="s">
         <v>379</v>
       </c>
@@ -4003,7 +4012,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="41" t="s">
         <v>380</v>
       </c>
@@ -4028,7 +4037,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="41" t="s">
         <v>381</v>
       </c>
@@ -4053,7 +4062,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="41" t="s">
         <v>256</v>
       </c>
@@ -4072,7 +4081,7 @@
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="41" t="s">
         <v>382</v>
       </c>
@@ -4097,7 +4106,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="41" t="s">
         <v>383</v>
       </c>
@@ -4122,7 +4131,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="41" t="s">
         <v>384</v>
       </c>
@@ -4147,7 +4156,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="41" t="s">
         <v>385</v>
       </c>
@@ -4172,7 +4181,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="41" t="s">
         <v>386</v>
       </c>
@@ -4197,7 +4206,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="41" t="s">
         <v>387</v>
       </c>
@@ -4222,7 +4231,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="41" t="s">
         <v>388</v>
       </c>
@@ -4247,7 +4256,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="41" t="s">
         <v>389</v>
       </c>
@@ -4272,7 +4281,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="41"/>
       <c r="B104" s="41"/>
       <c r="C104" s="54"/>
@@ -4283,7 +4292,7 @@
       <c r="H104" s="54"/>
       <c r="I104" s="54"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="41"/>
       <c r="B105" s="41"/>
       <c r="C105" s="54"/>
@@ -4294,7 +4303,7 @@
       <c r="H105" s="54"/>
       <c r="I105" s="54"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="41"/>
       <c r="B106" s="41"/>
       <c r="C106" s="54"/>
@@ -4305,7 +4314,7 @@
       <c r="H106" s="54"/>
       <c r="I106" s="54"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="41"/>
       <c r="B107" s="41"/>
       <c r="C107" s="54"/>
@@ -4316,7 +4325,7 @@
       <c r="H107" s="54"/>
       <c r="I107" s="54"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="41"/>
       <c r="B108" s="41"/>
       <c r="C108" s="54"/>
@@ -4327,7 +4336,7 @@
       <c r="H108" s="54"/>
       <c r="I108" s="54"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="41"/>
       <c r="B109" s="41"/>
       <c r="C109" s="54"/>
@@ -4338,7 +4347,7 @@
       <c r="H109" s="54"/>
       <c r="I109" s="54"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
       <c r="C110" s="54"/>
@@ -4349,7 +4358,7 @@
       <c r="H110" s="54"/>
       <c r="I110" s="54"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="41"/>
       <c r="B111" s="41"/>
       <c r="C111" s="54"/>
@@ -4360,7 +4369,7 @@
       <c r="H111" s="54"/>
       <c r="I111" s="54"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="41"/>
       <c r="B112" s="41"/>
       <c r="C112" s="54"/>
@@ -4371,7 +4380,7 @@
       <c r="H112" s="54"/>
       <c r="I112" s="54"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="41"/>
       <c r="B113" s="41"/>
       <c r="C113" s="54"/>
@@ -4382,7 +4391,7 @@
       <c r="H113" s="54"/>
       <c r="I113" s="54"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="41"/>
       <c r="B114" s="41"/>
       <c r="C114" s="54"/>
@@ -4393,7 +4402,7 @@
       <c r="H114" s="54"/>
       <c r="I114" s="54"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="41"/>
       <c r="B115" s="41"/>
       <c r="C115" s="54"/>
@@ -4404,7 +4413,7 @@
       <c r="H115" s="54"/>
       <c r="I115" s="54"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="41"/>
       <c r="B116" s="41"/>
       <c r="C116" s="54"/>
@@ -4415,7 +4424,7 @@
       <c r="H116" s="54"/>
       <c r="I116" s="54"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="41"/>
       <c r="B117" s="41"/>
       <c r="C117" s="54"/>
@@ -4426,7 +4435,7 @@
       <c r="H117" s="54"/>
       <c r="I117" s="54"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="41"/>
       <c r="B118" s="41"/>
       <c r="C118" s="54"/>
@@ -4437,7 +4446,7 @@
       <c r="H118" s="54"/>
       <c r="I118" s="54"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="41"/>
       <c r="B119" s="41"/>
       <c r="C119" s="54"/>
@@ -4448,7 +4457,7 @@
       <c r="H119" s="54"/>
       <c r="I119" s="54"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="41"/>
       <c r="B120" s="41"/>
       <c r="C120" s="54"/>
@@ -4459,7 +4468,7 @@
       <c r="H120" s="54"/>
       <c r="I120" s="54"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="41"/>
       <c r="B121" s="41"/>
       <c r="C121" s="54"/>
@@ -4470,7 +4479,7 @@
       <c r="H121" s="54"/>
       <c r="I121" s="54"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="41"/>
       <c r="B122" s="41"/>
       <c r="C122" s="54"/>
@@ -4481,7 +4490,7 @@
       <c r="H122" s="54"/>
       <c r="I122" s="54"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="41"/>
       <c r="B123" s="41"/>
       <c r="C123" s="54"/>
@@ -4492,7 +4501,7 @@
       <c r="H123" s="54"/>
       <c r="I123" s="54"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="41"/>
       <c r="B124" s="41"/>
       <c r="C124" s="54"/>
@@ -4503,7 +4512,7 @@
       <c r="H124" s="54"/>
       <c r="I124" s="54"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="41"/>
       <c r="B125" s="41"/>
       <c r="C125" s="54"/>
@@ -4514,7 +4523,7 @@
       <c r="H125" s="54"/>
       <c r="I125" s="54"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="54"/>
@@ -4525,7 +4534,7 @@
       <c r="H126" s="54"/>
       <c r="I126" s="54"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="41"/>
       <c r="B127" s="41"/>
       <c r="C127" s="54"/>
@@ -4536,7 +4545,7 @@
       <c r="H127" s="54"/>
       <c r="I127" s="54"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="41"/>
       <c r="B128" s="41"/>
       <c r="C128" s="54"/>
@@ -4547,7 +4556,7 @@
       <c r="H128" s="54"/>
       <c r="I128" s="54"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="41"/>
       <c r="B129" s="41"/>
       <c r="C129" s="54"/>
@@ -4558,7 +4567,7 @@
       <c r="H129" s="54"/>
       <c r="I129" s="54"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="41"/>
       <c r="B130" s="41"/>
       <c r="C130" s="54"/>
@@ -4569,7 +4578,7 @@
       <c r="H130" s="54"/>
       <c r="I130" s="54"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="41"/>
       <c r="B131" s="41"/>
       <c r="C131" s="54"/>
@@ -4580,7 +4589,7 @@
       <c r="H131" s="54"/>
       <c r="I131" s="54"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="41"/>
       <c r="B132" s="41"/>
       <c r="C132" s="54"/>
@@ -4591,7 +4600,7 @@
       <c r="H132" s="54"/>
       <c r="I132" s="54"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="41"/>
       <c r="B133" s="41"/>
       <c r="C133" s="54"/>
@@ -4602,7 +4611,7 @@
       <c r="H133" s="54"/>
       <c r="I133" s="54"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="41"/>
       <c r="B134" s="41"/>
       <c r="C134" s="54"/>
@@ -4613,7 +4622,7 @@
       <c r="H134" s="54"/>
       <c r="I134" s="54"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="41"/>
       <c r="B135" s="41"/>
       <c r="C135" s="54"/>
@@ -4624,7 +4633,7 @@
       <c r="H135" s="54"/>
       <c r="I135" s="54"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="41"/>
       <c r="B136" s="41"/>
       <c r="C136" s="54"/>
@@ -4635,7 +4644,7 @@
       <c r="H136" s="54"/>
       <c r="I136" s="54"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="41"/>
       <c r="B137" s="41"/>
       <c r="C137" s="54"/>
@@ -4646,7 +4655,7 @@
       <c r="H137" s="54"/>
       <c r="I137" s="54"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="41"/>
       <c r="B138" s="41"/>
       <c r="C138" s="54"/>
@@ -4657,7 +4666,7 @@
       <c r="H138" s="54"/>
       <c r="I138" s="54"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="41"/>
       <c r="B139" s="41"/>
       <c r="C139" s="54"/>
@@ -4668,7 +4677,7 @@
       <c r="H139" s="54"/>
       <c r="I139" s="54"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="41"/>
       <c r="B140" s="41"/>
       <c r="C140" s="54"/>
@@ -4679,7 +4688,7 @@
       <c r="H140" s="54"/>
       <c r="I140" s="54"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="41"/>
       <c r="B141" s="41"/>
       <c r="C141" s="54"/>
@@ -4690,7 +4699,7 @@
       <c r="H141" s="54"/>
       <c r="I141" s="54"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="41"/>
       <c r="B142" s="41"/>
       <c r="C142" s="54"/>
@@ -4701,7 +4710,7 @@
       <c r="H142" s="54"/>
       <c r="I142" s="54"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="41"/>
       <c r="B143" s="41"/>
       <c r="C143" s="54"/>
@@ -4712,7 +4721,7 @@
       <c r="H143" s="54"/>
       <c r="I143" s="54"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="41"/>
       <c r="B144" s="41"/>
       <c r="C144" s="54"/>
@@ -4723,7 +4732,7 @@
       <c r="H144" s="54"/>
       <c r="I144" s="54"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="41"/>
       <c r="B145" s="41"/>
       <c r="C145" s="54"/>
@@ -4734,7 +4743,7 @@
       <c r="H145" s="54"/>
       <c r="I145" s="54"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="41"/>
       <c r="B146" s="41"/>
       <c r="C146" s="54"/>
@@ -4745,7 +4754,7 @@
       <c r="H146" s="54"/>
       <c r="I146" s="54"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="41"/>
       <c r="B147" s="41"/>
       <c r="C147" s="54"/>
@@ -4756,7 +4765,7 @@
       <c r="H147" s="54"/>
       <c r="I147" s="54"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="41"/>
       <c r="B148" s="41"/>
       <c r="C148" s="54"/>
@@ -4767,7 +4776,7 @@
       <c r="H148" s="54"/>
       <c r="I148" s="54"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="41"/>
       <c r="B149" s="41"/>
       <c r="C149" s="54"/>
@@ -4778,7 +4787,7 @@
       <c r="H149" s="54"/>
       <c r="I149" s="54"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="41"/>
       <c r="B150" s="41"/>
       <c r="C150" s="54"/>
@@ -4789,7 +4798,7 @@
       <c r="H150" s="54"/>
       <c r="I150" s="54"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
       <c r="C151" s="54"/>
@@ -4800,7 +4809,7 @@
       <c r="H151" s="54"/>
       <c r="I151" s="54"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="41"/>
       <c r="B152" s="41"/>
       <c r="C152" s="54"/>
@@ -4811,7 +4820,7 @@
       <c r="H152" s="54"/>
       <c r="I152" s="54"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="41"/>
       <c r="B153" s="41"/>
       <c r="C153" s="54"/>
@@ -4822,7 +4831,7 @@
       <c r="H153" s="54"/>
       <c r="I153" s="54"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="41"/>
       <c r="B154" s="41"/>
       <c r="C154" s="54"/>
@@ -4833,7 +4842,7 @@
       <c r="H154" s="54"/>
       <c r="I154" s="54"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="41"/>
       <c r="B155" s="41"/>
       <c r="C155" s="54"/>
@@ -4844,7 +4853,7 @@
       <c r="H155" s="54"/>
       <c r="I155" s="54"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="41"/>
       <c r="B156" s="41"/>
       <c r="C156" s="54"/>
@@ -4855,7 +4864,7 @@
       <c r="H156" s="54"/>
       <c r="I156" s="54"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="41"/>
       <c r="B157" s="41"/>
       <c r="C157" s="54"/>
@@ -4866,7 +4875,7 @@
       <c r="H157" s="54"/>
       <c r="I157" s="54"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="41"/>
       <c r="B158" s="41"/>
       <c r="C158" s="54"/>
@@ -4877,7 +4886,7 @@
       <c r="H158" s="54"/>
       <c r="I158" s="54"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="41"/>
       <c r="B159" s="41"/>
       <c r="C159" s="54"/>
@@ -4888,7 +4897,7 @@
       <c r="H159" s="54"/>
       <c r="I159" s="54"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="41"/>
       <c r="B160" s="41"/>
       <c r="C160" s="54"/>
@@ -4899,7 +4908,7 @@
       <c r="H160" s="54"/>
       <c r="I160" s="54"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="41"/>
       <c r="B161" s="41"/>
       <c r="C161" s="54"/>
@@ -4910,7 +4919,7 @@
       <c r="H161" s="54"/>
       <c r="I161" s="54"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="41"/>
       <c r="B162" s="41"/>
       <c r="C162" s="54"/>
@@ -4921,7 +4930,7 @@
       <c r="H162" s="54"/>
       <c r="I162" s="54"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="41"/>
       <c r="B163" s="41"/>
       <c r="C163" s="54"/>
@@ -4932,7 +4941,7 @@
       <c r="H163" s="54"/>
       <c r="I163" s="54"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="41"/>
       <c r="B164" s="41"/>
       <c r="C164" s="54"/>
@@ -4943,7 +4952,7 @@
       <c r="H164" s="54"/>
       <c r="I164" s="54"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="41"/>
       <c r="B165" s="41"/>
       <c r="C165" s="54"/>
@@ -4954,7 +4963,7 @@
       <c r="H165" s="54"/>
       <c r="I165" s="54"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="41"/>
       <c r="B166" s="41"/>
       <c r="C166" s="54"/>
@@ -4965,7 +4974,7 @@
       <c r="H166" s="54"/>
       <c r="I166" s="54"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="41"/>
       <c r="B167" s="41"/>
       <c r="C167" s="54"/>
@@ -4976,7 +4985,7 @@
       <c r="H167" s="54"/>
       <c r="I167" s="54"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="41"/>
       <c r="B168" s="41"/>
       <c r="C168" s="54"/>
@@ -4987,7 +4996,7 @@
       <c r="H168" s="54"/>
       <c r="I168" s="54"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="41"/>
       <c r="B169" s="41"/>
       <c r="C169" s="54"/>
@@ -4998,7 +5007,7 @@
       <c r="H169" s="54"/>
       <c r="I169" s="54"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="41"/>
       <c r="B170" s="41"/>
       <c r="C170" s="54"/>
@@ -5009,7 +5018,7 @@
       <c r="H170" s="54"/>
       <c r="I170" s="54"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="41"/>
       <c r="B171" s="41"/>
       <c r="C171" s="54"/>
@@ -5020,7 +5029,7 @@
       <c r="H171" s="54"/>
       <c r="I171" s="54"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="41"/>
       <c r="B172" s="41"/>
       <c r="C172" s="54"/>
@@ -5031,7 +5040,7 @@
       <c r="H172" s="54"/>
       <c r="I172" s="54"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="41"/>
       <c r="B173" s="41"/>
       <c r="C173" s="54"/>
@@ -5042,7 +5051,7 @@
       <c r="H173" s="54"/>
       <c r="I173" s="54"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="41"/>
       <c r="B174" s="41"/>
       <c r="C174" s="54"/>
@@ -5053,7 +5062,7 @@
       <c r="H174" s="54"/>
       <c r="I174" s="54"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
       <c r="C175" s="54"/>
@@ -5064,7 +5073,7 @@
       <c r="H175" s="54"/>
       <c r="I175" s="54"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="41"/>
       <c r="B176" s="41"/>
       <c r="C176" s="54"/>
@@ -5075,7 +5084,7 @@
       <c r="H176" s="54"/>
       <c r="I176" s="54"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="41"/>
       <c r="B177" s="41"/>
       <c r="C177" s="54"/>
@@ -5086,7 +5095,7 @@
       <c r="H177" s="54"/>
       <c r="I177" s="54"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="41"/>
       <c r="B178" s="41"/>
       <c r="C178" s="54"/>
@@ -5097,7 +5106,7 @@
       <c r="H178" s="54"/>
       <c r="I178" s="54"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="41"/>
       <c r="B179" s="41"/>
       <c r="C179" s="54"/>
@@ -5108,7 +5117,7 @@
       <c r="H179" s="54"/>
       <c r="I179" s="54"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="41"/>
       <c r="B180" s="41"/>
       <c r="C180" s="54"/>
@@ -5119,7 +5128,7 @@
       <c r="H180" s="54"/>
       <c r="I180" s="54"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="41"/>
       <c r="B181" s="41"/>
       <c r="C181" s="54"/>
@@ -5130,7 +5139,7 @@
       <c r="H181" s="54"/>
       <c r="I181" s="54"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="41"/>
       <c r="B182" s="41"/>
       <c r="C182" s="54"/>
@@ -5141,7 +5150,7 @@
       <c r="H182" s="54"/>
       <c r="I182" s="54"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="41"/>
       <c r="B183" s="41"/>
       <c r="C183" s="54"/>
@@ -5152,7 +5161,7 @@
       <c r="H183" s="54"/>
       <c r="I183" s="54"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="41"/>
       <c r="B184" s="41"/>
       <c r="C184" s="54"/>
@@ -5163,7 +5172,7 @@
       <c r="H184" s="54"/>
       <c r="I184" s="54"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="41"/>
       <c r="B185" s="41"/>
       <c r="C185" s="54"/>
@@ -5174,7 +5183,7 @@
       <c r="H185" s="54"/>
       <c r="I185" s="54"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="41"/>
       <c r="B186" s="41"/>
       <c r="C186" s="54"/>
@@ -5185,7 +5194,7 @@
       <c r="H186" s="54"/>
       <c r="I186" s="54"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="41"/>
       <c r="B187" s="41"/>
       <c r="C187" s="54"/>
@@ -5196,7 +5205,7 @@
       <c r="H187" s="54"/>
       <c r="I187" s="54"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="41"/>
       <c r="B188" s="41"/>
       <c r="C188" s="54"/>
@@ -5207,7 +5216,7 @@
       <c r="H188" s="54"/>
       <c r="I188" s="54"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="41"/>
       <c r="B189" s="41"/>
       <c r="C189" s="54"/>
@@ -5218,7 +5227,7 @@
       <c r="H189" s="54"/>
       <c r="I189" s="54"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="41"/>
       <c r="B190" s="41"/>
       <c r="C190" s="54"/>
@@ -5229,7 +5238,7 @@
       <c r="H190" s="54"/>
       <c r="I190" s="54"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="41"/>
       <c r="B191" s="41"/>
       <c r="C191" s="54"/>
@@ -5240,7 +5249,7 @@
       <c r="H191" s="54"/>
       <c r="I191" s="54"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="41"/>
       <c r="B192" s="41"/>
       <c r="C192" s="54"/>
@@ -5251,7 +5260,7 @@
       <c r="H192" s="54"/>
       <c r="I192" s="54"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="41"/>
       <c r="B193" s="41"/>
       <c r="C193" s="54"/>
@@ -5262,7 +5271,7 @@
       <c r="H193" s="54"/>
       <c r="I193" s="54"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="41"/>
       <c r="B194" s="41"/>
       <c r="C194" s="54"/>
@@ -5273,7 +5282,7 @@
       <c r="H194" s="54"/>
       <c r="I194" s="54"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="41"/>
       <c r="B195" s="41"/>
       <c r="C195" s="54"/>
@@ -5284,7 +5293,7 @@
       <c r="H195" s="54"/>
       <c r="I195" s="54"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="41"/>
       <c r="B196" s="41"/>
       <c r="C196" s="54"/>
@@ -5295,7 +5304,7 @@
       <c r="H196" s="54"/>
       <c r="I196" s="54"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="41"/>
       <c r="B197" s="41"/>
       <c r="C197" s="54"/>
@@ -5306,7 +5315,7 @@
       <c r="H197" s="54"/>
       <c r="I197" s="54"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="41"/>
       <c r="B198" s="41"/>
       <c r="C198" s="54"/>
@@ -5317,7 +5326,7 @@
       <c r="H198" s="54"/>
       <c r="I198" s="54"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="41"/>
       <c r="B199" s="41"/>
       <c r="C199" s="54"/>
@@ -5328,7 +5337,7 @@
       <c r="H199" s="54"/>
       <c r="I199" s="54"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="41"/>
       <c r="B200" s="41"/>
       <c r="C200" s="54"/>
@@ -5339,7 +5348,7 @@
       <c r="H200" s="54"/>
       <c r="I200" s="54"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="41"/>
       <c r="B201" s="41"/>
       <c r="C201" s="54"/>
@@ -5350,7 +5359,7 @@
       <c r="H201" s="54"/>
       <c r="I201" s="54"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="41"/>
       <c r="B202" s="41"/>
       <c r="C202" s="54"/>
@@ -5361,7 +5370,7 @@
       <c r="H202" s="54"/>
       <c r="I202" s="54"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="41"/>
       <c r="B203" s="41"/>
       <c r="C203" s="54"/>
@@ -5372,7 +5381,7 @@
       <c r="H203" s="54"/>
       <c r="I203" s="54"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="41"/>
       <c r="B204" s="41"/>
       <c r="C204" s="54"/>
@@ -5383,7 +5392,7 @@
       <c r="H204" s="54"/>
       <c r="I204" s="54"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="41"/>
       <c r="B205" s="41"/>
       <c r="C205" s="54"/>
@@ -5394,7 +5403,7 @@
       <c r="H205" s="54"/>
       <c r="I205" s="54"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="41"/>
       <c r="B206" s="41"/>
       <c r="C206" s="54"/>
@@ -5405,7 +5414,7 @@
       <c r="H206" s="54"/>
       <c r="I206" s="54"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="41"/>
       <c r="B207" s="41"/>
       <c r="C207" s="54"/>
@@ -5416,7 +5425,7 @@
       <c r="H207" s="54"/>
       <c r="I207" s="54"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="41"/>
       <c r="B208" s="41"/>
       <c r="C208" s="54"/>
@@ -5427,7 +5436,7 @@
       <c r="H208" s="54"/>
       <c r="I208" s="54"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="41"/>
       <c r="B209" s="41"/>
       <c r="C209" s="54"/>
@@ -5438,7 +5447,7 @@
       <c r="H209" s="54"/>
       <c r="I209" s="54"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="41"/>
       <c r="B210" s="41"/>
       <c r="C210" s="54"/>
@@ -5449,7 +5458,7 @@
       <c r="H210" s="54"/>
       <c r="I210" s="54"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="41"/>
       <c r="B211" s="41"/>
       <c r="C211" s="54"/>
@@ -5460,7 +5469,7 @@
       <c r="H211" s="54"/>
       <c r="I211" s="54"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="41"/>
       <c r="B212" s="41"/>
       <c r="C212" s="54"/>
@@ -5471,7 +5480,7 @@
       <c r="H212" s="54"/>
       <c r="I212" s="54"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="41"/>
       <c r="B213" s="41"/>
       <c r="C213" s="54"/>
@@ -5482,7 +5491,7 @@
       <c r="H213" s="54"/>
       <c r="I213" s="54"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="41"/>
       <c r="B214" s="41"/>
       <c r="C214" s="54"/>
@@ -5493,7 +5502,7 @@
       <c r="H214" s="54"/>
       <c r="I214" s="54"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="41"/>
       <c r="B215" s="41"/>
       <c r="C215" s="54"/>
@@ -5504,7 +5513,7 @@
       <c r="H215" s="54"/>
       <c r="I215" s="54"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="41"/>
       <c r="B216" s="41"/>
       <c r="C216" s="54"/>
@@ -5515,7 +5524,7 @@
       <c r="H216" s="54"/>
       <c r="I216" s="54"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="41"/>
       <c r="B217" s="41"/>
       <c r="C217" s="54"/>
@@ -5526,7 +5535,7 @@
       <c r="H217" s="54"/>
       <c r="I217" s="54"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="41"/>
       <c r="B218" s="41"/>
       <c r="C218" s="54"/>
@@ -5537,7 +5546,7 @@
       <c r="H218" s="54"/>
       <c r="I218" s="54"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="41"/>
       <c r="B219" s="41"/>
       <c r="C219" s="54"/>
@@ -5548,7 +5557,7 @@
       <c r="H219" s="54"/>
       <c r="I219" s="54"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="41"/>
       <c r="B220" s="41"/>
       <c r="C220" s="54"/>
@@ -5559,7 +5568,7 @@
       <c r="H220" s="54"/>
       <c r="I220" s="54"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="41"/>
       <c r="B221" s="41"/>
       <c r="C221" s="54"/>
@@ -5570,7 +5579,7 @@
       <c r="H221" s="54"/>
       <c r="I221" s="54"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="41"/>
       <c r="B222" s="41"/>
       <c r="C222" s="54"/>
@@ -5581,7 +5590,7 @@
       <c r="H222" s="54"/>
       <c r="I222" s="54"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="41"/>
       <c r="B223" s="41"/>
       <c r="C223" s="54"/>
@@ -5592,7 +5601,7 @@
       <c r="H223" s="54"/>
       <c r="I223" s="54"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="41"/>
       <c r="B224" s="41"/>
       <c r="C224" s="54"/>
@@ -5603,7 +5612,7 @@
       <c r="H224" s="54"/>
       <c r="I224" s="54"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="41"/>
       <c r="B225" s="41"/>
       <c r="C225" s="54"/>
@@ -5614,7 +5623,7 @@
       <c r="H225" s="54"/>
       <c r="I225" s="54"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="41"/>
       <c r="B226" s="41"/>
       <c r="C226" s="54"/>
@@ -5625,7 +5634,7 @@
       <c r="H226" s="54"/>
       <c r="I226" s="54"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="41"/>
       <c r="B227" s="41"/>
       <c r="C227" s="54"/>
@@ -5636,7 +5645,7 @@
       <c r="H227" s="54"/>
       <c r="I227" s="54"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="41"/>
       <c r="B228" s="41"/>
       <c r="C228" s="54"/>
@@ -5647,7 +5656,7 @@
       <c r="H228" s="54"/>
       <c r="I228" s="54"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="41"/>
       <c r="B229" s="41"/>
       <c r="C229" s="54"/>
@@ -5658,7 +5667,7 @@
       <c r="H229" s="54"/>
       <c r="I229" s="54"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="41"/>
       <c r="B230" s="41"/>
       <c r="C230" s="54"/>
@@ -5669,7 +5678,7 @@
       <c r="H230" s="54"/>
       <c r="I230" s="54"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="41"/>
       <c r="B231" s="41"/>
       <c r="C231" s="54"/>
@@ -5680,7 +5689,7 @@
       <c r="H231" s="54"/>
       <c r="I231" s="54"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="41"/>
       <c r="B232" s="41"/>
       <c r="C232" s="54"/>
@@ -5691,7 +5700,7 @@
       <c r="H232" s="54"/>
       <c r="I232" s="54"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="41"/>
       <c r="B233" s="41"/>
       <c r="C233" s="54"/>
@@ -5702,7 +5711,7 @@
       <c r="H233" s="54"/>
       <c r="I233" s="54"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="41"/>
       <c r="B234" s="41"/>
       <c r="C234" s="54"/>
@@ -5713,7 +5722,7 @@
       <c r="H234" s="54"/>
       <c r="I234" s="54"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="41"/>
       <c r="B235" s="41"/>
       <c r="C235" s="54"/>
@@ -5724,7 +5733,7 @@
       <c r="H235" s="54"/>
       <c r="I235" s="54"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="41"/>
       <c r="B236" s="41"/>
       <c r="C236" s="54"/>
@@ -5735,7 +5744,7 @@
       <c r="H236" s="54"/>
       <c r="I236" s="54"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="41"/>
       <c r="B237" s="41"/>
       <c r="C237" s="54"/>
@@ -5746,7 +5755,7 @@
       <c r="H237" s="54"/>
       <c r="I237" s="54"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="41"/>
       <c r="B238" s="41"/>
       <c r="C238" s="54"/>
@@ -5757,7 +5766,7 @@
       <c r="H238" s="54"/>
       <c r="I238" s="54"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="41"/>
       <c r="B239" s="41"/>
       <c r="C239" s="54"/>
@@ -5768,7 +5777,7 @@
       <c r="H239" s="54"/>
       <c r="I239" s="54"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="41"/>
       <c r="B240" s="41"/>
       <c r="C240" s="54"/>
@@ -5779,7 +5788,7 @@
       <c r="H240" s="54"/>
       <c r="I240" s="54"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="41"/>
       <c r="B241" s="41"/>
       <c r="C241" s="54"/>
@@ -5790,7 +5799,7 @@
       <c r="H241" s="54"/>
       <c r="I241" s="54"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="41"/>
       <c r="B242" s="41"/>
       <c r="C242" s="54"/>
@@ -5801,7 +5810,7 @@
       <c r="H242" s="54"/>
       <c r="I242" s="54"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="41"/>
       <c r="B243" s="41"/>
       <c r="C243" s="54"/>
@@ -5812,7 +5821,7 @@
       <c r="H243" s="54"/>
       <c r="I243" s="54"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="41"/>
       <c r="B244" s="41"/>
       <c r="C244" s="54"/>
@@ -5823,7 +5832,7 @@
       <c r="H244" s="54"/>
       <c r="I244" s="54"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="41"/>
       <c r="B245" s="41"/>
       <c r="C245" s="54"/>
@@ -5834,7 +5843,7 @@
       <c r="H245" s="54"/>
       <c r="I245" s="54"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="41"/>
       <c r="B246" s="41"/>
       <c r="C246" s="54"/>
@@ -5845,7 +5854,7 @@
       <c r="H246" s="54"/>
       <c r="I246" s="54"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="41"/>
       <c r="B247" s="41"/>
       <c r="C247" s="54"/>
@@ -5856,7 +5865,7 @@
       <c r="H247" s="54"/>
       <c r="I247" s="54"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="41"/>
       <c r="B248" s="41"/>
       <c r="C248" s="54"/>
@@ -5867,7 +5876,7 @@
       <c r="H248" s="54"/>
       <c r="I248" s="54"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="41"/>
       <c r="B249" s="41"/>
       <c r="C249" s="54"/>
@@ -5878,7 +5887,7 @@
       <c r="H249" s="54"/>
       <c r="I249" s="54"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="41"/>
       <c r="B250" s="41"/>
       <c r="C250" s="54"/>
@@ -5889,7 +5898,7 @@
       <c r="H250" s="54"/>
       <c r="I250" s="54"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="41"/>
       <c r="B251" s="41"/>
       <c r="C251" s="54"/>
@@ -5900,7 +5909,7 @@
       <c r="H251" s="54"/>
       <c r="I251" s="54"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="41"/>
       <c r="B252" s="41"/>
       <c r="C252" s="54"/>
@@ -5911,7 +5920,7 @@
       <c r="H252" s="54"/>
       <c r="I252" s="54"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="41"/>
       <c r="B253" s="41"/>
       <c r="C253" s="54"/>
@@ -5922,7 +5931,7 @@
       <c r="H253" s="54"/>
       <c r="I253" s="54"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="41"/>
       <c r="B254" s="41"/>
       <c r="C254" s="54"/>
@@ -5933,7 +5942,7 @@
       <c r="H254" s="54"/>
       <c r="I254" s="54"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="41"/>
       <c r="B255" s="41"/>
       <c r="C255" s="54"/>
@@ -5944,7 +5953,7 @@
       <c r="H255" s="54"/>
       <c r="I255" s="54"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="41"/>
       <c r="B256" s="41"/>
       <c r="C256" s="54"/>
@@ -5955,7 +5964,7 @@
       <c r="H256" s="54"/>
       <c r="I256" s="54"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="41"/>
       <c r="B257" s="41"/>
       <c r="C257" s="54"/>
@@ -5966,7 +5975,7 @@
       <c r="H257" s="54"/>
       <c r="I257" s="54"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="41"/>
       <c r="B258" s="41"/>
       <c r="C258" s="54"/>
@@ -5977,7 +5986,7 @@
       <c r="H258" s="54"/>
       <c r="I258" s="54"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="41"/>
       <c r="B259" s="41"/>
       <c r="C259" s="54"/>
@@ -5988,7 +5997,7 @@
       <c r="H259" s="54"/>
       <c r="I259" s="54"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="41"/>
       <c r="B260" s="41"/>
       <c r="C260" s="54"/>
@@ -5999,7 +6008,7 @@
       <c r="H260" s="54"/>
       <c r="I260" s="54"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="41"/>
       <c r="B261" s="41"/>
       <c r="C261" s="54"/>
@@ -6010,7 +6019,7 @@
       <c r="H261" s="54"/>
       <c r="I261" s="54"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="41"/>
       <c r="B262" s="41"/>
       <c r="C262" s="54"/>
@@ -6021,7 +6030,7 @@
       <c r="H262" s="54"/>
       <c r="I262" s="54"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="41"/>
       <c r="B263" s="41"/>
       <c r="C263" s="54"/>
@@ -6032,7 +6041,7 @@
       <c r="H263" s="54"/>
       <c r="I263" s="54"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="41"/>
       <c r="B264" s="41"/>
       <c r="C264" s="54"/>
@@ -6043,7 +6052,7 @@
       <c r="H264" s="54"/>
       <c r="I264" s="54"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="41"/>
       <c r="B265" s="41"/>
       <c r="C265" s="54"/>
@@ -6054,7 +6063,7 @@
       <c r="H265" s="54"/>
       <c r="I265" s="54"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="41"/>
       <c r="B266" s="41"/>
       <c r="C266" s="54"/>
@@ -6065,7 +6074,7 @@
       <c r="H266" s="54"/>
       <c r="I266" s="54"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="41"/>
       <c r="B267" s="41"/>
       <c r="C267" s="54"/>
@@ -6076,7 +6085,7 @@
       <c r="H267" s="54"/>
       <c r="I267" s="54"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="41"/>
       <c r="B268" s="41"/>
       <c r="C268" s="54"/>
@@ -6087,7 +6096,7 @@
       <c r="H268" s="54"/>
       <c r="I268" s="54"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="41"/>
       <c r="B269" s="41"/>
       <c r="C269" s="54"/>
@@ -6098,7 +6107,7 @@
       <c r="H269" s="54"/>
       <c r="I269" s="54"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="41"/>
       <c r="B270" s="41"/>
       <c r="C270" s="54"/>
@@ -6109,7 +6118,7 @@
       <c r="H270" s="54"/>
       <c r="I270" s="54"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="41"/>
       <c r="B271" s="41"/>
       <c r="C271" s="54"/>
@@ -6120,7 +6129,7 @@
       <c r="H271" s="54"/>
       <c r="I271" s="54"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="41"/>
       <c r="B272" s="41"/>
       <c r="C272" s="54"/>
@@ -6131,7 +6140,7 @@
       <c r="H272" s="54"/>
       <c r="I272" s="54"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="41"/>
       <c r="B273" s="41"/>
       <c r="C273" s="54"/>
@@ -6142,7 +6151,7 @@
       <c r="H273" s="54"/>
       <c r="I273" s="54"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="41"/>
       <c r="B274" s="41"/>
       <c r="C274" s="54"/>
@@ -6153,7 +6162,7 @@
       <c r="H274" s="54"/>
       <c r="I274" s="54"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="41"/>
       <c r="B275" s="41"/>
       <c r="C275" s="54"/>
@@ -6164,7 +6173,7 @@
       <c r="H275" s="54"/>
       <c r="I275" s="54"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="41"/>
       <c r="B276" s="41"/>
       <c r="C276" s="54"/>
@@ -6175,7 +6184,7 @@
       <c r="H276" s="54"/>
       <c r="I276" s="54"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="41"/>
       <c r="B277" s="41"/>
       <c r="C277" s="54"/>
@@ -6186,7 +6195,7 @@
       <c r="H277" s="54"/>
       <c r="I277" s="54"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="41"/>
       <c r="B278" s="41"/>
       <c r="C278" s="54"/>
@@ -6197,7 +6206,7 @@
       <c r="H278" s="54"/>
       <c r="I278" s="54"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="41"/>
       <c r="B279" s="41"/>
       <c r="C279" s="54"/>
@@ -6208,7 +6217,7 @@
       <c r="H279" s="54"/>
       <c r="I279" s="54"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="41"/>
       <c r="B280" s="41"/>
       <c r="C280" s="54"/>
@@ -6219,7 +6228,7 @@
       <c r="H280" s="54"/>
       <c r="I280" s="54"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="41"/>
       <c r="B281" s="41"/>
       <c r="C281" s="54"/>
@@ -6230,7 +6239,7 @@
       <c r="H281" s="54"/>
       <c r="I281" s="54"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="41"/>
       <c r="B282" s="41"/>
       <c r="C282" s="54"/>
@@ -6241,7 +6250,7 @@
       <c r="H282" s="54"/>
       <c r="I282" s="54"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="41"/>
       <c r="B283" s="41"/>
       <c r="C283" s="54"/>
@@ -6252,7 +6261,7 @@
       <c r="H283" s="54"/>
       <c r="I283" s="54"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="41"/>
       <c r="B284" s="41"/>
       <c r="C284" s="54"/>
@@ -6263,7 +6272,7 @@
       <c r="H284" s="54"/>
       <c r="I284" s="54"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="41"/>
       <c r="B285" s="41"/>
       <c r="C285" s="54"/>
@@ -6274,7 +6283,7 @@
       <c r="H285" s="54"/>
       <c r="I285" s="54"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="41"/>
       <c r="B286" s="41"/>
       <c r="C286" s="54"/>
@@ -6285,7 +6294,7 @@
       <c r="H286" s="54"/>
       <c r="I286" s="54"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="41"/>
       <c r="B287" s="41"/>
       <c r="C287" s="54"/>
@@ -6296,7 +6305,7 @@
       <c r="H287" s="54"/>
       <c r="I287" s="54"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="41"/>
       <c r="B288" s="41"/>
       <c r="C288" s="54"/>
@@ -6307,7 +6316,7 @@
       <c r="H288" s="54"/>
       <c r="I288" s="54"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="41"/>
       <c r="B289" s="41"/>
       <c r="C289" s="54"/>
@@ -6318,7 +6327,7 @@
       <c r="H289" s="54"/>
       <c r="I289" s="54"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="41"/>
       <c r="B290" s="41"/>
       <c r="C290" s="54"/>
@@ -6329,7 +6338,7 @@
       <c r="H290" s="54"/>
       <c r="I290" s="54"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="41"/>
       <c r="B291" s="41"/>
       <c r="C291" s="54"/>
@@ -6340,7 +6349,7 @@
       <c r="H291" s="54"/>
       <c r="I291" s="54"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="41"/>
       <c r="B292" s="41"/>
       <c r="C292" s="54"/>
@@ -6351,7 +6360,7 @@
       <c r="H292" s="54"/>
       <c r="I292" s="54"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="41"/>
       <c r="B293" s="41"/>
       <c r="C293" s="54"/>
@@ -6362,7 +6371,7 @@
       <c r="H293" s="54"/>
       <c r="I293" s="54"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="41"/>
       <c r="B294" s="41"/>
       <c r="C294" s="54"/>
@@ -6373,7 +6382,7 @@
       <c r="H294" s="54"/>
       <c r="I294" s="54"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="41"/>
       <c r="B295" s="41"/>
       <c r="C295" s="54"/>
@@ -6384,7 +6393,7 @@
       <c r="H295" s="54"/>
       <c r="I295" s="54"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="41"/>
       <c r="B296" s="41"/>
       <c r="C296" s="54"/>
@@ -6395,7 +6404,7 @@
       <c r="H296" s="54"/>
       <c r="I296" s="54"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="41"/>
       <c r="B297" s="41"/>
       <c r="C297" s="54"/>
@@ -6406,7 +6415,7 @@
       <c r="H297" s="54"/>
       <c r="I297" s="54"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="41"/>
       <c r="B298" s="41"/>
       <c r="C298" s="54"/>
@@ -6417,7 +6426,7 @@
       <c r="H298" s="54"/>
       <c r="I298" s="54"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="41"/>
       <c r="B299" s="41"/>
       <c r="C299" s="54"/>
@@ -6428,7 +6437,7 @@
       <c r="H299" s="54"/>
       <c r="I299" s="54"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="41"/>
       <c r="B300" s="41"/>
       <c r="C300" s="54"/>
@@ -6439,7 +6448,7 @@
       <c r="H300" s="54"/>
       <c r="I300" s="54"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="41"/>
       <c r="B301" s="41"/>
       <c r="C301" s="54"/>
@@ -6450,7 +6459,7 @@
       <c r="H301" s="54"/>
       <c r="I301" s="54"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="41"/>
       <c r="B302" s="41"/>
       <c r="C302" s="54"/>
@@ -6461,7 +6470,7 @@
       <c r="H302" s="54"/>
       <c r="I302" s="54"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="41"/>
       <c r="B303" s="41"/>
       <c r="C303" s="54"/>
@@ -6472,7 +6481,7 @@
       <c r="H303" s="54"/>
       <c r="I303" s="54"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="41"/>
       <c r="B304" s="41"/>
       <c r="C304" s="54"/>
@@ -6483,7 +6492,7 @@
       <c r="H304" s="54"/>
       <c r="I304" s="54"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="41"/>
       <c r="B305" s="41"/>
       <c r="C305" s="54"/>
@@ -6494,7 +6503,7 @@
       <c r="H305" s="54"/>
       <c r="I305" s="54"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="41"/>
       <c r="B306" s="41"/>
       <c r="C306" s="54"/>
@@ -6505,7 +6514,7 @@
       <c r="H306" s="54"/>
       <c r="I306" s="54"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="41"/>
       <c r="B307" s="41"/>
       <c r="C307" s="54"/>
@@ -6516,7 +6525,7 @@
       <c r="H307" s="54"/>
       <c r="I307" s="54"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="41"/>
       <c r="B308" s="41"/>
       <c r="C308" s="54"/>
@@ -6527,7 +6536,7 @@
       <c r="H308" s="54"/>
       <c r="I308" s="54"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="41"/>
       <c r="B309" s="41"/>
       <c r="C309" s="54"/>
@@ -6538,7 +6547,7 @@
       <c r="H309" s="54"/>
       <c r="I309" s="54"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="41"/>
       <c r="B310" s="41"/>
       <c r="C310" s="54"/>
@@ -6549,7 +6558,7 @@
       <c r="H310" s="54"/>
       <c r="I310" s="54"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="41"/>
       <c r="B311" s="41"/>
       <c r="C311" s="54"/>
@@ -6560,7 +6569,7 @@
       <c r="H311" s="54"/>
       <c r="I311" s="54"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="41"/>
       <c r="B312" s="41"/>
       <c r="C312" s="54"/>
@@ -6571,7 +6580,7 @@
       <c r="H312" s="54"/>
       <c r="I312" s="54"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="41"/>
       <c r="B313" s="41"/>
       <c r="C313" s="54"/>
@@ -6582,7 +6591,7 @@
       <c r="H313" s="54"/>
       <c r="I313" s="54"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="41"/>
       <c r="B314" s="41"/>
       <c r="C314" s="54"/>
@@ -6593,7 +6602,7 @@
       <c r="H314" s="54"/>
       <c r="I314" s="54"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="41"/>
       <c r="B315" s="41"/>
       <c r="C315" s="54"/>
@@ -6604,7 +6613,7 @@
       <c r="H315" s="54"/>
       <c r="I315" s="54"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="41"/>
       <c r="B316" s="41"/>
       <c r="C316" s="54"/>
@@ -6615,7 +6624,7 @@
       <c r="H316" s="54"/>
       <c r="I316" s="54"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="41"/>
       <c r="B317" s="41"/>
       <c r="C317" s="54"/>
@@ -6626,7 +6635,7 @@
       <c r="H317" s="54"/>
       <c r="I317" s="54"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="41"/>
       <c r="B318" s="41"/>
       <c r="C318" s="54"/>
@@ -6637,7 +6646,7 @@
       <c r="H318" s="54"/>
       <c r="I318" s="54"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="41"/>
       <c r="B319" s="41"/>
       <c r="C319" s="54"/>
@@ -6648,7 +6657,7 @@
       <c r="H319" s="54"/>
       <c r="I319" s="54"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="41"/>
       <c r="B320" s="41"/>
       <c r="C320" s="54"/>
@@ -6659,7 +6668,7 @@
       <c r="H320" s="54"/>
       <c r="I320" s="54"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="41"/>
       <c r="B321" s="41"/>
       <c r="C321" s="54"/>
@@ -6670,7 +6679,7 @@
       <c r="H321" s="54"/>
       <c r="I321" s="54"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="41"/>
       <c r="B322" s="41"/>
       <c r="C322" s="54"/>
@@ -6681,7 +6690,7 @@
       <c r="H322" s="54"/>
       <c r="I322" s="54"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="41"/>
       <c r="B323" s="41"/>
       <c r="C323" s="54"/>
@@ -6692,7 +6701,7 @@
       <c r="H323" s="54"/>
       <c r="I323" s="54"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="41"/>
       <c r="B324" s="41"/>
       <c r="C324" s="54"/>
@@ -6703,7 +6712,7 @@
       <c r="H324" s="54"/>
       <c r="I324" s="54"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="41"/>
       <c r="B325" s="41"/>
       <c r="C325" s="54"/>
@@ -6714,7 +6723,7 @@
       <c r="H325" s="54"/>
       <c r="I325" s="54"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="41"/>
       <c r="B326" s="41"/>
       <c r="C326" s="54"/>
@@ -6725,7 +6734,7 @@
       <c r="H326" s="54"/>
       <c r="I326" s="54"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="41"/>
       <c r="B327" s="41"/>
       <c r="C327" s="54"/>
@@ -6736,7 +6745,7 @@
       <c r="H327" s="54"/>
       <c r="I327" s="54"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="41"/>
       <c r="B328" s="41"/>
       <c r="C328" s="54"/>
@@ -6747,7 +6756,7 @@
       <c r="H328" s="54"/>
       <c r="I328" s="54"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="41"/>
       <c r="B329" s="41"/>
       <c r="C329" s="54"/>
@@ -6758,7 +6767,7 @@
       <c r="H329" s="54"/>
       <c r="I329" s="54"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="41"/>
       <c r="B330" s="41"/>
       <c r="C330" s="54"/>
@@ -6769,7 +6778,7 @@
       <c r="H330" s="54"/>
       <c r="I330" s="54"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="41"/>
       <c r="B331" s="41"/>
       <c r="C331" s="54"/>
@@ -6780,7 +6789,7 @@
       <c r="H331" s="54"/>
       <c r="I331" s="54"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="41"/>
       <c r="B332" s="41"/>
       <c r="C332" s="54"/>
@@ -6791,7 +6800,7 @@
       <c r="H332" s="54"/>
       <c r="I332" s="54"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="41"/>
       <c r="B333" s="41"/>
       <c r="C333" s="54"/>
@@ -6802,7 +6811,7 @@
       <c r="H333" s="54"/>
       <c r="I333" s="54"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="41"/>
       <c r="B334" s="41"/>
       <c r="C334" s="54"/>
@@ -6813,7 +6822,7 @@
       <c r="H334" s="54"/>
       <c r="I334" s="54"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="41"/>
       <c r="B335" s="41"/>
       <c r="C335" s="54"/>
@@ -6824,7 +6833,7 @@
       <c r="H335" s="54"/>
       <c r="I335" s="54"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="41"/>
       <c r="B336" s="41"/>
       <c r="C336" s="54"/>
@@ -6835,7 +6844,7 @@
       <c r="H336" s="54"/>
       <c r="I336" s="54"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="41"/>
       <c r="B337" s="41"/>
       <c r="C337" s="54"/>
@@ -6846,7 +6855,7 @@
       <c r="H337" s="54"/>
       <c r="I337" s="54"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="41"/>
       <c r="B338" s="41"/>
       <c r="C338" s="54"/>
@@ -6857,7 +6866,7 @@
       <c r="H338" s="54"/>
       <c r="I338" s="54"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="41"/>
       <c r="B339" s="41"/>
       <c r="C339" s="54"/>
@@ -6868,7 +6877,7 @@
       <c r="H339" s="54"/>
       <c r="I339" s="54"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="41"/>
       <c r="B340" s="41"/>
       <c r="C340" s="54"/>
@@ -6879,7 +6888,7 @@
       <c r="H340" s="54"/>
       <c r="I340" s="54"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="41"/>
       <c r="B341" s="41"/>
       <c r="C341" s="54"/>
@@ -6890,7 +6899,7 @@
       <c r="H341" s="54"/>
       <c r="I341" s="54"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="41"/>
       <c r="B342" s="41"/>
       <c r="C342" s="54"/>
@@ -6901,7 +6910,7 @@
       <c r="H342" s="54"/>
       <c r="I342" s="54"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="41"/>
       <c r="B343" s="41"/>
       <c r="C343" s="54"/>
@@ -6912,7 +6921,7 @@
       <c r="H343" s="54"/>
       <c r="I343" s="54"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="41"/>
       <c r="B344" s="41"/>
       <c r="C344" s="54"/>
@@ -6923,7 +6932,7 @@
       <c r="H344" s="54"/>
       <c r="I344" s="54"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="41"/>
       <c r="B345" s="41"/>
       <c r="C345" s="54"/>
@@ -6934,7 +6943,7 @@
       <c r="H345" s="54"/>
       <c r="I345" s="54"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="41"/>
       <c r="B346" s="41"/>
       <c r="C346" s="54"/>
@@ -6945,7 +6954,7 @@
       <c r="H346" s="54"/>
       <c r="I346" s="54"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="41"/>
       <c r="B347" s="41"/>
       <c r="C347" s="54"/>
@@ -6956,7 +6965,7 @@
       <c r="H347" s="54"/>
       <c r="I347" s="54"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="41"/>
       <c r="B348" s="41"/>
       <c r="C348" s="54"/>
@@ -6967,7 +6976,7 @@
       <c r="H348" s="54"/>
       <c r="I348" s="54"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="41"/>
       <c r="B349" s="41"/>
       <c r="C349" s="54"/>
@@ -6978,7 +6987,7 @@
       <c r="H349" s="54"/>
       <c r="I349" s="54"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="41"/>
       <c r="B350" s="41"/>
       <c r="C350" s="54"/>
@@ -6989,7 +6998,7 @@
       <c r="H350" s="54"/>
       <c r="I350" s="54"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="41"/>
       <c r="B351" s="41"/>
       <c r="C351" s="54"/>
@@ -7000,7 +7009,7 @@
       <c r="H351" s="54"/>
       <c r="I351" s="54"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="41"/>
       <c r="B352" s="41"/>
       <c r="C352" s="54"/>
@@ -7011,7 +7020,7 @@
       <c r="H352" s="54"/>
       <c r="I352" s="54"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="41"/>
       <c r="B353" s="41"/>
       <c r="C353" s="54"/>
@@ -7022,7 +7031,7 @@
       <c r="H353" s="54"/>
       <c r="I353" s="54"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="41"/>
       <c r="B354" s="41"/>
       <c r="C354" s="54"/>
@@ -7033,7 +7042,7 @@
       <c r="H354" s="54"/>
       <c r="I354" s="54"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="41"/>
       <c r="B355" s="41"/>
       <c r="C355" s="54"/>
@@ -7044,7 +7053,7 @@
       <c r="H355" s="54"/>
       <c r="I355" s="54"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="41"/>
       <c r="B356" s="41"/>
       <c r="C356" s="54"/>
@@ -7055,7 +7064,7 @@
       <c r="H356" s="54"/>
       <c r="I356" s="54"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="41"/>
       <c r="B357" s="41"/>
       <c r="C357" s="54"/>
@@ -7066,7 +7075,7 @@
       <c r="H357" s="54"/>
       <c r="I357" s="54"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="41"/>
       <c r="B358" s="41"/>
       <c r="C358" s="54"/>
@@ -7077,7 +7086,7 @@
       <c r="H358" s="54"/>
       <c r="I358" s="54"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="41"/>
       <c r="B359" s="41"/>
       <c r="C359" s="54"/>
@@ -7088,7 +7097,7 @@
       <c r="H359" s="54"/>
       <c r="I359" s="54"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="41"/>
       <c r="B360" s="41"/>
       <c r="C360" s="54"/>
@@ -7099,7 +7108,7 @@
       <c r="H360" s="54"/>
       <c r="I360" s="54"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="41"/>
       <c r="B361" s="41"/>
       <c r="C361" s="54"/>
@@ -7110,7 +7119,7 @@
       <c r="H361" s="54"/>
       <c r="I361" s="54"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="41"/>
       <c r="B362" s="41"/>
       <c r="C362" s="54"/>
@@ -7121,7 +7130,7 @@
       <c r="H362" s="54"/>
       <c r="I362" s="54"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="41"/>
       <c r="B363" s="41"/>
       <c r="C363" s="54"/>
@@ -7132,7 +7141,7 @@
       <c r="H363" s="54"/>
       <c r="I363" s="54"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="41"/>
       <c r="B364" s="41"/>
       <c r="C364" s="54"/>
@@ -7143,7 +7152,7 @@
       <c r="H364" s="54"/>
       <c r="I364" s="54"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="41"/>
       <c r="B365" s="41"/>
       <c r="C365" s="54"/>
@@ -7154,7 +7163,7 @@
       <c r="H365" s="54"/>
       <c r="I365" s="54"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="41"/>
       <c r="B366" s="41"/>
       <c r="C366" s="54"/>
@@ -7165,7 +7174,7 @@
       <c r="H366" s="54"/>
       <c r="I366" s="54"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="41"/>
       <c r="B367" s="41"/>
       <c r="C367" s="54"/>
@@ -7176,7 +7185,7 @@
       <c r="H367" s="54"/>
       <c r="I367" s="54"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="41"/>
       <c r="B368" s="41"/>
       <c r="C368" s="54"/>
@@ -7187,7 +7196,7 @@
       <c r="H368" s="54"/>
       <c r="I368" s="54"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="41"/>
       <c r="B369" s="41"/>
       <c r="C369" s="54"/>
@@ -7198,7 +7207,7 @@
       <c r="H369" s="54"/>
       <c r="I369" s="54"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="41"/>
       <c r="B370" s="41"/>
       <c r="C370" s="54"/>
@@ -7209,7 +7218,7 @@
       <c r="H370" s="54"/>
       <c r="I370" s="54"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="41"/>
       <c r="B371" s="41"/>
       <c r="C371" s="54"/>
@@ -7220,7 +7229,7 @@
       <c r="H371" s="54"/>
       <c r="I371" s="54"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="41"/>
       <c r="B372" s="41"/>
       <c r="C372" s="54"/>
@@ -7231,7 +7240,7 @@
       <c r="H372" s="54"/>
       <c r="I372" s="54"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="41"/>
       <c r="B373" s="41"/>
       <c r="C373" s="54"/>
@@ -7242,7 +7251,7 @@
       <c r="H373" s="54"/>
       <c r="I373" s="54"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="41"/>
       <c r="B374" s="41"/>
       <c r="C374" s="54"/>
@@ -7253,7 +7262,7 @@
       <c r="H374" s="54"/>
       <c r="I374" s="54"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="41"/>
       <c r="B375" s="41"/>
       <c r="C375" s="54"/>
@@ -7264,7 +7273,7 @@
       <c r="H375" s="54"/>
       <c r="I375" s="54"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="41"/>
       <c r="B376" s="41"/>
       <c r="C376" s="54"/>
@@ -7275,7 +7284,7 @@
       <c r="H376" s="54"/>
       <c r="I376" s="54"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="41"/>
       <c r="B377" s="41"/>
       <c r="C377" s="54"/>
@@ -7286,7 +7295,7 @@
       <c r="H377" s="54"/>
       <c r="I377" s="54"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="41"/>
       <c r="B378" s="41"/>
       <c r="C378" s="54"/>
@@ -7297,7 +7306,7 @@
       <c r="H378" s="54"/>
       <c r="I378" s="54"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="41"/>
       <c r="B379" s="41"/>
       <c r="C379" s="54"/>
@@ -7308,7 +7317,7 @@
       <c r="H379" s="54"/>
       <c r="I379" s="54"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="41"/>
       <c r="B380" s="41"/>
       <c r="C380" s="54"/>
@@ -7319,7 +7328,7 @@
       <c r="H380" s="54"/>
       <c r="I380" s="54"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="41"/>
       <c r="B381" s="41"/>
       <c r="C381" s="54"/>
@@ -7330,7 +7339,7 @@
       <c r="H381" s="54"/>
       <c r="I381" s="54"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="41"/>
       <c r="B382" s="41"/>
       <c r="C382" s="54"/>
@@ -7341,7 +7350,7 @@
       <c r="H382" s="54"/>
       <c r="I382" s="54"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="41"/>
       <c r="B383" s="41"/>
       <c r="C383" s="54"/>
@@ -7352,7 +7361,7 @@
       <c r="H383" s="54"/>
       <c r="I383" s="54"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="41"/>
       <c r="B384" s="41"/>
       <c r="C384" s="54"/>
@@ -7363,7 +7372,7 @@
       <c r="H384" s="54"/>
       <c r="I384" s="54"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="41"/>
       <c r="B385" s="41"/>
       <c r="C385" s="54"/>
@@ -7374,7 +7383,7 @@
       <c r="H385" s="54"/>
       <c r="I385" s="54"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="41"/>
       <c r="B386" s="41"/>
       <c r="C386" s="54"/>
@@ -7385,7 +7394,7 @@
       <c r="H386" s="54"/>
       <c r="I386" s="54"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="41"/>
       <c r="B387" s="41"/>
       <c r="C387" s="54"/>
@@ -7396,7 +7405,7 @@
       <c r="H387" s="54"/>
       <c r="I387" s="54"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="41"/>
       <c r="B388" s="41"/>
       <c r="C388" s="54"/>
@@ -7407,7 +7416,7 @@
       <c r="H388" s="54"/>
       <c r="I388" s="54"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="41"/>
       <c r="B389" s="41"/>
       <c r="C389" s="54"/>
@@ -7418,7 +7427,7 @@
       <c r="H389" s="54"/>
       <c r="I389" s="54"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="41"/>
       <c r="B390" s="41"/>
       <c r="C390" s="54"/>
@@ -7429,7 +7438,7 @@
       <c r="H390" s="54"/>
       <c r="I390" s="54"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="41"/>
       <c r="B391" s="41"/>
       <c r="C391" s="54"/>
@@ -7440,7 +7449,7 @@
       <c r="H391" s="54"/>
       <c r="I391" s="54"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="41"/>
       <c r="B392" s="41"/>
       <c r="C392" s="54"/>
@@ -7451,7 +7460,7 @@
       <c r="H392" s="54"/>
       <c r="I392" s="54"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="41"/>
       <c r="B393" s="41"/>
       <c r="C393" s="54"/>
@@ -7462,7 +7471,7 @@
       <c r="H393" s="54"/>
       <c r="I393" s="54"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="41"/>
       <c r="B394" s="41"/>
       <c r="C394" s="54"/>
@@ -7473,7 +7482,7 @@
       <c r="H394" s="54"/>
       <c r="I394" s="54"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="41"/>
       <c r="B395" s="41"/>
       <c r="C395" s="54"/>
@@ -7484,7 +7493,7 @@
       <c r="H395" s="54"/>
       <c r="I395" s="54"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="41"/>
       <c r="B396" s="41"/>
       <c r="C396" s="54"/>
@@ -7495,7 +7504,7 @@
       <c r="H396" s="54"/>
       <c r="I396" s="54"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="41"/>
       <c r="B397" s="41"/>
       <c r="C397" s="54"/>
@@ -7506,7 +7515,7 @@
       <c r="H397" s="54"/>
       <c r="I397" s="54"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="41"/>
       <c r="B398" s="41"/>
       <c r="C398" s="54"/>
@@ -7517,7 +7526,7 @@
       <c r="H398" s="54"/>
       <c r="I398" s="54"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="41"/>
       <c r="B399" s="41"/>
       <c r="C399" s="54"/>
@@ -7528,7 +7537,7 @@
       <c r="H399" s="54"/>
       <c r="I399" s="54"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="41"/>
       <c r="B400" s="41"/>
       <c r="C400" s="54"/>
@@ -7539,7 +7548,7 @@
       <c r="H400" s="54"/>
       <c r="I400" s="54"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="41"/>
       <c r="B401" s="41"/>
       <c r="C401" s="54"/>
@@ -7550,7 +7559,7 @@
       <c r="H401" s="54"/>
       <c r="I401" s="54"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="41"/>
       <c r="B402" s="41"/>
       <c r="C402" s="54"/>
@@ -7561,7 +7570,7 @@
       <c r="H402" s="54"/>
       <c r="I402" s="54"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="41"/>
       <c r="B403" s="41"/>
       <c r="C403" s="54"/>
@@ -7572,7 +7581,7 @@
       <c r="H403" s="54"/>
       <c r="I403" s="54"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="41"/>
       <c r="B404" s="41"/>
       <c r="C404" s="54"/>
@@ -7583,7 +7592,7 @@
       <c r="H404" s="54"/>
       <c r="I404" s="54"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="41"/>
       <c r="B405" s="41"/>
       <c r="C405" s="54"/>
@@ -7594,7 +7603,7 @@
       <c r="H405" s="54"/>
       <c r="I405" s="54"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="41"/>
       <c r="B406" s="41"/>
       <c r="C406" s="54"/>
@@ -7605,7 +7614,7 @@
       <c r="H406" s="54"/>
       <c r="I406" s="54"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="41"/>
       <c r="B407" s="41"/>
       <c r="C407" s="54"/>
@@ -7616,7 +7625,7 @@
       <c r="H407" s="54"/>
       <c r="I407" s="54"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="41"/>
       <c r="B408" s="41"/>
       <c r="C408" s="54"/>
@@ -7627,7 +7636,7 @@
       <c r="H408" s="54"/>
       <c r="I408" s="54"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="41"/>
       <c r="B409" s="41"/>
       <c r="C409" s="54"/>
@@ -7638,7 +7647,7 @@
       <c r="H409" s="54"/>
       <c r="I409" s="54"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="41"/>
       <c r="B410" s="41"/>
       <c r="C410" s="54"/>
@@ -7657,52 +7666,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEW275"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.15625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.15625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.41796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.41796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.15625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.5703125" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="6" customWidth="1"/>
-    <col min="14" max="15" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.7109375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.28515625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.5703125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.5703125" style="1" customWidth="1"/>
-    <col min="41" max="42" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.140625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.83984375" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.578125" style="6" customWidth="1"/>
+    <col min="14" max="15" width="7.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="7.578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.68359375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="11.15625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="9.15625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.26171875" style="1" customWidth="1"/>
+    <col min="34" max="34" width="8.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="7.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.578125" style="1" customWidth="1"/>
+    <col min="38" max="39" width="4.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.578125" style="1" customWidth="1"/>
+    <col min="41" max="42" width="5.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.15625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="17.41796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.83984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.68359375" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="5" style="1" customWidth="1"/>
-    <col min="48" max="48" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.15625" style="1" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="18" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="16376" width="12" style="1"/>
     <col min="16377" max="16377" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="16378" max="16384" width="1.85546875" style="1" customWidth="1"/>
+    <col min="16378" max="16384" width="1.83984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -7807,7 +7816,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
@@ -7928,7 +7937,7 @@
         <v>8792</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="28" t="s">
         <v>12</v>
       </c>
@@ -7970,7 +7979,7 @@
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
@@ -8012,7 +8021,7 @@
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="27" t="s">
         <v>295</v>
       </c>
@@ -8130,7 +8139,7 @@
         <v>19821</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="28" t="s">
         <v>296</v>
       </c>
@@ -8168,7 +8177,7 @@
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="28" t="s">
         <v>297</v>
       </c>
@@ -8206,7 +8215,7 @@
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2"/>
     </row>
-    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="20" t="s">
         <v>298</v>
       </c>
@@ -8277,7 +8286,7 @@
       <c r="AS8" s="52"/>
       <c r="AT8" s="52"/>
     </row>
-    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="50" t="s">
         <v>299</v>
       </c>
@@ -8321,7 +8330,7 @@
       <c r="AI9" s="6"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="50" t="s">
         <v>300</v>
       </c>
@@ -8365,7 +8374,7 @@
       <c r="AI10" s="6"/>
       <c r="AJ10" s="6"/>
     </row>
-    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" s="51" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="50" t="s">
         <v>301</v>
       </c>
@@ -8414,7 +8423,7 @@
       <c r="AI11" s="6"/>
       <c r="AJ11" s="6"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="27" t="s">
         <v>15</v>
       </c>
@@ -8535,7 +8544,7 @@
         <v>44088</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="28" t="s">
         <v>16</v>
       </c>
@@ -8577,7 +8586,7 @@
       <c r="AI13" s="2"/>
       <c r="AJ13" s="2"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="28" t="s">
         <v>17</v>
       </c>
@@ -8619,7 +8628,7 @@
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="27" t="s">
         <v>18</v>
       </c>
@@ -8748,7 +8757,7 @@
         <v>33167</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28" t="s">
         <v>19</v>
       </c>
@@ -8800,7 +8809,7 @@
       <c r="AI16" s="2"/>
       <c r="AJ16" s="2"/>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="28" t="s">
         <v>20</v>
       </c>
@@ -8852,7 +8861,7 @@
       <c r="AI17" s="2"/>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="27" t="s">
         <v>21</v>
       </c>
@@ -8983,7 +8992,7 @@
         <v>76684</v>
       </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="28" t="s">
         <v>22</v>
       </c>
@@ -9037,7 +9046,7 @@
       <c r="AI19" s="2"/>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
@@ -9091,7 +9100,7 @@
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="29" t="s">
         <v>24</v>
       </c>
@@ -9216,7 +9225,7 @@
         <v>38321</v>
       </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="28" t="s">
         <v>25</v>
       </c>
@@ -9264,7 +9273,7 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="28" t="s">
         <v>26</v>
       </c>
@@ -9312,7 +9321,7 @@
       <c r="AI23" s="2"/>
       <c r="AJ23" s="2"/>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="29" t="s">
         <v>27</v>
       </c>
@@ -9443,7 +9452,7 @@
         <v>99899</v>
       </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="28" t="s">
         <v>28</v>
       </c>
@@ -9497,7 +9506,7 @@
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="28" t="s">
         <v>29</v>
       </c>
@@ -9551,7 +9560,7 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="29" t="s">
         <v>30</v>
       </c>
@@ -9672,7 +9681,7 @@
         <v>36336</v>
       </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="28" t="s">
         <v>31</v>
       </c>
@@ -9714,7 +9723,7 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="28" t="s">
         <v>32</v>
       </c>
@@ -9756,7 +9765,7 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
@@ -9881,7 +9890,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="28" t="s">
         <v>34</v>
       </c>
@@ -9929,7 +9938,7 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="28" t="s">
         <v>35</v>
       </c>
@@ -9977,7 +9986,7 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
@@ -10106,7 +10115,7 @@
         <v>36280</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="28" t="s">
         <v>37</v>
       </c>
@@ -10158,7 +10167,7 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="28" t="s">
         <v>38</v>
       </c>
@@ -10210,7 +10219,7 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="29" t="s">
         <v>39</v>
       </c>
@@ -10327,7 +10336,7 @@
         <v>55174</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="28" t="s">
         <v>40</v>
       </c>
@@ -10365,7 +10374,7 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="28" t="s">
         <v>41</v>
       </c>
@@ -10403,7 +10412,7 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="29" t="s">
         <v>42</v>
       </c>
@@ -10534,7 +10543,7 @@
         <v>77982</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="28" t="s">
         <v>43</v>
       </c>
@@ -10588,7 +10597,7 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="28" t="s">
         <v>44</v>
       </c>
@@ -10642,7 +10651,7 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="30" t="s">
         <v>45</v>
       </c>
@@ -10756,7 +10765,7 @@
         <v>-9503</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="29" t="s">
         <v>46</v>
       </c>
@@ -10848,7 +10857,7 @@
         <v>12531</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="29" t="s">
         <v>47</v>
       </c>
@@ -10979,7 +10988,7 @@
         <v>25499</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="28" t="s">
         <v>48</v>
       </c>
@@ -11033,7 +11042,7 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="28" t="s">
         <v>49</v>
       </c>
@@ -11087,7 +11096,7 @@
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="29" t="s">
         <v>50</v>
       </c>
@@ -11210,7 +11219,7 @@
         <v>20432</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="28" t="s">
         <v>51</v>
       </c>
@@ -11255,7 +11264,7 @@
       <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
     </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="28" t="s">
         <v>52</v>
       </c>
@@ -11300,7 +11309,7 @@
       <c r="AI49" s="2"/>
       <c r="AJ49" s="2"/>
     </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="29" t="s">
         <v>53</v>
       </c>
@@ -11421,7 +11430,7 @@
         <v>15551</v>
       </c>
     </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="28" t="s">
         <v>54</v>
       </c>
@@ -11463,7 +11472,7 @@
       <c r="AI51" s="2"/>
       <c r="AJ51" s="2"/>
     </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="28" t="s">
         <v>55</v>
       </c>
@@ -11505,7 +11514,7 @@
       <c r="AI52" s="2"/>
       <c r="AJ52" s="2"/>
     </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="29" t="s">
         <v>56</v>
       </c>
@@ -11628,7 +11637,7 @@
         <v>17783</v>
       </c>
     </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="28" t="s">
         <v>57</v>
       </c>
@@ -11673,7 +11682,7 @@
       <c r="AI54" s="2"/>
       <c r="AJ54" s="2"/>
     </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="28" t="s">
         <v>58</v>
       </c>
@@ -11718,7 +11727,7 @@
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
     </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="29" t="s">
         <v>59</v>
       </c>
@@ -11845,7 +11854,7 @@
         <v>25432</v>
       </c>
     </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="28" t="s">
         <v>60</v>
       </c>
@@ -11895,7 +11904,7 @@
       <c r="AI57" s="2"/>
       <c r="AJ57" s="2"/>
     </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="28" t="s">
         <v>61</v>
       </c>
@@ -11945,7 +11954,7 @@
       <c r="AI58" s="2"/>
       <c r="AJ58" s="2"/>
     </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="29" t="s">
         <v>62</v>
       </c>
@@ -12068,7 +12077,7 @@
         <v>24399</v>
       </c>
     </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="28" t="s">
         <v>63</v>
       </c>
@@ -12113,7 +12122,7 @@
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
     </row>
-    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="28" t="s">
         <v>64</v>
       </c>
@@ -12158,7 +12167,7 @@
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
     </row>
-    <row r="62" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="29" t="s">
         <v>65</v>
       </c>
@@ -12275,7 +12284,7 @@
         <v>15757</v>
       </c>
     </row>
-    <row r="63" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="28" t="s">
         <v>66</v>
       </c>
@@ -12320,7 +12329,7 @@
       <c r="AI63" s="2"/>
       <c r="AJ63" s="2"/>
     </row>
-    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="28" t="s">
         <v>67</v>
       </c>
@@ -12365,7 +12374,7 @@
       <c r="AI64" s="2"/>
       <c r="AJ64" s="2"/>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="29" t="s">
         <v>68</v>
       </c>
@@ -12486,7 +12495,7 @@
         <v>17247</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="28" t="s">
         <v>69</v>
       </c>
@@ -12528,7 +12537,7 @@
       <c r="AI66" s="2"/>
       <c r="AJ66" s="2"/>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="28" t="s">
         <v>70</v>
       </c>
@@ -12570,7 +12579,7 @@
       <c r="AI67" s="2"/>
       <c r="AJ67" s="2"/>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="29" t="s">
         <v>71</v>
       </c>
@@ -12691,7 +12700,7 @@
         <v>15416</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="28" t="s">
         <v>72</v>
       </c>
@@ -12733,7 +12742,7 @@
       <c r="AI69" s="2"/>
       <c r="AJ69" s="2"/>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="28" t="s">
         <v>73</v>
       </c>
@@ -12775,7 +12784,7 @@
       <c r="AI70" s="2"/>
       <c r="AJ70" s="2"/>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="29" t="s">
         <v>74</v>
       </c>
@@ -12900,7 +12909,7 @@
         <v>17010</v>
       </c>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="28" t="s">
         <v>75</v>
       </c>
@@ -12948,7 +12957,7 @@
       <c r="AI72" s="2"/>
       <c r="AJ72" s="2"/>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="28" t="s">
         <v>76</v>
       </c>
@@ -12996,7 +13005,7 @@
       <c r="AI73" s="2"/>
       <c r="AJ73" s="2"/>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="30" t="s">
         <v>77</v>
       </c>
@@ -13110,7 +13119,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="16" t="s">
         <v>78</v>
       </c>
@@ -13238,7 +13247,7 @@
         <v>12183</v>
       </c>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="10" t="s">
         <v>79</v>
       </c>
@@ -13298,7 +13307,7 @@
       <c r="AI76" s="2"/>
       <c r="AJ76" s="2"/>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="10" t="s">
         <v>80</v>
       </c>
@@ -13358,7 +13367,7 @@
       <c r="AI77" s="2"/>
       <c r="AJ77" s="2"/>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="16" t="s">
         <v>81</v>
       </c>
@@ -13368,8 +13377,8 @@
       <c r="C78" s="15">
         <v>37124</v>
       </c>
-      <c r="D78" s="15">
-        <v>5130</v>
+      <c r="D78" s="65">
+        <v>25662</v>
       </c>
       <c r="E78" s="15">
         <v>254115</v>
@@ -13453,7 +13462,7 @@
       </c>
       <c r="AJ78" s="12">
         <f>AF78-D78</f>
-        <v>20</v>
+        <v>-20512</v>
       </c>
       <c r="AL78" s="47">
         <f>C78/B78*1000</f>
@@ -13461,7 +13470,7 @@
       </c>
       <c r="AM78" s="47">
         <f>D78/B78*1000</f>
-        <v>4.00093901180706</v>
+        <v>20.014053980700343</v>
       </c>
       <c r="AO78" s="47">
         <f>AL78-K78</f>
@@ -13469,7 +13478,7 @@
       </c>
       <c r="AP78" s="47">
         <f>AM78-L78</f>
-        <v>-15.999060988192941</v>
+        <v>1.4053980700342805E-2</v>
       </c>
       <c r="AR78" s="12">
         <f t="shared" ref="AR78" si="70">H78</f>
@@ -13484,7 +13493,7 @@
         <v>26309</v>
       </c>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="10" t="s">
         <v>82</v>
       </c>
@@ -13542,7 +13551,7 @@
       <c r="AI79" s="2"/>
       <c r="AJ79" s="2"/>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="10" t="s">
         <v>83</v>
       </c>
@@ -13600,7 +13609,7 @@
       <c r="AI80" s="2"/>
       <c r="AJ80" s="2"/>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="16" t="s">
         <v>84</v>
       </c>
@@ -13688,7 +13697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="10" t="s">
         <v>85</v>
       </c>
@@ -13736,7 +13745,7 @@
       <c r="AI82" s="2"/>
       <c r="AJ82" s="2"/>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="10" t="s">
         <v>86</v>
       </c>
@@ -13784,7 +13793,7 @@
       <c r="AI83" s="2"/>
       <c r="AJ83" s="2"/>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="44" t="s">
         <v>87</v>
       </c>
@@ -13899,7 +13908,7 @@
         <v>8257</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="16" t="s">
         <v>88</v>
       </c>
@@ -14023,7 +14032,7 @@
         <v>44683</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="10" t="s">
         <v>89</v>
       </c>
@@ -14079,7 +14088,7 @@
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="10" t="s">
         <v>90</v>
       </c>
@@ -14135,7 +14144,7 @@
       <c r="AI87" s="2"/>
       <c r="AJ87" s="2"/>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="16" t="s">
         <v>91</v>
       </c>
@@ -14271,7 +14280,7 @@
         <v>60082</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="10" t="s">
         <v>92</v>
       </c>
@@ -14339,7 +14348,7 @@
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="10" t="s">
         <v>93</v>
       </c>
@@ -14407,7 +14416,7 @@
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="16" t="s">
         <v>94</v>
       </c>
@@ -14529,7 +14538,7 @@
         <v>40347</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="10" t="s">
         <v>95</v>
       </c>
@@ -14589,7 +14598,7 @@
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="10" t="s">
         <v>96</v>
       </c>
@@ -14649,7 +14658,7 @@
       <c r="AI93" s="2"/>
       <c r="AJ93" s="2"/>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="16" t="s">
         <v>97</v>
       </c>
@@ -14781,7 +14790,7 @@
         <v>98935</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="10" t="s">
         <v>98</v>
       </c>
@@ -14845,7 +14854,7 @@
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="10" t="s">
         <v>99</v>
       </c>
@@ -14909,7 +14918,7 @@
       <c r="AI96" s="2"/>
       <c r="AJ96" s="2"/>
     </row>
-    <row r="97" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="16" t="s">
         <v>100</v>
       </c>
@@ -15039,7 +15048,7 @@
         <v>120135</v>
       </c>
     </row>
-    <row r="98" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="10" t="s">
         <v>101</v>
       </c>
@@ -15101,7 +15110,7 @@
       <c r="AI98" s="2"/>
       <c r="AJ98" s="2"/>
     </row>
-    <row r="99" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="10" t="s">
         <v>102</v>
       </c>
@@ -15163,7 +15172,7 @@
       <c r="AI99" s="2"/>
       <c r="AJ99" s="2"/>
     </row>
-    <row r="100" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="16" t="s">
         <v>103</v>
       </c>
@@ -15287,7 +15296,7 @@
         <v>59074</v>
       </c>
     </row>
-    <row r="101" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="10" t="s">
         <v>104</v>
       </c>
@@ -15343,7 +15352,7 @@
       <c r="AI101" s="2"/>
       <c r="AJ101" s="2"/>
     </row>
-    <row r="102" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="10" t="s">
         <v>105</v>
       </c>
@@ -15399,7 +15408,7 @@
       <c r="AI102" s="2"/>
       <c r="AJ102" s="2"/>
     </row>
-    <row r="103" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="18" t="s">
         <v>106</v>
       </c>
@@ -15531,7 +15540,7 @@
         <v>72188</v>
       </c>
     </row>
-    <row r="104" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="11" t="s">
         <v>107</v>
       </c>
@@ -15595,7 +15604,7 @@
       <c r="AI104" s="2"/>
       <c r="AJ104" s="2"/>
     </row>
-    <row r="105" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="11" t="s">
         <v>108</v>
       </c>
@@ -15659,7 +15668,7 @@
       <c r="AI105" s="2"/>
       <c r="AJ105" s="2"/>
     </row>
-    <row r="106" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="18" t="s">
         <v>109</v>
       </c>
@@ -15789,7 +15798,7 @@
         <v>44326</v>
       </c>
     </row>
-    <row r="107" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="11" t="s">
         <v>110</v>
       </c>
@@ -15851,7 +15860,7 @@
       <c r="AI107" s="2"/>
       <c r="AJ107" s="2"/>
     </row>
-    <row r="108" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="11" t="s">
         <v>111</v>
       </c>
@@ -15913,7 +15922,7 @@
       <c r="AI108" s="2"/>
       <c r="AJ108" s="2"/>
     </row>
-    <row r="109" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="18" t="s">
         <v>112</v>
       </c>
@@ -16045,7 +16054,7 @@
         <v>51040</v>
       </c>
     </row>
-    <row r="110" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="11" t="s">
         <v>113</v>
       </c>
@@ -16109,7 +16118,7 @@
       <c r="AI110" s="2"/>
       <c r="AJ110" s="2"/>
     </row>
-    <row r="111" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="11" t="s">
         <v>114</v>
       </c>
@@ -16173,7 +16182,7 @@
       <c r="AI111" s="2"/>
       <c r="AJ111" s="2"/>
     </row>
-    <row r="112" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="18" t="s">
         <v>115</v>
       </c>
@@ -16311,7 +16320,7 @@
         <v>78783</v>
       </c>
     </row>
-    <row r="113" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="11" t="s">
         <v>116</v>
       </c>
@@ -16381,7 +16390,7 @@
       <c r="AI113" s="2"/>
       <c r="AJ113" s="2"/>
     </row>
-    <row r="114" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="11" t="s">
         <v>117</v>
       </c>
@@ -16451,7 +16460,7 @@
       <c r="AI114" s="2"/>
       <c r="AJ114" s="2"/>
     </row>
-    <row r="115" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="18" t="s">
         <v>118</v>
       </c>
@@ -16585,7 +16594,7 @@
         <v>58051</v>
       </c>
     </row>
-    <row r="116" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="11" t="s">
         <v>119</v>
       </c>
@@ -16651,7 +16660,7 @@
       <c r="AI116" s="2"/>
       <c r="AJ116" s="2"/>
     </row>
-    <row r="117" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="11" t="s">
         <v>120</v>
       </c>
@@ -16717,7 +16726,7 @@
       <c r="AI117" s="2"/>
       <c r="AJ117" s="2"/>
     </row>
-    <row r="118" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="18" t="s">
         <v>121</v>
       </c>
@@ -16847,7 +16856,7 @@
         <v>65761</v>
       </c>
     </row>
-    <row r="119" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="11" t="s">
         <v>122</v>
       </c>
@@ -16909,7 +16918,7 @@
       <c r="AI119" s="2"/>
       <c r="AJ119" s="2"/>
     </row>
-    <row r="120" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="11" t="s">
         <v>123</v>
       </c>
@@ -16971,7 +16980,7 @@
       <c r="AI120" s="2"/>
       <c r="AJ120" s="2"/>
     </row>
-    <row r="121" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="18" t="s">
         <v>124</v>
       </c>
@@ -17103,7 +17112,7 @@
         <v>39804</v>
       </c>
     </row>
-    <row r="122" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="11" t="s">
         <v>125</v>
       </c>
@@ -17167,7 +17176,7 @@
       <c r="AI122" s="2"/>
       <c r="AJ122" s="2"/>
     </row>
-    <row r="123" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="11" t="s">
         <v>126</v>
       </c>
@@ -17231,7 +17240,7 @@
       <c r="AI123" s="2"/>
       <c r="AJ123" s="2"/>
     </row>
-    <row r="124" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="18" t="s">
         <v>127</v>
       </c>
@@ -17353,7 +17362,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="125" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="11" t="s">
         <v>128</v>
       </c>
@@ -17407,7 +17416,7 @@
       <c r="AI125" s="2"/>
       <c r="AJ125" s="2"/>
     </row>
-    <row r="126" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="11" t="s">
         <v>129</v>
       </c>
@@ -17461,7 +17470,7 @@
       <c r="AI126" s="2"/>
       <c r="AJ126" s="2"/>
     </row>
-    <row r="127" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="18" t="s">
         <v>130</v>
       </c>
@@ -17593,7 +17602,7 @@
         <v>75183</v>
       </c>
     </row>
-    <row r="128" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="11" t="s">
         <v>131</v>
       </c>
@@ -17657,7 +17666,7 @@
       <c r="AI128" s="2"/>
       <c r="AJ128" s="2"/>
     </row>
-    <row r="129" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="11" t="s">
         <v>132</v>
       </c>
@@ -17721,7 +17730,7 @@
       <c r="AI129" s="2"/>
       <c r="AJ129" s="2"/>
     </row>
-    <row r="130" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="18" t="s">
         <v>133</v>
       </c>
@@ -17851,7 +17860,7 @@
         <v>60505</v>
       </c>
     </row>
-    <row r="131" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="11" t="s">
         <v>134</v>
       </c>
@@ -17913,7 +17922,7 @@
       <c r="AI131" s="2"/>
       <c r="AJ131" s="2"/>
     </row>
-    <row r="132" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="11" t="s">
         <v>135</v>
       </c>
@@ -17975,7 +17984,7 @@
       <c r="AI132" s="2"/>
       <c r="AJ132" s="2"/>
     </row>
-    <row r="133" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="18" t="s">
         <v>136</v>
       </c>
@@ -18107,7 +18116,7 @@
         <v>121495</v>
       </c>
     </row>
-    <row r="134" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="11" t="s">
         <v>137</v>
       </c>
@@ -18171,7 +18180,7 @@
       <c r="AI134" s="2"/>
       <c r="AJ134" s="2"/>
     </row>
-    <row r="135" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="11" t="s">
         <v>138</v>
       </c>
@@ -18235,7 +18244,7 @@
       <c r="AI135" s="2"/>
       <c r="AJ135" s="2"/>
     </row>
-    <row r="136" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="18" t="s">
         <v>139</v>
       </c>
@@ -18373,7 +18382,7 @@
         <v>82146</v>
       </c>
     </row>
-    <row r="137" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="11" t="s">
         <v>140</v>
       </c>
@@ -18443,7 +18452,7 @@
       <c r="AI137" s="2"/>
       <c r="AJ137" s="2"/>
     </row>
-    <row r="138" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="11" t="s">
         <v>141</v>
       </c>
@@ -18513,7 +18522,7 @@
       <c r="AI138" s="2"/>
       <c r="AJ138" s="2"/>
     </row>
-    <row r="139" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="18" t="s">
         <v>142</v>
       </c>
@@ -18637,7 +18646,7 @@
         <v>34066</v>
       </c>
     </row>
-    <row r="140" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="11" t="s">
         <v>143</v>
       </c>
@@ -18693,7 +18702,7 @@
       <c r="AI140" s="2"/>
       <c r="AJ140" s="2"/>
     </row>
-    <row r="141" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="11" t="s">
         <v>144</v>
       </c>
@@ -18749,7 +18758,7 @@
       <c r="AI141" s="2"/>
       <c r="AJ141" s="2"/>
     </row>
-    <row r="142" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="18" t="s">
         <v>145</v>
       </c>
@@ -18883,7 +18892,7 @@
         <v>62602</v>
       </c>
     </row>
-    <row r="143" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="11" t="s">
         <v>146</v>
       </c>
@@ -18949,7 +18958,7 @@
       <c r="AI143" s="2"/>
       <c r="AJ143" s="2"/>
     </row>
-    <row r="144" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="11" t="s">
         <v>147</v>
       </c>
@@ -19015,7 +19024,7 @@
       <c r="AI144" s="2"/>
       <c r="AJ144" s="2"/>
     </row>
-    <row r="145" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="18" t="s">
         <v>148</v>
       </c>
@@ -19137,7 +19146,7 @@
         <v>102581</v>
       </c>
     </row>
-    <row r="146" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="11" t="s">
         <v>149</v>
       </c>
@@ -19191,7 +19200,7 @@
       <c r="AI146" s="2"/>
       <c r="AJ146" s="2"/>
     </row>
-    <row r="147" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="11" t="s">
         <v>150</v>
       </c>
@@ -19245,7 +19254,7 @@
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
     </row>
-    <row r="148" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="20" t="s">
         <v>151</v>
       </c>
@@ -19337,7 +19346,7 @@
         <v>28401</v>
       </c>
     </row>
-    <row r="149" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="20" t="s">
         <v>152</v>
       </c>
@@ -19429,7 +19438,7 @@
         <v>26234</v>
       </c>
     </row>
-    <row r="150" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="18" t="s">
         <v>153</v>
       </c>
@@ -19555,7 +19564,7 @@
         <v>25550</v>
       </c>
     </row>
-    <row r="151" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="11" t="s">
         <v>154</v>
       </c>
@@ -19613,7 +19622,7 @@
       <c r="AI151" s="2"/>
       <c r="AJ151" s="2"/>
     </row>
-    <row r="152" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="11" t="s">
         <v>155</v>
       </c>
@@ -19671,7 +19680,7 @@
       <c r="AI152" s="2"/>
       <c r="AJ152" s="2"/>
     </row>
-    <row r="153" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="18" t="s">
         <v>156</v>
       </c>
@@ -19799,7 +19808,7 @@
         <v>86961</v>
       </c>
     </row>
-    <row r="154" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="11" t="s">
         <v>157</v>
       </c>
@@ -19859,7 +19868,7 @@
       <c r="AI154" s="2"/>
       <c r="AJ154" s="2"/>
     </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="11" t="s">
         <v>158</v>
       </c>
@@ -19919,7 +19928,7 @@
       <c r="AI155" s="2"/>
       <c r="AJ155" s="2"/>
     </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="18" t="s">
         <v>159</v>
       </c>
@@ -20045,7 +20054,7 @@
         <v>56268</v>
       </c>
     </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="11" t="s">
         <v>160</v>
       </c>
@@ -20103,7 +20112,7 @@
       <c r="AI157" s="2"/>
       <c r="AJ157" s="2"/>
     </row>
-    <row r="158" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="11" t="s">
         <v>161</v>
       </c>
@@ -20161,7 +20170,7 @@
       <c r="AI158" s="2"/>
       <c r="AJ158" s="2"/>
     </row>
-    <row r="159" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="18" t="s">
         <v>162</v>
       </c>
@@ -20295,7 +20304,7 @@
         <v>53594</v>
       </c>
     </row>
-    <row r="160" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="11" t="s">
         <v>163</v>
       </c>
@@ -20361,7 +20370,7 @@
       <c r="AI160" s="2"/>
       <c r="AJ160" s="2"/>
     </row>
-    <row r="161" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="11" t="s">
         <v>164</v>
       </c>
@@ -20427,7 +20436,7 @@
       <c r="AI161" s="2"/>
       <c r="AJ161" s="2"/>
     </row>
-    <row r="162" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="18" t="s">
         <v>165</v>
       </c>
@@ -20553,7 +20562,7 @@
         <v>34141</v>
       </c>
     </row>
-    <row r="163" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="11" t="s">
         <v>166</v>
       </c>
@@ -20611,7 +20620,7 @@
       <c r="AI163" s="2"/>
       <c r="AJ163" s="2"/>
     </row>
-    <row r="164" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="11" t="s">
         <v>167</v>
       </c>
@@ -20669,7 +20678,7 @@
       <c r="AI164" s="2"/>
       <c r="AJ164" s="2"/>
     </row>
-    <row r="165" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="18" t="s">
         <v>168</v>
       </c>
@@ -20800,7 +20809,7 @@
         <v>94346</v>
       </c>
     </row>
-    <row r="166" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="11" t="s">
         <v>169</v>
       </c>
@@ -20864,7 +20873,7 @@
       <c r="AI166" s="2"/>
       <c r="AJ166" s="2"/>
     </row>
-    <row r="167" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="11" t="s">
         <v>170</v>
       </c>
@@ -20928,7 +20937,7 @@
       <c r="AI167" s="2"/>
       <c r="AJ167" s="2"/>
     </row>
-    <row r="168" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="18" t="s">
         <v>171</v>
       </c>
@@ -21061,7 +21070,7 @@
         <v>59944</v>
       </c>
     </row>
-    <row r="169" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="11" t="s">
         <v>172</v>
       </c>
@@ -21127,7 +21136,7 @@
       <c r="AI169" s="2"/>
       <c r="AJ169" s="2"/>
     </row>
-    <row r="170" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="11" t="s">
         <v>173</v>
       </c>
@@ -21193,7 +21202,7 @@
       <c r="AI170" s="2"/>
       <c r="AJ170" s="2"/>
     </row>
-    <row r="171" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="18" t="s">
         <v>174</v>
       </c>
@@ -21324,7 +21333,7 @@
         <v>56895</v>
       </c>
     </row>
-    <row r="172" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="11" t="s">
         <v>175</v>
       </c>
@@ -21388,7 +21397,7 @@
       <c r="AI172" s="2"/>
       <c r="AJ172" s="2"/>
     </row>
-    <row r="173" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="11" t="s">
         <v>176</v>
       </c>
@@ -21452,7 +21461,7 @@
       <c r="AI173" s="2"/>
       <c r="AJ173" s="2"/>
     </row>
-    <row r="174" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="18" t="s">
         <v>177</v>
       </c>
@@ -21571,7 +21580,7 @@
         <v>63824</v>
       </c>
     </row>
-    <row r="175" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="11" t="s">
         <v>178</v>
       </c>
@@ -21623,7 +21632,7 @@
       <c r="AI175" s="2"/>
       <c r="AJ175" s="2"/>
     </row>
-    <row r="176" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="11" t="s">
         <v>179</v>
       </c>
@@ -21675,7 +21684,7 @@
       <c r="AI176" s="2"/>
       <c r="AJ176" s="2"/>
     </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="18" t="s">
         <v>180</v>
       </c>
@@ -21804,7 +21813,7 @@
         <v>85859</v>
       </c>
     </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="11" t="s">
         <v>181</v>
       </c>
@@ -21866,7 +21875,7 @@
       <c r="AI178" s="2"/>
       <c r="AJ178" s="2"/>
     </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="11" t="s">
         <v>182</v>
       </c>
@@ -21928,7 +21937,7 @@
       <c r="AI179" s="2"/>
       <c r="AJ179" s="2"/>
     </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="18" t="s">
         <v>183</v>
       </c>
@@ -22047,7 +22056,7 @@
         <v>57290</v>
       </c>
     </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="11" t="s">
         <v>184</v>
       </c>
@@ -22099,7 +22108,7 @@
       <c r="AI181" s="2"/>
       <c r="AJ181" s="2"/>
     </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="11" t="s">
         <v>185</v>
       </c>
@@ -22151,7 +22160,7 @@
       <c r="AI182" s="2"/>
       <c r="AJ182" s="2"/>
     </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="20" t="s">
         <v>186</v>
       </c>
@@ -22243,7 +22252,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="20" t="s">
         <v>187</v>
       </c>
@@ -22335,7 +22344,7 @@
         <v>7737</v>
       </c>
     </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="18" t="s">
         <v>188</v>
       </c>
@@ -22472,7 +22481,7 @@
         <v>69619</v>
       </c>
     </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="11" t="s">
         <v>189</v>
       </c>
@@ -22542,7 +22551,7 @@
       <c r="AI186" s="2"/>
       <c r="AJ186" s="2"/>
     </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="11" t="s">
         <v>190</v>
       </c>
@@ -22612,7 +22621,7 @@
       <c r="AI187" s="2"/>
       <c r="AJ187" s="2"/>
     </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="18" t="s">
         <v>191</v>
       </c>
@@ -22741,7 +22750,7 @@
         <v>36205</v>
       </c>
     </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="11" t="s">
         <v>192</v>
       </c>
@@ -22803,7 +22812,7 @@
       <c r="AI189" s="2"/>
       <c r="AJ189" s="2"/>
     </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="11" t="s">
         <v>193</v>
       </c>
@@ -22865,7 +22874,7 @@
       <c r="AI190" s="2"/>
       <c r="AJ190" s="2"/>
     </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="45" t="s">
         <v>194</v>
       </c>
@@ -22979,7 +22988,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="18" t="s">
         <v>195</v>
       </c>
@@ -23104,7 +23113,7 @@
         <v>68890</v>
       </c>
     </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="11" t="s">
         <v>196</v>
       </c>
@@ -23162,7 +23171,7 @@
       <c r="AI193" s="2"/>
       <c r="AJ193" s="2"/>
     </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="11" t="s">
         <v>197</v>
       </c>
@@ -23220,7 +23229,7 @@
       <c r="AI194" s="2"/>
       <c r="AJ194" s="2"/>
     </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="45" t="s">
         <v>198</v>
       </c>
@@ -23334,7 +23343,7 @@
         <v>-252189</v>
       </c>
     </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="18" t="s">
         <v>199</v>
       </c>
@@ -23457,7 +23466,7 @@
         <v>15719</v>
       </c>
     </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="11" t="s">
         <v>200</v>
       </c>
@@ -23513,7 +23522,7 @@
       <c r="AI197" s="2"/>
       <c r="AJ197" s="2"/>
     </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="11" t="s">
         <v>201</v>
       </c>
@@ -23569,7 +23578,7 @@
       <c r="AI198" s="2"/>
       <c r="AJ198" s="2"/>
     </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="18" t="s">
         <v>202</v>
       </c>
@@ -23690,7 +23699,7 @@
         <v>12320</v>
       </c>
     </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="11" t="s">
         <v>203</v>
       </c>
@@ -23750,7 +23759,7 @@
       <c r="AI200" s="2"/>
       <c r="AJ200" s="2"/>
     </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="11" t="s">
         <v>204</v>
       </c>
@@ -23810,7 +23819,7 @@
       <c r="AI201" s="2"/>
       <c r="AJ201" s="2"/>
     </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="18" t="s">
         <v>205</v>
       </c>
@@ -23933,7 +23942,7 @@
         <v>13860</v>
       </c>
     </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="11" t="s">
         <v>206</v>
       </c>
@@ -23989,7 +23998,7 @@
       <c r="AI203" s="2"/>
       <c r="AJ203" s="2"/>
     </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="11" t="s">
         <v>207</v>
       </c>
@@ -24045,7 +24054,7 @@
       <c r="AI204" s="2"/>
       <c r="AJ204" s="2"/>
     </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="20" t="s">
         <v>208</v>
       </c>
@@ -24128,7 +24137,7 @@
       <c r="AS205" s="12"/>
       <c r="AT205" s="12"/>
     </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="18" t="s">
         <v>209</v>
       </c>
@@ -24251,7 +24260,7 @@
         <v>57139</v>
       </c>
     </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="11" t="s">
         <v>210</v>
       </c>
@@ -24307,7 +24316,7 @@
       <c r="AI207" s="2"/>
       <c r="AJ207" s="2"/>
     </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="11" t="s">
         <v>211</v>
       </c>
@@ -24363,7 +24372,7 @@
       <c r="AI208" s="2"/>
       <c r="AJ208" s="2"/>
     </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="18" t="s">
         <v>212</v>
       </c>
@@ -24490,7 +24499,7 @@
         <v>14579</v>
       </c>
     </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="11" t="s">
         <v>213</v>
       </c>
@@ -24550,7 +24559,7 @@
       <c r="AI210" s="2"/>
       <c r="AJ210" s="2"/>
     </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="11" t="s">
         <v>214</v>
       </c>
@@ -24610,7 +24619,7 @@
       <c r="AI211" s="2"/>
       <c r="AJ211" s="2"/>
     </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="18" t="s">
         <v>215</v>
       </c>
@@ -24727,7 +24736,7 @@
         <v>28752</v>
       </c>
     </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="11" t="s">
         <v>216</v>
       </c>
@@ -24777,7 +24786,7 @@
       <c r="AI213" s="2"/>
       <c r="AJ213" s="2"/>
     </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="11" t="s">
         <v>217</v>
       </c>
@@ -24827,7 +24836,7 @@
       <c r="AI214" s="2"/>
       <c r="AJ214" s="2"/>
     </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="18" t="s">
         <v>218</v>
       </c>
@@ -24948,7 +24957,7 @@
         <v>16626</v>
       </c>
     </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="11" t="s">
         <v>219</v>
       </c>
@@ -25002,7 +25011,7 @@
       <c r="AI216" s="2"/>
       <c r="AJ216" s="2"/>
     </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="11" t="s">
         <v>220</v>
       </c>
@@ -25056,7 +25065,7 @@
       <c r="AI217" s="2"/>
       <c r="AJ217" s="2"/>
     </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="18" t="s">
         <v>221</v>
       </c>
@@ -25181,7 +25190,7 @@
         <v>17424</v>
       </c>
     </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="11" t="s">
         <v>222</v>
       </c>
@@ -25239,7 +25248,7 @@
       <c r="AI219" s="2"/>
       <c r="AJ219" s="2"/>
     </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="11" t="s">
         <v>223</v>
       </c>
@@ -25297,7 +25306,7 @@
       <c r="AI220" s="2"/>
       <c r="AJ220" s="2"/>
     </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="18" t="s">
         <v>224</v>
       </c>
@@ -25414,7 +25423,7 @@
         <v>14815</v>
       </c>
     </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="11" t="s">
         <v>225</v>
       </c>
@@ -25470,7 +25479,7 @@
       <c r="AI222" s="2"/>
       <c r="AJ222" s="2"/>
     </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="11" t="s">
         <v>226</v>
       </c>
@@ -25526,7 +25535,7 @@
       <c r="AI223" s="2"/>
       <c r="AJ223" s="2"/>
     </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="45" t="s">
         <v>227</v>
       </c>
@@ -25640,7 +25649,7 @@
         <v>-2679</v>
       </c>
     </row>
-    <row r="225" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="18" t="s">
         <v>228</v>
       </c>
@@ -25717,7 +25726,7 @@
       <c r="AS225" s="12"/>
       <c r="AT225" s="12"/>
     </row>
-    <row r="226" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="18" t="s">
         <v>229</v>
       </c>
@@ -25836,7 +25845,7 @@
         <v>17487</v>
       </c>
     </row>
-    <row r="227" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="11" t="s">
         <v>230</v>
       </c>
@@ -25888,7 +25897,7 @@
       <c r="AI227" s="2"/>
       <c r="AJ227" s="2"/>
     </row>
-    <row r="228" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="11" t="s">
         <v>231</v>
       </c>
@@ -25940,7 +25949,7 @@
       <c r="AI228" s="2"/>
       <c r="AJ228" s="2"/>
     </row>
-    <row r="229" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="18" t="s">
         <v>232</v>
       </c>
@@ -26063,7 +26072,7 @@
         <v>12724</v>
       </c>
     </row>
-    <row r="230" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="11" t="s">
         <v>233</v>
       </c>
@@ -26119,7 +26128,7 @@
       <c r="AI230" s="2"/>
       <c r="AJ230" s="2"/>
     </row>
-    <row r="231" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="11" t="s">
         <v>234</v>
       </c>
@@ -26175,7 +26184,7 @@
       <c r="AI231" s="2"/>
       <c r="AJ231" s="2"/>
     </row>
-    <row r="232" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="18" t="s">
         <v>235</v>
       </c>
@@ -26292,7 +26301,7 @@
         <v>16324</v>
       </c>
     </row>
-    <row r="233" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="11" t="s">
         <v>236</v>
       </c>
@@ -26342,7 +26351,7 @@
       <c r="AI233" s="2"/>
       <c r="AJ233" s="2"/>
     </row>
-    <row r="234" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="11" t="s">
         <v>237</v>
       </c>
@@ -26392,7 +26401,7 @@
       <c r="AI234" s="2"/>
       <c r="AJ234" s="2"/>
     </row>
-    <row r="235" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="18" t="s">
         <v>238</v>
       </c>
@@ -26511,7 +26520,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="236" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="11" t="s">
         <v>239</v>
       </c>
@@ -26569,7 +26578,7 @@
       <c r="AI236" s="2"/>
       <c r="AJ236" s="2"/>
     </row>
-    <row r="237" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="11" t="s">
         <v>240</v>
       </c>
@@ -26627,7 +26636,7 @@
       <c r="AI237" s="2"/>
       <c r="AJ237" s="2"/>
     </row>
-    <row r="238" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="18" t="s">
         <v>241</v>
       </c>
@@ -26754,7 +26763,7 @@
         <v>60357</v>
       </c>
     </row>
-    <row r="239" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="11" t="s">
         <v>242</v>
       </c>
@@ -26807,7 +26816,7 @@
       <c r="AB239" s="9"/>
       <c r="AC239" s="2"/>
     </row>
-    <row r="240" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="11" t="s">
         <v>243</v>
       </c>
@@ -26867,7 +26876,7 @@
       <c r="AI240" s="2"/>
       <c r="AJ240" s="2"/>
     </row>
-    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="18" t="s">
         <v>244</v>
       </c>
@@ -26986,7 +26995,7 @@
         <v>36016</v>
       </c>
     </row>
-    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="11" t="s">
         <v>245</v>
       </c>
@@ -27038,7 +27047,7 @@
       <c r="AI242" s="2"/>
       <c r="AJ242" s="2"/>
     </row>
-    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="11" t="s">
         <v>246</v>
       </c>
@@ -27090,7 +27099,7 @@
       <c r="AI243" s="2"/>
       <c r="AJ243" s="2"/>
     </row>
-    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="18" t="s">
         <v>247</v>
       </c>
@@ -27207,7 +27216,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="11" t="s">
         <v>248</v>
       </c>
@@ -27257,7 +27266,7 @@
       <c r="AI245" s="2"/>
       <c r="AJ245" s="2"/>
     </row>
-    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="11" t="s">
         <v>249</v>
       </c>
@@ -27307,7 +27316,7 @@
       <c r="AI246" s="2"/>
       <c r="AJ246" s="2"/>
     </row>
-    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="18" t="s">
         <v>250</v>
       </c>
@@ -27420,7 +27429,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="11" t="s">
         <v>251</v>
       </c>
@@ -27466,7 +27475,7 @@
       <c r="AI248" s="2"/>
       <c r="AJ248" s="2"/>
     </row>
-    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="11" t="s">
         <v>252</v>
       </c>
@@ -27512,7 +27521,7 @@
       <c r="AI249" s="2"/>
       <c r="AJ249" s="2"/>
     </row>
-    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="45" t="s">
         <v>253</v>
       </c>
@@ -27626,7 +27635,7 @@
         <v>-5324</v>
       </c>
     </row>
-    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="14" t="s">
         <v>254</v>
       </c>
@@ -27725,7 +27734,7 @@
         <v>10239</v>
       </c>
     </row>
-    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="14" t="s">
         <v>255</v>
       </c>
@@ -27803,7 +27812,7 @@
       <c r="AS252" s="12"/>
       <c r="AT252" s="12"/>
     </row>
-    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="14" t="s">
         <v>256</v>
       </c>
@@ -27899,7 +27908,7 @@
         <v>18.045821337734392</v>
       </c>
     </row>
-    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
         <v>257</v>
       </c>
@@ -27947,7 +27956,7 @@
       <c r="AI254" s="2"/>
       <c r="AJ254" s="2"/>
     </row>
-    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
         <v>258</v>
       </c>
@@ -27995,7 +28004,7 @@
       <c r="AI255" s="2"/>
       <c r="AJ255" s="2"/>
     </row>
-    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:50" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="14" t="s">
         <v>259</v>
       </c>
@@ -28103,7 +28112,7 @@
       <c r="AS256" s="12"/>
       <c r="AT256" s="12"/>
     </row>
-    <row r="257" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
         <v>260</v>
       </c>
@@ -28155,7 +28164,7 @@
       <c r="AI257" s="2"/>
       <c r="AJ257" s="2"/>
     </row>
-    <row r="258" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
         <v>261</v>
       </c>
@@ -28207,7 +28216,7 @@
       <c r="AI258" s="2"/>
       <c r="AJ258" s="2"/>
     </row>
-    <row r="259" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="14" t="s">
         <v>262</v>
       </c>
@@ -28321,7 +28330,7 @@
         <v>9335</v>
       </c>
     </row>
-    <row r="260" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
         <v>263</v>
       </c>
@@ -28373,7 +28382,7 @@
       <c r="AI260" s="2"/>
       <c r="AJ260" s="2"/>
     </row>
-    <row r="261" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
         <v>264</v>
       </c>
@@ -28425,7 +28434,7 @@
       <c r="AI261" s="2"/>
       <c r="AJ261" s="2"/>
     </row>
-    <row r="262" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="14" t="s">
         <v>265</v>
       </c>
@@ -28533,7 +28542,7 @@
       <c r="AS262" s="12"/>
       <c r="AT262" s="12"/>
     </row>
-    <row r="263" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -28585,7 +28594,7 @@
       <c r="AI263" s="2"/>
       <c r="AJ263" s="2"/>
     </row>
-    <row r="264" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
         <v>267</v>
       </c>
@@ -28637,7 +28646,7 @@
       <c r="AI264" s="2"/>
       <c r="AJ264" s="2"/>
     </row>
-    <row r="265" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="14" t="s">
         <v>268</v>
       </c>
@@ -28743,7 +28752,7 @@
       <c r="AS265" s="12"/>
       <c r="AT265" s="12"/>
     </row>
-    <row r="266" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -28793,7 +28802,7 @@
       <c r="AI266" s="2"/>
       <c r="AJ266" s="2"/>
     </row>
-    <row r="267" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" t="s">
         <v>270</v>
       </c>
@@ -28843,7 +28852,7 @@
       <c r="AI267" s="2"/>
       <c r="AJ267" s="2"/>
     </row>
-    <row r="268" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="14" t="s">
         <v>271</v>
       </c>
@@ -28955,7 +28964,7 @@
         <v>4397</v>
       </c>
     </row>
-    <row r="269" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" t="s">
         <v>272</v>
       </c>
@@ -29005,7 +29014,7 @@
       <c r="AI269" s="2"/>
       <c r="AJ269" s="2"/>
     </row>
-    <row r="270" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" t="s">
         <v>273</v>
       </c>
@@ -29055,7 +29064,7 @@
       <c r="AI270" s="2"/>
       <c r="AJ270" s="2"/>
     </row>
-    <row r="271" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="14" t="s">
         <v>274</v>
       </c>
@@ -29167,7 +29176,7 @@
       <c r="AS271" s="12"/>
       <c r="AT271" s="12"/>
     </row>
-    <row r="272" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:46" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
         <v>275</v>
       </c>
@@ -29217,7 +29226,7 @@
       <c r="AI272" s="2"/>
       <c r="AJ272" s="2"/>
     </row>
-    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>276</v>
       </c>
@@ -29267,7 +29276,7 @@
       <c r="AI273" s="2"/>
       <c r="AJ273" s="2"/>
     </row>
-    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="21" t="s">
         <v>277</v>
       </c>
@@ -29380,7 +29389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:50 16377:16377" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="21" t="s">
         <v>278</v>
       </c>
